--- a/mig_shocks.xlsx
+++ b/mig_shocks.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <si>
     <t>Var40</t>
   </si>
@@ -133,6 +133,102 @@
   </si>
   <si>
     <t>Var79</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
   </si>
   <si>
     <t>mig_Q_2</t>
@@ -345,7 +441,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -357,16 +453,20 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,7 +480,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="true"/>
-    <col min="2" max="2" width="13.42578125" customWidth="true"/>
+    <col min="2" max="2" width="14.42578125" customWidth="true"/>
     <col min="3" max="3" width="16.42578125" customWidth="true"/>
     <col min="4" max="4" width="16.42578125" customWidth="true"/>
     <col min="5" max="5" width="16.42578125" customWidth="true"/>
@@ -424,10 +524,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="B1" s="0">
-        <v>-0.15967272058620607</v>
+        <v>0.2753267546775866</v>
       </c>
       <c r="C1" s="0">
         <v>0.002214154581450245</v>
@@ -549,10 +649,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.24565717190814917</v>
+        <v>0.18944091200051794</v>
       </c>
       <c r="C2" s="0">
         <v>-0.008798052235841184</v>
@@ -561,7 +661,7 @@
         <v>0.0024929074421023954</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.021373270782093393</v>
+        <v>-0.02137327078209339</v>
       </c>
       <c r="F2" s="0">
         <v>-0.0086453951054279478</v>
@@ -585,7 +685,7 @@
         <v>0.033933903565056878</v>
       </c>
       <c r="M2" s="0">
-        <v>0.030383907874593656</v>
+        <v>0.03038390787459366</v>
       </c>
       <c r="N2" s="0">
         <v>0.047839256681225573</v>
@@ -597,40 +697,40 @@
         <v>0.039490915288615258</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.036536510565018603</v>
+        <v>0.036536510565018609</v>
       </c>
       <c r="R2" s="0">
-        <v>0.042142916628999709</v>
+        <v>0.042142916628999716</v>
       </c>
       <c r="S2" s="0">
-        <v>0.046470535159674135</v>
+        <v>0.046470535159674142</v>
       </c>
       <c r="T2" s="0">
         <v>0.074841309368095077</v>
       </c>
       <c r="U2" s="0">
-        <v>0.054583454125459951</v>
+        <v>0.054583454125459945</v>
       </c>
       <c r="V2" s="0">
-        <v>0.055003826390571886</v>
+        <v>0.055003826390571879</v>
       </c>
       <c r="W2" s="0">
         <v>0.065383546651785807</v>
       </c>
       <c r="X2" s="0">
-        <v>0.061813519294937391</v>
+        <v>0.061813519294937606</v>
       </c>
       <c r="Y2" s="0">
         <v>0.065356164722600418</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.063794944403975595</v>
+        <v>0.063794944403975373</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.061654781829491911</v>
+        <v>0.061654781829491904</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.062307356539842318</v>
+        <v>0.062307356539842311</v>
       </c>
       <c r="AC2" s="0">
         <v>0.063362208607063986</v>
@@ -642,25 +742,25 @@
         <v>0.064188713044355028</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.061814578816645427</v>
+        <v>0.06181457881664542</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.060425638744489363</v>
+        <v>0.060425638744489356</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.060816741782236616</v>
+        <v>0.060816741782236609</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.061455653716094405</v>
+        <v>0.061455653716094398</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.061922434122747338</v>
+        <v>0.061922434122747332</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.061888309307405409</v>
+        <v>0.061888309307405402</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.06115230770110347</v>
+        <v>0.061152307701103463</v>
       </c>
       <c r="AM2" s="0">
         <v>0.060103532554758754</v>
@@ -674,10 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.26155473045267985</v>
+        <v>0.17236558985102601</v>
       </c>
       <c r="C3" s="0">
         <v>-0.0007236851580176909</v>
@@ -728,25 +828,25 @@
         <v>0.026039029199987899</v>
       </c>
       <c r="S3" s="0">
-        <v>0.036717245073956788</v>
+        <v>0.036717245073956781</v>
       </c>
       <c r="T3" s="0">
         <v>0.062434500490324389</v>
       </c>
       <c r="U3" s="0">
-        <v>0.046318139893231074</v>
+        <v>0.046318139893231067</v>
       </c>
       <c r="V3" s="0">
         <v>0.05135931795910563</v>
       </c>
       <c r="W3" s="0">
-        <v>0.063306729060164532</v>
+        <v>0.063306729060164546</v>
       </c>
       <c r="X3" s="0">
         <v>0.064793987221842819</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.067801677319718298</v>
+        <v>0.067801677319718312</v>
       </c>
       <c r="Z3" s="0">
         <v>0.066660882767059615</v>
@@ -758,16 +858,16 @@
         <v>0.063914424269086556</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.064829697214101589</v>
+        <v>0.064829697214101478</v>
       </c>
       <c r="AD3" s="0">
         <v>0.06615753944350633</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.067667415928057237</v>
+        <v>0.067667415928057251</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.067112657448067367</v>
+        <v>0.067112657448067381</v>
       </c>
       <c r="AG3" s="0">
         <v>0.064605800891545329</v>
@@ -799,70 +899,70 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.30679603837354075</v>
+        <v>0.1254070895445526</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.0059408663182357775</v>
+        <v>-0.005940866318235774</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.00052210796294517928</v>
+        <v>-0.00052210796294517581</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.011217645657931173</v>
+        <v>-0.011217645657931166</v>
       </c>
       <c r="F4" s="0">
         <v>0.0047936319832520939</v>
       </c>
       <c r="G4" s="0">
-        <v>0.012300780327542872</v>
+        <v>0.012300780327542877</v>
       </c>
       <c r="H4" s="0">
         <v>0.0036018982593929265</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.010632310666801502</v>
+        <v>-0.010632310666801495</v>
       </c>
       <c r="J4" s="0">
-        <v>-0.061418031984663245</v>
+        <v>-0.061418031984663238</v>
       </c>
       <c r="K4" s="0">
         <v>0.083506772794188819</v>
       </c>
       <c r="L4" s="0">
-        <v>0.042098509327472035</v>
+        <v>0.042098509327472042</v>
       </c>
       <c r="M4" s="0">
-        <v>0.021277843934306522</v>
+        <v>0.021277843934306526</v>
       </c>
       <c r="N4" s="0">
-        <v>0.032427341011736256</v>
+        <v>0.032427341011736263</v>
       </c>
       <c r="O4" s="0">
-        <v>0.041599468865491242</v>
+        <v>0.041599468865491249</v>
       </c>
       <c r="P4" s="0">
         <v>0.033459220219192877</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.02251123900569283</v>
+        <v>0.022511239005692834</v>
       </c>
       <c r="R4" s="0">
-        <v>0.02258295303613609</v>
+        <v>0.022582953036136093</v>
       </c>
       <c r="S4" s="0">
         <v>0.025075531682969145</v>
       </c>
       <c r="T4" s="0">
-        <v>0.054937600323355464</v>
+        <v>0.054937600323355457</v>
       </c>
       <c r="U4" s="0">
-        <v>0.041640307135442069</v>
+        <v>0.041640307135442062</v>
       </c>
       <c r="V4" s="0">
-        <v>0.044439142707816327</v>
+        <v>0.04443914270781632</v>
       </c>
       <c r="W4" s="0">
         <v>0.055212886244188714</v>
@@ -871,34 +971,34 @@
         <v>0.05618081009162032</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.054722622480382489</v>
+        <v>0.054722622480382482</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.051066943946999489</v>
+        <v>0.051066943946999482</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.052200109377753524</v>
+        <v>0.052200109377753517</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.05225936691619102</v>
+        <v>0.052259366916191013</v>
       </c>
       <c r="AC4" s="0">
         <v>0.050570034717299019</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.051734782894280885</v>
+        <v>0.051734782894280879</v>
       </c>
       <c r="AE4" s="0">
         <v>0.053243420655319153</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.054949081267275469</v>
+        <v>0.054949081267275462</v>
       </c>
       <c r="AG4" s="0">
         <v>0.054397351488425262</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.051711484709427748</v>
+        <v>0.051711484709427637</v>
       </c>
       <c r="AI4" s="0">
         <v>0.050164603436464762</v>
@@ -910,7 +1010,7 @@
         <v>0.051499939203650348</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.052104933092651941</v>
+        <v>0.05210493309265183</v>
       </c>
       <c r="AM4" s="0">
         <v>0.052116584423815705</v>
@@ -924,162 +1024,162 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="B5" s="0">
-        <v>-0.37443848101655242</v>
+        <v>0.055486024490896124</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.012702194956710489</v>
+        <v>-0.012702194956710565</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.0053741464852489762</v>
+        <v>-0.005374146485249056</v>
       </c>
       <c r="E5" s="0">
-        <v>0.013202308870674251</v>
+        <v>0.013202308870674173</v>
       </c>
       <c r="F5" s="0">
-        <v>0.020226923364166038</v>
+        <v>0.020226923364166066</v>
       </c>
       <c r="G5" s="0">
-        <v>0.0038681168096839601</v>
+        <v>0.0038681168096838768</v>
       </c>
       <c r="H5" s="0">
-        <v>-0.0014069022719456793</v>
+        <v>-0.0014069022719457626</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.010746652435382701</v>
+        <v>-0.010746652435382781</v>
       </c>
       <c r="J5" s="0">
-        <v>-0.038672715018868549</v>
+        <v>-0.038672715018868625</v>
       </c>
       <c r="K5" s="0">
-        <v>0.046242670608277851</v>
+        <v>0.046242670608277768</v>
       </c>
       <c r="L5" s="0">
-        <v>0.032087587651180735</v>
+        <v>0.032087587651180645</v>
       </c>
       <c r="M5" s="0">
-        <v>0.020549004741740859</v>
+        <v>0.020549004741740769</v>
       </c>
       <c r="N5" s="0">
-        <v>0.028630609697237797</v>
+        <v>0.028630609697237724</v>
       </c>
       <c r="O5" s="0">
-        <v>0.025809721325159296</v>
+        <v>0.025809721325159334</v>
       </c>
       <c r="P5" s="0">
-        <v>0.026436049586985234</v>
+        <v>0.026436049586985248</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.01878120487739502</v>
+        <v>0.018781204877395034</v>
       </c>
       <c r="R5" s="0">
-        <v>0.019427291127762467</v>
+        <v>0.01942729112776248</v>
       </c>
       <c r="S5" s="0">
-        <v>0.018842827998864428</v>
+        <v>0.018842827998864345</v>
       </c>
       <c r="T5" s="0">
-        <v>0.039848805662785737</v>
+        <v>0.039848805662785751</v>
       </c>
       <c r="U5" s="0">
-        <v>0.0368354748338462</v>
+        <v>0.036835474833846187</v>
       </c>
       <c r="V5" s="0">
-        <v>0.041295026842261835</v>
+        <v>0.041295026842261828</v>
       </c>
       <c r="W5" s="0">
-        <v>0.048146828548922833</v>
+        <v>0.04814682854892282</v>
       </c>
       <c r="X5" s="0">
-        <v>0.048803883237712682</v>
+        <v>0.048803883237712661</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.048887690302795057</v>
+        <v>0.048887690302795037</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.04338826851800804</v>
+        <v>0.043388268518008033</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.043315476262297384</v>
+        <v>0.04331547626229737</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.044697988409070813</v>
+        <v>0.044697988409070799</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.044708888724039456</v>
+        <v>0.044708888724039442</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.04304110553234166</v>
+        <v>0.043041105532341653</v>
       </c>
       <c r="AE5" s="0">
         <v>0.044448454850834609</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.046217389546187496</v>
+        <v>0.046217389546187489</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.04820173184352728</v>
+        <v>0.048201731843527273</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.047693422755138895</v>
+        <v>0.047693422755138881</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.044825064135562552</v>
+        <v>0.044825064135562545</v>
       </c>
       <c r="AJ5" s="0">
         <v>0.043202834678336549</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.043856471237945248</v>
+        <v>0.043856471237945255</v>
       </c>
       <c r="AL5" s="0">
         <v>0.044819082596581759</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.045550537967718151</v>
+        <v>0.045550537967718262</v>
       </c>
       <c r="AN5" s="0">
         <v>0.045619038144155709</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.044756495508269233</v>
+        <v>0.04475649550826924</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.39477406481363475</v>
+        <v>0.032263302252500826</v>
       </c>
       <c r="C6" s="0">
-        <v>-0.0094274541427797065</v>
+        <v>-0.0094274541427796996</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.0098165612929002333</v>
+        <v>-0.0098165612929002263</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.0023487080085657086</v>
+        <v>-0.0023487080085657017</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.0086583804029078115</v>
+        <v>-0.0086583804029078046</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.0054340259083950626</v>
+        <v>-0.0054340259083950557</v>
       </c>
       <c r="H6" s="0">
-        <v>-0.0065539401508452333</v>
+        <v>-0.0065539401508452264</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.013651670884479744</v>
+        <v>-0.013651670884479737</v>
       </c>
       <c r="J6" s="0">
         <v>-0.035139292967922203</v>
       </c>
       <c r="K6" s="0">
-        <v>0.024831739846267381</v>
+        <v>0.024831739846267388</v>
       </c>
       <c r="L6" s="0">
         <v>0.016870479800516897</v>
@@ -1091,10 +1191,10 @@
         <v>0.023562270899732257</v>
       </c>
       <c r="O6" s="0">
-        <v>0.022503835982026071</v>
+        <v>0.022503835982026078</v>
       </c>
       <c r="P6" s="0">
-        <v>0.016627122488387241</v>
+        <v>0.016627122488387248</v>
       </c>
       <c r="Q6" s="0">
         <v>0.016294200651658847</v>
@@ -1109,34 +1209,34 @@
         <v>0.033677227950180105</v>
       </c>
       <c r="U6" s="0">
-        <v>0.030801701882456865</v>
+        <v>0.030801701882456869</v>
       </c>
       <c r="V6" s="0">
-        <v>0.043793562001004115</v>
+        <v>0.043793562001004108</v>
       </c>
       <c r="W6" s="0">
-        <v>0.046527981823540863</v>
+        <v>0.046527981823540857</v>
       </c>
       <c r="X6" s="0">
-        <v>0.045534778306406586</v>
+        <v>0.045534778306406579</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.04701621914579298</v>
+        <v>0.047016219145792973</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.042204248431996404</v>
+        <v>0.042204248431996397</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.042186777917608574</v>
+        <v>0.042186777917608567</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.042399357228157984</v>
+        <v>0.042399357228157977</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.043862301147063319</v>
+        <v>0.043862301147063312</v>
       </c>
       <c r="AD6" s="0">
-        <v>0.044074140935555138</v>
+        <v>0.044074140935555131</v>
       </c>
       <c r="AE6" s="0">
         <v>0.042516374851200488</v>
@@ -1145,13 +1245,13 @@
         <v>0.044270114989099794</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.046403055946117232</v>
+        <v>0.046403055946117225</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.04876923028997978</v>
+        <v>0.048769230289979773</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.048383908285399811</v>
+        <v>0.048383908285399804</v>
       </c>
       <c r="AJ6" s="0">
         <v>0.045371764879791519</v>
@@ -1166,7 +1266,7 @@
         <v>0.045740860162084528</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.046658586496614217</v>
+        <v>0.046658586496614106</v>
       </c>
       <c r="AO6" s="0">
         <v>0.046827914600688213</v>
@@ -1174,67 +1274,67 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="B7" s="0">
-        <v>-0.44667298808583028</v>
+        <v>-0.024362696747206626</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.019744143023249609</v>
+        <v>-0.019744143023249595</v>
       </c>
       <c r="D7" s="0">
-        <v>-0.015694522694105643</v>
+        <v>-0.01569452269410563</v>
       </c>
       <c r="E7" s="0">
-        <v>-0.013803534801163191</v>
+        <v>-0.013803534801163177</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.0056008504068616946</v>
+        <v>-0.0056008504068616807</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.011072434743251085</v>
+        <v>-0.011072434743251078</v>
       </c>
       <c r="H7" s="0">
-        <v>-0.011630240244701988</v>
+        <v>-0.011630240244701981</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.015827651241563205</v>
+        <v>-0.015827651241563198</v>
       </c>
       <c r="J7" s="0">
-        <v>-0.03310727451521616</v>
+        <v>-0.033107274515216153</v>
       </c>
       <c r="K7" s="0">
-        <v>0.016949583156538335</v>
+        <v>0.016949583156538345</v>
       </c>
       <c r="L7" s="0">
-        <v>0.011694021451363834</v>
+        <v>0.011694021451363851</v>
       </c>
       <c r="M7" s="0">
-        <v>0.0066070355231971356</v>
+        <v>0.006607035523197146</v>
       </c>
       <c r="N7" s="0">
-        <v>0.016179132674044194</v>
+        <v>0.01617913267404409</v>
       </c>
       <c r="O7" s="0">
-        <v>0.019926990479983864</v>
+        <v>0.01992699047998376</v>
       </c>
       <c r="P7" s="0">
-        <v>0.011600062759427765</v>
+        <v>0.011600062759427779</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.011348239910148161</v>
+        <v>0.011348239910148179</v>
       </c>
       <c r="R7" s="0">
-        <v>0.017647398240613066</v>
+        <v>0.017647398240613069</v>
       </c>
       <c r="S7" s="0">
-        <v>0.020410556529964541</v>
+        <v>0.020410556529964433</v>
       </c>
       <c r="T7" s="0">
-        <v>0.034731058335620346</v>
+        <v>0.034731058335620353</v>
       </c>
       <c r="U7" s="0">
-        <v>0.027111581932348916</v>
+        <v>0.027111581932348923</v>
       </c>
       <c r="V7" s="0">
         <v>0.037972505161053161</v>
@@ -1258,31 +1358,31 @@
         <v>0.049972656292513504</v>
       </c>
       <c r="AC7" s="0">
-        <v>0.050367205191953639</v>
+        <v>0.050367205191953632</v>
       </c>
       <c r="AD7" s="0">
         <v>0.052324027316411989</v>
       </c>
       <c r="AE7" s="0">
-        <v>0.052839647456881682</v>
+        <v>0.052839647456881675</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.05128470322715855</v>
+        <v>0.051284703227158661</v>
       </c>
       <c r="AG7" s="0">
-        <v>0.053524444794866115</v>
+        <v>0.053524444794866108</v>
       </c>
       <c r="AH7" s="0">
-        <v>0.056196092357453091</v>
+        <v>0.056196092357453084</v>
       </c>
       <c r="AI7" s="0">
         <v>0.059140392258269989</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.058861085693118813</v>
+        <v>0.058861085693118806</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.055482472390448505</v>
+        <v>0.055482472390448616</v>
       </c>
       <c r="AL7" s="0">
         <v>0.053666018053928059</v>
@@ -1294,81 +1394,81 @@
         <v>0.056281623903386695</v>
       </c>
       <c r="AO7" s="0">
-        <v>0.057466221853147585</v>
+        <v>0.057466221853147696</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="B8" s="0">
-        <v>-0.49360419959189489</v>
+        <v>-0.077681981575542222</v>
       </c>
       <c r="C8" s="0">
-        <v>-0.023277271395060535</v>
+        <v>-0.023277271395060518</v>
       </c>
       <c r="D8" s="0">
-        <v>-0.024987170380011477</v>
+        <v>-0.024987170380011459</v>
       </c>
       <c r="E8" s="0">
-        <v>-0.0022380335949466271</v>
+        <v>-0.0022380335949466045</v>
       </c>
       <c r="F8" s="0">
-        <v>-0.003774767171564504</v>
+        <v>-0.0037747671715644814</v>
       </c>
       <c r="G8" s="0">
-        <v>-0.018837995105936929</v>
+        <v>-0.018837995105936915</v>
       </c>
       <c r="H8" s="0">
-        <v>-0.018099542588297497</v>
+        <v>-0.018099542588297483</v>
       </c>
       <c r="I8" s="0">
-        <v>-0.023618017476338245</v>
+        <v>-0.023618017476338342</v>
       </c>
       <c r="J8" s="0">
-        <v>-0.036927158134320411</v>
+        <v>-0.036927158134320508</v>
       </c>
       <c r="K8" s="0">
-        <v>0.007065565109499676</v>
+        <v>0.0070655651094995806</v>
       </c>
       <c r="L8" s="0">
-        <v>0.0037115214991423826</v>
+        <v>0.0037115214991422867</v>
       </c>
       <c r="M8" s="0">
-        <v>0.00046446070404598111</v>
+        <v>0.00046446070404588478</v>
       </c>
       <c r="N8" s="0">
-        <v>0.0081538935903364002</v>
+        <v>0.008153893590336303</v>
       </c>
       <c r="O8" s="0">
-        <v>0.0092240250353885916</v>
+        <v>0.0092240250353885986</v>
       </c>
       <c r="P8" s="0">
-        <v>0.0069506092481375487</v>
+        <v>0.0069506092481375547</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.0082444176885352813</v>
+        <v>0.0082444176885351841</v>
       </c>
       <c r="R8" s="0">
-        <v>0.012443883907405744</v>
+        <v>0.012443883907405643</v>
       </c>
       <c r="S8" s="0">
-        <v>0.017292850567156161</v>
+        <v>0.017292850567156171</v>
       </c>
       <c r="T8" s="0">
-        <v>0.031521434602123012</v>
+        <v>0.031521434602123026</v>
       </c>
       <c r="U8" s="0">
-        <v>0.027082537533778685</v>
+        <v>0.027082537533778699</v>
       </c>
       <c r="V8" s="0">
-        <v>0.032384978759609814</v>
+        <v>0.032384978759609821</v>
       </c>
       <c r="W8" s="0">
-        <v>0.041678498616248873</v>
+        <v>0.04167849861624888</v>
       </c>
       <c r="X8" s="0">
-        <v>0.046740050040789204</v>
+        <v>0.046740050040789197</v>
       </c>
       <c r="Y8" s="0">
         <v>0.051460424840708799</v>
@@ -1386,28 +1486,28 @@
         <v>0.059285298673382406</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.060157936055520139</v>
+        <v>0.060157936055520132</v>
       </c>
       <c r="AE8" s="0">
-        <v>0.062814644599020003</v>
+        <v>0.062814644599019989</v>
       </c>
       <c r="AF8" s="0">
-        <v>0.063767816462993926</v>
+        <v>0.063767816462993912</v>
       </c>
       <c r="AG8" s="0">
-        <v>0.062263152718157105</v>
+        <v>0.062263152718157112</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.065180589669482064</v>
+        <v>0.06518058966948205</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.068591157893913263</v>
+        <v>0.068591157893913249</v>
       </c>
       <c r="AJ8" s="0">
         <v>0.072326527671071963</v>
       </c>
       <c r="AK8" s="0">
-        <v>0.072218810292072361</v>
+        <v>0.072218810292072347</v>
       </c>
       <c r="AL8" s="0">
         <v>0.06839029681186129</v>
@@ -1424,85 +1524,85 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="B9" s="0">
-        <v>-0.56305776842292055</v>
+        <v>-0.15514258183260632</v>
       </c>
       <c r="C9" s="0">
-        <v>-0.037199091661566056</v>
+        <v>-0.037199091661566021</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.036004194110941704</v>
+        <v>-0.036004194110941669</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.034009631774868723</v>
+        <v>-0.034009631774868689</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.038667025253932251</v>
+        <v>-0.038667025253932216</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.033762485938915753</v>
+        <v>-0.033762485938915718</v>
       </c>
       <c r="H9" s="0">
-        <v>-0.031649879133818698</v>
+        <v>-0.031649879133818677</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.034137274010349966</v>
+        <v>-0.034137274010349945</v>
       </c>
       <c r="J9" s="0">
-        <v>-0.043899557951590937</v>
+        <v>-0.043899557951590965</v>
       </c>
       <c r="K9" s="0">
-        <v>-0.010537820685555289</v>
+        <v>-0.01053782068555531</v>
       </c>
       <c r="L9" s="0">
-        <v>-0.008743488884343488</v>
+        <v>-0.0087434888843435209</v>
       </c>
       <c r="M9" s="0">
-        <v>-0.010566105072038125</v>
+        <v>-0.010566105072038159</v>
       </c>
       <c r="N9" s="0">
-        <v>-0.0030381415838877518</v>
+        <v>-0.003038141583887672</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.0023588494353154466</v>
+        <v>-0.0023588494353154938</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.0050283536279328092</v>
+        <v>-0.0050283536279328639</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.0011611979587263163</v>
+        <v>0.0011611979587262615</v>
       </c>
       <c r="R9" s="0">
-        <v>0.0039062506038237202</v>
+        <v>0.0039062506038237974</v>
       </c>
       <c r="S9" s="0">
-        <v>0.011517652170845723</v>
+        <v>0.011517652170845801</v>
       </c>
       <c r="T9" s="0">
-        <v>0.027024673757968055</v>
+        <v>0.02702467375796799</v>
       </c>
       <c r="U9" s="0">
-        <v>0.0226823134521991</v>
+        <v>0.022682313452199031</v>
       </c>
       <c r="V9" s="0">
-        <v>0.031198898782945052</v>
+        <v>0.031198898782944989</v>
       </c>
       <c r="W9" s="0">
-        <v>0.034877454123141513</v>
+        <v>0.034877454123141451</v>
       </c>
       <c r="X9" s="0">
-        <v>0.036961729073535926</v>
+        <v>0.036961729073535843</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.054339186864002284</v>
+        <v>0.054339186864002277</v>
       </c>
       <c r="Z9" s="0">
-        <v>0.052703664240623435</v>
+        <v>0.052703664240623428</v>
       </c>
       <c r="AA9" s="0">
-        <v>0.057869015600664361</v>
+        <v>0.057869015600664347</v>
       </c>
       <c r="AB9" s="0">
         <v>0.063396858649342386</v>
@@ -1511,37 +1611,37 @@
         <v>0.066801046139085857</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.067031310904129712</v>
+        <v>0.067031310904129698</v>
       </c>
       <c r="AE9" s="0">
-        <v>0.068527730407746401</v>
+        <v>0.068527730407746498</v>
       </c>
       <c r="AF9" s="0">
-        <v>0.072040010733636403</v>
+        <v>0.072040010733636389</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.073528539983840902</v>
+        <v>0.073528539983840888</v>
       </c>
       <c r="AH9" s="0">
         <v>0.072081871265615161</v>
       </c>
       <c r="AI9" s="0">
-        <v>0.075831399120298792</v>
+        <v>0.075831399120298779</v>
       </c>
       <c r="AJ9" s="0">
-        <v>0.080163584725834722</v>
+        <v>0.080163584725834708</v>
       </c>
       <c r="AK9" s="0">
         <v>0.084886327220696195</v>
       </c>
       <c r="AL9" s="0">
-        <v>0.08500565772529188</v>
+        <v>0.085005657725291867</v>
       </c>
       <c r="AM9" s="0">
         <v>0.080633336811407608</v>
       </c>
       <c r="AN9" s="0">
-        <v>0.078429760642341417</v>
+        <v>0.078429760642341431</v>
       </c>
       <c r="AO9" s="0">
         <v>0.080404472206152766</v>
@@ -1549,106 +1649,106 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B10" s="0">
-        <v>-0.63283476123326854</v>
+        <v>-0.2336411048282977</v>
       </c>
       <c r="C10" s="0">
-        <v>-0.052037642757123095</v>
+        <v>-0.052037642757123061</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.052427197860636612</v>
+        <v>-0.052427197860636578</v>
       </c>
       <c r="E10" s="0">
-        <v>-0.046107837924667675</v>
+        <v>-0.04610783792466764</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.042071983317046716</v>
+        <v>-0.042071983317046681</v>
       </c>
       <c r="G10" s="0">
-        <v>-0.046706357299421478</v>
+        <v>-0.046706357299421457</v>
       </c>
       <c r="H10" s="0">
-        <v>-0.048835170295939825</v>
+        <v>-0.048835170295939805</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.050145710164612917</v>
+        <v>-0.050145710164612882</v>
       </c>
       <c r="J10" s="0">
-        <v>-0.057982793637873037</v>
+        <v>-0.057982793637873002</v>
       </c>
       <c r="K10" s="0">
-        <v>-0.034758791616538803</v>
+        <v>-0.034758791616538838</v>
       </c>
       <c r="L10" s="0">
-        <v>-0.030807569915452276</v>
+        <v>-0.030807569915452259</v>
       </c>
       <c r="M10" s="0">
-        <v>-0.029071464908344197</v>
+        <v>-0.029071464908344179</v>
       </c>
       <c r="N10" s="0">
-        <v>-0.020415995927386105</v>
+        <v>-0.020415995927386087</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.016114372976254815</v>
+        <v>-0.016114372976254867</v>
       </c>
       <c r="P10" s="0">
         <v>-0.024037370796022736</v>
       </c>
       <c r="Q10" s="0">
-        <v>-0.016994802059183682</v>
+        <v>-0.016994802059183634</v>
       </c>
       <c r="R10" s="0">
-        <v>-0.0089083952660905519</v>
+        <v>-0.0089083952660904964</v>
       </c>
       <c r="S10" s="0">
-        <v>-0.0031001449426675612</v>
+        <v>-0.0031001449426676072</v>
       </c>
       <c r="T10" s="0">
-        <v>0.012822225808479706</v>
+        <v>0.012822225808479715</v>
       </c>
       <c r="U10" s="0">
-        <v>0.014650831894722605</v>
+        <v>0.014650831894722638</v>
       </c>
       <c r="V10" s="0">
-        <v>0.022492956868268577</v>
+        <v>0.022492956868268608</v>
       </c>
       <c r="W10" s="0">
-        <v>0.030610684006430411</v>
+        <v>0.030610684006430446</v>
       </c>
       <c r="X10" s="0">
-        <v>0.029085253769752462</v>
+        <v>0.029085253769752503</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.04001302546674855</v>
+        <v>0.040013025466748578</v>
       </c>
       <c r="Z10" s="0">
-        <v>0.048993111566340397</v>
+        <v>0.048993111566340293</v>
       </c>
       <c r="AA10" s="0">
-        <v>0.051938305422385589</v>
+        <v>0.051938305422385485</v>
       </c>
       <c r="AB10" s="0">
-        <v>0.057929186365458019</v>
+        <v>0.057929186365457908</v>
       </c>
       <c r="AC10" s="0">
-        <v>0.064747300591034784</v>
+        <v>0.06474730059103477</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.069432461292525838</v>
+        <v>0.069432461292525824</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.07050681580248791</v>
+        <v>0.070506815802488021</v>
       </c>
       <c r="AF10" s="0">
-        <v>0.073059685358416948</v>
+        <v>0.073059685358416837</v>
       </c>
       <c r="AG10" s="0">
         <v>0.077627298958828972</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.079937592374988709</v>
+        <v>0.079937592374988597</v>
       </c>
       <c r="AI10" s="0">
         <v>0.078913323318595643</v>
@@ -1657,10 +1757,10 @@
         <v>0.083707308737051955</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.089127787434477745</v>
+        <v>0.089127787434477634</v>
       </c>
       <c r="AL10" s="0">
-        <v>0.095003213782684559</v>
+        <v>0.095003213782684545</v>
       </c>
       <c r="AM10" s="0">
         <v>0.095569887732861181</v>
@@ -1669,15 +1769,15 @@
         <v>0.090922408542367827</v>
       </c>
       <c r="AO10" s="0">
-        <v>0.088734932072262088</v>
+        <v>0.088734932072262102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="B11" s="0">
-        <v>-0.71421675204726509</v>
+        <v>-0.32390276212599578</v>
       </c>
       <c r="C11" s="0">
         <v>-0.063095807121780478</v>
@@ -1701,64 +1801,64 @@
         <v>-0.062601565455874586</v>
       </c>
       <c r="J11" s="0">
-        <v>-0.071900696615017926</v>
+        <v>-0.071900696615017939</v>
       </c>
       <c r="K11" s="0">
         <v>-0.056389295960481069</v>
       </c>
       <c r="L11" s="0">
-        <v>-0.05351963079214133</v>
+        <v>-0.053519630792141344</v>
       </c>
       <c r="M11" s="0">
-        <v>-0.052387330617470411</v>
+        <v>-0.052387330617470425</v>
       </c>
       <c r="N11" s="0">
-        <v>-0.044351996998709224</v>
+        <v>-0.044351996998709238</v>
       </c>
       <c r="O11" s="0">
-        <v>-0.039156312930785579</v>
+        <v>-0.039156312930785607</v>
       </c>
       <c r="P11" s="0">
-        <v>-0.043064026664249626</v>
+        <v>-0.043064026664249654</v>
       </c>
       <c r="Q11" s="0">
-        <v>-0.043426805538880016</v>
+        <v>-0.043426805538880002</v>
       </c>
       <c r="R11" s="0">
-        <v>-0.037189685831258229</v>
+        <v>-0.03718968583125825</v>
       </c>
       <c r="S11" s="0">
-        <v>-0.027270322534959895</v>
+        <v>-0.027270322534959875</v>
       </c>
       <c r="T11" s="0">
-        <v>-0.0093583961450495259</v>
+        <v>-0.0093583961450494982</v>
       </c>
       <c r="U11" s="0">
-        <v>-0.0031568683343509846</v>
+        <v>-0.0031568683343509494</v>
       </c>
       <c r="V11" s="0">
-        <v>0.0012758384819101104</v>
+        <v>0.0012758384819101709</v>
       </c>
       <c r="W11" s="0">
-        <v>0.012176445807687578</v>
+        <v>0.012176445807687631</v>
       </c>
       <c r="X11" s="0">
-        <v>0.015351071580688228</v>
+        <v>0.015351071580688288</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.022716677505166219</v>
+        <v>0.022716677505166288</v>
       </c>
       <c r="Z11" s="0">
-        <v>0.027638269636964211</v>
+        <v>0.027638269636964242</v>
       </c>
       <c r="AA11" s="0">
-        <v>0.038452279376099879</v>
+        <v>0.038452279376099886</v>
       </c>
       <c r="AB11" s="0">
-        <v>0.041301010444640657</v>
+        <v>0.041301010444640664</v>
       </c>
       <c r="AC11" s="0">
-        <v>0.04796399875360681</v>
+        <v>0.047963998753606824</v>
       </c>
       <c r="AD11" s="0">
         <v>0.056287149449450694</v>
@@ -1767,19 +1867,19 @@
         <v>0.062829846873620823</v>
       </c>
       <c r="AF11" s="0">
-        <v>0.065683415624833055</v>
+        <v>0.065683415624833069</v>
       </c>
       <c r="AG11" s="0">
         <v>0.070191718917387874</v>
       </c>
       <c r="AH11" s="0">
-        <v>0.0761950887609011</v>
+        <v>0.076195088760901114</v>
       </c>
       <c r="AI11" s="0">
-        <v>0.079951042190502433</v>
+        <v>0.079951042190502447</v>
       </c>
       <c r="AJ11" s="0">
-        <v>0.080218701882241145</v>
+        <v>0.080218701882241158</v>
       </c>
       <c r="AK11" s="0">
         <v>0.086397575908968266</v>
@@ -1788,7 +1888,7 @@
         <v>0.093151961142697096</v>
       </c>
       <c r="AM11" s="0">
-        <v>0.10040439131758706</v>
+        <v>0.10040439131758705</v>
       </c>
       <c r="AN11" s="0">
         <v>0.10193129163395233</v>
@@ -1799,31 +1899,31 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="B12" s="0">
-        <v>-0.77912343740203005</v>
+        <v>-0.39596462147111655</v>
       </c>
       <c r="C12" s="0">
-        <v>-0.057882462110618434</v>
+        <v>-0.057882462110618427</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.058502182241174393</v>
+        <v>-0.058502182241174386</v>
       </c>
       <c r="E12" s="0">
-        <v>-0.055487365748173013</v>
+        <v>-0.055487365748173006</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.058398778806590008</v>
+        <v>-0.058398778806590002</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.061221379632603525</v>
+        <v>-0.061221379632603518</v>
       </c>
       <c r="H12" s="0">
         <v>-0.063109714086543131</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.061028222051366966</v>
+        <v>-0.061028222051366959</v>
       </c>
       <c r="J12" s="0">
         <v>-0.071770928129587075</v>
@@ -1835,82 +1935,82 @@
         <v>-0.060416401237069629</v>
       </c>
       <c r="M12" s="0">
-        <v>-0.067543286206199607</v>
+        <v>-0.067543286206199593</v>
       </c>
       <c r="N12" s="0">
-        <v>-0.062255815915461143</v>
+        <v>-0.06225581591546115</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.061660531178651529</v>
+        <v>-0.061660531178651536</v>
       </c>
       <c r="P12" s="0">
-        <v>-0.062259141649635114</v>
+        <v>-0.06225914164963512</v>
       </c>
       <c r="Q12" s="0">
-        <v>-0.061028771065346432</v>
+        <v>-0.061028771065346439</v>
       </c>
       <c r="R12" s="0">
-        <v>-0.063646586060022228</v>
+        <v>-0.063646586060022242</v>
       </c>
       <c r="S12" s="0">
-        <v>-0.06226801879858819</v>
+        <v>-0.062268018798588183</v>
       </c>
       <c r="T12" s="0">
-        <v>-0.047715992430325829</v>
+        <v>-0.047715992430325822</v>
       </c>
       <c r="U12" s="0">
-        <v>-0.035240744956108086</v>
+        <v>-0.035240744956108051</v>
       </c>
       <c r="V12" s="0">
-        <v>-0.026376491651412051</v>
+        <v>-0.02637649165141203</v>
       </c>
       <c r="W12" s="0">
-        <v>-0.025943043178616038</v>
+        <v>-0.025943043178616034</v>
       </c>
       <c r="X12" s="0">
-        <v>-0.021897463176828752</v>
+        <v>-0.021897463176828762</v>
       </c>
       <c r="Y12" s="0">
-        <v>-0.0099024715330879587</v>
+        <v>-0.0099024715330879691</v>
       </c>
       <c r="Z12" s="0">
-        <v>-0.0045045624943921558</v>
+        <v>-0.0045045624943921515</v>
       </c>
       <c r="AA12" s="0">
-        <v>0.0018896324776878221</v>
+        <v>0.0018896324776877553</v>
       </c>
       <c r="AB12" s="0">
-        <v>0.0043655702827180981</v>
+        <v>0.004365570282718125</v>
       </c>
       <c r="AC12" s="0">
-        <v>0.0073417494248764065</v>
+        <v>0.0073417494248764334</v>
       </c>
       <c r="AD12" s="0">
-        <v>0.015324723570639284</v>
+        <v>0.015324723570639296</v>
       </c>
       <c r="AE12" s="0">
-        <v>0.025357244804214626</v>
+        <v>0.02535724480421463</v>
       </c>
       <c r="AF12" s="0">
         <v>0.034700380701019759</v>
       </c>
       <c r="AG12" s="0">
-        <v>0.041054146586258708</v>
+        <v>0.041054146586258715</v>
       </c>
       <c r="AH12" s="0">
-        <v>0.04902412598894966</v>
+        <v>0.049024125988949674</v>
       </c>
       <c r="AI12" s="0">
-        <v>0.057071189215417747</v>
+        <v>0.057071189215417754</v>
       </c>
       <c r="AJ12" s="0">
         <v>0.063365854611260194</v>
       </c>
       <c r="AK12" s="0">
-        <v>0.066576855081792993</v>
+        <v>0.066576855081793007</v>
       </c>
       <c r="AL12" s="0">
-        <v>0.07460381519617397</v>
+        <v>0.074603815196173984</v>
       </c>
       <c r="AM12" s="0">
         <v>0.082989221957588052</v>
@@ -1924,10 +2024,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="B13" s="0">
-        <v>-0.81696434357021708</v>
+        <v>-0.43927762026361944</v>
       </c>
       <c r="C13" s="0">
         <v>-0.038499867934799592</v>
@@ -1963,10 +2063,10 @@
         <v>-0.052025480713557004</v>
       </c>
       <c r="N13" s="0">
-        <v>-0.05694144674551474</v>
+        <v>-0.056941446745514747</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.060921105529923733</v>
+        <v>-0.060921105529923726</v>
       </c>
       <c r="P13" s="0">
         <v>-0.063235788810306268</v>
@@ -1984,64 +2084,64 @@
         <v>-0.072324230884668841</v>
       </c>
       <c r="U13" s="0">
-        <v>-0.071012069490101068</v>
+        <v>-0.07101206949010104</v>
       </c>
       <c r="V13" s="0">
-        <v>-0.060751002163581883</v>
+        <v>-0.060751002163581862</v>
       </c>
       <c r="W13" s="0">
-        <v>-0.052671560158189842</v>
+        <v>-0.052671560158189815</v>
       </c>
       <c r="X13" s="0">
-        <v>-0.06893749032213195</v>
+        <v>-0.068937490322132006</v>
       </c>
       <c r="Y13" s="0">
-        <v>-0.061465805543283215</v>
+        <v>-0.061465805543283208</v>
       </c>
       <c r="Z13" s="0">
-        <v>-0.0552906917100826</v>
+        <v>-0.055290691710082628</v>
       </c>
       <c r="AA13" s="0">
-        <v>-0.044809964072162457</v>
+        <v>-0.04480996407216245</v>
       </c>
       <c r="AB13" s="0">
-        <v>-0.044386436561787701</v>
+        <v>-0.044386436561787687</v>
       </c>
       <c r="AC13" s="0">
-        <v>-0.057069717185191403</v>
+        <v>-0.057069717185191375</v>
       </c>
       <c r="AD13" s="0">
-        <v>-0.054037897288023128</v>
+        <v>-0.0540378972880231</v>
       </c>
       <c r="AE13" s="0">
-        <v>-0.046904188690595455</v>
+        <v>-0.046904188690595414</v>
       </c>
       <c r="AF13" s="0">
-        <v>-0.038415503548994284</v>
+        <v>-0.038415503548994263</v>
       </c>
       <c r="AG13" s="0">
-        <v>-0.028105353051253543</v>
+        <v>-0.028105353051253508</v>
       </c>
       <c r="AH13" s="0">
-        <v>-0.018604447039354849</v>
+        <v>-0.018604447039354832</v>
       </c>
       <c r="AI13" s="0">
-        <v>-0.0068676179986192631</v>
+        <v>-0.0068676179986192449</v>
       </c>
       <c r="AJ13" s="0">
-        <v>0.0017731315482683724</v>
+        <v>0.0017731315482683941</v>
       </c>
       <c r="AK13" s="0">
-        <v>0.010506404215373924</v>
+        <v>0.010506404215373947</v>
       </c>
       <c r="AL13" s="0">
-        <v>0.018258941888178518</v>
+        <v>0.018258941888178549</v>
       </c>
       <c r="AM13" s="0">
-        <v>0.027482244375284862</v>
+        <v>0.027482244375284886</v>
       </c>
       <c r="AN13" s="0">
-        <v>0.036363293737241287</v>
+        <v>0.036363293737241308</v>
       </c>
       <c r="AO13" s="0">
         <v>0.045797794273245998</v>
@@ -2049,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="B14" s="0">
-        <v>-0.82743038255087886</v>
+        <v>-0.45322080250298341</v>
       </c>
       <c r="C14" s="0">
         <v>-0.014391441276768537</v>
@@ -2121,63 +2221,63 @@
         <v>-0.069499559313150217</v>
       </c>
       <c r="Y14" s="0">
-        <v>-0.09323917844778061</v>
+        <v>-0.093239178447780624</v>
       </c>
       <c r="Z14" s="0">
-        <v>-0.097383452624637865</v>
+        <v>-0.097383452624637892</v>
       </c>
       <c r="AA14" s="0">
         <v>-0.095190578088595504</v>
       </c>
       <c r="AB14" s="0">
-        <v>-0.090152375335023113</v>
+        <v>-0.090152375335023141</v>
       </c>
       <c r="AC14" s="0">
-        <v>-0.102576641790045</v>
+        <v>-0.10257664179004501</v>
       </c>
       <c r="AD14" s="0">
-        <v>-0.13417950705034012</v>
+        <v>-0.13417950705034015</v>
       </c>
       <c r="AE14" s="0">
-        <v>-0.13293766279002708</v>
+        <v>-0.13293766279002711</v>
       </c>
       <c r="AF14" s="0">
-        <v>-0.1335880302465654</v>
+        <v>-0.13358803024656543</v>
       </c>
       <c r="AG14" s="0">
         <v>-0.13557314433976142</v>
       </c>
       <c r="AH14" s="0">
-        <v>-0.13226872978540294</v>
+        <v>-0.13226872978540297</v>
       </c>
       <c r="AI14" s="0">
-        <v>-0.12459140471888019</v>
+        <v>-0.12459140471888018</v>
       </c>
       <c r="AJ14" s="0">
-        <v>-0.11535101057565567</v>
+        <v>-0.11535101057565568</v>
       </c>
       <c r="AK14" s="0">
-        <v>-0.11302040291566937</v>
+        <v>-0.11302040291566935</v>
       </c>
       <c r="AL14" s="0">
-        <v>-0.10699752375611601</v>
+        <v>-0.106997523756116</v>
       </c>
       <c r="AM14" s="0">
-        <v>-0.09653127121046276</v>
+        <v>-0.096531271210462746</v>
       </c>
       <c r="AN14" s="0">
-        <v>-0.092826748981408774</v>
+        <v>-0.092826748981408719</v>
       </c>
       <c r="AO14" s="0">
-        <v>-0.090435411379077096</v>
+        <v>-0.090435411379077069</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="B15" s="0">
-        <v>-0.82593455233002355</v>
+        <v>-0.454063972031513</v>
       </c>
       <c r="C15" s="0">
         <v>-0.002978950400279384</v>
@@ -2299,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="B16" s="0">
-        <v>-0.82237107008060717</v>
+        <v>-0.452291760434334</v>
       </c>
       <c r="C16" s="0">
         <v>-0.00033334425406091809</v>
@@ -2424,10 +2524,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="B17" s="0">
-        <v>-0.15967272058620607</v>
+        <v>0.2753267546775866</v>
       </c>
       <c r="C17" s="0">
         <v>0.002214154581450245</v>
@@ -2549,10 +2649,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="B18" s="0">
-        <v>-0.24565717190814917</v>
+        <v>0.18944091200051794</v>
       </c>
       <c r="C18" s="0">
         <v>-0.008798052235841184</v>
@@ -2561,7 +2661,7 @@
         <v>0.0024929074421023954</v>
       </c>
       <c r="E18" s="0">
-        <v>-0.021373270782093393</v>
+        <v>-0.02137327078209339</v>
       </c>
       <c r="F18" s="0">
         <v>-0.0086453951054279478</v>
@@ -2585,7 +2685,7 @@
         <v>0.033933903565056878</v>
       </c>
       <c r="M18" s="0">
-        <v>0.030383907874593656</v>
+        <v>0.03038390787459366</v>
       </c>
       <c r="N18" s="0">
         <v>0.047839256681225573</v>
@@ -2597,40 +2697,40 @@
         <v>0.039490915288615258</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.036536510565018603</v>
+        <v>0.036536510565018609</v>
       </c>
       <c r="R18" s="0">
-        <v>0.042142916628999709</v>
+        <v>0.042142916628999716</v>
       </c>
       <c r="S18" s="0">
-        <v>0.046470535159674135</v>
+        <v>0.046470535159674142</v>
       </c>
       <c r="T18" s="0">
         <v>0.074841309368095077</v>
       </c>
       <c r="U18" s="0">
-        <v>0.054583454125459951</v>
+        <v>0.054583454125459945</v>
       </c>
       <c r="V18" s="0">
-        <v>0.055003826390571886</v>
+        <v>0.055003826390571879</v>
       </c>
       <c r="W18" s="0">
         <v>0.065383546651785807</v>
       </c>
       <c r="X18" s="0">
-        <v>0.061813519294937391</v>
+        <v>0.061813519294937606</v>
       </c>
       <c r="Y18" s="0">
         <v>0.065356164722600418</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.063794944403975595</v>
+        <v>0.063794944403975373</v>
       </c>
       <c r="AA18" s="0">
-        <v>0.061654781829491911</v>
+        <v>0.061654781829491904</v>
       </c>
       <c r="AB18" s="0">
-        <v>0.062307356539842318</v>
+        <v>0.062307356539842311</v>
       </c>
       <c r="AC18" s="0">
         <v>0.063362208607063986</v>
@@ -2642,25 +2742,25 @@
         <v>0.064188713044355028</v>
       </c>
       <c r="AF18" s="0">
-        <v>0.061814578816645427</v>
+        <v>0.06181457881664542</v>
       </c>
       <c r="AG18" s="0">
-        <v>0.060425638744489363</v>
+        <v>0.060425638744489356</v>
       </c>
       <c r="AH18" s="0">
-        <v>0.060816741782236616</v>
+        <v>0.060816741782236609</v>
       </c>
       <c r="AI18" s="0">
-        <v>0.061455653716094405</v>
+        <v>0.061455653716094398</v>
       </c>
       <c r="AJ18" s="0">
-        <v>0.061922434122747338</v>
+        <v>0.061922434122747332</v>
       </c>
       <c r="AK18" s="0">
-        <v>0.061888309307405409</v>
+        <v>0.061888309307405402</v>
       </c>
       <c r="AL18" s="0">
-        <v>0.06115230770110347</v>
+        <v>0.061152307701103463</v>
       </c>
       <c r="AM18" s="0">
         <v>0.060103532554758754</v>
@@ -2674,10 +2774,10 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="B19" s="0">
-        <v>-0.26155473045267985</v>
+        <v>0.17236558985102601</v>
       </c>
       <c r="C19" s="0">
         <v>-0.0007236851580176909</v>
@@ -2728,25 +2828,25 @@
         <v>0.026039029199987899</v>
       </c>
       <c r="S19" s="0">
-        <v>0.036717245073956788</v>
+        <v>0.036717245073956781</v>
       </c>
       <c r="T19" s="0">
         <v>0.062434500490324389</v>
       </c>
       <c r="U19" s="0">
-        <v>0.046318139893231074</v>
+        <v>0.046318139893231067</v>
       </c>
       <c r="V19" s="0">
         <v>0.05135931795910563</v>
       </c>
       <c r="W19" s="0">
-        <v>0.063306729060164532</v>
+        <v>0.063306729060164546</v>
       </c>
       <c r="X19" s="0">
         <v>0.064793987221842819</v>
       </c>
       <c r="Y19" s="0">
-        <v>0.067801677319718298</v>
+        <v>0.067801677319718312</v>
       </c>
       <c r="Z19" s="0">
         <v>0.066660882767059615</v>
@@ -2758,16 +2858,16 @@
         <v>0.063914424269086556</v>
       </c>
       <c r="AC19" s="0">
-        <v>0.064829697214101589</v>
+        <v>0.064829697214101478</v>
       </c>
       <c r="AD19" s="0">
         <v>0.06615753944350633</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.067667415928057237</v>
+        <v>0.067667415928057251</v>
       </c>
       <c r="AF19" s="0">
-        <v>0.067112657448067367</v>
+        <v>0.067112657448067381</v>
       </c>
       <c r="AG19" s="0">
         <v>0.064605800891545329</v>
@@ -2799,70 +2899,70 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="B20" s="0">
-        <v>-0.30679603837354075</v>
+        <v>0.1254070895445526</v>
       </c>
       <c r="C20" s="0">
-        <v>-0.0059408663182357775</v>
+        <v>-0.005940866318235774</v>
       </c>
       <c r="D20" s="0">
-        <v>-0.00052210796294517928</v>
+        <v>-0.00052210796294517581</v>
       </c>
       <c r="E20" s="0">
-        <v>-0.011217645657931173</v>
+        <v>-0.011217645657931166</v>
       </c>
       <c r="F20" s="0">
         <v>0.0047936319832520939</v>
       </c>
       <c r="G20" s="0">
-        <v>0.012300780327542872</v>
+        <v>0.012300780327542877</v>
       </c>
       <c r="H20" s="0">
         <v>0.0036018982593929265</v>
       </c>
       <c r="I20" s="0">
-        <v>-0.010632310666801502</v>
+        <v>-0.010632310666801495</v>
       </c>
       <c r="J20" s="0">
-        <v>-0.061418031984663245</v>
+        <v>-0.061418031984663238</v>
       </c>
       <c r="K20" s="0">
         <v>0.083506772794188819</v>
       </c>
       <c r="L20" s="0">
-        <v>0.042098509327472035</v>
+        <v>0.042098509327472042</v>
       </c>
       <c r="M20" s="0">
-        <v>0.021277843934306522</v>
+        <v>0.021277843934306526</v>
       </c>
       <c r="N20" s="0">
-        <v>0.032427341011736256</v>
+        <v>0.032427341011736263</v>
       </c>
       <c r="O20" s="0">
-        <v>0.041599468865491242</v>
+        <v>0.041599468865491249</v>
       </c>
       <c r="P20" s="0">
         <v>0.033459220219192877</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.02251123900569283</v>
+        <v>0.022511239005692834</v>
       </c>
       <c r="R20" s="0">
-        <v>0.02258295303613609</v>
+        <v>0.022582953036136093</v>
       </c>
       <c r="S20" s="0">
         <v>0.025075531682969145</v>
       </c>
       <c r="T20" s="0">
-        <v>0.054937600323355464</v>
+        <v>0.054937600323355457</v>
       </c>
       <c r="U20" s="0">
-        <v>0.041640307135442069</v>
+        <v>0.041640307135442062</v>
       </c>
       <c r="V20" s="0">
-        <v>0.044439142707816327</v>
+        <v>0.04443914270781632</v>
       </c>
       <c r="W20" s="0">
         <v>0.055212886244188714</v>
@@ -2871,34 +2971,34 @@
         <v>0.05618081009162032</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.054722622480382489</v>
+        <v>0.054722622480382482</v>
       </c>
       <c r="Z20" s="0">
-        <v>0.051066943946999489</v>
+        <v>0.051066943946999482</v>
       </c>
       <c r="AA20" s="0">
-        <v>0.052200109377753524</v>
+        <v>0.052200109377753517</v>
       </c>
       <c r="AB20" s="0">
-        <v>0.05225936691619102</v>
+        <v>0.052259366916191013</v>
       </c>
       <c r="AC20" s="0">
         <v>0.050570034717299019</v>
       </c>
       <c r="AD20" s="0">
-        <v>0.051734782894280885</v>
+        <v>0.051734782894280879</v>
       </c>
       <c r="AE20" s="0">
         <v>0.053243420655319153</v>
       </c>
       <c r="AF20" s="0">
-        <v>0.054949081267275469</v>
+        <v>0.054949081267275462</v>
       </c>
       <c r="AG20" s="0">
         <v>0.054397351488425262</v>
       </c>
       <c r="AH20" s="0">
-        <v>0.051711484709427748</v>
+        <v>0.051711484709427637</v>
       </c>
       <c r="AI20" s="0">
         <v>0.050164603436464762</v>
@@ -2910,7 +3010,7 @@
         <v>0.051499939203650348</v>
       </c>
       <c r="AL20" s="0">
-        <v>0.052104933092651941</v>
+        <v>0.05210493309265183</v>
       </c>
       <c r="AM20" s="0">
         <v>0.052116584423815705</v>
@@ -2924,162 +3024,162 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="B21" s="0">
-        <v>-0.37443848101655242</v>
+        <v>0.055486024490896124</v>
       </c>
       <c r="C21" s="0">
-        <v>-0.012702194956710489</v>
+        <v>-0.012702194956710565</v>
       </c>
       <c r="D21" s="0">
-        <v>-0.0053741464852489762</v>
+        <v>-0.005374146485249056</v>
       </c>
       <c r="E21" s="0">
-        <v>0.013202308870674251</v>
+        <v>0.013202308870674173</v>
       </c>
       <c r="F21" s="0">
-        <v>0.020226923364166038</v>
+        <v>0.020226923364166066</v>
       </c>
       <c r="G21" s="0">
-        <v>0.0038681168096839601</v>
+        <v>0.0038681168096838768</v>
       </c>
       <c r="H21" s="0">
-        <v>-0.0014069022719456793</v>
+        <v>-0.0014069022719457626</v>
       </c>
       <c r="I21" s="0">
-        <v>-0.010746652435382701</v>
+        <v>-0.010746652435382781</v>
       </c>
       <c r="J21" s="0">
-        <v>-0.038672715018868549</v>
+        <v>-0.038672715018868625</v>
       </c>
       <c r="K21" s="0">
-        <v>0.046242670608277851</v>
+        <v>0.046242670608277768</v>
       </c>
       <c r="L21" s="0">
-        <v>0.032087587651180735</v>
+        <v>0.032087587651180645</v>
       </c>
       <c r="M21" s="0">
-        <v>0.020549004741740859</v>
+        <v>0.020549004741740769</v>
       </c>
       <c r="N21" s="0">
-        <v>0.028630609697237797</v>
+        <v>0.028630609697237724</v>
       </c>
       <c r="O21" s="0">
-        <v>0.025809721325159296</v>
+        <v>0.025809721325159334</v>
       </c>
       <c r="P21" s="0">
-        <v>0.026436049586985234</v>
+        <v>0.026436049586985248</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.01878120487739502</v>
+        <v>0.018781204877395034</v>
       </c>
       <c r="R21" s="0">
-        <v>0.019427291127762467</v>
+        <v>0.01942729112776248</v>
       </c>
       <c r="S21" s="0">
-        <v>0.018842827998864428</v>
+        <v>0.018842827998864345</v>
       </c>
       <c r="T21" s="0">
-        <v>0.039848805662785737</v>
+        <v>0.039848805662785751</v>
       </c>
       <c r="U21" s="0">
-        <v>0.0368354748338462</v>
+        <v>0.036835474833846187</v>
       </c>
       <c r="V21" s="0">
-        <v>0.041295026842261835</v>
+        <v>0.041295026842261828</v>
       </c>
       <c r="W21" s="0">
-        <v>0.048146828548922833</v>
+        <v>0.04814682854892282</v>
       </c>
       <c r="X21" s="0">
-        <v>0.048803883237712682</v>
+        <v>0.048803883237712661</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.048887690302795057</v>
+        <v>0.048887690302795037</v>
       </c>
       <c r="Z21" s="0">
-        <v>0.04338826851800804</v>
+        <v>0.043388268518008033</v>
       </c>
       <c r="AA21" s="0">
-        <v>0.043315476262297384</v>
+        <v>0.04331547626229737</v>
       </c>
       <c r="AB21" s="0">
-        <v>0.044697988409070813</v>
+        <v>0.044697988409070799</v>
       </c>
       <c r="AC21" s="0">
-        <v>0.044708888724039456</v>
+        <v>0.044708888724039442</v>
       </c>
       <c r="AD21" s="0">
-        <v>0.04304110553234166</v>
+        <v>0.043041105532341653</v>
       </c>
       <c r="AE21" s="0">
         <v>0.044448454850834609</v>
       </c>
       <c r="AF21" s="0">
-        <v>0.046217389546187496</v>
+        <v>0.046217389546187489</v>
       </c>
       <c r="AG21" s="0">
-        <v>0.04820173184352728</v>
+        <v>0.048201731843527273</v>
       </c>
       <c r="AH21" s="0">
-        <v>0.047693422755138895</v>
+        <v>0.047693422755138881</v>
       </c>
       <c r="AI21" s="0">
-        <v>0.044825064135562552</v>
+        <v>0.044825064135562545</v>
       </c>
       <c r="AJ21" s="0">
         <v>0.043202834678336549</v>
       </c>
       <c r="AK21" s="0">
-        <v>0.043856471237945248</v>
+        <v>0.043856471237945255</v>
       </c>
       <c r="AL21" s="0">
         <v>0.044819082596581759</v>
       </c>
       <c r="AM21" s="0">
-        <v>0.045550537967718151</v>
+        <v>0.045550537967718262</v>
       </c>
       <c r="AN21" s="0">
         <v>0.045619038144155709</v>
       </c>
       <c r="AO21" s="0">
-        <v>0.044756495508269233</v>
+        <v>0.04475649550826924</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="B22" s="0">
-        <v>-0.39477406481363475</v>
+        <v>0.032263302252500826</v>
       </c>
       <c r="C22" s="0">
-        <v>-0.0094274541427797065</v>
+        <v>-0.0094274541427796996</v>
       </c>
       <c r="D22" s="0">
-        <v>-0.0098165612929002333</v>
+        <v>-0.0098165612929002263</v>
       </c>
       <c r="E22" s="0">
-        <v>-0.0023487080085657086</v>
+        <v>-0.0023487080085657017</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.0086583804029078115</v>
+        <v>-0.0086583804029078046</v>
       </c>
       <c r="G22" s="0">
-        <v>-0.0054340259083950626</v>
+        <v>-0.0054340259083950557</v>
       </c>
       <c r="H22" s="0">
-        <v>-0.0065539401508452333</v>
+        <v>-0.0065539401508452264</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.013651670884479744</v>
+        <v>-0.013651670884479737</v>
       </c>
       <c r="J22" s="0">
         <v>-0.035139292967922203</v>
       </c>
       <c r="K22" s="0">
-        <v>0.024831739846267381</v>
+        <v>0.024831739846267388</v>
       </c>
       <c r="L22" s="0">
         <v>0.016870479800516897</v>
@@ -3091,10 +3191,10 @@
         <v>0.023562270899732257</v>
       </c>
       <c r="O22" s="0">
-        <v>0.022503835982026071</v>
+        <v>0.022503835982026078</v>
       </c>
       <c r="P22" s="0">
-        <v>0.016627122488387241</v>
+        <v>0.016627122488387248</v>
       </c>
       <c r="Q22" s="0">
         <v>0.016294200651658847</v>
@@ -3109,34 +3209,34 @@
         <v>0.033677227950180105</v>
       </c>
       <c r="U22" s="0">
-        <v>0.030801701882456865</v>
+        <v>0.030801701882456869</v>
       </c>
       <c r="V22" s="0">
-        <v>0.043793562001004115</v>
+        <v>0.043793562001004108</v>
       </c>
       <c r="W22" s="0">
-        <v>0.046527981823540863</v>
+        <v>0.046527981823540857</v>
       </c>
       <c r="X22" s="0">
-        <v>0.045534778306406586</v>
+        <v>0.045534778306406579</v>
       </c>
       <c r="Y22" s="0">
-        <v>0.04701621914579298</v>
+        <v>0.047016219145792973</v>
       </c>
       <c r="Z22" s="0">
-        <v>0.042204248431996404</v>
+        <v>0.042204248431996397</v>
       </c>
       <c r="AA22" s="0">
-        <v>0.042186777917608574</v>
+        <v>0.042186777917608567</v>
       </c>
       <c r="AB22" s="0">
-        <v>0.042399357228157984</v>
+        <v>0.042399357228157977</v>
       </c>
       <c r="AC22" s="0">
-        <v>0.043862301147063319</v>
+        <v>0.043862301147063312</v>
       </c>
       <c r="AD22" s="0">
-        <v>0.044074140935555138</v>
+        <v>0.044074140935555131</v>
       </c>
       <c r="AE22" s="0">
         <v>0.042516374851200488</v>
@@ -3145,13 +3245,13 @@
         <v>0.044270114989099794</v>
       </c>
       <c r="AG22" s="0">
-        <v>0.046403055946117232</v>
+        <v>0.046403055946117225</v>
       </c>
       <c r="AH22" s="0">
-        <v>0.04876923028997978</v>
+        <v>0.048769230289979773</v>
       </c>
       <c r="AI22" s="0">
-        <v>0.048383908285399811</v>
+        <v>0.048383908285399804</v>
       </c>
       <c r="AJ22" s="0">
         <v>0.045371764879791519</v>
@@ -3166,7 +3266,7 @@
         <v>0.045740860162084528</v>
       </c>
       <c r="AN22" s="0">
-        <v>0.046658586496614217</v>
+        <v>0.046658586496614106</v>
       </c>
       <c r="AO22" s="0">
         <v>0.046827914600688213</v>
@@ -3174,67 +3274,67 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B23" s="0">
-        <v>-0.44667298808583028</v>
+        <v>-0.024362696747206626</v>
       </c>
       <c r="C23" s="0">
-        <v>-0.019744143023249609</v>
+        <v>-0.019744143023249595</v>
       </c>
       <c r="D23" s="0">
-        <v>-0.015694522694105643</v>
+        <v>-0.01569452269410563</v>
       </c>
       <c r="E23" s="0">
-        <v>-0.013803534801163191</v>
+        <v>-0.013803534801163177</v>
       </c>
       <c r="F23" s="0">
-        <v>-0.0056008504068616946</v>
+        <v>-0.0056008504068616807</v>
       </c>
       <c r="G23" s="0">
-        <v>-0.011072434743251085</v>
+        <v>-0.011072434743251078</v>
       </c>
       <c r="H23" s="0">
-        <v>-0.011630240244701988</v>
+        <v>-0.011630240244701981</v>
       </c>
       <c r="I23" s="0">
-        <v>-0.015827651241563205</v>
+        <v>-0.015827651241563198</v>
       </c>
       <c r="J23" s="0">
-        <v>-0.03310727451521616</v>
+        <v>-0.033107274515216153</v>
       </c>
       <c r="K23" s="0">
-        <v>0.016949583156538335</v>
+        <v>0.016949583156538345</v>
       </c>
       <c r="L23" s="0">
-        <v>0.011694021451363834</v>
+        <v>0.011694021451363851</v>
       </c>
       <c r="M23" s="0">
-        <v>0.0066070355231971356</v>
+        <v>0.006607035523197146</v>
       </c>
       <c r="N23" s="0">
-        <v>0.016179132674044194</v>
+        <v>0.01617913267404409</v>
       </c>
       <c r="O23" s="0">
-        <v>0.019926990479983864</v>
+        <v>0.01992699047998376</v>
       </c>
       <c r="P23" s="0">
-        <v>0.011600062759427765</v>
+        <v>0.011600062759427779</v>
       </c>
       <c r="Q23" s="0">
-        <v>0.011348239910148161</v>
+        <v>0.011348239910148179</v>
       </c>
       <c r="R23" s="0">
-        <v>0.017647398240613066</v>
+        <v>0.017647398240613069</v>
       </c>
       <c r="S23" s="0">
-        <v>0.020410556529964541</v>
+        <v>0.020410556529964433</v>
       </c>
       <c r="T23" s="0">
-        <v>0.034731058335620346</v>
+        <v>0.034731058335620353</v>
       </c>
       <c r="U23" s="0">
-        <v>0.027111581932348916</v>
+        <v>0.027111581932348923</v>
       </c>
       <c r="V23" s="0">
         <v>0.037972505161053161</v>
@@ -3258,31 +3358,31 @@
         <v>0.049972656292513504</v>
       </c>
       <c r="AC23" s="0">
-        <v>0.050367205191953639</v>
+        <v>0.050367205191953632</v>
       </c>
       <c r="AD23" s="0">
         <v>0.052324027316411989</v>
       </c>
       <c r="AE23" s="0">
-        <v>0.052839647456881682</v>
+        <v>0.052839647456881675</v>
       </c>
       <c r="AF23" s="0">
-        <v>0.05128470322715855</v>
+        <v>0.051284703227158661</v>
       </c>
       <c r="AG23" s="0">
-        <v>0.053524444794866115</v>
+        <v>0.053524444794866108</v>
       </c>
       <c r="AH23" s="0">
-        <v>0.056196092357453091</v>
+        <v>0.056196092357453084</v>
       </c>
       <c r="AI23" s="0">
         <v>0.059140392258269989</v>
       </c>
       <c r="AJ23" s="0">
-        <v>0.058861085693118813</v>
+        <v>0.058861085693118806</v>
       </c>
       <c r="AK23" s="0">
-        <v>0.055482472390448505</v>
+        <v>0.055482472390448616</v>
       </c>
       <c r="AL23" s="0">
         <v>0.053666018053928059</v>
@@ -3294,81 +3394,81 @@
         <v>0.056281623903386695</v>
       </c>
       <c r="AO23" s="0">
-        <v>0.057466221853147585</v>
+        <v>0.057466221853147696</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="B24" s="0">
-        <v>-0.49360419959189489</v>
+        <v>-0.077681981575542222</v>
       </c>
       <c r="C24" s="0">
-        <v>-0.023277271395060535</v>
+        <v>-0.023277271395060518</v>
       </c>
       <c r="D24" s="0">
-        <v>-0.024987170380011477</v>
+        <v>-0.024987170380011459</v>
       </c>
       <c r="E24" s="0">
-        <v>-0.0022380335949466271</v>
+        <v>-0.0022380335949466045</v>
       </c>
       <c r="F24" s="0">
-        <v>-0.003774767171564504</v>
+        <v>-0.0037747671715644814</v>
       </c>
       <c r="G24" s="0">
-        <v>-0.018837995105936929</v>
+        <v>-0.018837995105936915</v>
       </c>
       <c r="H24" s="0">
-        <v>-0.018099542588297497</v>
+        <v>-0.018099542588297483</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.023618017476338245</v>
+        <v>-0.023618017476338342</v>
       </c>
       <c r="J24" s="0">
-        <v>-0.036927158134320411</v>
+        <v>-0.036927158134320508</v>
       </c>
       <c r="K24" s="0">
-        <v>0.007065565109499676</v>
+        <v>0.0070655651094995806</v>
       </c>
       <c r="L24" s="0">
-        <v>0.0037115214991423826</v>
+        <v>0.0037115214991422867</v>
       </c>
       <c r="M24" s="0">
-        <v>0.00046446070404598111</v>
+        <v>0.00046446070404588478</v>
       </c>
       <c r="N24" s="0">
-        <v>0.0081538935903364002</v>
+        <v>0.008153893590336303</v>
       </c>
       <c r="O24" s="0">
-        <v>0.0092240250353885916</v>
+        <v>0.0092240250353885986</v>
       </c>
       <c r="P24" s="0">
-        <v>0.0069506092481375487</v>
+        <v>0.0069506092481375547</v>
       </c>
       <c r="Q24" s="0">
-        <v>0.0082444176885352813</v>
+        <v>0.0082444176885351841</v>
       </c>
       <c r="R24" s="0">
-        <v>0.012443883907405744</v>
+        <v>0.012443883907405643</v>
       </c>
       <c r="S24" s="0">
-        <v>0.017292850567156161</v>
+        <v>0.017292850567156171</v>
       </c>
       <c r="T24" s="0">
-        <v>0.031521434602123012</v>
+        <v>0.031521434602123026</v>
       </c>
       <c r="U24" s="0">
-        <v>0.027082537533778685</v>
+        <v>0.027082537533778699</v>
       </c>
       <c r="V24" s="0">
-        <v>0.032384978759609814</v>
+        <v>0.032384978759609821</v>
       </c>
       <c r="W24" s="0">
-        <v>0.041678498616248873</v>
+        <v>0.04167849861624888</v>
       </c>
       <c r="X24" s="0">
-        <v>0.046740050040789204</v>
+        <v>0.046740050040789197</v>
       </c>
       <c r="Y24" s="0">
         <v>0.051460424840708799</v>
@@ -3386,28 +3486,28 @@
         <v>0.059285298673382406</v>
       </c>
       <c r="AD24" s="0">
-        <v>0.060157936055520139</v>
+        <v>0.060157936055520132</v>
       </c>
       <c r="AE24" s="0">
-        <v>0.062814644599020003</v>
+        <v>0.062814644599019989</v>
       </c>
       <c r="AF24" s="0">
-        <v>0.063767816462993926</v>
+        <v>0.063767816462993912</v>
       </c>
       <c r="AG24" s="0">
-        <v>0.062263152718157105</v>
+        <v>0.062263152718157112</v>
       </c>
       <c r="AH24" s="0">
-        <v>0.065180589669482064</v>
+        <v>0.06518058966948205</v>
       </c>
       <c r="AI24" s="0">
-        <v>0.068591157893913263</v>
+        <v>0.068591157893913249</v>
       </c>
       <c r="AJ24" s="0">
         <v>0.072326527671071963</v>
       </c>
       <c r="AK24" s="0">
-        <v>0.072218810292072361</v>
+        <v>0.072218810292072347</v>
       </c>
       <c r="AL24" s="0">
         <v>0.06839029681186129</v>
@@ -3424,85 +3524,85 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="B25" s="0">
-        <v>-0.56305776842292055</v>
+        <v>-0.15514258183260632</v>
       </c>
       <c r="C25" s="0">
-        <v>-0.037199091661566056</v>
+        <v>-0.037199091661566021</v>
       </c>
       <c r="D25" s="0">
-        <v>-0.036004194110941704</v>
+        <v>-0.036004194110941669</v>
       </c>
       <c r="E25" s="0">
-        <v>-0.034009631774868723</v>
+        <v>-0.034009631774868689</v>
       </c>
       <c r="F25" s="0">
-        <v>-0.038667025253932251</v>
+        <v>-0.038667025253932216</v>
       </c>
       <c r="G25" s="0">
-        <v>-0.033762485938915753</v>
+        <v>-0.033762485938915718</v>
       </c>
       <c r="H25" s="0">
-        <v>-0.031649879133818698</v>
+        <v>-0.031649879133818677</v>
       </c>
       <c r="I25" s="0">
-        <v>-0.034137274010349966</v>
+        <v>-0.034137274010349945</v>
       </c>
       <c r="J25" s="0">
-        <v>-0.043899557951590937</v>
+        <v>-0.043899557951590965</v>
       </c>
       <c r="K25" s="0">
-        <v>-0.010537820685555289</v>
+        <v>-0.01053782068555531</v>
       </c>
       <c r="L25" s="0">
-        <v>-0.008743488884343488</v>
+        <v>-0.0087434888843435209</v>
       </c>
       <c r="M25" s="0">
-        <v>-0.010566105072038125</v>
+        <v>-0.010566105072038159</v>
       </c>
       <c r="N25" s="0">
-        <v>-0.0030381415838877518</v>
+        <v>-0.003038141583887672</v>
       </c>
       <c r="O25" s="0">
-        <v>-0.0023588494353154466</v>
+        <v>-0.0023588494353154938</v>
       </c>
       <c r="P25" s="0">
-        <v>-0.0050283536279328092</v>
+        <v>-0.0050283536279328639</v>
       </c>
       <c r="Q25" s="0">
-        <v>0.0011611979587263163</v>
+        <v>0.0011611979587262615</v>
       </c>
       <c r="R25" s="0">
-        <v>0.0039062506038237202</v>
+        <v>0.0039062506038237974</v>
       </c>
       <c r="S25" s="0">
-        <v>0.011517652170845723</v>
+        <v>0.011517652170845801</v>
       </c>
       <c r="T25" s="0">
-        <v>0.027024673757968055</v>
+        <v>0.02702467375796799</v>
       </c>
       <c r="U25" s="0">
-        <v>0.0226823134521991</v>
+        <v>0.022682313452199031</v>
       </c>
       <c r="V25" s="0">
-        <v>0.031198898782945052</v>
+        <v>0.031198898782944989</v>
       </c>
       <c r="W25" s="0">
-        <v>0.034877454123141513</v>
+        <v>0.034877454123141451</v>
       </c>
       <c r="X25" s="0">
-        <v>0.036961729073535926</v>
+        <v>0.036961729073535843</v>
       </c>
       <c r="Y25" s="0">
-        <v>0.054339186864002284</v>
+        <v>0.054339186864002277</v>
       </c>
       <c r="Z25" s="0">
-        <v>0.052703664240623435</v>
+        <v>0.052703664240623428</v>
       </c>
       <c r="AA25" s="0">
-        <v>0.057869015600664361</v>
+        <v>0.057869015600664347</v>
       </c>
       <c r="AB25" s="0">
         <v>0.063396858649342386</v>
@@ -3511,37 +3611,37 @@
         <v>0.066801046139085857</v>
       </c>
       <c r="AD25" s="0">
-        <v>0.067031310904129712</v>
+        <v>0.067031310904129698</v>
       </c>
       <c r="AE25" s="0">
-        <v>0.068527730407746401</v>
+        <v>0.068527730407746498</v>
       </c>
       <c r="AF25" s="0">
-        <v>0.072040010733636403</v>
+        <v>0.072040010733636389</v>
       </c>
       <c r="AG25" s="0">
-        <v>0.073528539983840902</v>
+        <v>0.073528539983840888</v>
       </c>
       <c r="AH25" s="0">
         <v>0.072081871265615161</v>
       </c>
       <c r="AI25" s="0">
-        <v>0.075831399120298792</v>
+        <v>0.075831399120298779</v>
       </c>
       <c r="AJ25" s="0">
-        <v>0.080163584725834722</v>
+        <v>0.080163584725834708</v>
       </c>
       <c r="AK25" s="0">
         <v>0.084886327220696195</v>
       </c>
       <c r="AL25" s="0">
-        <v>0.08500565772529188</v>
+        <v>0.085005657725291867</v>
       </c>
       <c r="AM25" s="0">
         <v>0.080633336811407608</v>
       </c>
       <c r="AN25" s="0">
-        <v>0.078429760642341417</v>
+        <v>0.078429760642341431</v>
       </c>
       <c r="AO25" s="0">
         <v>0.080404472206152766</v>
@@ -3549,106 +3649,106 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="B26" s="0">
-        <v>-0.63283476123326854</v>
+        <v>-0.2336411048282977</v>
       </c>
       <c r="C26" s="0">
-        <v>-0.052037642757123095</v>
+        <v>-0.052037642757123061</v>
       </c>
       <c r="D26" s="0">
-        <v>-0.052427197860636612</v>
+        <v>-0.052427197860636578</v>
       </c>
       <c r="E26" s="0">
-        <v>-0.046107837924667675</v>
+        <v>-0.04610783792466764</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.042071983317046716</v>
+        <v>-0.042071983317046681</v>
       </c>
       <c r="G26" s="0">
-        <v>-0.046706357299421478</v>
+        <v>-0.046706357299421457</v>
       </c>
       <c r="H26" s="0">
-        <v>-0.048835170295939825</v>
+        <v>-0.048835170295939805</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.050145710164612917</v>
+        <v>-0.050145710164612882</v>
       </c>
       <c r="J26" s="0">
-        <v>-0.057982793637873037</v>
+        <v>-0.057982793637873002</v>
       </c>
       <c r="K26" s="0">
-        <v>-0.034758791616538803</v>
+        <v>-0.034758791616538838</v>
       </c>
       <c r="L26" s="0">
-        <v>-0.030807569915452276</v>
+        <v>-0.030807569915452259</v>
       </c>
       <c r="M26" s="0">
-        <v>-0.029071464908344197</v>
+        <v>-0.029071464908344179</v>
       </c>
       <c r="N26" s="0">
-        <v>-0.020415995927386105</v>
+        <v>-0.020415995927386087</v>
       </c>
       <c r="O26" s="0">
-        <v>-0.016114372976254815</v>
+        <v>-0.016114372976254867</v>
       </c>
       <c r="P26" s="0">
         <v>-0.024037370796022736</v>
       </c>
       <c r="Q26" s="0">
-        <v>-0.016994802059183682</v>
+        <v>-0.016994802059183634</v>
       </c>
       <c r="R26" s="0">
-        <v>-0.0089083952660905519</v>
+        <v>-0.0089083952660904964</v>
       </c>
       <c r="S26" s="0">
-        <v>-0.0031001449426675612</v>
+        <v>-0.0031001449426676072</v>
       </c>
       <c r="T26" s="0">
-        <v>0.012822225808479706</v>
+        <v>0.012822225808479715</v>
       </c>
       <c r="U26" s="0">
-        <v>0.014650831894722605</v>
+        <v>0.014650831894722638</v>
       </c>
       <c r="V26" s="0">
-        <v>0.022492956868268577</v>
+        <v>0.022492956868268608</v>
       </c>
       <c r="W26" s="0">
-        <v>0.030610684006430411</v>
+        <v>0.030610684006430446</v>
       </c>
       <c r="X26" s="0">
-        <v>0.029085253769752462</v>
+        <v>0.029085253769752503</v>
       </c>
       <c r="Y26" s="0">
-        <v>0.04001302546674855</v>
+        <v>0.040013025466748578</v>
       </c>
       <c r="Z26" s="0">
-        <v>0.048993111566340397</v>
+        <v>0.048993111566340293</v>
       </c>
       <c r="AA26" s="0">
-        <v>0.051938305422385589</v>
+        <v>0.051938305422385485</v>
       </c>
       <c r="AB26" s="0">
-        <v>0.057929186365458019</v>
+        <v>0.057929186365457908</v>
       </c>
       <c r="AC26" s="0">
-        <v>0.064747300591034784</v>
+        <v>0.06474730059103477</v>
       </c>
       <c r="AD26" s="0">
-        <v>0.069432461292525838</v>
+        <v>0.069432461292525824</v>
       </c>
       <c r="AE26" s="0">
-        <v>0.07050681580248791</v>
+        <v>0.070506815802488021</v>
       </c>
       <c r="AF26" s="0">
-        <v>0.073059685358416948</v>
+        <v>0.073059685358416837</v>
       </c>
       <c r="AG26" s="0">
         <v>0.077627298958828972</v>
       </c>
       <c r="AH26" s="0">
-        <v>0.079937592374988709</v>
+        <v>0.079937592374988597</v>
       </c>
       <c r="AI26" s="0">
         <v>0.078913323318595643</v>
@@ -3657,10 +3757,10 @@
         <v>0.083707308737051955</v>
       </c>
       <c r="AK26" s="0">
-        <v>0.089127787434477745</v>
+        <v>0.089127787434477634</v>
       </c>
       <c r="AL26" s="0">
-        <v>0.095003213782684559</v>
+        <v>0.095003213782684545</v>
       </c>
       <c r="AM26" s="0">
         <v>0.095569887732861181</v>
@@ -3669,15 +3769,15 @@
         <v>0.090922408542367827</v>
       </c>
       <c r="AO26" s="0">
-        <v>0.088734932072262088</v>
+        <v>0.088734932072262102</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="B27" s="0">
-        <v>-0.71421675204726509</v>
+        <v>-0.32390276212599578</v>
       </c>
       <c r="C27" s="0">
         <v>-0.063095807121780478</v>
@@ -3701,64 +3801,64 @@
         <v>-0.062601565455874586</v>
       </c>
       <c r="J27" s="0">
-        <v>-0.071900696615017926</v>
+        <v>-0.071900696615017939</v>
       </c>
       <c r="K27" s="0">
         <v>-0.056389295960481069</v>
       </c>
       <c r="L27" s="0">
-        <v>-0.05351963079214133</v>
+        <v>-0.053519630792141344</v>
       </c>
       <c r="M27" s="0">
-        <v>-0.052387330617470411</v>
+        <v>-0.052387330617470425</v>
       </c>
       <c r="N27" s="0">
-        <v>-0.044351996998709224</v>
+        <v>-0.044351996998709238</v>
       </c>
       <c r="O27" s="0">
-        <v>-0.039156312930785579</v>
+        <v>-0.039156312930785607</v>
       </c>
       <c r="P27" s="0">
-        <v>-0.043064026664249626</v>
+        <v>-0.043064026664249654</v>
       </c>
       <c r="Q27" s="0">
-        <v>-0.043426805538880016</v>
+        <v>-0.043426805538880002</v>
       </c>
       <c r="R27" s="0">
-        <v>-0.037189685831258229</v>
+        <v>-0.03718968583125825</v>
       </c>
       <c r="S27" s="0">
-        <v>-0.027270322534959895</v>
+        <v>-0.027270322534959875</v>
       </c>
       <c r="T27" s="0">
-        <v>-0.0093583961450495259</v>
+        <v>-0.0093583961450494982</v>
       </c>
       <c r="U27" s="0">
-        <v>-0.0031568683343509846</v>
+        <v>-0.0031568683343509494</v>
       </c>
       <c r="V27" s="0">
-        <v>0.0012758384819101104</v>
+        <v>0.0012758384819101709</v>
       </c>
       <c r="W27" s="0">
-        <v>0.012176445807687578</v>
+        <v>0.012176445807687631</v>
       </c>
       <c r="X27" s="0">
-        <v>0.015351071580688228</v>
+        <v>0.015351071580688288</v>
       </c>
       <c r="Y27" s="0">
-        <v>0.022716677505166219</v>
+        <v>0.022716677505166288</v>
       </c>
       <c r="Z27" s="0">
-        <v>0.027638269636964211</v>
+        <v>0.027638269636964242</v>
       </c>
       <c r="AA27" s="0">
-        <v>0.038452279376099879</v>
+        <v>0.038452279376099886</v>
       </c>
       <c r="AB27" s="0">
-        <v>0.041301010444640657</v>
+        <v>0.041301010444640664</v>
       </c>
       <c r="AC27" s="0">
-        <v>0.04796399875360681</v>
+        <v>0.047963998753606824</v>
       </c>
       <c r="AD27" s="0">
         <v>0.056287149449450694</v>
@@ -3767,19 +3867,19 @@
         <v>0.062829846873620823</v>
       </c>
       <c r="AF27" s="0">
-        <v>0.065683415624833055</v>
+        <v>0.065683415624833069</v>
       </c>
       <c r="AG27" s="0">
         <v>0.070191718917387874</v>
       </c>
       <c r="AH27" s="0">
-        <v>0.0761950887609011</v>
+        <v>0.076195088760901114</v>
       </c>
       <c r="AI27" s="0">
-        <v>0.079951042190502433</v>
+        <v>0.079951042190502447</v>
       </c>
       <c r="AJ27" s="0">
-        <v>0.080218701882241145</v>
+        <v>0.080218701882241158</v>
       </c>
       <c r="AK27" s="0">
         <v>0.086397575908968266</v>
@@ -3788,7 +3888,7 @@
         <v>0.093151961142697096</v>
       </c>
       <c r="AM27" s="0">
-        <v>0.10040439131758706</v>
+        <v>0.10040439131758705</v>
       </c>
       <c r="AN27" s="0">
         <v>0.10193129163395233</v>
@@ -3799,31 +3899,31 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="B28" s="0">
-        <v>-0.77912343740203005</v>
+        <v>-0.39596462147111655</v>
       </c>
       <c r="C28" s="0">
-        <v>-0.057882462110618434</v>
+        <v>-0.057882462110618427</v>
       </c>
       <c r="D28" s="0">
-        <v>-0.058502182241174393</v>
+        <v>-0.058502182241174386</v>
       </c>
       <c r="E28" s="0">
-        <v>-0.055487365748173013</v>
+        <v>-0.055487365748173006</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.058398778806590008</v>
+        <v>-0.058398778806590002</v>
       </c>
       <c r="G28" s="0">
-        <v>-0.061221379632603525</v>
+        <v>-0.061221379632603518</v>
       </c>
       <c r="H28" s="0">
         <v>-0.063109714086543131</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.061028222051366966</v>
+        <v>-0.061028222051366959</v>
       </c>
       <c r="J28" s="0">
         <v>-0.071770928129587075</v>
@@ -3835,82 +3935,82 @@
         <v>-0.060416401237069629</v>
       </c>
       <c r="M28" s="0">
-        <v>-0.067543286206199607</v>
+        <v>-0.067543286206199593</v>
       </c>
       <c r="N28" s="0">
-        <v>-0.062255815915461143</v>
+        <v>-0.06225581591546115</v>
       </c>
       <c r="O28" s="0">
-        <v>-0.061660531178651529</v>
+        <v>-0.061660531178651536</v>
       </c>
       <c r="P28" s="0">
-        <v>-0.062259141649635114</v>
+        <v>-0.06225914164963512</v>
       </c>
       <c r="Q28" s="0">
-        <v>-0.061028771065346432</v>
+        <v>-0.061028771065346439</v>
       </c>
       <c r="R28" s="0">
-        <v>-0.063646586060022228</v>
+        <v>-0.063646586060022242</v>
       </c>
       <c r="S28" s="0">
-        <v>-0.06226801879858819</v>
+        <v>-0.062268018798588183</v>
       </c>
       <c r="T28" s="0">
-        <v>-0.047715992430325829</v>
+        <v>-0.047715992430325822</v>
       </c>
       <c r="U28" s="0">
-        <v>-0.035240744956108086</v>
+        <v>-0.035240744956108051</v>
       </c>
       <c r="V28" s="0">
-        <v>-0.026376491651412051</v>
+        <v>-0.02637649165141203</v>
       </c>
       <c r="W28" s="0">
-        <v>-0.025943043178616038</v>
+        <v>-0.025943043178616034</v>
       </c>
       <c r="X28" s="0">
-        <v>-0.021897463176828752</v>
+        <v>-0.021897463176828762</v>
       </c>
       <c r="Y28" s="0">
-        <v>-0.0099024715330879587</v>
+        <v>-0.0099024715330879691</v>
       </c>
       <c r="Z28" s="0">
-        <v>-0.0045045624943921558</v>
+        <v>-0.0045045624943921515</v>
       </c>
       <c r="AA28" s="0">
-        <v>0.0018896324776878221</v>
+        <v>0.0018896324776877553</v>
       </c>
       <c r="AB28" s="0">
-        <v>0.0043655702827180981</v>
+        <v>0.004365570282718125</v>
       </c>
       <c r="AC28" s="0">
-        <v>0.0073417494248764065</v>
+        <v>0.0073417494248764334</v>
       </c>
       <c r="AD28" s="0">
-        <v>0.015324723570639284</v>
+        <v>0.015324723570639296</v>
       </c>
       <c r="AE28" s="0">
-        <v>0.025357244804214626</v>
+        <v>0.02535724480421463</v>
       </c>
       <c r="AF28" s="0">
         <v>0.034700380701019759</v>
       </c>
       <c r="AG28" s="0">
-        <v>0.041054146586258708</v>
+        <v>0.041054146586258715</v>
       </c>
       <c r="AH28" s="0">
-        <v>0.04902412598894966</v>
+        <v>0.049024125988949674</v>
       </c>
       <c r="AI28" s="0">
-        <v>0.057071189215417747</v>
+        <v>0.057071189215417754</v>
       </c>
       <c r="AJ28" s="0">
         <v>0.063365854611260194</v>
       </c>
       <c r="AK28" s="0">
-        <v>0.066576855081792993</v>
+        <v>0.066576855081793007</v>
       </c>
       <c r="AL28" s="0">
-        <v>0.07460381519617397</v>
+        <v>0.074603815196173984</v>
       </c>
       <c r="AM28" s="0">
         <v>0.082989221957588052</v>
@@ -3924,10 +4024,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="B29" s="0">
-        <v>-0.81696434357021708</v>
+        <v>-0.43927762026361944</v>
       </c>
       <c r="C29" s="0">
         <v>-0.038499867934799592</v>
@@ -3963,10 +4063,10 @@
         <v>-0.052025480713557004</v>
       </c>
       <c r="N29" s="0">
-        <v>-0.05694144674551474</v>
+        <v>-0.056941446745514747</v>
       </c>
       <c r="O29" s="0">
-        <v>-0.060921105529923733</v>
+        <v>-0.060921105529923726</v>
       </c>
       <c r="P29" s="0">
         <v>-0.063235788810306268</v>
@@ -3984,64 +4084,64 @@
         <v>-0.072324230884668841</v>
       </c>
       <c r="U29" s="0">
-        <v>-0.071012069490101068</v>
+        <v>-0.07101206949010104</v>
       </c>
       <c r="V29" s="0">
-        <v>-0.060751002163581883</v>
+        <v>-0.060751002163581862</v>
       </c>
       <c r="W29" s="0">
-        <v>-0.052671560158189842</v>
+        <v>-0.052671560158189815</v>
       </c>
       <c r="X29" s="0">
-        <v>-0.06893749032213195</v>
+        <v>-0.068937490322132006</v>
       </c>
       <c r="Y29" s="0">
-        <v>-0.061465805543283215</v>
+        <v>-0.061465805543283208</v>
       </c>
       <c r="Z29" s="0">
-        <v>-0.0552906917100826</v>
+        <v>-0.055290691710082628</v>
       </c>
       <c r="AA29" s="0">
-        <v>-0.044809964072162457</v>
+        <v>-0.04480996407216245</v>
       </c>
       <c r="AB29" s="0">
-        <v>-0.044386436561787701</v>
+        <v>-0.044386436561787687</v>
       </c>
       <c r="AC29" s="0">
-        <v>-0.057069717185191403</v>
+        <v>-0.057069717185191375</v>
       </c>
       <c r="AD29" s="0">
-        <v>-0.054037897288023128</v>
+        <v>-0.0540378972880231</v>
       </c>
       <c r="AE29" s="0">
-        <v>-0.046904188690595455</v>
+        <v>-0.046904188690595414</v>
       </c>
       <c r="AF29" s="0">
-        <v>-0.038415503548994284</v>
+        <v>-0.038415503548994263</v>
       </c>
       <c r="AG29" s="0">
-        <v>-0.028105353051253543</v>
+        <v>-0.028105353051253508</v>
       </c>
       <c r="AH29" s="0">
-        <v>-0.018604447039354849</v>
+        <v>-0.018604447039354832</v>
       </c>
       <c r="AI29" s="0">
-        <v>-0.0068676179986192631</v>
+        <v>-0.0068676179986192449</v>
       </c>
       <c r="AJ29" s="0">
-        <v>0.0017731315482683724</v>
+        <v>0.0017731315482683941</v>
       </c>
       <c r="AK29" s="0">
-        <v>0.010506404215373924</v>
+        <v>0.010506404215373947</v>
       </c>
       <c r="AL29" s="0">
-        <v>0.018258941888178518</v>
+        <v>0.018258941888178549</v>
       </c>
       <c r="AM29" s="0">
-        <v>0.027482244375284862</v>
+        <v>0.027482244375284886</v>
       </c>
       <c r="AN29" s="0">
-        <v>0.036363293737241287</v>
+        <v>0.036363293737241308</v>
       </c>
       <c r="AO29" s="0">
         <v>0.045797794273245998</v>
@@ -4049,10 +4149,10 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="B30" s="0">
-        <v>-0.82743038255087886</v>
+        <v>-0.45322080250298341</v>
       </c>
       <c r="C30" s="0">
         <v>-0.014391441276768537</v>
@@ -4121,63 +4221,63 @@
         <v>-0.069499559313150217</v>
       </c>
       <c r="Y30" s="0">
-        <v>-0.09323917844778061</v>
+        <v>-0.093239178447780624</v>
       </c>
       <c r="Z30" s="0">
-        <v>-0.097383452624637865</v>
+        <v>-0.097383452624637892</v>
       </c>
       <c r="AA30" s="0">
         <v>-0.095190578088595504</v>
       </c>
       <c r="AB30" s="0">
-        <v>-0.090152375335023113</v>
+        <v>-0.090152375335023141</v>
       </c>
       <c r="AC30" s="0">
-        <v>-0.102576641790045</v>
+        <v>-0.10257664179004501</v>
       </c>
       <c r="AD30" s="0">
-        <v>-0.13417950705034012</v>
+        <v>-0.13417950705034015</v>
       </c>
       <c r="AE30" s="0">
-        <v>-0.13293766279002708</v>
+        <v>-0.13293766279002711</v>
       </c>
       <c r="AF30" s="0">
-        <v>-0.1335880302465654</v>
+        <v>-0.13358803024656543</v>
       </c>
       <c r="AG30" s="0">
         <v>-0.13557314433976142</v>
       </c>
       <c r="AH30" s="0">
-        <v>-0.13226872978540294</v>
+        <v>-0.13226872978540297</v>
       </c>
       <c r="AI30" s="0">
-        <v>-0.12459140471888019</v>
+        <v>-0.12459140471888018</v>
       </c>
       <c r="AJ30" s="0">
-        <v>-0.11535101057565567</v>
+        <v>-0.11535101057565568</v>
       </c>
       <c r="AK30" s="0">
-        <v>-0.11302040291566937</v>
+        <v>-0.11302040291566935</v>
       </c>
       <c r="AL30" s="0">
-        <v>-0.10699752375611601</v>
+        <v>-0.106997523756116</v>
       </c>
       <c r="AM30" s="0">
-        <v>-0.09653127121046276</v>
+        <v>-0.096531271210462746</v>
       </c>
       <c r="AN30" s="0">
-        <v>-0.092826748981408774</v>
+        <v>-0.092826748981408719</v>
       </c>
       <c r="AO30" s="0">
-        <v>-0.090435411379077096</v>
+        <v>-0.090435411379077069</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="B31" s="0">
-        <v>-0.82593455233002355</v>
+        <v>-0.454063972031513</v>
       </c>
       <c r="C31" s="0">
         <v>-0.002978950400279384</v>
@@ -4299,10 +4399,10 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="B32" s="0">
-        <v>-0.82237107008060717</v>
+        <v>-0.452291760434334</v>
       </c>
       <c r="C32" s="0">
         <v>-0.00033334425406091809</v>

--- a/mig_shocks.xlsx
+++ b/mig_shocks.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t>Var40</t>
   </si>
@@ -133,6 +133,198 @@
   </si>
   <si>
     <t>Var79</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
   </si>
   <si>
     <t>mig_Q_2</t>
@@ -441,7 +633,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -455,11 +647,13 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -467,6 +661,8 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,7 +676,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="true"/>
-    <col min="2" max="2" width="14.42578125" customWidth="true"/>
+    <col min="2" max="2" width="13.42578125" customWidth="true"/>
     <col min="3" max="3" width="16.42578125" customWidth="true"/>
     <col min="4" max="4" width="16.42578125" customWidth="true"/>
     <col min="5" max="5" width="16.42578125" customWidth="true"/>
@@ -488,4038 +684,4038 @@
     <col min="7" max="7" width="16.42578125" customWidth="true"/>
     <col min="8" max="8" width="16.42578125" customWidth="true"/>
     <col min="9" max="9" width="16.42578125" customWidth="true"/>
-    <col min="10" max="10" width="15.42578125" customWidth="true"/>
+    <col min="10" max="10" width="16.42578125" customWidth="true"/>
     <col min="11" max="11" width="16.42578125" customWidth="true"/>
     <col min="12" max="12" width="16.42578125" customWidth="true"/>
-    <col min="13" max="13" width="15.42578125" customWidth="true"/>
-    <col min="14" max="14" width="15.42578125" customWidth="true"/>
-    <col min="15" max="15" width="15.42578125" customWidth="true"/>
-    <col min="16" max="16" width="15.42578125" customWidth="true"/>
-    <col min="17" max="17" width="15.42578125" customWidth="true"/>
-    <col min="18" max="18" width="15.42578125" customWidth="true"/>
-    <col min="19" max="19" width="15.42578125" customWidth="true"/>
-    <col min="20" max="20" width="15.42578125" customWidth="true"/>
-    <col min="21" max="21" width="15.42578125" customWidth="true"/>
-    <col min="22" max="22" width="14.7109375" customWidth="true"/>
-    <col min="23" max="23" width="14.42578125" customWidth="true"/>
-    <col min="24" max="24" width="14.42578125" customWidth="true"/>
-    <col min="25" max="25" width="15.42578125" customWidth="true"/>
-    <col min="26" max="26" width="15.42578125" customWidth="true"/>
-    <col min="27" max="27" width="14.7109375" customWidth="true"/>
-    <col min="28" max="28" width="14.7109375" customWidth="true"/>
-    <col min="29" max="29" width="14.7109375" customWidth="true"/>
-    <col min="30" max="30" width="14.42578125" customWidth="true"/>
-    <col min="31" max="31" width="14.42578125" customWidth="true"/>
-    <col min="32" max="32" width="14.7109375" customWidth="true"/>
-    <col min="33" max="33" width="14.7109375" customWidth="true"/>
-    <col min="34" max="34" width="14.42578125" customWidth="true"/>
-    <col min="35" max="35" width="15.42578125" customWidth="true"/>
-    <col min="36" max="36" width="14.7109375" customWidth="true"/>
-    <col min="37" max="37" width="14.7109375" customWidth="true"/>
-    <col min="38" max="38" width="14.7109375" customWidth="true"/>
-    <col min="39" max="39" width="14.7109375" customWidth="true"/>
-    <col min="40" max="40" width="14.7109375" customWidth="true"/>
-    <col min="41" max="41" width="14.7109375" customWidth="true"/>
+    <col min="13" max="13" width="16.42578125" customWidth="true"/>
+    <col min="14" max="14" width="16.42578125" customWidth="true"/>
+    <col min="15" max="15" width="16.42578125" customWidth="true"/>
+    <col min="16" max="16" width="16.42578125" customWidth="true"/>
+    <col min="17" max="17" width="15.7109375" customWidth="true"/>
+    <col min="18" max="18" width="16.42578125" customWidth="true"/>
+    <col min="19" max="19" width="16.42578125" customWidth="true"/>
+    <col min="20" max="20" width="16.42578125" customWidth="true"/>
+    <col min="21" max="21" width="16.42578125" customWidth="true"/>
+    <col min="22" max="22" width="16.42578125" customWidth="true"/>
+    <col min="23" max="23" width="15.7109375" customWidth="true"/>
+    <col min="24" max="24" width="15.42578125" customWidth="true"/>
+    <col min="25" max="25" width="16.42578125" customWidth="true"/>
+    <col min="26" max="26" width="16.42578125" customWidth="true"/>
+    <col min="27" max="27" width="15.7109375" customWidth="true"/>
+    <col min="28" max="28" width="15.7109375" customWidth="true"/>
+    <col min="29" max="29" width="15.7109375" customWidth="true"/>
+    <col min="30" max="30" width="15.42578125" customWidth="true"/>
+    <col min="31" max="31" width="15.42578125" customWidth="true"/>
+    <col min="32" max="32" width="15.42578125" customWidth="true"/>
+    <col min="33" max="33" width="15.42578125" customWidth="true"/>
+    <col min="34" max="34" width="15.42578125" customWidth="true"/>
+    <col min="35" max="35" width="16.42578125" customWidth="true"/>
+    <col min="36" max="36" width="15.7109375" customWidth="true"/>
+    <col min="37" max="37" width="15.7109375" customWidth="true"/>
+    <col min="38" max="38" width="15.42578125" customWidth="true"/>
+    <col min="39" max="39" width="15.42578125" customWidth="true"/>
+    <col min="40" max="40" width="15.42578125" customWidth="true"/>
+    <col min="41" max="41" width="15.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="B1" s="0">
-        <v>0.2753267546775866</v>
+        <v>-0.44726131189217022</v>
       </c>
       <c r="C1" s="0">
-        <v>0.002214154581450245</v>
+        <v>-0.36914315052464836</v>
       </c>
       <c r="D1" s="0">
-        <v>0.0020969026118662359</v>
+        <v>-0.37300933490262422</v>
       </c>
       <c r="E1" s="0">
-        <v>-0.026594646879579242</v>
+        <v>-0.37252326236856126</v>
       </c>
       <c r="F1" s="0">
-        <v>-0.017264998647291141</v>
+        <v>-0.35442939666455564</v>
       </c>
       <c r="G1" s="0">
-        <v>0.075312207731849878</v>
+        <v>-0.3325867631175855</v>
       </c>
       <c r="H1" s="0">
-        <v>0.044107744327227305</v>
+        <v>-0.33589175986139724</v>
       </c>
       <c r="I1" s="0">
-        <v>0.0074306878013155053</v>
+        <v>-0.3405174763785298</v>
       </c>
       <c r="J1" s="0">
-        <v>-0.10381488332175026</v>
+        <v>-0.36332093854591141</v>
       </c>
       <c r="K1" s="0">
-        <v>0.055285829264906106</v>
+        <v>-0.3411407980530059</v>
       </c>
       <c r="L1" s="0">
-        <v>0.043889678247849506</v>
+        <v>-0.32796983850718536</v>
       </c>
       <c r="M1" s="0">
-        <v>0.032099008156623032</v>
+        <v>-0.35816074040762857</v>
       </c>
       <c r="N1" s="0">
-        <v>0.047958925923629048</v>
+        <v>-0.39199561409953987</v>
       </c>
       <c r="O1" s="0">
-        <v>0.053791950516346332</v>
+        <v>-0.4471368803890074</v>
       </c>
       <c r="P1" s="0">
-        <v>0.05023523129253149</v>
+        <v>-0.48084828304877447</v>
       </c>
       <c r="Q1" s="0">
-        <v>0.052178211439875888</v>
+        <v>-0.46652123327721062</v>
       </c>
       <c r="R1" s="0">
-        <v>0.039916341570719105</v>
+        <v>-0.46390298605986258</v>
       </c>
       <c r="S1" s="0">
-        <v>0.040757859576883826</v>
+        <v>-0.45153292834668868</v>
       </c>
       <c r="T1" s="0">
-        <v>0.064280967857023308</v>
+        <v>-0.43592860767132346</v>
       </c>
       <c r="U1" s="0">
-        <v>0.027969880109576462</v>
+        <v>-0.43672168946432383</v>
       </c>
       <c r="V1" s="0">
-        <v>0.029818805979649143</v>
+        <v>-0.43261945944728797</v>
       </c>
       <c r="W1" s="0">
-        <v>0.038109528909003432</v>
+        <v>-0.43758192652992484</v>
       </c>
       <c r="X1" s="0">
-        <v>0.019947091901443059</v>
+        <v>-0.44440202423966135</v>
       </c>
       <c r="Y1" s="0">
-        <v>0.015431544119309359</v>
+        <v>-0.45149807951239551</v>
       </c>
       <c r="Z1" s="0">
-        <v>0.010086923354631017</v>
+        <v>-0.46292639152740389</v>
       </c>
       <c r="AA1" s="0">
-        <v>0.010742228642999008</v>
+        <v>-0.45248147114409781</v>
       </c>
       <c r="AB1" s="0">
-        <v>0.012343224380187978</v>
+        <v>-0.43772372803985582</v>
       </c>
       <c r="AC1" s="0">
-        <v>0.013817919855534377</v>
+        <v>-0.41783594159099446</v>
       </c>
       <c r="AD1" s="0">
-        <v>0.013225269577308962</v>
+        <v>-0.40655877800291129</v>
       </c>
       <c r="AE1" s="0">
-        <v>0.010785740753344375</v>
+        <v>-0.41091630005462393</v>
       </c>
       <c r="AF1" s="0">
-        <v>0.0093511461640726212</v>
+        <v>-0.41843819002776772</v>
       </c>
       <c r="AG1" s="0">
-        <v>0.0097274509172733392</v>
+        <v>-0.41756202764977474</v>
       </c>
       <c r="AH1" s="0">
-        <v>0.010355313666312593</v>
+        <v>-0.40971265710146298</v>
       </c>
       <c r="AI1" s="0">
-        <v>0.01080986075802115</v>
+        <v>-0.39789833865400437</v>
       </c>
       <c r="AJ1" s="0">
-        <v>0.010759643901127824</v>
+        <v>-0.38746318626010229</v>
       </c>
       <c r="AK1" s="0">
-        <v>0.0099987301754477231</v>
+        <v>-0.3821398646666968</v>
       </c>
       <c r="AL1" s="0">
-        <v>0.0089247910447557421</v>
+        <v>-0.38192233664322683</v>
       </c>
       <c r="AM1" s="0">
-        <v>0.008235705473447319</v>
+        <v>-0.38234125283036119</v>
       </c>
       <c r="AN1" s="0">
-        <v>0.0081987783782420109</v>
+        <v>-0.37912346563453064</v>
       </c>
       <c r="AO1" s="0">
-        <v>0.0084290432624750666</v>
+        <v>-0.37207387365439981</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="B2" s="0">
-        <v>0.18944091200051794</v>
+        <v>-0.47880771499948205</v>
       </c>
       <c r="C2" s="0">
-        <v>-0.008798052235841184</v>
+        <v>-0.00064627396979410889</v>
       </c>
       <c r="D2" s="0">
-        <v>0.0024929074421023954</v>
+        <v>0.00018312026495126421</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.02137327078209339</v>
+        <v>-0.0015700047159400432</v>
       </c>
       <c r="F2" s="0">
-        <v>-0.0086453951054279478</v>
+        <v>-0.00063505995688339922</v>
       </c>
       <c r="G2" s="0">
-        <v>0.036646461971322597</v>
+        <v>0.0026919206285099251</v>
       </c>
       <c r="H2" s="0">
-        <v>0.022723685303813409</v>
+        <v>0.0016692021167747373</v>
       </c>
       <c r="I2" s="0">
-        <v>-0.0011769599015129008</v>
+        <v>-8.6455450690969826e-05</v>
       </c>
       <c r="J2" s="0">
-        <v>-0.11303953290302049</v>
+        <v>-0.008303486742639421</v>
       </c>
       <c r="K2" s="0">
-        <v>0.083466674259414675</v>
+        <v>0.0061311684188237736</v>
       </c>
       <c r="L2" s="0">
-        <v>0.033933903565056878</v>
+        <v>0.002492665390036175</v>
       </c>
       <c r="M2" s="0">
-        <v>0.03038390787459366</v>
+        <v>0.0022318949756262585</v>
       </c>
       <c r="N2" s="0">
-        <v>0.047839256681225573</v>
+        <v>0.0035715495223050397</v>
       </c>
       <c r="O2" s="0">
-        <v>0.048225141307962183</v>
+        <v>0.0034555337579774137</v>
       </c>
       <c r="P2" s="0">
-        <v>0.039490915288615258</v>
+        <v>0.0029008637925752034</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.036536510565018609</v>
+        <v>0.0026838434061236538</v>
       </c>
       <c r="R2" s="0">
-        <v>0.042142916628999716</v>
+        <v>0.0030956704666160739</v>
       </c>
       <c r="S2" s="0">
-        <v>0.046470535159674142</v>
+        <v>0.0034135617514798877</v>
       </c>
       <c r="T2" s="0">
-        <v>0.074841309368095077</v>
+        <v>0.0054975792200159801</v>
       </c>
       <c r="U2" s="0">
-        <v>0.054583454125459945</v>
+        <v>0.0040095088043512472</v>
       </c>
       <c r="V2" s="0">
-        <v>0.055003826390571879</v>
+        <v>0.0040403876502772551</v>
       </c>
       <c r="W2" s="0">
-        <v>0.065383546651785807</v>
+        <v>0.0048028451673184924</v>
       </c>
       <c r="X2" s="0">
-        <v>0.061813519294937606</v>
+        <v>0.0045406036708912634</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.065356164722600418</v>
+        <v>0.0048008342744096932</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.063794944403975373</v>
+        <v>0.0046861521274530471</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.061654781829491904</v>
+        <v>0.0045289433363621123</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.062307356539842311</v>
+        <v>0.00457687873561341</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.063362208607063986</v>
+        <v>0.0046543657206043476</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.064740168214057592</v>
+        <v>0.0047555844295341099</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.064188713044355028</v>
+        <v>0.0047150777167476177</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.06181457881664542</v>
+        <v>0.0045406817779693465</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.060425638744489356</v>
+        <v>0.0044386551399621665</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.060816741782236609</v>
+        <v>0.004467384214106751</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.061455653716094398</v>
+        <v>0.0045143161269602938</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.061922434122747332</v>
+        <v>0.0045486035792373647</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.061888309307405402</v>
+        <v>0.004546098008672228</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.061152307701103463</v>
+        <v>0.0044920337440940705</v>
       </c>
       <c r="AM2" s="0">
-        <v>0.060103532554758754</v>
+        <v>0.0044149938224959939</v>
       </c>
       <c r="AN2" s="0">
-        <v>0.059434075184621626</v>
+        <v>0.0043658186224450057</v>
       </c>
       <c r="AO2" s="0">
-        <v>0.059407259181559091</v>
+        <v>0.0043638484198814664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="B3" s="0">
-        <v>0.17236558985102601</v>
+        <v>-0.47872825914897399</v>
       </c>
       <c r="C3" s="0">
-        <v>-0.0007236851580176909</v>
+        <v>-5.3159446124939613e-05</v>
       </c>
       <c r="D3" s="0">
-        <v>0.00069276141809603703</v>
+        <v>5.0888083150180119e-05</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.0095856840114783085</v>
+        <v>-0.00070412999249941377</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.0025688894489046613</v>
+        <v>-0.00018870197301190661</v>
       </c>
       <c r="G3" s="0">
-        <v>0.026340217047261187</v>
+        <v>0.001934859810363565</v>
       </c>
       <c r="H3" s="0">
-        <v>0.014428121797097619</v>
+        <v>0.0010598391742976387</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.0047140371583156496</v>
+        <v>-0.00034627662091551992</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.095264455875445089</v>
+        <v>-0.0069977922497858058</v>
       </c>
       <c r="K3" s="0">
-        <v>0.10330429514448047</v>
+        <v>0.007588370611202544</v>
       </c>
       <c r="L3" s="0">
-        <v>0.044713988905011985</v>
+        <v>0.0032845330520310245</v>
       </c>
       <c r="M3" s="0">
-        <v>0.023324587711579851</v>
+        <v>0.0017133420005925881</v>
       </c>
       <c r="N3" s="0">
-        <v>0.043297518338707645</v>
+        <v>0.0032920311670212032</v>
       </c>
       <c r="O3" s="0">
-        <v>0.047792397575503569</v>
+        <v>0.0034552685786040649</v>
       </c>
       <c r="P3" s="0">
-        <v>0.037713166916316314</v>
+        <v>0.0027702768133184841</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.023925055991070081</v>
+        <v>0.0017574502021153182</v>
       </c>
       <c r="R3" s="0">
-        <v>0.026039029199987899</v>
+        <v>0.0019127355944216773</v>
       </c>
       <c r="S3" s="0">
-        <v>0.036717245073956781</v>
+        <v>0.0026971190458636718</v>
       </c>
       <c r="T3" s="0">
-        <v>0.062434500490324389</v>
+        <v>0.0045862193011654839</v>
       </c>
       <c r="U3" s="0">
-        <v>0.046318139893231067</v>
+        <v>0.0034023674734629528</v>
       </c>
       <c r="V3" s="0">
-        <v>0.05135931795910563</v>
+        <v>0.0037726743049525391</v>
       </c>
       <c r="W3" s="0">
-        <v>0.063306729060164546</v>
+        <v>0.0046502891450257433</v>
       </c>
       <c r="X3" s="0">
-        <v>0.064793987221842819</v>
+        <v>0.0047595381535229242</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.067801677319718312</v>
+        <v>0.0049804731047050632</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.066660882767059615</v>
+        <v>0.0048966742190908463</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.065830052440522646</v>
+        <v>0.004835644269742867</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.063914424269086556</v>
+        <v>0.0046949291268807425</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.064829697214101478</v>
+        <v>0.0047621613869786028</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.06615753944350633</v>
+        <v>0.0048596996696590455</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.067667415928057251</v>
+        <v>0.0049706111034334977</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.067112657448067381</v>
+        <v>0.0049298593550914926</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.064605800891545329</v>
+        <v>0.0047457154038292315</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.063149809906858034</v>
+        <v>0.0046387628960360416</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.063594866213666723</v>
+        <v>0.0046714550160493196</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.064301359480121167</v>
+        <v>0.0047233514406865851</v>
       </c>
       <c r="AK3" s="0">
-        <v>0.064822590458610718</v>
+        <v>0.0047616394041393173</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.06480623573094868</v>
+        <v>0.0047604381944313379</v>
       </c>
       <c r="AM3" s="0">
-        <v>0.064033551347578821</v>
+        <v>0.0047036793708022384</v>
       </c>
       <c r="AN3" s="0">
-        <v>0.062924375865055393</v>
+        <v>0.0046222036243005471</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.062221212457083112</v>
+        <v>0.0045705513897718042</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="B4" s="0">
-        <v>0.1254070895445526</v>
+        <v>-0.48023304445544734</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.005940866318235774</v>
+        <v>-0.00043639452705629411</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.00052210796294517581</v>
+        <v>-3.8351879539655354e-05</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.011217645657931166</v>
+        <v>-0.0008240093634657164</v>
       </c>
       <c r="F4" s="0">
-        <v>0.0047936319832520939</v>
+        <v>0.00035212347230745289</v>
       </c>
       <c r="G4" s="0">
-        <v>0.012300780327542877</v>
+        <v>0.00090357224249476564</v>
       </c>
       <c r="H4" s="0">
-        <v>0.0036018982593929265</v>
+        <v>0.00026458229105325026</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.010632310666801495</v>
+        <v>-0.00078101204498864929</v>
       </c>
       <c r="J4" s="0">
-        <v>-0.061418031984663238</v>
+        <v>-0.0045115521179441842</v>
       </c>
       <c r="K4" s="0">
-        <v>0.083506772794188819</v>
+        <v>0.006134114311951655</v>
       </c>
       <c r="L4" s="0">
-        <v>0.042098509327472042</v>
+        <v>0.003092407832651356</v>
       </c>
       <c r="M4" s="0">
-        <v>0.021277843934306526</v>
+        <v>0.0015629952349722198</v>
       </c>
       <c r="N4" s="0">
-        <v>0.032427341011736263</v>
+        <v>0.0023688418161338931</v>
       </c>
       <c r="O4" s="0">
-        <v>0.041599468865491249</v>
+        <v>0.0029486138349620328</v>
       </c>
       <c r="P4" s="0">
-        <v>0.033459220219192877</v>
+        <v>0.0024577969624251517</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.022511239005692834</v>
+        <v>0.0016535966698173477</v>
       </c>
       <c r="R4" s="0">
-        <v>0.022582953036136093</v>
+        <v>0.0016588644538443331</v>
       </c>
       <c r="S4" s="0">
-        <v>0.025075531682969145</v>
+        <v>0.001841960035304735</v>
       </c>
       <c r="T4" s="0">
-        <v>0.054937600323355457</v>
+        <v>0.004035523325018997</v>
       </c>
       <c r="U4" s="0">
-        <v>0.041640307135442062</v>
+        <v>0.003058749930472171</v>
       </c>
       <c r="V4" s="0">
-        <v>0.04443914270781632</v>
+        <v>0.003264342585644342</v>
       </c>
       <c r="W4" s="0">
-        <v>0.055212886244188714</v>
+        <v>0.0040557442544742472</v>
       </c>
       <c r="X4" s="0">
-        <v>0.05618081009162032</v>
+        <v>0.0041268448420505588</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.054722622480382482</v>
+        <v>0.0040197311931188251</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.051066943946999482</v>
+        <v>0.0037511977156240439</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.052200109377753517</v>
+        <v>0.0038344358745150964</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.052259366916191013</v>
+        <v>0.0038387898041483126</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.050570034717299019</v>
+        <v>0.0037146966706816387</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.051734782894280879</v>
+        <v>0.0038002551304623933</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.053243420655319153</v>
+        <v>0.0039110739527127292</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.054949081267275462</v>
+        <v>0.0040363656872483</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.054397351488425262</v>
+        <v>0.0039958378264378092</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.051711484709427637</v>
+        <v>0.0037985432340723602</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.050164603436464762</v>
+        <v>0.0036849148403184095</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.050690862890173528</v>
+        <v>0.003723572386509777</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.051499939203650348</v>
+        <v>0.0037830049458139614</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.05210493309265183</v>
+        <v>0.0038274449440508507</v>
       </c>
       <c r="AM4" s="0">
-        <v>0.052116584423815705</v>
+        <v>0.0038283012458907306</v>
       </c>
       <c r="AN4" s="0">
-        <v>0.051296686303533658</v>
+        <v>0.0037680738524394908</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.050103899429395062</v>
+        <v>0.0036804563481211972</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="B5" s="0">
-        <v>0.055486024490896124</v>
+        <v>-0.4827887915091037</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.012702194956710565</v>
+        <v>-0.00093305878912203211</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.005374146485249056</v>
+        <v>-0.00039476648597719377</v>
       </c>
       <c r="E5" s="0">
-        <v>0.013202308870674173</v>
+        <v>0.00096979470390512468</v>
       </c>
       <c r="F5" s="0">
-        <v>0.020226923364166066</v>
+        <v>0.0014857990543022392</v>
       </c>
       <c r="G5" s="0">
-        <v>0.0038681168096838768</v>
+        <v>0.00028413810071137302</v>
       </c>
       <c r="H5" s="0">
-        <v>-0.0014069022719457626</v>
+        <v>-0.00010334559595664983</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.010746652435382781</v>
+        <v>-0.0007894111737963283</v>
       </c>
       <c r="J5" s="0">
-        <v>-0.038672715018868625</v>
+        <v>-0.0028407615835654432</v>
       </c>
       <c r="K5" s="0">
-        <v>0.046242670608277768</v>
+        <v>0.0033968240278848261</v>
       </c>
       <c r="L5" s="0">
-        <v>0.032087587651180645</v>
+        <v>0.0023570413477065344</v>
       </c>
       <c r="M5" s="0">
-        <v>0.020549004741740769</v>
+        <v>0.0015094581776927685</v>
       </c>
       <c r="N5" s="0">
-        <v>0.028630609697237724</v>
+        <v>0.0021125915897757253</v>
       </c>
       <c r="O5" s="0">
-        <v>0.025809721325159334</v>
+        <v>0.0019084614321338567</v>
       </c>
       <c r="P5" s="0">
-        <v>0.026436049586985248</v>
+        <v>0.0019418997467842147</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.018781204877395034</v>
+        <v>0.0013796007075831396</v>
       </c>
       <c r="R5" s="0">
-        <v>0.01942729112776248</v>
+        <v>0.0014270607882068131</v>
       </c>
       <c r="S5" s="0">
-        <v>0.018842827998864345</v>
+        <v>0.0013841283584009045</v>
       </c>
       <c r="T5" s="0">
-        <v>0.039848805662785751</v>
+        <v>0.0029271538241418815</v>
       </c>
       <c r="U5" s="0">
-        <v>0.036835474833846187</v>
+        <v>0.0027058040595424604</v>
       </c>
       <c r="V5" s="0">
-        <v>0.041295026842261828</v>
+        <v>0.0030333876344351141</v>
       </c>
       <c r="W5" s="0">
-        <v>0.04814682854892282</v>
+        <v>0.0035366971368161471</v>
       </c>
       <c r="X5" s="0">
-        <v>0.048803883237712661</v>
+        <v>0.0035849620568428331</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.048887690302795037</v>
+        <v>0.0035911178332263538</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.043388268518008033</v>
+        <v>0.0031871496164249113</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.04331547626229737</v>
+        <v>0.0031818022912238897</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.044697988409070799</v>
+        <v>0.0032833576772886008</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.044708888724039442</v>
+        <v>0.0032841576486102309</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.043041105532341653</v>
+        <v>0.0031616482061682105</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.044448454850834609</v>
+        <v>0.0032650272767845157</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.046217389546187489</v>
+        <v>0.0033949676435666709</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.048201731843527273</v>
+        <v>0.0035407298414859567</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.047693422755138881</v>
+        <v>0.0035033909035794286</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.044825064135562545</v>
+        <v>0.0032926918956808771</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.043202834678336549</v>
+        <v>0.0031735287858333239</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.043856471237945255</v>
+        <v>0.0032215423000871435</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.044819082596581759</v>
+        <v>0.003292251469204921</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.045550537967718262</v>
+        <v>0.003345982329356012</v>
       </c>
       <c r="AN5" s="0">
-        <v>0.045619038144155709</v>
+        <v>0.0033510137443018007</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.04475649550826924</v>
+        <v>0.0032876550610315691</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="B6" s="0">
-        <v>0.032263302252500826</v>
+        <v>-0.48122513474749917</v>
       </c>
       <c r="C6" s="0">
-        <v>-0.0094274541427796996</v>
+        <v>-0.00069250784800500842</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.0098165612929002263</v>
+        <v>-0.00072108933922543361</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.0023487080085657017</v>
+        <v>-0.00017252818368934664</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.0086583804029078046</v>
+        <v>-0.00063601395281320805</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.0054340259083950557</v>
+        <v>-0.00039916462106276418</v>
       </c>
       <c r="H6" s="0">
-        <v>-0.0065539401508452264</v>
+        <v>-0.00048142949975665816</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.013651670884479737</v>
+        <v>-0.0010028043989358526</v>
       </c>
       <c r="J6" s="0">
-        <v>-0.035139292967922203</v>
+        <v>-0.0025812088772941277</v>
       </c>
       <c r="K6" s="0">
-        <v>0.024831739846267388</v>
+        <v>0.0018240523753960125</v>
       </c>
       <c r="L6" s="0">
-        <v>0.016870479800516897</v>
+        <v>0.0012392455903026955</v>
       </c>
       <c r="M6" s="0">
-        <v>0.012457460043845264</v>
+        <v>0.00091508063954931496</v>
       </c>
       <c r="N6" s="0">
-        <v>0.023562270899732257</v>
+        <v>0.0018266515949459383</v>
       </c>
       <c r="O6" s="0">
-        <v>0.022503835982026078</v>
+        <v>0.0016440489266426606</v>
       </c>
       <c r="P6" s="0">
-        <v>0.016627122488387248</v>
+        <v>0.0012213701768027385</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.016294200651658847</v>
+        <v>0.0011969144506278062</v>
       </c>
       <c r="R6" s="0">
-        <v>0.016605395586983235</v>
+        <v>0.0012197740889111075</v>
       </c>
       <c r="S6" s="0">
-        <v>0.017333469709593902</v>
+        <v>0.001273255678725993</v>
       </c>
       <c r="T6" s="0">
-        <v>0.033677227950180105</v>
+        <v>0.0024738097868804987</v>
       </c>
       <c r="U6" s="0">
-        <v>0.030801701882456869</v>
+        <v>0.002262584166552839</v>
       </c>
       <c r="V6" s="0">
-        <v>0.043793562001004108</v>
+        <v>0.0032169208956970285</v>
       </c>
       <c r="W6" s="0">
-        <v>0.046527981823540857</v>
+        <v>0.0034177816179182252</v>
       </c>
       <c r="X6" s="0">
-        <v>0.045534778306406579</v>
+        <v>0.0033448249670005037</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.047016219145792973</v>
+        <v>0.0034536461093880866</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.042204248431996397</v>
+        <v>0.0031001760098184339</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.042186777917608567</v>
+        <v>0.0030988927970268532</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.042399357228157977</v>
+        <v>0.0031145081655162277</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.043862301147063312</v>
+        <v>0.0032219700726250911</v>
       </c>
       <c r="AD6" s="0">
-        <v>0.044074140935555131</v>
+        <v>0.00323753089180423</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.042516374851200488</v>
+        <v>0.0031231030976869856</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.044270114989099794</v>
+        <v>0.0032519266498872157</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.046403055946117225</v>
+        <v>0.003408605062526826</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.048769230289979773</v>
+        <v>0.0035824161462768567</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.048383908285399804</v>
+        <v>0.0035541118943258621</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.045371764879791519</v>
+        <v>0.0033328496453527423</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.043712146312225052</v>
+        <v>0.0032109406821726472</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.044559517923885426</v>
+        <v>0.0032731859843662114</v>
       </c>
       <c r="AM6" s="0">
-        <v>0.045740860162084528</v>
+        <v>0.0033599629452635282</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.046658586496614106</v>
+        <v>0.003427376166149132</v>
       </c>
       <c r="AO6" s="0">
-        <v>0.046827914600688213</v>
+        <v>0.0034398137263500494</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>110</v>
+        <v>174</v>
       </c>
       <c r="B7" s="0">
-        <v>-0.024362696747206626</v>
+        <v>-0.48003154174720664</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.019744143023249595</v>
+        <v>-0.001450334737728487</v>
       </c>
       <c r="D7" s="0">
-        <v>-0.01569452269410563</v>
+        <v>-0.0011528640951902203</v>
       </c>
       <c r="E7" s="0">
-        <v>-0.013803534801163177</v>
+        <v>-0.0010139597323016725</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.0056008504068616807</v>
+        <v>-0.00041141794567517431</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.011072434743251078</v>
+        <v>-0.00081334240700015048</v>
       </c>
       <c r="H7" s="0">
-        <v>-0.011630240244701981</v>
+        <v>-0.00085431658771822905</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.015827651241563198</v>
+        <v>-0.0011626440656327675</v>
       </c>
       <c r="J7" s="0">
-        <v>-0.033107274515216153</v>
+        <v>-0.00243194361383825</v>
       </c>
       <c r="K7" s="0">
-        <v>0.016949583156538345</v>
+        <v>0.0012450565408889114</v>
       </c>
       <c r="L7" s="0">
-        <v>0.011694021451363851</v>
+        <v>0.00085900126009885724</v>
       </c>
       <c r="M7" s="0">
-        <v>0.006607035523197146</v>
+        <v>0.00048532935517886511</v>
       </c>
       <c r="N7" s="0">
-        <v>0.01617913267404409</v>
+        <v>0.0012033349275739624</v>
       </c>
       <c r="O7" s="0">
-        <v>0.01992699047998376</v>
+        <v>0.0013738142284016042</v>
       </c>
       <c r="P7" s="0">
-        <v>0.011600062759427779</v>
+        <v>0.00085210026992715848</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.011348239910148179</v>
+        <v>0.00083360156583511813</v>
       </c>
       <c r="R7" s="0">
-        <v>0.017647398240613069</v>
+        <v>0.0012963156906844464</v>
       </c>
       <c r="S7" s="0">
-        <v>0.020410556529964433</v>
+        <v>0.0014992877190453946</v>
       </c>
       <c r="T7" s="0">
-        <v>0.034731058335620353</v>
+        <v>0.0025512208341338383</v>
       </c>
       <c r="U7" s="0">
-        <v>0.027111581932348923</v>
+        <v>0.0019915218097699694</v>
       </c>
       <c r="V7" s="0">
-        <v>0.037972505161053161</v>
+        <v>0.0027893266793266314</v>
       </c>
       <c r="W7" s="0">
-        <v>0.052949745292688963</v>
+        <v>0.0038895022470258334</v>
       </c>
       <c r="X7" s="0">
-        <v>0.047259414959930954</v>
+        <v>0.0034715106376480009</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.049825874889601149</v>
+        <v>0.0036600328521652625</v>
       </c>
       <c r="Z7" s="0">
-        <v>0.047764659474170676</v>
+        <v>0.0035086239902280547</v>
       </c>
       <c r="AA7" s="0">
-        <v>0.050331475063538342</v>
+        <v>0.0036971730467271757</v>
       </c>
       <c r="AB7" s="0">
-        <v>0.049972656292513504</v>
+        <v>0.0036708151967850822</v>
       </c>
       <c r="AC7" s="0">
-        <v>0.050367205191953632</v>
+        <v>0.0036997970643742328</v>
       </c>
       <c r="AD7" s="0">
-        <v>0.052324027316411989</v>
+        <v>0.0038435386097986357</v>
       </c>
       <c r="AE7" s="0">
-        <v>0.052839647456881675</v>
+        <v>0.0038814152138405</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.051284703227158661</v>
+        <v>0.0037671939015503364</v>
       </c>
       <c r="AG7" s="0">
-        <v>0.053524444794866108</v>
+        <v>0.003931717232402987</v>
       </c>
       <c r="AH7" s="0">
-        <v>0.056196092357453084</v>
+        <v>0.0041279671577751365</v>
       </c>
       <c r="AI7" s="0">
-        <v>0.059140392258269989</v>
+        <v>0.0043442449969414709</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.058861085693118806</v>
+        <v>0.0043237287584966255</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.055482472390448616</v>
+        <v>0.0040755477010931962</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.053666018053928059</v>
+        <v>0.0039421162005892629</v>
       </c>
       <c r="AM7" s="0">
-        <v>0.05478128979802404</v>
+        <v>0.0040240406716185451</v>
       </c>
       <c r="AN7" s="0">
-        <v>0.056281623903386695</v>
+        <v>0.0041342505921941886</v>
       </c>
       <c r="AO7" s="0">
-        <v>0.057466221853147696</v>
+        <v>0.0042212661305847665</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="B8" s="0">
-        <v>-0.077681981575542222</v>
+        <v>-0.47671406557554208</v>
       </c>
       <c r="C8" s="0">
-        <v>-0.023277271395060518</v>
+        <v>-0.0017098659653945747</v>
       </c>
       <c r="D8" s="0">
-        <v>-0.024987170380011459</v>
+        <v>-0.0018354693796918675</v>
       </c>
       <c r="E8" s="0">
-        <v>-0.0022380335949466045</v>
+        <v>-0.00016439814433139022</v>
       </c>
       <c r="F8" s="0">
-        <v>-0.0037747671715644814</v>
+        <v>-0.00027728107600588636</v>
       </c>
       <c r="G8" s="0">
-        <v>-0.018837995105936915</v>
+        <v>-0.0013837728688707585</v>
       </c>
       <c r="H8" s="0">
-        <v>-0.018099542588297483</v>
+        <v>-0.001329528114448808</v>
       </c>
       <c r="I8" s="0">
-        <v>-0.023618017476338342</v>
+        <v>-0.0017348961874466551</v>
       </c>
       <c r="J8" s="0">
-        <v>-0.036927158134320508</v>
+        <v>-0.002712538629090766</v>
       </c>
       <c r="K8" s="0">
-        <v>0.0070655651094995806</v>
+        <v>0.00051901192337694413</v>
       </c>
       <c r="L8" s="0">
-        <v>0.0037115214991422867</v>
+        <v>0.00027263569268209942</v>
       </c>
       <c r="M8" s="0">
-        <v>0.00046446070404588478</v>
+        <v>3.4117418769241681e-05</v>
       </c>
       <c r="N8" s="0">
-        <v>0.008153893590336303</v>
+        <v>0.00060493111728621152</v>
       </c>
       <c r="O8" s="0">
-        <v>0.0092240250353885986</v>
+        <v>0.00066381839077489513</v>
       </c>
       <c r="P8" s="0">
-        <v>0.0069506092481375547</v>
+        <v>0.00051056718228953413</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.0082444176885351841</v>
+        <v>0.00060560566792888793</v>
       </c>
       <c r="R8" s="0">
-        <v>0.012443883907405643</v>
+        <v>0.00091408372590306985</v>
       </c>
       <c r="S8" s="0">
-        <v>0.017292850567156171</v>
+        <v>0.0012702720208886409</v>
       </c>
       <c r="T8" s="0">
-        <v>0.031521434602123026</v>
+        <v>0.0023154534243786662</v>
       </c>
       <c r="U8" s="0">
-        <v>0.027082537533778699</v>
+        <v>0.0019893879099134315</v>
       </c>
       <c r="V8" s="0">
-        <v>0.032384978759609821</v>
+        <v>0.0023788866607457604</v>
       </c>
       <c r="W8" s="0">
-        <v>0.04167849861624888</v>
+        <v>0.0030615555283495244</v>
       </c>
       <c r="X8" s="0">
-        <v>0.046740050040789197</v>
+        <v>0.0034333596317617787</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.051460424840708799</v>
+        <v>0.0037801013399258454</v>
       </c>
       <c r="Z8" s="0">
-        <v>0.051460490801871331</v>
+        <v>0.0037801072901120225</v>
       </c>
       <c r="AA8" s="0">
-        <v>0.056738231769675532</v>
+        <v>0.0041677908944367514</v>
       </c>
       <c r="AB8" s="0">
-        <v>0.05953193706251704</v>
+        <v>0.0043730065770713478</v>
       </c>
       <c r="AC8" s="0">
-        <v>0.059285298673382406</v>
+        <v>0.0043548898152495075</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.060157936055520132</v>
+        <v>0.0044189907254966188</v>
       </c>
       <c r="AE8" s="0">
-        <v>0.062814644599019989</v>
+        <v>0.0046141428370075066</v>
       </c>
       <c r="AF8" s="0">
-        <v>0.063767816462993912</v>
+        <v>0.0046841592435456492</v>
       </c>
       <c r="AG8" s="0">
-        <v>0.062263152718157112</v>
+        <v>0.004573632742059297</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.06518058966948205</v>
+        <v>0.0047879370161840185</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.068591157893913249</v>
+        <v>0.0050384650218069371</v>
       </c>
       <c r="AJ8" s="0">
-        <v>0.072326527671071963</v>
+        <v>0.0053128523035827491</v>
       </c>
       <c r="AK8" s="0">
-        <v>0.072218810292072347</v>
+        <v>0.0053049396703973573</v>
       </c>
       <c r="AL8" s="0">
-        <v>0.06839029681186129</v>
+        <v>0.0050237100054028594</v>
       </c>
       <c r="AM8" s="0">
-        <v>0.066397676469754946</v>
+        <v>0.0048773403591650388</v>
       </c>
       <c r="AN8" s="0">
-        <v>0.067891885063147611</v>
+        <v>0.0049870990495839984</v>
       </c>
       <c r="AO8" s="0">
-        <v>0.069838963181413943</v>
+        <v>0.0051301242250866297</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="B9" s="0">
-        <v>-0.15514258183260632</v>
+        <v>-0.47333654983260626</v>
       </c>
       <c r="C9" s="0">
-        <v>-0.037199091661566021</v>
+        <v>-0.0027325144384951483</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.036004194110941669</v>
+        <v>-0.0026447414233570221</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.034009631774868689</v>
+        <v>-0.0024982279448358957</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.038667025253932216</v>
+        <v>-0.0028403443420224606</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.033762485938915718</v>
+        <v>-0.002480072873055239</v>
       </c>
       <c r="H9" s="0">
-        <v>-0.031649879133818677</v>
+        <v>-0.0023248894493110295</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.034137274010349945</v>
+        <v>-0.0025076044603681846</v>
       </c>
       <c r="J9" s="0">
-        <v>-0.043899557951590965</v>
+        <v>-0.003224707639192359</v>
       </c>
       <c r="K9" s="0">
-        <v>-0.01053782068555531</v>
+        <v>-0.00077407130855550177</v>
       </c>
       <c r="L9" s="0">
-        <v>-0.0087434888843435209</v>
+        <v>-0.00064226584115906205</v>
       </c>
       <c r="M9" s="0">
-        <v>-0.010566105072038159</v>
+        <v>-0.00077614945192422402</v>
       </c>
       <c r="N9" s="0">
-        <v>-0.003038141583887672</v>
+        <v>-0.00017087640009838534</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.0023588494353154938</v>
+        <v>-0.00017868852626112819</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.0050283536279328639</v>
+        <v>-0.00036936482825578043</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.0011611979587262615</v>
+        <v>8.5297883985091527e-05</v>
       </c>
       <c r="R9" s="0">
-        <v>0.0039062506038237974</v>
+        <v>0.00028693882621100286</v>
       </c>
       <c r="S9" s="0">
-        <v>0.011517652170845801</v>
+        <v>0.00084604653083242276</v>
       </c>
       <c r="T9" s="0">
-        <v>0.02702467375796799</v>
+        <v>0.0019851376048860558</v>
       </c>
       <c r="U9" s="0">
-        <v>0.022682313452199031</v>
+        <v>0.0016661635322137158</v>
       </c>
       <c r="V9" s="0">
-        <v>0.031198898782944989</v>
+        <v>0.0022917611520406056</v>
       </c>
       <c r="W9" s="0">
-        <v>0.034877454123141451</v>
+        <v>0.0025619749858899477</v>
       </c>
       <c r="X9" s="0">
-        <v>0.036961729073535843</v>
+        <v>0.002715078811804883</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.054339186864002277</v>
+        <v>0.0039915650714220097</v>
       </c>
       <c r="Z9" s="0">
-        <v>0.052703664240623428</v>
+        <v>0.0038714263748072519</v>
       </c>
       <c r="AA9" s="0">
-        <v>0.057869015600664347</v>
+        <v>0.0042508537418281533</v>
       </c>
       <c r="AB9" s="0">
-        <v>0.063396858649342386</v>
+        <v>0.0046569094560783286</v>
       </c>
       <c r="AC9" s="0">
-        <v>0.066801046139085857</v>
+        <v>0.0049069695840325278</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.067031310904129698</v>
+        <v>0.0049238840993690025</v>
       </c>
       <c r="AE9" s="0">
-        <v>0.068527730407746498</v>
+        <v>0.005033805466738539</v>
       </c>
       <c r="AF9" s="0">
-        <v>0.072040010733636389</v>
+        <v>0.0052918058714209182</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.073528539983840888</v>
+        <v>0.0054011478690863535</v>
       </c>
       <c r="AH9" s="0">
-        <v>0.072081871265615161</v>
+        <v>0.0052948802667586725</v>
       </c>
       <c r="AI9" s="0">
-        <v>0.075831399120298779</v>
+        <v>0.0055703082854008934</v>
       </c>
       <c r="AJ9" s="0">
-        <v>0.080163584725834708</v>
+        <v>0.0058885349099337403</v>
       </c>
       <c r="AK9" s="0">
-        <v>0.084886327220696195</v>
+        <v>0.0062354506725634806</v>
       </c>
       <c r="AL9" s="0">
-        <v>0.085005657725291867</v>
+        <v>0.0062442161141966213</v>
       </c>
       <c r="AM9" s="0">
-        <v>0.080633336811407608</v>
+        <v>0.0059230421370876085</v>
       </c>
       <c r="AN9" s="0">
-        <v>0.078429760642341431</v>
+        <v>0.0057611739534196849</v>
       </c>
       <c r="AO9" s="0">
-        <v>0.080404472206152766</v>
+        <v>0.0059062291576458814</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="B10" s="0">
-        <v>-0.2336411048282977</v>
+        <v>-0.46922614682829761</v>
       </c>
       <c r="C10" s="0">
-        <v>-0.052037642757123061</v>
+        <v>-0.0038225017972868813</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.052427197860636578</v>
+        <v>-0.0038511176792528912</v>
       </c>
       <c r="E10" s="0">
-        <v>-0.04610783792466764</v>
+        <v>-0.0033869195487313264</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.042071983317046681</v>
+        <v>-0.0030904602475158027</v>
       </c>
       <c r="G10" s="0">
-        <v>-0.046706357299421457</v>
+        <v>-0.0034308840470465007</v>
       </c>
       <c r="H10" s="0">
-        <v>-0.048835170295939805</v>
+        <v>-0.0035872600856778347</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.050145710164612882</v>
+        <v>-0.0036835273636638965</v>
       </c>
       <c r="J10" s="0">
-        <v>-0.057982793637873002</v>
+        <v>-0.0042592122504391816</v>
       </c>
       <c r="K10" s="0">
-        <v>-0.034758791616538838</v>
+        <v>-0.0025532582155671224</v>
       </c>
       <c r="L10" s="0">
-        <v>-0.030807569915452259</v>
+        <v>-0.0022630159069482736</v>
       </c>
       <c r="M10" s="0">
-        <v>-0.029071464908344179</v>
+        <v>-0.0021354875205431556</v>
       </c>
       <c r="N10" s="0">
-        <v>-0.020415995927386087</v>
+        <v>-0.001483743230543344</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.016114372976254867</v>
+        <v>-0.0012300954904311268</v>
       </c>
       <c r="P10" s="0">
-        <v>-0.024037370796022736</v>
+        <v>-0.001765701031080813</v>
       </c>
       <c r="Q10" s="0">
-        <v>-0.016994802059183634</v>
+        <v>-0.0012483789202817897</v>
       </c>
       <c r="R10" s="0">
-        <v>-0.0089083952660904964</v>
+        <v>-0.00065437972308440839</v>
       </c>
       <c r="S10" s="0">
-        <v>-0.0031001449426676072</v>
+        <v>-0.00022772535217158163</v>
       </c>
       <c r="T10" s="0">
-        <v>0.012822225808479715</v>
+        <v>0.00094187529684258697</v>
       </c>
       <c r="U10" s="0">
-        <v>0.014650831894722638</v>
+        <v>0.0010761990535097521</v>
       </c>
       <c r="V10" s="0">
-        <v>0.022492956868268608</v>
+        <v>0.0016522528209919063</v>
       </c>
       <c r="W10" s="0">
-        <v>0.030610684006430446</v>
+        <v>0.0022485538850229858</v>
       </c>
       <c r="X10" s="0">
-        <v>0.029085253769752503</v>
+        <v>0.0021365009932022838</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.040013025466748578</v>
+        <v>0.0029392161919400972</v>
       </c>
       <c r="Z10" s="0">
-        <v>0.048993111566340293</v>
+        <v>0.0035988616855635036</v>
       </c>
       <c r="AA10" s="0">
-        <v>0.051938305422385485</v>
+        <v>0.0038152045589892603</v>
       </c>
       <c r="AB10" s="0">
-        <v>0.057929186365457908</v>
+        <v>0.0042552745189372021</v>
       </c>
       <c r="AC10" s="0">
-        <v>0.06474730059103477</v>
+        <v>0.0047561092749863754</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.069432461292525824</v>
+        <v>0.0051002648481903723</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.070506815802488021</v>
+        <v>0.0051791823498448242</v>
       </c>
       <c r="AF10" s="0">
-        <v>0.073059685358416837</v>
+        <v>0.0053667073763332129</v>
       </c>
       <c r="AG10" s="0">
-        <v>0.077627298958828972</v>
+        <v>0.0057022284316892713</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.079937592374988597</v>
+        <v>0.0058719343624971665</v>
       </c>
       <c r="AI10" s="0">
-        <v>0.078913323318595643</v>
+        <v>0.0057966955060015923</v>
       </c>
       <c r="AJ10" s="0">
-        <v>0.083707308737051955</v>
+        <v>0.0061488443809375459</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.089127787434477634</v>
+        <v>0.006547014303586729</v>
       </c>
       <c r="AL10" s="0">
-        <v>0.095003213782684545</v>
+        <v>0.0069786023773559802</v>
       </c>
       <c r="AM10" s="0">
-        <v>0.095569887732861181</v>
+        <v>0.0070202280928007843</v>
       </c>
       <c r="AN10" s="0">
-        <v>0.090922408542367827</v>
+        <v>0.0066788395172929227</v>
       </c>
       <c r="AO10" s="0">
-        <v>0.088734932072262102</v>
+        <v>0.0065181561088925033</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="B11" s="0">
-        <v>-0.32390276212599578</v>
+        <v>-0.46580074312599562</v>
       </c>
       <c r="C11" s="0">
-        <v>-0.063095807121780478</v>
+        <v>-0.0046347963244698365</v>
       </c>
       <c r="D11" s="0">
-        <v>-0.063344097033946584</v>
+        <v>-0.0046530351509976309</v>
       </c>
       <c r="E11" s="0">
-        <v>-0.06197778369510832</v>
+        <v>-0.0045526697213157385</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.060500490711444178</v>
+        <v>-0.0044441535597322668</v>
       </c>
       <c r="G11" s="0">
-        <v>-0.06122486555626392</v>
+        <v>-0.0044973629793343406</v>
       </c>
       <c r="H11" s="0">
-        <v>-0.061354425011505405</v>
+        <v>-0.0045068807682909218</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.062601565455874586</v>
+        <v>-0.0045984910873528295</v>
       </c>
       <c r="J11" s="0">
-        <v>-0.071900696615017939</v>
+        <v>-0.0052815717251761818</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.056389295960481069</v>
+        <v>-0.0041421596000414951</v>
       </c>
       <c r="L11" s="0">
-        <v>-0.053519630792141344</v>
+        <v>-0.0039313638760848924</v>
       </c>
       <c r="M11" s="0">
-        <v>-0.052387330617470425</v>
+        <v>-0.0038481888975432921</v>
       </c>
       <c r="N11" s="0">
-        <v>-0.044351996998709238</v>
+        <v>-0.003255247148021112</v>
       </c>
       <c r="O11" s="0">
-        <v>-0.039156312930785607</v>
+        <v>-0.002890113533134675</v>
       </c>
       <c r="P11" s="0">
-        <v>-0.043064026664249654</v>
+        <v>-0.0031633324284907616</v>
       </c>
       <c r="Q11" s="0">
-        <v>-0.043426805538880002</v>
+        <v>-0.0031899801155906293</v>
       </c>
       <c r="R11" s="0">
-        <v>-0.03718968583125825</v>
+        <v>-0.0027318237462555239</v>
       </c>
       <c r="S11" s="0">
-        <v>-0.027270322534959875</v>
+        <v>-0.0020031819978312271</v>
       </c>
       <c r="T11" s="0">
-        <v>-0.0093583961450494982</v>
+        <v>-0.0006874345707475471</v>
       </c>
       <c r="U11" s="0">
-        <v>-0.0031568683343509494</v>
+        <v>-0.00023189254339839316</v>
       </c>
       <c r="V11" s="0">
-        <v>0.0012758384819101709</v>
+        <v>9.3717840789708795e-05</v>
       </c>
       <c r="W11" s="0">
-        <v>0.012176445807687631</v>
+        <v>0.00089443870661587432</v>
       </c>
       <c r="X11" s="0">
-        <v>0.015351071580688288</v>
+        <v>0.0011276352669762346</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.022716677505166288</v>
+        <v>0.0016686869296466122</v>
       </c>
       <c r="Z11" s="0">
-        <v>0.027638269636964242</v>
+        <v>0.0020302098547785308</v>
       </c>
       <c r="AA11" s="0">
-        <v>0.038452279376099886</v>
+        <v>0.0028245698318855039</v>
       </c>
       <c r="AB11" s="0">
-        <v>0.041301010444640664</v>
+        <v>0.0030338277491364085</v>
       </c>
       <c r="AC11" s="0">
-        <v>0.047963998753606824</v>
+        <v>0.003523266823841853</v>
       </c>
       <c r="AD11" s="0">
-        <v>0.056287149449450694</v>
+        <v>0.0041346559081435474</v>
       </c>
       <c r="AE11" s="0">
-        <v>0.062829846873620823</v>
+        <v>0.0046152596016577063</v>
       </c>
       <c r="AF11" s="0">
-        <v>0.065683415624833069</v>
+        <v>0.0048248732562815588</v>
       </c>
       <c r="AG11" s="0">
-        <v>0.070191718917387874</v>
+        <v>0.0051560371069968025</v>
       </c>
       <c r="AH11" s="0">
-        <v>0.076195088760901114</v>
+        <v>0.0055970230031713308</v>
       </c>
       <c r="AI11" s="0">
-        <v>0.079951042190502447</v>
+        <v>0.0058729221667762066</v>
       </c>
       <c r="AJ11" s="0">
-        <v>0.080218701882241158</v>
+        <v>0.005892583392077988</v>
       </c>
       <c r="AK11" s="0">
-        <v>0.086397575908968266</v>
+        <v>0.0063464615137763247</v>
       </c>
       <c r="AL11" s="0">
-        <v>0.093151961142697096</v>
+        <v>0.0068426148763114369</v>
       </c>
       <c r="AM11" s="0">
-        <v>0.10040439131758705</v>
+        <v>0.0073753528072630914</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.10193129163395233</v>
+        <v>0.0074875140062831136</v>
       </c>
       <c r="AO11" s="0">
-        <v>0.097765396936698418</v>
+        <v>0.0071815022250575344</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="B12" s="0">
-        <v>-0.39596462147111655</v>
+        <v>-0.46299133347111643</v>
       </c>
       <c r="C12" s="0">
-        <v>-0.057882462110618427</v>
+        <v>-0.0042518415929578279</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.058502182241174386</v>
+        <v>-0.0042973649919578194</v>
       </c>
       <c r="E12" s="0">
-        <v>-0.055487365748173006</v>
+        <v>-0.0040759065308804687</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.058398778806590002</v>
+        <v>-0.0042897694640181006</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.061221379632603518</v>
+        <v>-0.0044971072432772874</v>
       </c>
       <c r="H12" s="0">
-        <v>-0.063109714086543131</v>
+        <v>-0.0046358179102136132</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.061028222051366959</v>
+        <v>-0.004482918420275539</v>
       </c>
       <c r="J12" s="0">
-        <v>-0.071770928129587075</v>
+        <v>-0.0052720398913033151</v>
       </c>
       <c r="K12" s="0">
-        <v>-0.066770445994011357</v>
+        <v>-0.00490472243618717</v>
       </c>
       <c r="L12" s="0">
-        <v>-0.060416401237069629</v>
+        <v>-0.0044379756244972146</v>
       </c>
       <c r="M12" s="0">
-        <v>-0.067543286206199593</v>
+        <v>-0.004961491959499631</v>
       </c>
       <c r="N12" s="0">
-        <v>-0.06225581591546115</v>
+        <v>-0.0045739158272504743</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.061660531178651536</v>
+        <v>-0.0045316604982063025</v>
       </c>
       <c r="P12" s="0">
-        <v>-0.06225914164963512</v>
+        <v>-0.0045733374856247178</v>
       </c>
       <c r="Q12" s="0">
-        <v>-0.061028771065346439</v>
+        <v>-0.0044829587438070528</v>
       </c>
       <c r="R12" s="0">
-        <v>-0.063646586060022242</v>
+        <v>-0.0046752546350502522</v>
       </c>
       <c r="S12" s="0">
-        <v>-0.062268018798588183</v>
+        <v>-0.0045739894159584904</v>
       </c>
       <c r="T12" s="0">
-        <v>-0.047715992430325822</v>
+        <v>-0.0035050489756459635</v>
       </c>
       <c r="U12" s="0">
-        <v>-0.035240744956108051</v>
+        <v>-0.0025886618697923414</v>
       </c>
       <c r="V12" s="0">
-        <v>-0.02637649165141203</v>
+        <v>-0.0019375240396663496</v>
       </c>
       <c r="W12" s="0">
-        <v>-0.025943043178616034</v>
+        <v>-0.0019056842230233406</v>
       </c>
       <c r="X12" s="0">
-        <v>-0.021897463176828762</v>
+        <v>-0.0016085104008307649</v>
       </c>
       <c r="Y12" s="0">
-        <v>-0.0099024715330879691</v>
+        <v>-0.00072740080405769847</v>
       </c>
       <c r="Z12" s="0">
-        <v>-0.0045045624943921515</v>
+        <v>-0.00033088900843530888</v>
       </c>
       <c r="AA12" s="0">
-        <v>0.0018896324776877553</v>
+        <v>0.00013880602062171787</v>
       </c>
       <c r="AB12" s="0">
-        <v>0.004365570282718125</v>
+        <v>0.00032067958366216454</v>
       </c>
       <c r="AC12" s="0">
-        <v>0.0073417494248764334</v>
+        <v>0.00053929908436184393</v>
       </c>
       <c r="AD12" s="0">
-        <v>0.015324723570639296</v>
+        <v>0.0011257000385050397</v>
       </c>
       <c r="AE12" s="0">
-        <v>0.02535724480421463</v>
+        <v>0.0018626545562051011</v>
       </c>
       <c r="AF12" s="0">
-        <v>0.034700380701019759</v>
+        <v>0.002548967504293842</v>
       </c>
       <c r="AG12" s="0">
-        <v>0.041054146586258715</v>
+        <v>0.0030156930015521333</v>
       </c>
       <c r="AH12" s="0">
-        <v>0.049024125988949674</v>
+        <v>0.0036011396080772307</v>
       </c>
       <c r="AI12" s="0">
-        <v>0.057071189215417754</v>
+        <v>0.0041922489350655345</v>
       </c>
       <c r="AJ12" s="0">
-        <v>0.063365854611260194</v>
+        <v>0.0046546324246899418</v>
       </c>
       <c r="AK12" s="0">
-        <v>0.066576855081793007</v>
+        <v>0.0048905014364045707</v>
       </c>
       <c r="AL12" s="0">
-        <v>0.074603815196173984</v>
+        <v>0.0054801345306000337</v>
       </c>
       <c r="AM12" s="0">
-        <v>0.082989221957588052</v>
+        <v>0.0060960963610020014</v>
       </c>
       <c r="AN12" s="0">
-        <v>0.091877474542847754</v>
+        <v>0.0067489962565769335</v>
       </c>
       <c r="AO12" s="0">
-        <v>0.09534078845253588</v>
+        <v>0.0070033991602961865</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="B13" s="0">
-        <v>-0.43927762026361944</v>
+        <v>-0.45997612626361922</v>
       </c>
       <c r="C13" s="0">
-        <v>-0.038499867934799592</v>
+        <v>-0.0028280648696995536</v>
       </c>
       <c r="D13" s="0">
-        <v>-0.03781505726028124</v>
+        <v>-0.0027777613547997348</v>
       </c>
       <c r="E13" s="0">
-        <v>-0.039469267793152393</v>
+        <v>-0.0028992729317079413</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.039513880288648877</v>
+        <v>-0.002902550466579612</v>
       </c>
       <c r="G13" s="0">
-        <v>-0.040716593697025689</v>
+        <v>-0.002990897329596065</v>
       </c>
       <c r="H13" s="0">
-        <v>-0.042923862445277107</v>
+        <v>-0.0031530363004935169</v>
       </c>
       <c r="I13" s="0">
-        <v>-0.043042427504489562</v>
+        <v>-0.0031617454646445942</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.047896689435817832</v>
+        <v>-0.0035183220881225274</v>
       </c>
       <c r="K13" s="0">
-        <v>-0.047944276159499699</v>
+        <v>-0.0035218176517475275</v>
       </c>
       <c r="L13" s="0">
-        <v>-0.046782231883812295</v>
+        <v>-0.0034364580888188723</v>
       </c>
       <c r="M13" s="0">
-        <v>-0.052025480713557004</v>
+        <v>-0.0038216088593286957</v>
       </c>
       <c r="N13" s="0">
-        <v>-0.056941446745514747</v>
+        <v>-0.0042034235322278568</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.060921105529923726</v>
+        <v>-0.004474359985212728</v>
       </c>
       <c r="P13" s="0">
-        <v>-0.063235788810306268</v>
+        <v>-0.0046450779681558307</v>
       </c>
       <c r="Q13" s="0">
-        <v>-0.065094723991020301</v>
+        <v>-0.0047816297102924454</v>
       </c>
       <c r="R13" s="0">
-        <v>-0.066605600103884041</v>
+        <v>-0.0048926128790389711</v>
       </c>
       <c r="S13" s="0">
-        <v>-0.075158659017573154</v>
+        <v>-0.005520890232192821</v>
       </c>
       <c r="T13" s="0">
-        <v>-0.072324230884668841</v>
+        <v>-0.0053126840034615763</v>
       </c>
       <c r="U13" s="0">
-        <v>-0.07101206949010104</v>
+        <v>-0.0052162971277612269</v>
       </c>
       <c r="V13" s="0">
-        <v>-0.060751002163581862</v>
+        <v>-0.0044625549657682506</v>
       </c>
       <c r="W13" s="0">
-        <v>-0.052671560158189815</v>
+        <v>-0.003869067654803271</v>
       </c>
       <c r="X13" s="0">
-        <v>-0.068937490322132006</v>
+        <v>-0.0050639054102452064</v>
       </c>
       <c r="Y13" s="0">
-        <v>-0.061465805543283208</v>
+        <v>-0.0045150614785918752</v>
       </c>
       <c r="Z13" s="0">
-        <v>-0.055290691710082628</v>
+        <v>-0.0040614599039330845</v>
       </c>
       <c r="AA13" s="0">
-        <v>-0.04480996407216245</v>
+        <v>-0.0032915828275329462</v>
       </c>
       <c r="AB13" s="0">
-        <v>-0.044386436561787687</v>
+        <v>-0.0032604713470853475</v>
       </c>
       <c r="AC13" s="0">
-        <v>-0.057069717185191375</v>
+        <v>-0.0041921407980913261</v>
       </c>
       <c r="AD13" s="0">
-        <v>-0.0540378972880231</v>
+        <v>-0.0039694340804264372</v>
       </c>
       <c r="AE13" s="0">
-        <v>-0.046904188690595414</v>
+        <v>-0.0034454168487788039</v>
       </c>
       <c r="AF13" s="0">
-        <v>-0.038415503548994263</v>
+        <v>-0.002821868179392506</v>
       </c>
       <c r="AG13" s="0">
-        <v>-0.028105353051253508</v>
+        <v>-0.0020645199674011461</v>
       </c>
       <c r="AH13" s="0">
-        <v>-0.018604447039354832</v>
+        <v>-0.0013666174998336333</v>
       </c>
       <c r="AI13" s="0">
-        <v>-0.0068676179986192449</v>
+        <v>-0.00050447041027629203</v>
       </c>
       <c r="AJ13" s="0">
-        <v>0.0017731315482683941</v>
+        <v>0.00013024756931018233</v>
       </c>
       <c r="AK13" s="0">
-        <v>0.010506404215373947</v>
+        <v>0.0007717637972144975</v>
       </c>
       <c r="AL13" s="0">
-        <v>0.018258941888178549</v>
+        <v>0.0013412376673299642</v>
       </c>
       <c r="AM13" s="0">
-        <v>0.027482244375284886</v>
+        <v>0.0020187487426246431</v>
       </c>
       <c r="AN13" s="0">
-        <v>0.036363293737241308</v>
+        <v>0.0026711191724088645</v>
       </c>
       <c r="AO13" s="0">
-        <v>0.045797794273245998</v>
+        <v>0.003364145181511291</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="B14" s="0">
-        <v>-0.45322080250298341</v>
+        <v>-0.45706267950298318</v>
       </c>
       <c r="C14" s="0">
-        <v>-0.014391441276768537</v>
+        <v>-0.0010571449703710711</v>
       </c>
       <c r="D14" s="0">
-        <v>-0.014185780568283067</v>
+        <v>-0.0010420372526225297</v>
       </c>
       <c r="E14" s="0">
-        <v>-0.014745915416440493</v>
+        <v>-0.0010831834292016618</v>
       </c>
       <c r="F14" s="0">
-        <v>-0.015174612545567543</v>
+        <v>-0.0011146743225792788</v>
       </c>
       <c r="G14" s="0">
-        <v>-0.015769628235248506</v>
+        <v>-0.0011583813347889049</v>
       </c>
       <c r="H14" s="0">
-        <v>-0.017311365332880982</v>
+        <v>-0.0012716324072058471</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.017590551165628861</v>
+        <v>-0.0012921391135378157</v>
       </c>
       <c r="J14" s="0">
-        <v>-0.021119698265685573</v>
+        <v>-0.0015513781708056396</v>
       </c>
       <c r="K14" s="0">
-        <v>-0.020162611412202186</v>
+        <v>-0.0014810746453941537</v>
       </c>
       <c r="L14" s="0">
-        <v>-0.020844026162118601</v>
+        <v>-0.0015311291412434813</v>
       </c>
       <c r="M14" s="0">
-        <v>-0.025208633199429932</v>
+        <v>-0.0018517376341583014</v>
       </c>
       <c r="N14" s="0">
-        <v>-0.02802248755317692</v>
+        <v>-0.0020528633191080337</v>
       </c>
       <c r="O14" s="0">
-        <v>-0.035418985024541563</v>
+        <v>-0.0025845364445012953</v>
       </c>
       <c r="P14" s="0">
-        <v>-0.038945643806771853</v>
+        <v>-0.0028608095050117743</v>
       </c>
       <c r="Q14" s="0">
-        <v>-0.043587816521869223</v>
+        <v>-0.0032018081503859541</v>
       </c>
       <c r="R14" s="0">
-        <v>-0.047308626851927646</v>
+        <v>-0.0034751248687193703</v>
       </c>
       <c r="S14" s="0">
-        <v>-0.05247699253953584</v>
+        <v>-0.0038547752168035521</v>
       </c>
       <c r="T14" s="0">
-        <v>-0.059025171214809082</v>
+        <v>-0.0043357814658718796</v>
       </c>
       <c r="U14" s="0">
-        <v>-0.067805280644949908</v>
+        <v>-0.0049807372528715699</v>
       </c>
       <c r="V14" s="0">
-        <v>-0.077154484049994268</v>
+        <v>-0.0056674962378029936</v>
       </c>
       <c r="W14" s="0">
-        <v>-0.066684672671697989</v>
+        <v>-0.0048984206311136758</v>
       </c>
       <c r="X14" s="0">
-        <v>-0.069499559313150217</v>
+        <v>-0.0051051929667324525</v>
       </c>
       <c r="Y14" s="0">
-        <v>-0.093239178447780624</v>
+        <v>-0.0068490227580884078</v>
       </c>
       <c r="Z14" s="0">
-        <v>-0.097383452624637892</v>
+        <v>-0.0071534458198518336</v>
       </c>
       <c r="AA14" s="0">
-        <v>-0.095190578088595504</v>
+        <v>-0.0069923648856798915</v>
       </c>
       <c r="AB14" s="0">
-        <v>-0.090152375335023141</v>
+        <v>-0.006622276334814714</v>
       </c>
       <c r="AC14" s="0">
-        <v>-0.10257664179004501</v>
+        <v>-0.0075349189055119448</v>
       </c>
       <c r="AD14" s="0">
-        <v>-0.13417950705034015</v>
+        <v>-0.0098563548791290589</v>
       </c>
       <c r="AE14" s="0">
-        <v>-0.13293766279002711</v>
+        <v>-0.0097651334087855424</v>
       </c>
       <c r="AF14" s="0">
-        <v>-0.13358803024656543</v>
+        <v>-0.0098129069578811179</v>
       </c>
       <c r="AG14" s="0">
-        <v>-0.13557314433976142</v>
+        <v>-0.0099587263071218568</v>
       </c>
       <c r="AH14" s="0">
-        <v>-0.13226872978540297</v>
+        <v>-0.0097159958675542835</v>
       </c>
       <c r="AI14" s="0">
-        <v>-0.12459140471888018</v>
+        <v>-0.0091520460244908231</v>
       </c>
       <c r="AJ14" s="0">
-        <v>-0.11535101057565568</v>
+        <v>-0.0084732801191806373</v>
       </c>
       <c r="AK14" s="0">
-        <v>-0.11302040291566935</v>
+        <v>-0.0083020812828148993</v>
       </c>
       <c r="AL14" s="0">
-        <v>-0.106997523756116</v>
+        <v>-0.0078596616087951432</v>
       </c>
       <c r="AM14" s="0">
-        <v>-0.096531271210462746</v>
+        <v>-0.0070908471903534664</v>
       </c>
       <c r="AN14" s="0">
-        <v>-0.092826748981408719</v>
+        <v>-0.0068187266301604765</v>
       </c>
       <c r="AO14" s="0">
-        <v>-0.090435411379077069</v>
+        <v>-0.0066430668884595034</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="B15" s="0">
-        <v>-0.454063972031513</v>
+        <v>-0.4544758345315128</v>
       </c>
       <c r="C15" s="0">
-        <v>-0.002978950400279384</v>
+        <v>-0.00021882356822267024</v>
       </c>
       <c r="D15" s="0">
-        <v>-0.0030062085162957186</v>
+        <v>-0.00022082520252508786</v>
       </c>
       <c r="E15" s="0">
-        <v>-0.0030862706518147566</v>
+        <v>-0.00022670684913689287</v>
       </c>
       <c r="F15" s="0">
-        <v>-0.0031722515295798145</v>
+        <v>-0.00023302216038983969</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.0033688957243321821</v>
+        <v>-0.00024746685234733334</v>
       </c>
       <c r="H15" s="0">
-        <v>-0.003585495526715045</v>
+        <v>-0.00026337800718589932</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.0039284153984325571</v>
+        <v>-0.00028856718161646144</v>
       </c>
       <c r="J15" s="0">
-        <v>-0.0046381968917296483</v>
+        <v>-0.00034070605698777179</v>
       </c>
       <c r="K15" s="0">
-        <v>-0.0047131873282389375</v>
+        <v>-0.00034621447970101249</v>
       </c>
       <c r="L15" s="0">
-        <v>-0.0045658735636676176</v>
+        <v>-0.00033539299245144427</v>
       </c>
       <c r="M15" s="0">
-        <v>-0.0062915456504424793</v>
+        <v>-0.00046215420676193331</v>
       </c>
       <c r="N15" s="0">
-        <v>-0.0075410431131946636</v>
+        <v>-0.00055387382428051524</v>
       </c>
       <c r="O15" s="0">
-        <v>-0.0093842093182386239</v>
+        <v>-0.00069393367241260551</v>
       </c>
       <c r="P15" s="0">
-        <v>-0.012865144368908885</v>
+        <v>-0.00094502805750340535</v>
       </c>
       <c r="Q15" s="0">
-        <v>-0.015677255727079571</v>
+        <v>-0.0011515967151416451</v>
       </c>
       <c r="R15" s="0">
-        <v>-0.018402270985914033</v>
+        <v>-0.0013517656613510898</v>
       </c>
       <c r="S15" s="0">
-        <v>-0.021118700058253038</v>
+        <v>-0.0015513056528376756</v>
       </c>
       <c r="T15" s="0">
-        <v>-0.025192716682703176</v>
+        <v>-0.0018505687481742417</v>
       </c>
       <c r="U15" s="0">
-        <v>-0.033223044061519519</v>
+        <v>-0.0024404485168751933</v>
       </c>
       <c r="V15" s="0">
-        <v>-0.043183149912283433</v>
+        <v>-0.0031720815884108133</v>
       </c>
       <c r="W15" s="0">
-        <v>-0.050210995580123888</v>
+        <v>-0.0036883230642568154</v>
       </c>
       <c r="X15" s="0">
-        <v>-0.046165130268513224</v>
+        <v>-0.0033911283599077913</v>
       </c>
       <c r="Y15" s="0">
-        <v>-0.055270060657399367</v>
+        <v>-0.0040599444211939506</v>
       </c>
       <c r="Z15" s="0">
-        <v>-0.078865934371395413</v>
+        <v>-0.0057932139829883211</v>
       </c>
       <c r="AA15" s="0">
-        <v>-0.085776101900268867</v>
+        <v>-0.0063008109814751689</v>
       </c>
       <c r="AB15" s="0">
-        <v>-0.091595513817306337</v>
+        <v>-0.0067282844595136782</v>
       </c>
       <c r="AC15" s="0">
-        <v>-0.092177698449861734</v>
+        <v>-0.0067710495719411901</v>
       </c>
       <c r="AD15" s="0">
-        <v>-0.1113268211669261</v>
+        <v>-0.0081776772164711686</v>
       </c>
       <c r="AE15" s="0">
-        <v>-0.14554245403984639</v>
+        <v>-0.010691036382916963</v>
       </c>
       <c r="AF15" s="0">
-        <v>-0.14754267578901673</v>
+        <v>-0.010837966058514725</v>
       </c>
       <c r="AG15" s="0">
-        <v>-0.15625634045444023</v>
+        <v>-0.011478040554670443</v>
       </c>
       <c r="AH15" s="0">
-        <v>-0.16757571497986429</v>
+        <v>-0.012309522129443085</v>
       </c>
       <c r="AI15" s="0">
-        <v>-0.17345691237201269</v>
+        <v>-0.012741534092863882</v>
       </c>
       <c r="AJ15" s="0">
-        <v>-0.17101754816274012</v>
+        <v>-0.01256234783951421</v>
       </c>
       <c r="AK15" s="0">
-        <v>-0.17169643088125933</v>
+        <v>-0.012612215720783637</v>
       </c>
       <c r="AL15" s="0">
-        <v>-0.1779383578220084</v>
+        <v>-0.013070724969404923</v>
       </c>
       <c r="AM15" s="0">
-        <v>-0.17910094993093595</v>
+        <v>-0.01315612610941258</v>
       </c>
       <c r="AN15" s="0">
-        <v>-0.17270062993940863</v>
+        <v>-0.01268598063398213</v>
       </c>
       <c r="AO15" s="0">
-        <v>-0.17922485759417767</v>
+        <v>-0.013165227767042376</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="B16" s="0">
-        <v>-0.452291760434334</v>
+        <v>-0.45231714383433369</v>
       </c>
       <c r="C16" s="0">
-        <v>-0.00033334425406091809</v>
+        <v>-2.4486285907121541e-05</v>
       </c>
       <c r="D16" s="0">
-        <v>-0.00034597983092969392</v>
+        <v>-2.5414501399534384e-05</v>
       </c>
       <c r="E16" s="0">
-        <v>-0.00034909184318239093</v>
+        <v>-2.5643048990497963e-05</v>
       </c>
       <c r="F16" s="0">
-        <v>-0.00035544910359617057</v>
+        <v>-2.611008635317047e-05</v>
       </c>
       <c r="G16" s="0">
-        <v>-0.0003721273913372587</v>
+        <v>-2.7335182329835117e-05</v>
       </c>
       <c r="H16" s="0">
-        <v>-0.00043209398046407412</v>
+        <v>-3.174009328571481e-05</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.00057699696555798218</v>
+        <v>-4.2384103439818688e-05</v>
       </c>
       <c r="J16" s="0">
-        <v>-0.00065272450399398384</v>
+        <v>-4.7946899678796839e-05</v>
       </c>
       <c r="K16" s="0">
-        <v>-0.0006311458588503095</v>
+        <v>-4.636176113270718e-05</v>
       </c>
       <c r="L16" s="0">
-        <v>-0.00071039355161692957</v>
+        <v>-5.2182991936766676e-05</v>
       </c>
       <c r="M16" s="0">
-        <v>-0.0010550368991119816</v>
+        <v>-7.7499295111194133e-05</v>
       </c>
       <c r="N16" s="0">
-        <v>-0.0012308093136172518</v>
+        <v>-9.1649016949690854e-05</v>
       </c>
       <c r="O16" s="0">
-        <v>-0.0014502343671583069</v>
+        <v>-0.00010658222541531925</v>
       </c>
       <c r="P16" s="0">
-        <v>-0.0018686621620274942</v>
+        <v>-0.00013726566629967962</v>
       </c>
       <c r="Q16" s="0">
-        <v>-0.0029270408631835148</v>
+        <v>-0.0002150102580149027</v>
       </c>
       <c r="R16" s="0">
-        <v>-0.0035170334078489336</v>
+        <v>-0.00025834856054507416</v>
       </c>
       <c r="S16" s="0">
-        <v>-0.004416430616909074</v>
+        <v>-0.00032441576282388196</v>
       </c>
       <c r="T16" s="0">
-        <v>-0.0054161607914803584</v>
+        <v>-0.00039785222209759441</v>
       </c>
       <c r="U16" s="0">
-        <v>-0.0076012592925799004</v>
+        <v>-0.00055836115857749169</v>
       </c>
       <c r="V16" s="0">
-        <v>-0.011096661750890835</v>
+        <v>-0.00081512089676866184</v>
       </c>
       <c r="W16" s="0">
-        <v>-0.014600838958597328</v>
+        <v>-0.0010725270413565746</v>
       </c>
       <c r="X16" s="0">
-        <v>-0.017817466319240381</v>
+        <v>-0.0013088088358125805</v>
       </c>
       <c r="Y16" s="0">
-        <v>-0.017467476233566211</v>
+        <v>-0.0012830993519907796</v>
       </c>
       <c r="Z16" s="0">
-        <v>-0.023738829518760871</v>
+        <v>-0.0017437709560330639</v>
       </c>
       <c r="AA16" s="0">
-        <v>-0.033804475070951669</v>
+        <v>-0.002483157854851592</v>
       </c>
       <c r="AB16" s="0">
-        <v>-0.039062780648447537</v>
+        <v>-0.0028694146788614816</v>
       </c>
       <c r="AC16" s="0">
-        <v>-0.042661971461493323</v>
+        <v>-0.0031337977260460503</v>
       </c>
       <c r="AD16" s="0">
-        <v>-0.043796446293101865</v>
+        <v>-0.0032171327007279316</v>
       </c>
       <c r="AE16" s="0">
-        <v>-0.055476334937258939</v>
+        <v>-0.0040750963797110962</v>
       </c>
       <c r="AF16" s="0">
-        <v>-0.071915076321652865</v>
+        <v>-0.0052826286270493683</v>
       </c>
       <c r="AG16" s="0">
-        <v>-0.073113086621749507</v>
+        <v>-0.0053706295514880376</v>
       </c>
       <c r="AH16" s="0">
-        <v>-0.079954882037466035</v>
+        <v>-0.0058732045004176725</v>
       </c>
       <c r="AI16" s="0">
-        <v>-0.087850209518657532</v>
+        <v>-0.0064531672280942476</v>
       </c>
       <c r="AJ16" s="0">
-        <v>-0.092862603138524985</v>
+        <v>-0.0068213610465700514</v>
       </c>
       <c r="AK16" s="0">
-        <v>-0.091961809904449368</v>
+        <v>-0.0067551904750610126</v>
       </c>
       <c r="AL16" s="0">
-        <v>-0.095780029323117175</v>
+        <v>-0.007035663967127348</v>
       </c>
       <c r="AM16" s="0">
-        <v>-0.10056693499447066</v>
+        <v>-0.0073872938537746236</v>
       </c>
       <c r="AN16" s="0">
-        <v>-0.10196481794227819</v>
+        <v>-0.0074899764976742444</v>
       </c>
       <c r="AO16" s="0">
-        <v>-0.09863613991389153</v>
+        <v>-0.0072454638997024867</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="B17" s="0">
-        <v>0.2753267546775866</v>
+        <v>-0.32180801969403589</v>
       </c>
       <c r="C17" s="0">
-        <v>0.002214154581450245</v>
+        <v>-0.24835391559249614</v>
       </c>
       <c r="D17" s="0">
-        <v>0.0020969026118662359</v>
+        <v>-0.24106280321397716</v>
       </c>
       <c r="E17" s="0">
-        <v>-0.026594646879579242</v>
+        <v>-0.25204606578150579</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.017264998647291141</v>
+        <v>-0.23647635633247516</v>
       </c>
       <c r="G17" s="0">
-        <v>0.075312207731849878</v>
+        <v>-0.20380063737077947</v>
       </c>
       <c r="H17" s="0">
-        <v>0.044107744327227305</v>
+        <v>-0.20358581062784248</v>
       </c>
       <c r="I17" s="0">
-        <v>0.0074306878013155053</v>
+        <v>-0.2129573704653433</v>
       </c>
       <c r="J17" s="0">
-        <v>-0.10381488332175026</v>
+        <v>-0.26268537140661191</v>
       </c>
       <c r="K17" s="0">
-        <v>0.055285829264906106</v>
+        <v>-0.23550634104633489</v>
       </c>
       <c r="L17" s="0">
-        <v>0.043889678247849506</v>
+        <v>-0.20065272573098819</v>
       </c>
       <c r="M17" s="0">
-        <v>0.032099008156623032</v>
+        <v>-0.22820829269792009</v>
       </c>
       <c r="N17" s="0">
-        <v>0.047958925923629048</v>
+        <v>-0.26095962894372471</v>
       </c>
       <c r="O17" s="0">
-        <v>0.053791950516346332</v>
+        <v>-0.31651067901876928</v>
       </c>
       <c r="P17" s="0">
-        <v>0.05023523129253149</v>
+        <v>-0.33516575233036111</v>
       </c>
       <c r="Q17" s="0">
-        <v>0.052178211439875888</v>
+        <v>-0.29577657503756777</v>
       </c>
       <c r="R17" s="0">
-        <v>0.039916341570719105</v>
+        <v>-0.29544165464999511</v>
       </c>
       <c r="S17" s="0">
-        <v>0.040757859576883826</v>
+        <v>-0.28332722052968318</v>
       </c>
       <c r="T17" s="0">
-        <v>0.064280967857023308</v>
+        <v>-0.26433955356375172</v>
       </c>
       <c r="U17" s="0">
-        <v>0.027969880109576462</v>
+        <v>-0.26656667277197676</v>
       </c>
       <c r="V17" s="0">
-        <v>0.029818805979649143</v>
+        <v>-0.26985882499920971</v>
       </c>
       <c r="W17" s="0">
-        <v>0.038109528909003432</v>
+        <v>-0.2778370240562813</v>
       </c>
       <c r="X17" s="0">
-        <v>0.019947091901443059</v>
+        <v>-0.28314950592105975</v>
       </c>
       <c r="Y17" s="0">
-        <v>0.015431544119309359</v>
+        <v>-0.29142796441726215</v>
       </c>
       <c r="Z17" s="0">
-        <v>0.010086923354631017</v>
+        <v>-0.30792782178134298</v>
       </c>
       <c r="AA17" s="0">
-        <v>0.010742228642999008</v>
+        <v>-0.29609850403139792</v>
       </c>
       <c r="AB17" s="0">
-        <v>0.012343224380187978</v>
+        <v>-0.27933588911271917</v>
       </c>
       <c r="AC17" s="0">
-        <v>0.013817919855534377</v>
+        <v>-0.25733682873041347</v>
       </c>
       <c r="AD17" s="0">
-        <v>0.013225269577308962</v>
+        <v>-0.24959548975679502</v>
       </c>
       <c r="AE17" s="0">
-        <v>0.010785740753344375</v>
+        <v>-0.26204215611929976</v>
       </c>
       <c r="AF17" s="0">
-        <v>0.0093511461640726212</v>
+        <v>-0.27396811903430662</v>
       </c>
       <c r="AG17" s="0">
-        <v>0.0097274509172733392</v>
+        <v>-0.27229398784930742</v>
       </c>
       <c r="AH17" s="0">
-        <v>0.010355313666312593</v>
+        <v>-0.26343876284208384</v>
       </c>
       <c r="AI17" s="0">
-        <v>0.01080986075802115</v>
+        <v>-0.25172374070099907</v>
       </c>
       <c r="AJ17" s="0">
-        <v>0.010759643901127824</v>
+        <v>-0.24271651795351434</v>
       </c>
       <c r="AK17" s="0">
-        <v>0.0099987301754477231</v>
+        <v>-0.24128398114117788</v>
       </c>
       <c r="AL17" s="0">
-        <v>0.0089247910447557421</v>
+        <v>-0.24557351815178197</v>
       </c>
       <c r="AM17" s="0">
-        <v>0.008235705473447319</v>
+        <v>-0.24934086584961379</v>
       </c>
       <c r="AN17" s="0">
-        <v>0.0081987783782420109</v>
+        <v>-0.24794350263994924</v>
       </c>
       <c r="AO17" s="0">
-        <v>0.0084290432624750666</v>
+        <v>-0.24229388427584642</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="B18" s="0">
-        <v>0.18944091200051794</v>
+        <v>-0.40816927199948205</v>
       </c>
       <c r="C18" s="0">
-        <v>-0.008798052235841184</v>
+        <v>-0.0015079719626350796</v>
       </c>
       <c r="D18" s="0">
-        <v>0.0024929074421023954</v>
+        <v>0.00042728031800165489</v>
       </c>
       <c r="E18" s="0">
-        <v>-0.02137327078209339</v>
+        <v>-0.003663345315116584</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.0086453951054279478</v>
+        <v>-0.0014818075439845257</v>
       </c>
       <c r="G18" s="0">
-        <v>0.036646461971322597</v>
+        <v>0.0062811478108948937</v>
       </c>
       <c r="H18" s="0">
-        <v>0.022723685303813409</v>
+        <v>0.0038948049391408501</v>
       </c>
       <c r="I18" s="0">
-        <v>-0.0011769599015129008</v>
+        <v>-0.00020172908472759765</v>
       </c>
       <c r="J18" s="0">
-        <v>-0.11303953290302049</v>
+        <v>-0.019374801743863967</v>
       </c>
       <c r="K18" s="0">
-        <v>0.083466674259414675</v>
+        <v>0.014306059354742662</v>
       </c>
       <c r="L18" s="0">
-        <v>0.033933903565056878</v>
+        <v>0.0058162189431997247</v>
       </c>
       <c r="M18" s="0">
-        <v>0.03038390787459366</v>
+        <v>0.005207754943127918</v>
       </c>
       <c r="N18" s="0">
-        <v>0.047839256681225573</v>
+        <v>0.0083336142407887115</v>
       </c>
       <c r="O18" s="0">
-        <v>0.048225141307962183</v>
+        <v>0.0080629137465370038</v>
       </c>
       <c r="P18" s="0">
-        <v>0.039490915288615258</v>
+        <v>0.0067686815380856857</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.036536510565018609</v>
+        <v>0.0062623016142885346</v>
       </c>
       <c r="R18" s="0">
-        <v>0.042142916628999716</v>
+        <v>0.0072232310556554213</v>
       </c>
       <c r="S18" s="0">
-        <v>0.046470535159674142</v>
+        <v>0.0079649784090813358</v>
       </c>
       <c r="T18" s="0">
-        <v>0.074841309368095077</v>
+        <v>0.012827684813588591</v>
       </c>
       <c r="U18" s="0">
-        <v>0.054583454125459945</v>
+        <v>0.0093555195434861793</v>
       </c>
       <c r="V18" s="0">
-        <v>0.055003826390571879</v>
+        <v>0.009427570528352025</v>
       </c>
       <c r="W18" s="0">
-        <v>0.065383546651785807</v>
+        <v>0.011206638379371359</v>
       </c>
       <c r="X18" s="0">
-        <v>0.061813519294937606</v>
+        <v>0.010594741565412957</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.065356164722600418</v>
+        <v>0.011201945995699458</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.063794944403975373</v>
+        <v>0.010934354663839019</v>
       </c>
       <c r="AA18" s="0">
-        <v>0.061654781829491904</v>
+        <v>0.010567534462549988</v>
       </c>
       <c r="AB18" s="0">
-        <v>0.062307356539842311</v>
+        <v>0.010679385016649279</v>
       </c>
       <c r="AC18" s="0">
-        <v>0.063362208607063986</v>
+        <v>0.010860185025781843</v>
       </c>
       <c r="AD18" s="0">
-        <v>0.064740168214057592</v>
+        <v>0.011096365635797523</v>
       </c>
       <c r="AE18" s="0">
-        <v>0.064188713044355028</v>
+        <v>0.011001847016782751</v>
       </c>
       <c r="AF18" s="0">
-        <v>0.06181457881664542</v>
+        <v>0.010594924170671982</v>
       </c>
       <c r="AG18" s="0">
-        <v>0.060425638744489356</v>
+        <v>0.010356861670950179</v>
       </c>
       <c r="AH18" s="0">
-        <v>0.060816741782236609</v>
+        <v>0.010423895532697791</v>
       </c>
       <c r="AI18" s="0">
-        <v>0.061455653716094398</v>
+        <v>0.010533404307279004</v>
       </c>
       <c r="AJ18" s="0">
-        <v>0.061922434122747332</v>
+        <v>0.010613409985105071</v>
       </c>
       <c r="AK18" s="0">
-        <v>0.061888309307405402</v>
+        <v>0.010607560720017117</v>
       </c>
       <c r="AL18" s="0">
-        <v>0.061152307701103463</v>
+        <v>0.010481411747257918</v>
       </c>
       <c r="AM18" s="0">
-        <v>0.060103532554758754</v>
+        <v>0.010301652930195804</v>
       </c>
       <c r="AN18" s="0">
-        <v>0.059434075184621626</v>
+        <v>0.01018690948548695</v>
       </c>
       <c r="AO18" s="0">
-        <v>0.059407259181559091</v>
+        <v>0.010182312957646433</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>122</v>
+        <v>186</v>
       </c>
       <c r="B19" s="0">
-        <v>0.17236558985102601</v>
+        <v>-0.409903193148974</v>
       </c>
       <c r="C19" s="0">
-        <v>-0.0007236851580176909</v>
+        <v>-0.00012403869571397941</v>
       </c>
       <c r="D19" s="0">
-        <v>0.00069276141809603703</v>
+        <v>0.00011873784877303173</v>
       </c>
       <c r="E19" s="0">
-        <v>-0.0095856840114783085</v>
+        <v>-0.0016429716253436033</v>
       </c>
       <c r="F19" s="0">
-        <v>-0.0025688894489046613</v>
+        <v>-0.00044030361560526421</v>
       </c>
       <c r="G19" s="0">
-        <v>0.026340217047261187</v>
+        <v>0.0045146722122708649</v>
       </c>
       <c r="H19" s="0">
-        <v>0.014428121797097619</v>
+        <v>0.0024729577400278702</v>
       </c>
       <c r="I19" s="0">
-        <v>-0.0047140371583156496</v>
+        <v>-0.00080797844880275971</v>
       </c>
       <c r="J19" s="0">
-        <v>-0.095264455875445089</v>
+        <v>-0.016328180273322002</v>
       </c>
       <c r="K19" s="0">
-        <v>0.10330429514448047</v>
+        <v>0.01770619677138352</v>
       </c>
       <c r="L19" s="0">
-        <v>0.044713988905011985</v>
+        <v>0.0076639084904716048</v>
       </c>
       <c r="M19" s="0">
-        <v>0.023324587711579851</v>
+        <v>0.003997797691870919</v>
       </c>
       <c r="N19" s="0">
-        <v>0.043297518338707645</v>
+        <v>0.0076814060563827891</v>
       </c>
       <c r="O19" s="0">
-        <v>0.047792397575503569</v>
+        <v>0.0080622943262543822</v>
       </c>
       <c r="P19" s="0">
-        <v>0.037713166916316314</v>
+        <v>0.0064639792668091944</v>
       </c>
       <c r="Q19" s="0">
-        <v>0.023925055991070081</v>
+        <v>0.0041007181382692881</v>
       </c>
       <c r="R19" s="0">
-        <v>0.026039029199987899</v>
+        <v>0.0044630497322280527</v>
       </c>
       <c r="S19" s="0">
-        <v>0.036717245073956781</v>
+        <v>0.0062932797379492977</v>
       </c>
       <c r="T19" s="0">
-        <v>0.062434500490324389</v>
+        <v>0.010701177059874611</v>
       </c>
       <c r="U19" s="0">
-        <v>0.046318139893231067</v>
+        <v>0.0079388580690142319</v>
       </c>
       <c r="V19" s="0">
-        <v>0.05135931795910563</v>
+        <v>0.008802908342489979</v>
       </c>
       <c r="W19" s="0">
-        <v>0.063306729060164546</v>
+        <v>0.010850675659815845</v>
       </c>
       <c r="X19" s="0">
-        <v>0.064793987221842819</v>
+        <v>0.011105589334398425</v>
       </c>
       <c r="Y19" s="0">
-        <v>0.067801677319718312</v>
+        <v>0.011621103565734259</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.066660882767059615</v>
+        <v>0.011425572844545262</v>
       </c>
       <c r="AA19" s="0">
-        <v>0.065830052440522646</v>
+        <v>0.011283169986555097</v>
       </c>
       <c r="AB19" s="0">
-        <v>0.063914424269086556</v>
+        <v>0.010954833641299289</v>
       </c>
       <c r="AC19" s="0">
-        <v>0.064829697214101478</v>
+        <v>0.011111709581527851</v>
       </c>
       <c r="AD19" s="0">
-        <v>0.06615753944350633</v>
+        <v>0.011339300514894346</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.067667415928057251</v>
+        <v>0.011598090610410727</v>
       </c>
       <c r="AF19" s="0">
-        <v>0.067112657448067381</v>
+        <v>0.01150300547139177</v>
       </c>
       <c r="AG19" s="0">
-        <v>0.064605800891545329</v>
+        <v>0.011073333966089949</v>
       </c>
       <c r="AH19" s="0">
-        <v>0.063149809906858034</v>
+        <v>0.010823779757417495</v>
       </c>
       <c r="AI19" s="0">
-        <v>0.063594866213666723</v>
+        <v>0.010900062704114921</v>
       </c>
       <c r="AJ19" s="0">
-        <v>0.064301359480121167</v>
+        <v>0.011021153706846198</v>
       </c>
       <c r="AK19" s="0">
-        <v>0.064822590458610718</v>
+        <v>0.011110491633479991</v>
       </c>
       <c r="AL19" s="0">
-        <v>0.06480623573094868</v>
+        <v>0.011107688775095659</v>
       </c>
       <c r="AM19" s="0">
-        <v>0.064033551347578821</v>
+        <v>0.01097525186520526</v>
       </c>
       <c r="AN19" s="0">
-        <v>0.062924375865055393</v>
+        <v>0.010785140492433842</v>
       </c>
       <c r="AO19" s="0">
-        <v>0.062221212457083112</v>
+        <v>0.010664619588045154</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="B20" s="0">
-        <v>0.1254070895445526</v>
+        <v>-0.41621274645544737</v>
       </c>
       <c r="C20" s="0">
-        <v>-0.005940866318235774</v>
+        <v>-0.0010182552034322945</v>
       </c>
       <c r="D20" s="0">
-        <v>-0.00052210796294517581</v>
+        <v>-8.9488705743212549e-05</v>
       </c>
       <c r="E20" s="0">
-        <v>-0.011217645657931166</v>
+        <v>-0.0019226865674850102</v>
       </c>
       <c r="F20" s="0">
-        <v>0.0047936319832520939</v>
+        <v>0.00082162139583535909</v>
       </c>
       <c r="G20" s="0">
-        <v>0.012300780327542877</v>
+        <v>0.0021083345921868446</v>
       </c>
       <c r="H20" s="0">
-        <v>0.0036018982593929265</v>
+        <v>0.00061735963957554318</v>
       </c>
       <c r="I20" s="0">
-        <v>-0.010632310666801495</v>
+        <v>-0.0018223614514897846</v>
       </c>
       <c r="J20" s="0">
-        <v>-0.061418031984663238</v>
+        <v>-0.010526956262020326</v>
       </c>
       <c r="K20" s="0">
-        <v>0.083506772794188819</v>
+        <v>0.014312931767435755</v>
       </c>
       <c r="L20" s="0">
-        <v>0.042098509327472042</v>
+        <v>0.0072156195699711323</v>
       </c>
       <c r="M20" s="0">
-        <v>0.021277843934306526</v>
+        <v>0.0036469901753863887</v>
       </c>
       <c r="N20" s="0">
-        <v>0.032427341011736263</v>
+        <v>0.0055272959174953451</v>
       </c>
       <c r="O20" s="0">
-        <v>0.041599468865491249</v>
+        <v>0.0068801002815780943</v>
       </c>
       <c r="P20" s="0">
-        <v>0.033459220219192877</v>
+        <v>0.0057348579255082077</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.022511239005692834</v>
+        <v>0.0038583912691222411</v>
       </c>
       <c r="R20" s="0">
-        <v>0.022582953036136093</v>
+        <v>0.003870683431851929</v>
       </c>
       <c r="S20" s="0">
-        <v>0.025075531682969145</v>
+        <v>0.0042979070955604937</v>
       </c>
       <c r="T20" s="0">
-        <v>0.054937600323355457</v>
+        <v>0.009416219797926062</v>
       </c>
       <c r="U20" s="0">
-        <v>0.041640307135442062</v>
+        <v>0.0071370838114025448</v>
       </c>
       <c r="V20" s="0">
-        <v>0.04443914270781632</v>
+        <v>0.0076168006866538795</v>
       </c>
       <c r="W20" s="0">
-        <v>0.055212886244188714</v>
+        <v>0.0094634036201390326</v>
       </c>
       <c r="X20" s="0">
-        <v>0.05618081009162032</v>
+        <v>0.0096293049911503892</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.054722622480382482</v>
+        <v>0.0093793734374276183</v>
       </c>
       <c r="Z20" s="0">
-        <v>0.051066943946999482</v>
+        <v>0.0087527949767569058</v>
       </c>
       <c r="AA20" s="0">
-        <v>0.052200109377753517</v>
+        <v>0.0089470186940189822</v>
       </c>
       <c r="AB20" s="0">
-        <v>0.052259366916191013</v>
+        <v>0.0089571742360450846</v>
       </c>
       <c r="AC20" s="0">
-        <v>0.050570034717299019</v>
+        <v>0.0086676262052247099</v>
       </c>
       <c r="AD20" s="0">
-        <v>0.051734782894280879</v>
+        <v>0.0088672629710788153</v>
       </c>
       <c r="AE20" s="0">
-        <v>0.053243420655319153</v>
+        <v>0.0091258398896630899</v>
       </c>
       <c r="AF20" s="0">
-        <v>0.054949081267275462</v>
+        <v>0.0094181878973640942</v>
       </c>
       <c r="AG20" s="0">
-        <v>0.054397351488425262</v>
+        <v>0.0093236225818386087</v>
       </c>
       <c r="AH20" s="0">
-        <v>0.051711484709427637</v>
+        <v>0.0088632684934372707</v>
       </c>
       <c r="AI20" s="0">
-        <v>0.050164603436464762</v>
+        <v>0.0085981352808932598</v>
       </c>
       <c r="AJ20" s="0">
-        <v>0.050690862890173528</v>
+        <v>0.008688335608071529</v>
       </c>
       <c r="AK20" s="0">
-        <v>0.051499939203650348</v>
+        <v>0.008827009899931737</v>
       </c>
       <c r="AL20" s="0">
-        <v>0.05210493309265183</v>
+        <v>0.0089307058826348928</v>
       </c>
       <c r="AM20" s="0">
-        <v>0.052116584423815705</v>
+        <v>0.008932702880712684</v>
       </c>
       <c r="AN20" s="0">
-        <v>0.051296686303533658</v>
+        <v>0.0087921726556920432</v>
       </c>
       <c r="AO20" s="0">
-        <v>0.050103899429395062</v>
+        <v>0.0085877317990998847</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>124</v>
+        <v>188</v>
       </c>
       <c r="B21" s="0">
-        <v>0.055486024490896124</v>
+        <v>-0.42588946850910375</v>
       </c>
       <c r="C21" s="0">
-        <v>-0.012702194956710565</v>
+        <v>-0.0021771368115430234</v>
       </c>
       <c r="D21" s="0">
-        <v>-0.005374146485249056</v>
+        <v>-0.00092112083035511549</v>
       </c>
       <c r="E21" s="0">
-        <v>0.013202308870674173</v>
+        <v>0.0022628552793705348</v>
       </c>
       <c r="F21" s="0">
-        <v>0.020226923364166066</v>
+        <v>0.0034668631564467312</v>
       </c>
       <c r="G21" s="0">
-        <v>0.0038681168096838768</v>
+        <v>0.00066298952371429687</v>
       </c>
       <c r="H21" s="0">
-        <v>-0.0014069022719457626</v>
+        <v>-0.00024114039056538639</v>
       </c>
       <c r="I21" s="0">
-        <v>-0.010746652435382781</v>
+        <v>-0.001841959405524729</v>
       </c>
       <c r="J21" s="0">
-        <v>-0.038672715018868625</v>
+        <v>-0.0066284440431901848</v>
       </c>
       <c r="K21" s="0">
-        <v>0.046242670608277768</v>
+        <v>0.0079259223537857526</v>
       </c>
       <c r="L21" s="0">
-        <v>0.032087587651180645</v>
+        <v>0.0054997634482404911</v>
       </c>
       <c r="M21" s="0">
-        <v>0.020549004741740769</v>
+        <v>0.0035220684294871574</v>
       </c>
       <c r="N21" s="0">
-        <v>0.028630609697237724</v>
+        <v>0.0049293807243475651</v>
       </c>
       <c r="O21" s="0">
-        <v>0.025809721325159334</v>
+        <v>0.004453077615495904</v>
       </c>
       <c r="P21" s="0">
-        <v>0.026436049586985248</v>
+        <v>0.0045310974686461059</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.018781204877395034</v>
+        <v>0.0032190702582109987</v>
       </c>
       <c r="R21" s="0">
-        <v>0.01942729112776248</v>
+        <v>0.0033298081724826289</v>
       </c>
       <c r="S21" s="0">
-        <v>0.018842827998864345</v>
+        <v>0.0032296308660102468</v>
       </c>
       <c r="T21" s="0">
-        <v>0.039848805662785751</v>
+        <v>0.0068300242860726557</v>
       </c>
       <c r="U21" s="0">
-        <v>0.036835474833846187</v>
+        <v>0.0063135431240617379</v>
       </c>
       <c r="V21" s="0">
-        <v>0.041295026842261828</v>
+        <v>0.0070779041470153126</v>
       </c>
       <c r="W21" s="0">
-        <v>0.04814682854892282</v>
+        <v>0.0082522916971833338</v>
       </c>
       <c r="X21" s="0">
-        <v>0.048803883237712661</v>
+        <v>0.0083649101772453882</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.048887690302795037</v>
+        <v>0.0083792743221403065</v>
       </c>
       <c r="Z21" s="0">
-        <v>0.043388268518008033</v>
+        <v>0.0074366821198623145</v>
       </c>
       <c r="AA21" s="0">
-        <v>0.04331547626229737</v>
+        <v>0.0074242063313184059</v>
       </c>
       <c r="AB21" s="0">
-        <v>0.044697988409070799</v>
+        <v>0.0076611656398231087</v>
       </c>
       <c r="AC21" s="0">
-        <v>0.044708888724039442</v>
+        <v>0.0076630347872742033</v>
       </c>
       <c r="AD21" s="0">
-        <v>0.043041105532341653</v>
+        <v>0.007377179481059315</v>
       </c>
       <c r="AE21" s="0">
-        <v>0.044448454850834609</v>
+        <v>0.0076183966904427303</v>
       </c>
       <c r="AF21" s="0">
-        <v>0.046217389546187489</v>
+        <v>0.0079215891980636277</v>
       </c>
       <c r="AG21" s="0">
-        <v>0.048201731843527273</v>
+        <v>0.0082617026450046427</v>
       </c>
       <c r="AH21" s="0">
-        <v>0.047693422755138881</v>
+        <v>0.0081745791380935517</v>
       </c>
       <c r="AI21" s="0">
-        <v>0.044825064135562545</v>
+        <v>0.0076829477417179604</v>
       </c>
       <c r="AJ21" s="0">
-        <v>0.043202834678336549</v>
+        <v>0.0074048998484819162</v>
       </c>
       <c r="AK21" s="0">
-        <v>0.043856471237945255</v>
+        <v>0.0075169314114821861</v>
       </c>
       <c r="AL21" s="0">
-        <v>0.044819082596581759</v>
+        <v>0.0076819220501992969</v>
       </c>
       <c r="AM21" s="0">
-        <v>0.045550537967718262</v>
+        <v>0.0078072914946468175</v>
       </c>
       <c r="AN21" s="0">
-        <v>0.045619038144155709</v>
+        <v>0.0078190320402959923</v>
       </c>
       <c r="AO21" s="0">
-        <v>0.04475649550826924</v>
+        <v>0.0076711944906110996</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="B22" s="0">
-        <v>0.032263302252500826</v>
+        <v>-0.42694590074749916</v>
       </c>
       <c r="C22" s="0">
-        <v>-0.0094274541427796996</v>
+        <v>-0.0016158510297062945</v>
       </c>
       <c r="D22" s="0">
-        <v>-0.0098165612929002263</v>
+        <v>-0.0016825434071647827</v>
       </c>
       <c r="E22" s="0">
-        <v>-0.0023487080085657017</v>
+        <v>-0.00040256541159894299</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.0086583804029078046</v>
+        <v>-0.0014840325395545917</v>
       </c>
       <c r="G22" s="0">
-        <v>-0.0054340259083950557</v>
+        <v>-0.00093138381649843227</v>
       </c>
       <c r="H22" s="0">
-        <v>-0.0065539401508452264</v>
+        <v>-0.0011233358497749202</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.013651670884479737</v>
+        <v>-0.002339875298202343</v>
       </c>
       <c r="J22" s="0">
-        <v>-0.035139292967922203</v>
+        <v>-0.0060228200470196502</v>
       </c>
       <c r="K22" s="0">
-        <v>0.024831739846267388</v>
+        <v>0.0042561215085720749</v>
       </c>
       <c r="L22" s="0">
-        <v>0.016870479800516897</v>
+        <v>0.0028915739760021486</v>
       </c>
       <c r="M22" s="0">
-        <v>0.012457460043845264</v>
+        <v>0.0021351891419389979</v>
       </c>
       <c r="N22" s="0">
-        <v>0.023562270899732257</v>
+        <v>0.0042621887045311002</v>
       </c>
       <c r="O22" s="0">
-        <v>0.022503835982026078</v>
+        <v>0.0038361138628514313</v>
       </c>
       <c r="P22" s="0">
-        <v>0.016627122488387248</v>
+        <v>0.0028498633955303387</v>
       </c>
       <c r="Q22" s="0">
-        <v>0.016294200651658847</v>
+        <v>0.0027928010174461115</v>
       </c>
       <c r="R22" s="0">
-        <v>0.016605395586983235</v>
+        <v>0.0028461385748112522</v>
       </c>
       <c r="S22" s="0">
-        <v>0.017333469709593902</v>
+        <v>0.0029709292333512383</v>
       </c>
       <c r="T22" s="0">
-        <v>0.033677227950180105</v>
+        <v>0.0057722247680171979</v>
       </c>
       <c r="U22" s="0">
-        <v>0.030801701882456869</v>
+        <v>0.0052793636879378547</v>
       </c>
       <c r="V22" s="0">
-        <v>0.043793562001004108</v>
+        <v>0.0075061494232930293</v>
       </c>
       <c r="W22" s="0">
-        <v>0.046527981823540857</v>
+        <v>0.007974824091466437</v>
       </c>
       <c r="X22" s="0">
-        <v>0.045534778306406579</v>
+        <v>0.0078045915556491097</v>
       </c>
       <c r="Y22" s="0">
-        <v>0.047016219145792973</v>
+        <v>0.0080585069048962343</v>
       </c>
       <c r="Z22" s="0">
-        <v>0.042204248431996397</v>
+        <v>0.0072337433732522771</v>
       </c>
       <c r="AA22" s="0">
-        <v>0.042186777917608567</v>
+        <v>0.0072307491930625467</v>
       </c>
       <c r="AB22" s="0">
-        <v>0.042399357228157977</v>
+        <v>0.0072671837535565054</v>
       </c>
       <c r="AC22" s="0">
-        <v>0.043862301147063312</v>
+        <v>0.0075179311184302988</v>
       </c>
       <c r="AD22" s="0">
-        <v>0.044074140935555131</v>
+        <v>0.0075542400298483914</v>
       </c>
       <c r="AE22" s="0">
-        <v>0.042516374851200488</v>
+        <v>0.0072872405782788974</v>
       </c>
       <c r="AF22" s="0">
-        <v>0.044270114989099794</v>
+        <v>0.0075878285504222265</v>
       </c>
       <c r="AG22" s="0">
-        <v>0.046403055946117225</v>
+        <v>0.0079534130778585732</v>
       </c>
       <c r="AH22" s="0">
-        <v>0.048769230289979773</v>
+        <v>0.0083589710079793877</v>
       </c>
       <c r="AI22" s="0">
-        <v>0.048383908285399804</v>
+        <v>0.0082929274711216472</v>
       </c>
       <c r="AJ22" s="0">
-        <v>0.045371764879791519</v>
+        <v>0.0077766504888135968</v>
       </c>
       <c r="AK22" s="0">
-        <v>0.043712146312225052</v>
+        <v>0.0074921942413934683</v>
       </c>
       <c r="AL22" s="0">
-        <v>0.044559517923885426</v>
+        <v>0.0076374329805304342</v>
       </c>
       <c r="AM22" s="0">
-        <v>0.045740860162084528</v>
+        <v>0.0078399125899761279</v>
       </c>
       <c r="AN22" s="0">
-        <v>0.046658586496614106</v>
+        <v>0.0079972097550333743</v>
       </c>
       <c r="AO22" s="0">
-        <v>0.046827914600688213</v>
+        <v>0.0080262326607979939</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="B23" s="0">
-        <v>-0.024362696747206626</v>
+        <v>-0.43186423374720662</v>
       </c>
       <c r="C23" s="0">
-        <v>-0.019744143023249595</v>
+        <v>-0.0033841156803448014</v>
       </c>
       <c r="D23" s="0">
-        <v>-0.01569452269410563</v>
+        <v>-0.0026900165759548567</v>
       </c>
       <c r="E23" s="0">
-        <v>-0.013803534801163177</v>
+        <v>-0.0023659047497256447</v>
       </c>
       <c r="F23" s="0">
-        <v>-0.0056008504068616807</v>
+        <v>-0.00095997716555379364</v>
       </c>
       <c r="G23" s="0">
-        <v>-0.011072434743251078</v>
+        <v>-0.0018977982624895917</v>
       </c>
       <c r="H23" s="0">
-        <v>-0.011630240244701981</v>
+        <v>-0.0019934053918534422</v>
       </c>
       <c r="I23" s="0">
-        <v>-0.015827651241563198</v>
+        <v>-0.0027128351941650419</v>
       </c>
       <c r="J23" s="0">
-        <v>-0.033107274515216153</v>
+        <v>-0.005674536037423461</v>
       </c>
       <c r="K23" s="0">
-        <v>0.016949583156538345</v>
+        <v>0.0029051316364292479</v>
       </c>
       <c r="L23" s="0">
-        <v>0.011694021451363851</v>
+        <v>0.0020043375248539053</v>
       </c>
       <c r="M23" s="0">
-        <v>0.006607035523197146</v>
+        <v>0.00113243614157299</v>
       </c>
       <c r="N23" s="0">
-        <v>0.01617913267404409</v>
+        <v>0.0028077802053609324</v>
       </c>
       <c r="O23" s="0">
-        <v>0.01992699047998376</v>
+        <v>0.0032055652816473379</v>
       </c>
       <c r="P23" s="0">
-        <v>0.011600062759427779</v>
+        <v>0.0019882329836743984</v>
       </c>
       <c r="Q23" s="0">
-        <v>0.011348239910148179</v>
+        <v>0.0019450706125934136</v>
       </c>
       <c r="R23" s="0">
-        <v>0.017647398240613069</v>
+        <v>0.003024737278263856</v>
       </c>
       <c r="S23" s="0">
-        <v>0.020410556529964433</v>
+        <v>0.0034983379905950684</v>
       </c>
       <c r="T23" s="0">
-        <v>0.034731058335620353</v>
+        <v>0.0059528505514463426</v>
       </c>
       <c r="U23" s="0">
-        <v>0.027111581932348923</v>
+        <v>0.0046468839304850129</v>
       </c>
       <c r="V23" s="0">
-        <v>0.037972505161053161</v>
+        <v>0.0065084289184287325</v>
       </c>
       <c r="W23" s="0">
-        <v>0.052949745292688963</v>
+        <v>0.009075504950748714</v>
       </c>
       <c r="X23" s="0">
-        <v>0.047259414959930954</v>
+        <v>0.0081001908211786877</v>
       </c>
       <c r="Y23" s="0">
-        <v>0.049825874889601149</v>
+        <v>0.0085400779473638333</v>
       </c>
       <c r="Z23" s="0">
-        <v>0.047764659474170676</v>
+        <v>0.0081867892489994043</v>
       </c>
       <c r="AA23" s="0">
-        <v>0.050331475063538342</v>
+        <v>0.0086267370885192429</v>
       </c>
       <c r="AB23" s="0">
-        <v>0.049972656292513504</v>
+        <v>0.0085652357514767186</v>
       </c>
       <c r="AC23" s="0">
-        <v>0.050367205191953632</v>
+        <v>0.0086328617348296333</v>
       </c>
       <c r="AD23" s="0">
-        <v>0.052324027316411989</v>
+        <v>0.008968257422863557</v>
       </c>
       <c r="AE23" s="0">
-        <v>0.052839647456881675</v>
+        <v>0.0090566341861387789</v>
       </c>
       <c r="AF23" s="0">
-        <v>0.051284703227158661</v>
+        <v>0.0087901197907951367</v>
       </c>
       <c r="AG23" s="0">
-        <v>0.053524444794866108</v>
+        <v>0.0091740072294510533</v>
       </c>
       <c r="AH23" s="0">
-        <v>0.056196092357453084</v>
+        <v>0.0096319237014751979</v>
       </c>
       <c r="AI23" s="0">
-        <v>0.059140392258269989</v>
+        <v>0.01013657199286333</v>
       </c>
       <c r="AJ23" s="0">
-        <v>0.058861085693118806</v>
+        <v>0.010088699144180591</v>
       </c>
       <c r="AK23" s="0">
-        <v>0.055482472390448616</v>
+        <v>0.0095096103640835428</v>
       </c>
       <c r="AL23" s="0">
-        <v>0.053666018053928059</v>
+        <v>0.0091982724065090005</v>
       </c>
       <c r="AM23" s="0">
-        <v>0.05478128979802404</v>
+        <v>0.009389428526088206</v>
       </c>
       <c r="AN23" s="0">
-        <v>0.056281623903386695</v>
+        <v>0.0096465837151198386</v>
       </c>
       <c r="AO23" s="0">
-        <v>0.057466221853147696</v>
+        <v>0.009849621597009306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="B24" s="0">
-        <v>-0.077681981575542222</v>
+        <v>-0.43453364957554208</v>
       </c>
       <c r="C24" s="0">
-        <v>-0.023277271395060518</v>
+        <v>-0.0039896875859208869</v>
       </c>
       <c r="D24" s="0">
-        <v>-0.024987170380011459</v>
+        <v>-0.0042827626031000654</v>
       </c>
       <c r="E24" s="0">
-        <v>-0.0022380335949466045</v>
+        <v>-0.00038359605392562779</v>
       </c>
       <c r="F24" s="0">
-        <v>-0.0037747671715644814</v>
+        <v>-0.00064698912686156351</v>
       </c>
       <c r="G24" s="0">
-        <v>-0.018837995105936915</v>
+        <v>-0.0032288024616695665</v>
       </c>
       <c r="H24" s="0">
-        <v>-0.018099542588297483</v>
+        <v>-0.0031022341913188867</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.023618017476338342</v>
+        <v>-0.0040480917959517804</v>
       </c>
       <c r="J24" s="0">
-        <v>-0.036927158134320508</v>
+        <v>-0.0063292574426357939</v>
       </c>
       <c r="K24" s="0">
-        <v>0.0070655651094995806</v>
+        <v>0.0012110271545461293</v>
       </c>
       <c r="L24" s="0">
-        <v>0.0037115214991422867</v>
+        <v>0.00063614930816757731</v>
       </c>
       <c r="M24" s="0">
-        <v>0.00046446070404588478</v>
+        <v>7.9607643794665783e-05</v>
       </c>
       <c r="N24" s="0">
-        <v>0.008153893590336303</v>
+        <v>0.001411504990820156</v>
       </c>
       <c r="O24" s="0">
-        <v>0.0092240250353885986</v>
+        <v>0.0015489098613225005</v>
       </c>
       <c r="P24" s="0">
-        <v>0.0069506092481375547</v>
+        <v>0.0011913240920088386</v>
       </c>
       <c r="Q24" s="0">
-        <v>0.0082444176885351841</v>
+        <v>0.0014130798413484191</v>
       </c>
       <c r="R24" s="0">
-        <v>0.012443883907405643</v>
+        <v>0.0021328620018644662</v>
       </c>
       <c r="S24" s="0">
-        <v>0.017292850567156171</v>
+        <v>0.0029639677658923058</v>
       </c>
       <c r="T24" s="0">
-        <v>0.031521434602123026</v>
+        <v>0.0054027259649738757</v>
       </c>
       <c r="U24" s="0">
-        <v>0.027082537533778699</v>
+        <v>0.0046419048655264028</v>
       </c>
       <c r="V24" s="0">
-        <v>0.032384978759609821</v>
+        <v>0.0055507355669827674</v>
       </c>
       <c r="W24" s="0">
-        <v>0.04167849861624888</v>
+        <v>0.007143630232815501</v>
       </c>
       <c r="X24" s="0">
-        <v>0.046740050040789197</v>
+        <v>0.0080111728326868192</v>
       </c>
       <c r="Y24" s="0">
-        <v>0.051460424840708799</v>
+        <v>0.0088202374093412916</v>
       </c>
       <c r="Z24" s="0">
-        <v>0.051460490801871331</v>
+        <v>0.0088202483940802434</v>
       </c>
       <c r="AA24" s="0">
-        <v>0.056738231769675532</v>
+        <v>0.0097248453446240335</v>
       </c>
       <c r="AB24" s="0">
-        <v>0.05953193706251704</v>
+        <v>0.010203681987923652</v>
       </c>
       <c r="AC24" s="0">
-        <v>0.059285298673382406</v>
+        <v>0.010161409543672728</v>
       </c>
       <c r="AD24" s="0">
-        <v>0.060157936055520132</v>
+        <v>0.010310977076644356</v>
       </c>
       <c r="AE24" s="0">
-        <v>0.062814644599019989</v>
+        <v>0.010766333003503104</v>
       </c>
       <c r="AF24" s="0">
-        <v>0.063767816462993912</v>
+        <v>0.010929705159211267</v>
       </c>
       <c r="AG24" s="0">
-        <v>0.062263152718157112</v>
+        <v>0.010671807473866646</v>
       </c>
       <c r="AH24" s="0">
-        <v>0.06518058966948205</v>
+        <v>0.011171853088248307</v>
       </c>
       <c r="AI24" s="0">
-        <v>0.068591157893913249</v>
+        <v>0.011756418409458846</v>
       </c>
       <c r="AJ24" s="0">
-        <v>0.072326527671071963</v>
+        <v>0.01239665506693588</v>
       </c>
       <c r="AK24" s="0">
-        <v>0.072218810292072347</v>
+        <v>0.012378192847108116</v>
       </c>
       <c r="AL24" s="0">
-        <v>0.06839029681186129</v>
+        <v>0.011721991345939875</v>
       </c>
       <c r="AM24" s="0">
-        <v>0.066397676469754946</v>
+        <v>0.011380459529961084</v>
       </c>
       <c r="AN24" s="0">
-        <v>0.067891885063147611</v>
+        <v>0.011636564423786466</v>
       </c>
       <c r="AO24" s="0">
-        <v>0.069838963181413943</v>
+        <v>0.011970290449473564</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="B25" s="0">
-        <v>-0.15514258183260632</v>
+        <v>-0.43970127483260618</v>
       </c>
       <c r="C25" s="0">
-        <v>-0.037199091661566021</v>
+        <v>-0.0063758676898219568</v>
       </c>
       <c r="D25" s="0">
-        <v>-0.036004194110941669</v>
+        <v>-0.0061710640190068555</v>
       </c>
       <c r="E25" s="0">
-        <v>-0.034009631774868689</v>
+        <v>-0.0058291983293127791</v>
       </c>
       <c r="F25" s="0">
-        <v>-0.038667025253932216</v>
+        <v>-0.0066274685582406456</v>
       </c>
       <c r="G25" s="0">
-        <v>-0.033762485938915718</v>
+        <v>-0.0057868386414476336</v>
       </c>
       <c r="H25" s="0">
-        <v>-0.031649879133818677</v>
+        <v>-0.0054247404128997534</v>
       </c>
       <c r="I25" s="0">
-        <v>-0.034137274010349945</v>
+        <v>-0.0058510761677140755</v>
       </c>
       <c r="J25" s="0">
-        <v>-0.043899557951590965</v>
+        <v>-0.0075243162516370199</v>
       </c>
       <c r="K25" s="0">
-        <v>-0.01053782068555531</v>
+        <v>-0.0018061664178034009</v>
       </c>
       <c r="L25" s="0">
-        <v>-0.0087434888843435209</v>
+        <v>-0.0014986210250522158</v>
       </c>
       <c r="M25" s="0">
-        <v>-0.010566105072038159</v>
+        <v>-0.0018110144189971145</v>
       </c>
       <c r="N25" s="0">
-        <v>-0.003038141583887672</v>
+        <v>-0.00039871123572216005</v>
       </c>
       <c r="O25" s="0">
-        <v>-0.0023588494353154938</v>
+        <v>-0.0004169399257831774</v>
       </c>
       <c r="P25" s="0">
-        <v>-0.0050283536279328639</v>
+        <v>-0.00086185229710411537</v>
       </c>
       <c r="Q25" s="0">
-        <v>0.0011611979587262615</v>
+        <v>0.00019902679164651715</v>
       </c>
       <c r="R25" s="0">
-        <v>0.0039062506038237974</v>
+        <v>0.0006695258654779157</v>
       </c>
       <c r="S25" s="0">
-        <v>0.011517652170845801</v>
+        <v>0.0019741082074348215</v>
       </c>
       <c r="T25" s="0">
-        <v>0.02702467375796799</v>
+        <v>0.0046319874425747587</v>
       </c>
       <c r="U25" s="0">
-        <v>0.022682313452199031</v>
+        <v>0.003887713668687176</v>
       </c>
       <c r="V25" s="0">
-        <v>0.031198898782944989</v>
+        <v>0.005347442750442688</v>
       </c>
       <c r="W25" s="0">
-        <v>0.034877454123141451</v>
+        <v>0.005977941664917219</v>
       </c>
       <c r="X25" s="0">
-        <v>0.036961729073535843</v>
+        <v>0.0063351836232259373</v>
       </c>
       <c r="Y25" s="0">
-        <v>0.054339186864002277</v>
+        <v>0.0093136522289993806</v>
       </c>
       <c r="Z25" s="0">
-        <v>0.052703664240623428</v>
+        <v>0.0090333272390577535</v>
       </c>
       <c r="AA25" s="0">
-        <v>0.057869015600664347</v>
+        <v>0.0099186602729033346</v>
       </c>
       <c r="AB25" s="0">
-        <v>0.063396858649342386</v>
+        <v>0.010866123970660946</v>
       </c>
       <c r="AC25" s="0">
-        <v>0.066801046139085857</v>
+        <v>0.011449596331568612</v>
       </c>
       <c r="AD25" s="0">
-        <v>0.067031310904129698</v>
+        <v>0.011489062534020433</v>
       </c>
       <c r="AE25" s="0">
-        <v>0.068527730407746498</v>
+        <v>0.011745548026708741</v>
       </c>
       <c r="AF25" s="0">
-        <v>0.072040010733636389</v>
+        <v>0.012347547731156094</v>
       </c>
       <c r="AG25" s="0">
-        <v>0.073528539983840888</v>
+        <v>0.012602678632187003</v>
       </c>
       <c r="AH25" s="0">
-        <v>0.072081871265615161</v>
+        <v>0.012354722497741166</v>
       </c>
       <c r="AI25" s="0">
-        <v>0.075831399120298779</v>
+        <v>0.012997384728283323</v>
       </c>
       <c r="AJ25" s="0">
-        <v>0.080163584725834708</v>
+        <v>0.013739914487686133</v>
       </c>
       <c r="AK25" s="0">
-        <v>0.084886327220696195</v>
+        <v>0.014549385902648149</v>
       </c>
       <c r="AL25" s="0">
-        <v>0.085005657725291867</v>
+        <v>0.014569838901951571</v>
       </c>
       <c r="AM25" s="0">
-        <v>0.080633336811407608</v>
+        <v>0.013820429111233656</v>
       </c>
       <c r="AN25" s="0">
-        <v>0.078429760642341431</v>
+        <v>0.013442740464457592</v>
       </c>
       <c r="AO25" s="0">
-        <v>0.080404472206152766</v>
+        <v>0.013781202003333104</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="B26" s="0">
-        <v>-0.2336411048282977</v>
+        <v>-0.44432319982829754</v>
       </c>
       <c r="C26" s="0">
-        <v>-0.052037642757123061</v>
+        <v>-0.0089191718227017991</v>
       </c>
       <c r="D26" s="0">
-        <v>-0.052427197860636578</v>
+        <v>-0.0089859406601919267</v>
       </c>
       <c r="E26" s="0">
-        <v>-0.04610783792466764</v>
+        <v>-0.0079028123932760042</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.042071983317046681</v>
+        <v>-0.007211072690439857</v>
       </c>
       <c r="G26" s="0">
-        <v>-0.046706357299421457</v>
+        <v>-0.0080053977011733668</v>
       </c>
       <c r="H26" s="0">
-        <v>-0.048835170295939805</v>
+        <v>-0.0083702726837856511</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.050145710164612882</v>
+        <v>-0.0085948976980118053</v>
       </c>
       <c r="J26" s="0">
-        <v>-0.057982793637873002</v>
+        <v>-0.009938161251024924</v>
       </c>
       <c r="K26" s="0">
-        <v>-0.034758791616538838</v>
+        <v>-0.0059576037610547528</v>
       </c>
       <c r="L26" s="0">
-        <v>-0.030807569915452259</v>
+        <v>-0.0052803698205134975</v>
       </c>
       <c r="M26" s="0">
-        <v>-0.029071464908344179</v>
+        <v>-0.0049828036984713164</v>
       </c>
       <c r="N26" s="0">
-        <v>-0.020415995927386087</v>
+        <v>-0.0034620681293324185</v>
       </c>
       <c r="O26" s="0">
-        <v>-0.016114372976254867</v>
+        <v>-0.0028702230690704766</v>
       </c>
       <c r="P26" s="0">
-        <v>-0.024037370796022736</v>
+        <v>-0.0041199681101561914</v>
       </c>
       <c r="Q26" s="0">
-        <v>-0.016994802059183634</v>
+        <v>-0.0029128822978613522</v>
       </c>
       <c r="R26" s="0">
-        <v>-0.0089083952660904964</v>
+        <v>-0.0015268848000998814</v>
       </c>
       <c r="S26" s="0">
-        <v>-0.0031001449426676072</v>
+        <v>-0.00053136067119646802</v>
       </c>
       <c r="T26" s="0">
-        <v>0.012822225808479715</v>
+        <v>0.0021977099506973463</v>
       </c>
       <c r="U26" s="0">
-        <v>0.014650831894722638</v>
+        <v>0.0025111301248560425</v>
       </c>
       <c r="V26" s="0">
-        <v>0.022492956868268608</v>
+        <v>0.0038552578780133295</v>
       </c>
       <c r="W26" s="0">
-        <v>0.030610684006430446</v>
+        <v>0.0052466241403223424</v>
       </c>
       <c r="X26" s="0">
-        <v>0.029085253769752503</v>
+        <v>0.0049851676884396512</v>
       </c>
       <c r="Y26" s="0">
-        <v>0.040013025466748578</v>
+        <v>0.0068581708188279467</v>
       </c>
       <c r="Z26" s="0">
-        <v>0.048993111566340293</v>
+        <v>0.0083973440458843251</v>
       </c>
       <c r="AA26" s="0">
-        <v>0.051938305422385485</v>
+        <v>0.008902145229039482</v>
       </c>
       <c r="AB26" s="0">
-        <v>0.057929186365457908</v>
+        <v>0.009928973248487849</v>
       </c>
       <c r="AC26" s="0">
-        <v>0.06474730059103477</v>
+        <v>0.011097587087871064</v>
       </c>
       <c r="AD26" s="0">
-        <v>0.069432461292525824</v>
+        <v>0.011900617350078468</v>
       </c>
       <c r="AE26" s="0">
-        <v>0.070506815802488021</v>
+        <v>0.012084760407702677</v>
       </c>
       <c r="AF26" s="0">
-        <v>0.073059685358416837</v>
+        <v>0.012522317028648089</v>
       </c>
       <c r="AG26" s="0">
-        <v>0.077627298958828972</v>
+        <v>0.013305199120177857</v>
       </c>
       <c r="AH26" s="0">
-        <v>0.079937592374988597</v>
+        <v>0.013701180474859076</v>
       </c>
       <c r="AI26" s="0">
-        <v>0.078913323318595643</v>
+        <v>0.013525621589272396</v>
       </c>
       <c r="AJ26" s="0">
-        <v>0.083707308737051955</v>
+        <v>0.014347304146918927</v>
       </c>
       <c r="AK26" s="0">
-        <v>0.089127787434477634</v>
+        <v>0.015276365375035683</v>
       </c>
       <c r="AL26" s="0">
-        <v>0.095003213782684545</v>
+        <v>0.016283404326733586</v>
       </c>
       <c r="AM26" s="0">
-        <v>0.095569887732861181</v>
+        <v>0.016380530662771398</v>
       </c>
       <c r="AN26" s="0">
-        <v>0.090922408542367827</v>
+        <v>0.015583960723146162</v>
       </c>
       <c r="AO26" s="0">
-        <v>0.088734932072262102</v>
+        <v>0.015209029958383524</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B27" s="0">
-        <v>-0.32390276212599578</v>
+        <v>-0.45080115812599564</v>
       </c>
       <c r="C27" s="0">
-        <v>-0.063095807121780478</v>
+        <v>-0.010814523556398503</v>
       </c>
       <c r="D27" s="0">
-        <v>-0.063344097033946584</v>
+        <v>-0.010857080440751732</v>
       </c>
       <c r="E27" s="0">
-        <v>-0.06197778369510832</v>
+        <v>-0.010622896349736899</v>
       </c>
       <c r="F27" s="0">
-        <v>-0.060500490711444178</v>
+        <v>-0.010369690772010831</v>
       </c>
       <c r="G27" s="0">
-        <v>-0.06122486555626392</v>
+        <v>-0.010493848240901715</v>
       </c>
       <c r="H27" s="0">
-        <v>-0.061354425011505405</v>
+        <v>-0.01051605392531435</v>
       </c>
       <c r="I27" s="0">
-        <v>-0.062601565455874586</v>
+        <v>-0.010729811914701681</v>
       </c>
       <c r="J27" s="0">
-        <v>-0.071900696615017939</v>
+        <v>-0.01232366827032072</v>
       </c>
       <c r="K27" s="0">
-        <v>-0.056389295960481069</v>
+        <v>-0.0096650383116729799</v>
       </c>
       <c r="L27" s="0">
-        <v>-0.053519630792141344</v>
+        <v>-0.0091731817992883879</v>
       </c>
       <c r="M27" s="0">
-        <v>-0.052387330617470425</v>
+        <v>-0.0089791077167225564</v>
       </c>
       <c r="N27" s="0">
-        <v>-0.044351996998709238</v>
+        <v>-0.0075955747671396789</v>
       </c>
       <c r="O27" s="0">
-        <v>-0.039156312930785607</v>
+        <v>-0.0067435992439810466</v>
       </c>
       <c r="P27" s="0">
-        <v>-0.043064026664249654</v>
+        <v>-0.0073811079556000414</v>
       </c>
       <c r="Q27" s="0">
-        <v>-0.043426805538880002</v>
+        <v>-0.0074432871812877832</v>
       </c>
       <c r="R27" s="0">
-        <v>-0.03718968583125825</v>
+        <v>-0.0063742556528392225</v>
       </c>
       <c r="S27" s="0">
-        <v>-0.027270322534959875</v>
+        <v>-0.0046740909507276829</v>
       </c>
       <c r="T27" s="0">
-        <v>-0.0093583961450494982</v>
+        <v>-0.0016040147092895585</v>
       </c>
       <c r="U27" s="0">
-        <v>-0.0031568683343509494</v>
+        <v>-0.00054108289038434787</v>
       </c>
       <c r="V27" s="0">
-        <v>0.0012758384819101709</v>
+        <v>0.00021867616254056532</v>
       </c>
       <c r="W27" s="0">
-        <v>0.012176445807687631</v>
+        <v>0.0020870234480727667</v>
       </c>
       <c r="X27" s="0">
-        <v>0.015351071580688288</v>
+        <v>0.0026311498236422093</v>
       </c>
       <c r="Y27" s="0">
-        <v>0.022716677505166288</v>
+        <v>0.0038936033698730443</v>
       </c>
       <c r="Z27" s="0">
-        <v>0.027638269636964242</v>
+        <v>0.0047371573278166546</v>
       </c>
       <c r="AA27" s="0">
-        <v>0.038452279376099886</v>
+        <v>0.0065906617403683754</v>
       </c>
       <c r="AB27" s="0">
-        <v>0.041301010444640664</v>
+        <v>0.0070789298364085651</v>
       </c>
       <c r="AC27" s="0">
-        <v>0.047963998753606824</v>
+        <v>0.0082209552114190787</v>
       </c>
       <c r="AD27" s="0">
-        <v>0.056287149449450694</v>
+        <v>0.009647531074789828</v>
       </c>
       <c r="AE27" s="0">
-        <v>0.062829846873620823</v>
+        <v>0.010768938692989394</v>
       </c>
       <c r="AF27" s="0">
-        <v>0.065683415624833069</v>
+        <v>0.011258035730625782</v>
       </c>
       <c r="AG27" s="0">
-        <v>0.070191718917387874</v>
+        <v>0.012030752715628146</v>
       </c>
       <c r="AH27" s="0">
-        <v>0.076195088760901114</v>
+        <v>0.013059721051611572</v>
       </c>
       <c r="AI27" s="0">
-        <v>0.079951042190502447</v>
+        <v>0.013703484722477788</v>
       </c>
       <c r="AJ27" s="0">
-        <v>0.080218701882241158</v>
+        <v>0.013749362159758194</v>
       </c>
       <c r="AK27" s="0">
-        <v>0.086397575908968266</v>
+        <v>0.014808411198811433</v>
       </c>
       <c r="AL27" s="0">
-        <v>0.093151961142697096</v>
+        <v>0.015966102534545945</v>
       </c>
       <c r="AM27" s="0">
-        <v>0.10040439131758705</v>
+        <v>0.017209158172735384</v>
       </c>
       <c r="AN27" s="0">
-        <v>0.10193129163395233</v>
+        <v>0.017470866592903589</v>
       </c>
       <c r="AO27" s="0">
-        <v>0.097765396936698418</v>
+        <v>0.016756838613557923</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="B28" s="0">
-        <v>-0.39596462147111655</v>
+        <v>-0.45590615247111643</v>
       </c>
       <c r="C28" s="0">
-        <v>-0.057882462110618427</v>
+        <v>-0.0099209637664135486</v>
       </c>
       <c r="D28" s="0">
-        <v>-0.058502182241174386</v>
+        <v>-0.010027184265056333</v>
       </c>
       <c r="E28" s="0">
-        <v>-0.055487365748173006</v>
+        <v>-0.0095104487568517526</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.058398778806590002</v>
+        <v>-0.010009460798887593</v>
       </c>
       <c r="G28" s="0">
-        <v>-0.061221379632603518</v>
+        <v>-0.0104932502343138</v>
       </c>
       <c r="H28" s="0">
-        <v>-0.063109714086543131</v>
+        <v>-0.010816907272367504</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.061028222051366959</v>
+        <v>-0.01046014326446415</v>
       </c>
       <c r="J28" s="0">
-        <v>-0.071770928129587075</v>
+        <v>-0.012301426696862183</v>
       </c>
       <c r="K28" s="0">
-        <v>-0.066770445994011357</v>
+        <v>-0.011444351400615393</v>
       </c>
       <c r="L28" s="0">
-        <v>-0.060416401237069629</v>
+        <v>-0.01035527792577895</v>
       </c>
       <c r="M28" s="0">
-        <v>-0.067543286206199593</v>
+        <v>-0.011576815572165833</v>
       </c>
       <c r="N28" s="0">
-        <v>-0.06225581591546115</v>
+        <v>-0.010672468930250867</v>
       </c>
       <c r="O28" s="0">
-        <v>-0.061660531178651536</v>
+        <v>-0.0105738752977666</v>
       </c>
       <c r="P28" s="0">
-        <v>-0.06225914164963512</v>
+        <v>-0.010671120281660118</v>
       </c>
       <c r="Q28" s="0">
-        <v>-0.061028771065346439</v>
+        <v>-0.010460237537501804</v>
       </c>
       <c r="R28" s="0">
-        <v>-0.063646586060022242</v>
+        <v>-0.010908927432271953</v>
       </c>
       <c r="S28" s="0">
-        <v>-0.062268018798588183</v>
+        <v>-0.010672641921057768</v>
       </c>
       <c r="T28" s="0">
-        <v>-0.047715992430325822</v>
+        <v>-0.0081784478441498942</v>
       </c>
       <c r="U28" s="0">
-        <v>-0.035240744956108051</v>
+        <v>-0.0060402095113846199</v>
       </c>
       <c r="V28" s="0">
-        <v>-0.02637649165141203</v>
+        <v>-0.0045208900925547968</v>
       </c>
       <c r="W28" s="0">
-        <v>-0.025943043178616034</v>
+        <v>-0.0044465974708758904</v>
       </c>
       <c r="X28" s="0">
-        <v>-0.021897463176828762</v>
+        <v>-0.003753191169581227</v>
       </c>
       <c r="Y28" s="0">
-        <v>-0.0099024715330879691</v>
+        <v>-0.0016972675428011397</v>
       </c>
       <c r="Z28" s="0">
-        <v>-0.0045045624943921515</v>
+        <v>-0.00077207473586099473</v>
       </c>
       <c r="AA28" s="0">
-        <v>0.0018896324776877553</v>
+        <v>0.00032387952998669256</v>
       </c>
       <c r="AB28" s="0">
-        <v>0.004365570282718125</v>
+        <v>0.00074825164569980451</v>
       </c>
       <c r="AC28" s="0">
-        <v>0.0073417494248764334</v>
+        <v>0.0012583640483083691</v>
       </c>
       <c r="AD28" s="0">
-        <v>0.015324723570639296</v>
+        <v>0.0026266339413092421</v>
       </c>
       <c r="AE28" s="0">
-        <v>0.02535724480421463</v>
+        <v>0.0043461923473238073</v>
       </c>
       <c r="AF28" s="0">
-        <v>0.034700380701019759</v>
+        <v>0.0059475920776617675</v>
       </c>
       <c r="AG28" s="0">
-        <v>0.041054146586258715</v>
+        <v>0.0070366175217523308</v>
       </c>
       <c r="AH28" s="0">
-        <v>0.049024125988949674</v>
+        <v>0.0084026591350254143</v>
       </c>
       <c r="AI28" s="0">
-        <v>0.057071189215417754</v>
+        <v>0.0097819133303556072</v>
       </c>
       <c r="AJ28" s="0">
-        <v>0.063365854611260194</v>
+        <v>0.010860809608097877</v>
       </c>
       <c r="AK28" s="0">
-        <v>0.066576855081793007</v>
+        <v>0.011411169734456106</v>
       </c>
       <c r="AL28" s="0">
-        <v>0.074603815196173984</v>
+        <v>0.012786979053269365</v>
       </c>
       <c r="AM28" s="0">
-        <v>0.082989221957588052</v>
+        <v>0.01422422517567129</v>
       </c>
       <c r="AN28" s="0">
-        <v>0.091877474542847754</v>
+        <v>0.015747657463394182</v>
       </c>
       <c r="AO28" s="0">
-        <v>0.09534078845253588</v>
+        <v>0.016341264040691139</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="B29" s="0">
-        <v>-0.43927762026361944</v>
+        <v>-0.45778815226361919</v>
       </c>
       <c r="C29" s="0">
-        <v>-0.038499867934799592</v>
+        <v>-0.0065988184161977492</v>
       </c>
       <c r="D29" s="0">
-        <v>-0.03781505726028124</v>
+        <v>-0.0064814432147647372</v>
       </c>
       <c r="E29" s="0">
-        <v>-0.039469267793152393</v>
+        <v>-0.0067649716799555448</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.039513880288648877</v>
+        <v>-0.0067726186482217621</v>
       </c>
       <c r="G29" s="0">
-        <v>-0.040716593697025689</v>
+        <v>-0.0069787612750279449</v>
       </c>
       <c r="H29" s="0">
-        <v>-0.042923862445277107</v>
+        <v>-0.0073570833678180958</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.043042427504489562</v>
+        <v>-0.0073774060306054934</v>
       </c>
       <c r="J29" s="0">
-        <v>-0.047896689435817832</v>
+        <v>-0.0082094188722860451</v>
       </c>
       <c r="K29" s="0">
-        <v>-0.047944276159499699</v>
+        <v>-0.0082175745207442863</v>
       </c>
       <c r="L29" s="0">
-        <v>-0.046782231883812295</v>
+        <v>-0.0080184027667799529</v>
       </c>
       <c r="M29" s="0">
-        <v>-0.052025480713557004</v>
+        <v>-0.0089170873919991456</v>
       </c>
       <c r="N29" s="0">
-        <v>-0.056941446745514747</v>
+        <v>-0.0098079867358946138</v>
       </c>
       <c r="O29" s="0">
-        <v>-0.060921105529923726</v>
+        <v>-0.010440173751234905</v>
       </c>
       <c r="P29" s="0">
-        <v>-0.063235788810306268</v>
+        <v>-0.010838516538798249</v>
       </c>
       <c r="Q29" s="0">
-        <v>-0.065094723991020301</v>
+        <v>-0.011157136044247895</v>
       </c>
       <c r="R29" s="0">
-        <v>-0.066605600103884041</v>
+        <v>-0.011416096610626869</v>
       </c>
       <c r="S29" s="0">
-        <v>-0.075158659017573154</v>
+        <v>-0.012882077488217791</v>
       </c>
       <c r="T29" s="0">
-        <v>-0.072324230884668841</v>
+        <v>-0.0123962619545116</v>
       </c>
       <c r="U29" s="0">
-        <v>-0.07101206949010104</v>
+        <v>-0.012171359244544044</v>
       </c>
       <c r="V29" s="0">
-        <v>-0.060751002163581862</v>
+        <v>-0.010412627812995123</v>
       </c>
       <c r="W29" s="0">
-        <v>-0.052671560158189815</v>
+        <v>-0.0090278243016717052</v>
       </c>
       <c r="X29" s="0">
-        <v>-0.068937490322132006</v>
+        <v>-0.011815779397702952</v>
       </c>
       <c r="Y29" s="0">
-        <v>-0.061465805543283208</v>
+        <v>-0.010535144063148871</v>
       </c>
       <c r="Z29" s="0">
-        <v>-0.055290691710082628</v>
+        <v>-0.0094767399484810833</v>
       </c>
       <c r="AA29" s="0">
-        <v>-0.04480996407216245</v>
+        <v>-0.0076803590380409292</v>
       </c>
       <c r="AB29" s="0">
-        <v>-0.044386436561787687</v>
+        <v>-0.0076077665300977593</v>
       </c>
       <c r="AC29" s="0">
-        <v>-0.057069717185191375</v>
+        <v>-0.0097816613562425325</v>
       </c>
       <c r="AD29" s="0">
-        <v>-0.0540378972880231</v>
+        <v>-0.0092620124019232586</v>
       </c>
       <c r="AE29" s="0">
-        <v>-0.046904188690595414</v>
+        <v>-0.008039305034049371</v>
       </c>
       <c r="AF29" s="0">
-        <v>-0.038415503548994263</v>
+        <v>-0.0065843582995107064</v>
       </c>
       <c r="AG29" s="0">
-        <v>-0.028105353051253508</v>
+        <v>-0.0048172144834719433</v>
       </c>
       <c r="AH29" s="0">
-        <v>-0.018604447039354832</v>
+        <v>-0.0031887732198438434</v>
       </c>
       <c r="AI29" s="0">
-        <v>-0.0068676179986192449</v>
+        <v>-0.001177098903745899</v>
       </c>
       <c r="AJ29" s="0">
-        <v>0.0017731315482683941</v>
+        <v>0.00030391166172377693</v>
       </c>
       <c r="AK29" s="0">
-        <v>0.010506404215373947</v>
+        <v>0.0018007822470658685</v>
       </c>
       <c r="AL29" s="0">
-        <v>0.018258941888178549</v>
+        <v>0.0031295545571032868</v>
       </c>
       <c r="AM29" s="0">
-        <v>0.027482244375284886</v>
+        <v>0.0047104139589932981</v>
       </c>
       <c r="AN29" s="0">
-        <v>0.036363293737241308</v>
+        <v>0.0062326121225194653</v>
       </c>
       <c r="AO29" s="0">
-        <v>0.045797794273245998</v>
+        <v>0.0078496715306570763</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="B30" s="0">
-        <v>-0.45322080250298341</v>
+        <v>-0.45665656750298311</v>
       </c>
       <c r="C30" s="0">
-        <v>-0.014391441276768537</v>
+        <v>-0.0024666714852504268</v>
       </c>
       <c r="D30" s="0">
-        <v>-0.014185780568283067</v>
+        <v>-0.0024314200350681325</v>
       </c>
       <c r="E30" s="0">
-        <v>-0.014745915416440493</v>
+        <v>-0.0025274267242783588</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.015174612545567543</v>
+        <v>-0.0026009048649671684</v>
       </c>
       <c r="G30" s="0">
-        <v>-0.015769628235248506</v>
+        <v>-0.0027028901706483421</v>
       </c>
       <c r="H30" s="0">
-        <v>-0.017311365332880982</v>
+        <v>-0.0029671412834801902</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.017590551165628861</v>
+        <v>-0.0030149933736907109</v>
       </c>
       <c r="J30" s="0">
-        <v>-0.021119698265685573</v>
+        <v>-0.0036198833424055388</v>
       </c>
       <c r="K30" s="0">
-        <v>-0.020162611412202186</v>
+        <v>-0.0034558399515352001</v>
       </c>
       <c r="L30" s="0">
-        <v>-0.020844026162118601</v>
+        <v>-0.0035726336629017252</v>
       </c>
       <c r="M30" s="0">
-        <v>-0.025208633199429932</v>
+        <v>-0.0043207214797026938</v>
       </c>
       <c r="N30" s="0">
-        <v>-0.02802248755317692</v>
+        <v>-0.004790015467392994</v>
       </c>
       <c r="O30" s="0">
-        <v>-0.035418985024541563</v>
+        <v>-0.0060305855915541162</v>
       </c>
       <c r="P30" s="0">
-        <v>-0.038945643806771853</v>
+        <v>-0.0066752233994118448</v>
       </c>
       <c r="Q30" s="0">
-        <v>-0.043587816521869223</v>
+        <v>-0.007470884852656956</v>
       </c>
       <c r="R30" s="0">
-        <v>-0.047308626851927646</v>
+        <v>-0.0081086250831529094</v>
       </c>
       <c r="S30" s="0">
-        <v>-0.05247699253953584</v>
+        <v>-0.0089944757269261877</v>
       </c>
       <c r="T30" s="0">
-        <v>-0.059025171214809082</v>
+        <v>-0.010116823420367738</v>
       </c>
       <c r="U30" s="0">
-        <v>-0.067805280644949908</v>
+        <v>-0.011621720421610637</v>
       </c>
       <c r="V30" s="0">
-        <v>-0.077154484049994268</v>
+        <v>-0.013224159386450773</v>
       </c>
       <c r="W30" s="0">
-        <v>-0.066684672671697989</v>
+        <v>-0.011429650304175587</v>
       </c>
       <c r="X30" s="0">
-        <v>-0.069499559313150217</v>
+        <v>-0.011912117311850157</v>
       </c>
       <c r="Y30" s="0">
-        <v>-0.093239178447780624</v>
+        <v>-0.015981051214488395</v>
       </c>
       <c r="Z30" s="0">
-        <v>-0.097383452624637892</v>
+        <v>-0.016691373969128898</v>
       </c>
       <c r="AA30" s="0">
-        <v>-0.095190578088595504</v>
+        <v>-0.01631551828763772</v>
       </c>
       <c r="AB30" s="0">
-        <v>-0.090152375335023141</v>
+        <v>-0.015451977725093158</v>
       </c>
       <c r="AC30" s="0">
-        <v>-0.10257664179004501</v>
+        <v>-0.01758147816900224</v>
       </c>
       <c r="AD30" s="0">
-        <v>-0.13417950705034015</v>
+        <v>-0.0229981607741091</v>
       </c>
       <c r="AE30" s="0">
-        <v>-0.13293766279002711</v>
+        <v>-0.022785309732781867</v>
       </c>
       <c r="AF30" s="0">
-        <v>-0.13358803024656543</v>
+        <v>-0.022896783122773712</v>
       </c>
       <c r="AG30" s="0">
-        <v>-0.13557314433976142</v>
+        <v>-0.023237027439425517</v>
       </c>
       <c r="AH30" s="0">
-        <v>-0.13226872978540297</v>
+        <v>-0.022670656803242151</v>
       </c>
       <c r="AI30" s="0">
-        <v>-0.12459140471888018</v>
+        <v>-0.021354774944863264</v>
       </c>
       <c r="AJ30" s="0">
-        <v>-0.11535101057565568</v>
+        <v>-0.01977098511317793</v>
       </c>
       <c r="AK30" s="0">
-        <v>-0.11302040291566935</v>
+        <v>-0.019371522547619313</v>
       </c>
       <c r="AL30" s="0">
-        <v>-0.106997523756116</v>
+        <v>-0.018339211364380936</v>
       </c>
       <c r="AM30" s="0">
-        <v>-0.096531271210462746</v>
+        <v>-0.016545310777491384</v>
       </c>
       <c r="AN30" s="0">
-        <v>-0.092826748981408719</v>
+        <v>-0.015910361526515537</v>
       </c>
       <c r="AO30" s="0">
-        <v>-0.090435411379077069</v>
+        <v>-0.015500489571315834</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>134</v>
+        <v>198</v>
       </c>
       <c r="B31" s="0">
-        <v>-0.454063972031513</v>
+        <v>-0.4544322979315128</v>
       </c>
       <c r="C31" s="0">
-        <v>-0.002978950400279384</v>
+        <v>-0.00051058732401432216</v>
       </c>
       <c r="D31" s="0">
-        <v>-0.0030062085162957186</v>
+        <v>-0.00051525939014451794</v>
       </c>
       <c r="E31" s="0">
-        <v>-0.0030862706518147566</v>
+        <v>-0.00052898240585952383</v>
       </c>
       <c r="F31" s="0">
-        <v>-0.0031722515295798145</v>
+        <v>-0.00054371923395535315</v>
       </c>
       <c r="G31" s="0">
-        <v>-0.0033688957243321821</v>
+        <v>-0.00057742369064911481</v>
       </c>
       <c r="H31" s="0">
-        <v>-0.003585495526715045</v>
+        <v>-0.00061454793251458639</v>
       </c>
       <c r="I31" s="0">
-        <v>-0.0039284153984325571</v>
+        <v>-0.00067332461681746114</v>
       </c>
       <c r="J31" s="0">
-        <v>-0.0046381968917296483</v>
+        <v>-0.00079498013992573835</v>
       </c>
       <c r="K31" s="0">
-        <v>-0.0047131873282389375</v>
+        <v>-0.00080783336838291531</v>
       </c>
       <c r="L31" s="0">
-        <v>-0.0045658735636676176</v>
+        <v>-0.00078258422451299436</v>
       </c>
       <c r="M31" s="0">
-        <v>-0.0062915456504424793</v>
+        <v>-0.0010783616421569109</v>
       </c>
       <c r="N31" s="0">
-        <v>-0.0075410431131946636</v>
+        <v>-0.0012923729811947782</v>
       </c>
       <c r="O31" s="0">
-        <v>-0.0093842093182386239</v>
+        <v>-0.001619178467124005</v>
       </c>
       <c r="P31" s="0">
-        <v>-0.012865144368908885</v>
+        <v>-0.0022050651341745664</v>
       </c>
       <c r="Q31" s="0">
-        <v>-0.015677255727079571</v>
+        <v>-0.0026870577844113064</v>
       </c>
       <c r="R31" s="0">
-        <v>-0.018402270985914033</v>
+        <v>-0.0031541202098193666</v>
       </c>
       <c r="S31" s="0">
-        <v>-0.021118700058253038</v>
+        <v>-0.0036197133057016551</v>
       </c>
       <c r="T31" s="0">
-        <v>-0.025192716682703176</v>
+        <v>-0.0043179926878662567</v>
       </c>
       <c r="U31" s="0">
-        <v>-0.033223044061519519</v>
+        <v>-0.005694378872708683</v>
       </c>
       <c r="V31" s="0">
-        <v>-0.043183149912283433</v>
+        <v>-0.0074015249238778003</v>
       </c>
       <c r="W31" s="0">
-        <v>-0.050210995580123888</v>
+        <v>-0.0086060875990128793</v>
       </c>
       <c r="X31" s="0">
-        <v>-0.046165130268513224</v>
+        <v>-0.0079126317379460409</v>
       </c>
       <c r="Y31" s="0">
-        <v>-0.055270060657399367</v>
+        <v>-0.0094732027651996953</v>
       </c>
       <c r="Z31" s="0">
-        <v>-0.078865934371395413</v>
+        <v>-0.013517499395478083</v>
       </c>
       <c r="AA31" s="0">
-        <v>-0.085776101900268867</v>
+        <v>-0.014701891072522677</v>
       </c>
       <c r="AB31" s="0">
-        <v>-0.091595513817306337</v>
+        <v>-0.015699329680991581</v>
       </c>
       <c r="AC31" s="0">
-        <v>-0.092177698449861734</v>
+        <v>-0.015799115885448911</v>
       </c>
       <c r="AD31" s="0">
-        <v>-0.1113268211669261</v>
+        <v>-0.019081245678720438</v>
       </c>
       <c r="AE31" s="0">
-        <v>-0.14554245403984639</v>
+        <v>-0.024945752502265772</v>
       </c>
       <c r="AF31" s="0">
-        <v>-0.14754267578901673</v>
+        <v>-0.025288587962913389</v>
       </c>
       <c r="AG31" s="0">
-        <v>-0.15625634045444023</v>
+        <v>-0.026782095569690856</v>
       </c>
       <c r="AH31" s="0">
-        <v>-0.16757571497986429</v>
+        <v>-0.028722219577493435</v>
       </c>
       <c r="AI31" s="0">
-        <v>-0.17345691237201269</v>
+        <v>-0.029730246941222616</v>
       </c>
       <c r="AJ31" s="0">
-        <v>-0.17101754816274012</v>
+        <v>-0.029312144350073399</v>
       </c>
       <c r="AK31" s="0">
-        <v>-0.17169643088125933</v>
+        <v>-0.029428504174874304</v>
       </c>
       <c r="AL31" s="0">
-        <v>-0.1779383578220084</v>
+        <v>-0.030498360421657045</v>
       </c>
       <c r="AM31" s="0">
-        <v>-0.17910094993093595</v>
+        <v>-0.030697626371043119</v>
       </c>
       <c r="AN31" s="0">
-        <v>-0.17270062993940863</v>
+        <v>-0.029600622261705678</v>
       </c>
       <c r="AO31" s="0">
-        <v>-0.17922485759417767</v>
+        <v>-0.030718864731891893</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="B32" s="0">
-        <v>-0.452291760434334</v>
+        <v>-0.45231446063433361</v>
       </c>
       <c r="C32" s="0">
-        <v>-0.00033334425406091809</v>
+        <v>-5.7134618956733441e-05</v>
       </c>
       <c r="D32" s="0">
-        <v>-0.00034597983092969392</v>
+        <v>-5.9300431025699485e-05</v>
       </c>
       <c r="E32" s="0">
-        <v>-0.00034909184318239093</v>
+        <v>-5.9833766897887664e-05</v>
       </c>
       <c r="F32" s="0">
-        <v>-0.00035544910359617057</v>
+        <v>-6.0923514077548813e-05</v>
       </c>
       <c r="G32" s="0">
-        <v>-0.0003721273913372587</v>
+        <v>-6.378205802293202e-05</v>
       </c>
       <c r="H32" s="0">
-        <v>-0.00043209398046407412</v>
+        <v>-7.4060272493292612e-05</v>
       </c>
       <c r="I32" s="0">
-        <v>-0.00057699696555798218</v>
+        <v>-9.8896412505933284e-05</v>
       </c>
       <c r="J32" s="0">
-        <v>-0.00065272450399398384</v>
+        <v>-0.00011187579770455258</v>
       </c>
       <c r="K32" s="0">
-        <v>-0.0006311458588503095</v>
+        <v>-0.00010817730557660665</v>
       </c>
       <c r="L32" s="0">
-        <v>-0.00071039355161692957</v>
+        <v>-0.00012176020486598382</v>
       </c>
       <c r="M32" s="0">
-        <v>-0.0010550368991119816</v>
+        <v>-0.00018083144187319711</v>
       </c>
       <c r="N32" s="0">
-        <v>-0.0012308093136172518</v>
+        <v>-0.00021384675048402579</v>
       </c>
       <c r="O32" s="0">
-        <v>-0.0014502343671583069</v>
+        <v>-0.00024869107023739456</v>
       </c>
       <c r="P32" s="0">
-        <v>-0.0018686621620274942</v>
+        <v>-0.00032028566563419014</v>
       </c>
       <c r="Q32" s="0">
-        <v>-0.0029270408631835148</v>
+        <v>-0.00050169074283423765</v>
       </c>
       <c r="R32" s="0">
-        <v>-0.0035170334078489336</v>
+        <v>-0.00060281375620402367</v>
       </c>
       <c r="S32" s="0">
-        <v>-0.004416430616909074</v>
+        <v>-0.00075697023912268957</v>
       </c>
       <c r="T32" s="0">
-        <v>-0.0054161607914803584</v>
+        <v>-0.00092832180329566194</v>
       </c>
       <c r="U32" s="0">
-        <v>-0.0076012592925799004</v>
+        <v>-0.0013028444665454386</v>
       </c>
       <c r="V32" s="0">
-        <v>-0.011096661750890835</v>
+        <v>-0.0019019505815254245</v>
       </c>
       <c r="W32" s="0">
-        <v>-0.014600838958597328</v>
+        <v>-0.0025025618815665562</v>
       </c>
       <c r="X32" s="0">
-        <v>-0.017817466319240381</v>
+        <v>-0.0030538861278310292</v>
       </c>
       <c r="Y32" s="0">
-        <v>-0.017467476233566211</v>
+        <v>-0.0029938981546451249</v>
       </c>
       <c r="Z32" s="0">
-        <v>-0.023738829518760871</v>
+        <v>-0.0040687991715432914</v>
       </c>
       <c r="AA32" s="0">
-        <v>-0.033804475070951669</v>
+        <v>-0.005794035150385568</v>
       </c>
       <c r="AB32" s="0">
-        <v>-0.039062780648447537</v>
+        <v>-0.0066953007989423718</v>
       </c>
       <c r="AC32" s="0">
-        <v>-0.042661971461493323</v>
+        <v>-0.0073121965165059422</v>
       </c>
       <c r="AD32" s="0">
-        <v>-0.043796446293101865</v>
+        <v>-0.0075066429091649178</v>
       </c>
       <c r="AE32" s="0">
-        <v>-0.055476334937258939</v>
+        <v>-0.0095085584934587741</v>
       </c>
       <c r="AF32" s="0">
-        <v>-0.071915076321652865</v>
+        <v>-0.01232613324818288</v>
       </c>
       <c r="AG32" s="0">
-        <v>-0.073113086621749507</v>
+        <v>-0.012531470227604924</v>
       </c>
       <c r="AH32" s="0">
-        <v>-0.079954882037466035</v>
+        <v>-0.013704143286042192</v>
       </c>
       <c r="AI32" s="0">
-        <v>-0.087850209518657532</v>
+        <v>-0.015057390376488178</v>
       </c>
       <c r="AJ32" s="0">
-        <v>-0.092862603138524985</v>
+        <v>-0.01591650761959823</v>
       </c>
       <c r="AK32" s="0">
-        <v>-0.091961809904449368</v>
+        <v>-0.015762112049275079</v>
       </c>
       <c r="AL32" s="0">
-        <v>-0.095780029323117175</v>
+        <v>-0.016416548589963942</v>
       </c>
       <c r="AM32" s="0">
-        <v>-0.10056693499447066</v>
+        <v>-0.017237017562276191</v>
       </c>
       <c r="AN32" s="0">
-        <v>-0.10196481794227819</v>
+        <v>-0.017476612376172262</v>
       </c>
       <c r="AO32" s="0">
-        <v>-0.09863613991389153</v>
+        <v>-0.016906082336107853</v>
       </c>
     </row>
     <row r="33">

--- a/mig_shocks.xlsx
+++ b/mig_shocks.xlsx
@@ -13,511 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
-  <si>
-    <t>Var40</t>
-  </si>
-  <si>
-    <t>Var41</t>
-  </si>
-  <si>
-    <t>Var42</t>
-  </si>
-  <si>
-    <t>Var43</t>
-  </si>
-  <si>
-    <t>Var44</t>
-  </si>
-  <si>
-    <t>Var45</t>
-  </si>
-  <si>
-    <t>Var46</t>
-  </si>
-  <si>
-    <t>Var47</t>
-  </si>
-  <si>
-    <t>Var48</t>
-  </si>
-  <si>
-    <t>Var49</t>
-  </si>
-  <si>
-    <t>Var50</t>
-  </si>
-  <si>
-    <t>Var51</t>
-  </si>
-  <si>
-    <t>Var52</t>
-  </si>
-  <si>
-    <t>Var53</t>
-  </si>
-  <si>
-    <t>Var54</t>
-  </si>
-  <si>
-    <t>Var55</t>
-  </si>
-  <si>
-    <t>Var56</t>
-  </si>
-  <si>
-    <t>Var57</t>
-  </si>
-  <si>
-    <t>Var58</t>
-  </si>
-  <si>
-    <t>Var59</t>
-  </si>
-  <si>
-    <t>Var60</t>
-  </si>
-  <si>
-    <t>Var61</t>
-  </si>
-  <si>
-    <t>Var62</t>
-  </si>
-  <si>
-    <t>Var63</t>
-  </si>
-  <si>
-    <t>Var64</t>
-  </si>
-  <si>
-    <t>Var65</t>
-  </si>
-  <si>
-    <t>Var66</t>
-  </si>
-  <si>
-    <t>Var67</t>
-  </si>
-  <si>
-    <t>Var68</t>
-  </si>
-  <si>
-    <t>Var69</t>
-  </si>
-  <si>
-    <t>Var70</t>
-  </si>
-  <si>
-    <t>Var71</t>
-  </si>
-  <si>
-    <t>Var72</t>
-  </si>
-  <si>
-    <t>Var73</t>
-  </si>
-  <si>
-    <t>Var74</t>
-  </si>
-  <si>
-    <t>Var75</t>
-  </si>
-  <si>
-    <t>Var76</t>
-  </si>
-  <si>
-    <t>Var77</t>
-  </si>
-  <si>
-    <t>Var78</t>
-  </si>
-  <si>
-    <t>Var79</t>
-  </si>
-  <si>
-    <t>mig_Q_2</t>
-  </si>
-  <si>
-    <t>mig_Q_3</t>
-  </si>
-  <si>
-    <t>mig_Q_4</t>
-  </si>
-  <si>
-    <t>mig_Q_5</t>
-  </si>
-  <si>
-    <t>mig_Q_6</t>
-  </si>
-  <si>
-    <t>mig_Q_7</t>
-  </si>
-  <si>
-    <t>mig_Q_8</t>
-  </si>
-  <si>
-    <t>mig_Q_9</t>
-  </si>
-  <si>
-    <t>mig_Q_10</t>
-  </si>
-  <si>
-    <t>mig_Q_11</t>
-  </si>
-  <si>
-    <t>mig_Q_12</t>
-  </si>
-  <si>
-    <t>mig_Q_13</t>
-  </si>
-  <si>
-    <t>mig_Q_14</t>
-  </si>
-  <si>
-    <t>mig_Q_15</t>
-  </si>
-  <si>
-    <t>mig_Q_16</t>
-  </si>
-  <si>
-    <t>mig_Q_17</t>
-  </si>
-  <si>
-    <t>mig_NQ_2</t>
-  </si>
-  <si>
-    <t>mig_NQ_3</t>
-  </si>
-  <si>
-    <t>mig_NQ_4</t>
-  </si>
-  <si>
-    <t>mig_NQ_5</t>
-  </si>
-  <si>
-    <t>mig_NQ_6</t>
-  </si>
-  <si>
-    <t>mig_NQ_7</t>
-  </si>
-  <si>
-    <t>mig_NQ_8</t>
-  </si>
-  <si>
-    <t>mig_NQ_9</t>
-  </si>
-  <si>
-    <t>mig_NQ_10</t>
-  </si>
-  <si>
-    <t>mig_NQ_11</t>
-  </si>
-  <si>
-    <t>mig_NQ_12</t>
-  </si>
-  <si>
-    <t>mig_NQ_13</t>
-  </si>
-  <si>
-    <t>mig_NQ_14</t>
-  </si>
-  <si>
-    <t>mig_NQ_15</t>
-  </si>
-  <si>
-    <t>mig_NQ_16</t>
-  </si>
-  <si>
-    <t>mig_NQ_17</t>
-  </si>
-  <si>
-    <t>mig_Q_2</t>
-  </si>
-  <si>
-    <t>mig_Q_3</t>
-  </si>
-  <si>
-    <t>mig_Q_4</t>
-  </si>
-  <si>
-    <t>mig_Q_5</t>
-  </si>
-  <si>
-    <t>mig_Q_6</t>
-  </si>
-  <si>
-    <t>mig_Q_7</t>
-  </si>
-  <si>
-    <t>mig_Q_8</t>
-  </si>
-  <si>
-    <t>mig_Q_9</t>
-  </si>
-  <si>
-    <t>mig_Q_10</t>
-  </si>
-  <si>
-    <t>mig_Q_11</t>
-  </si>
-  <si>
-    <t>mig_Q_12</t>
-  </si>
-  <si>
-    <t>mig_Q_13</t>
-  </si>
-  <si>
-    <t>mig_Q_14</t>
-  </si>
-  <si>
-    <t>mig_Q_15</t>
-  </si>
-  <si>
-    <t>mig_Q_16</t>
-  </si>
-  <si>
-    <t>mig_Q_17</t>
-  </si>
-  <si>
-    <t>mig_NQ_2</t>
-  </si>
-  <si>
-    <t>mig_NQ_3</t>
-  </si>
-  <si>
-    <t>mig_NQ_4</t>
-  </si>
-  <si>
-    <t>mig_NQ_5</t>
-  </si>
-  <si>
-    <t>mig_NQ_6</t>
-  </si>
-  <si>
-    <t>mig_NQ_7</t>
-  </si>
-  <si>
-    <t>mig_NQ_8</t>
-  </si>
-  <si>
-    <t>mig_NQ_9</t>
-  </si>
-  <si>
-    <t>mig_NQ_10</t>
-  </si>
-  <si>
-    <t>mig_NQ_11</t>
-  </si>
-  <si>
-    <t>mig_NQ_12</t>
-  </si>
-  <si>
-    <t>mig_NQ_13</t>
-  </si>
-  <si>
-    <t>mig_NQ_14</t>
-  </si>
-  <si>
-    <t>mig_NQ_15</t>
-  </si>
-  <si>
-    <t>mig_NQ_16</t>
-  </si>
-  <si>
-    <t>mig_NQ_17</t>
-  </si>
-  <si>
-    <t>mig_Q_2</t>
-  </si>
-  <si>
-    <t>mig_Q_3</t>
-  </si>
-  <si>
-    <t>mig_Q_4</t>
-  </si>
-  <si>
-    <t>mig_Q_5</t>
-  </si>
-  <si>
-    <t>mig_Q_6</t>
-  </si>
-  <si>
-    <t>mig_Q_7</t>
-  </si>
-  <si>
-    <t>mig_Q_8</t>
-  </si>
-  <si>
-    <t>mig_Q_9</t>
-  </si>
-  <si>
-    <t>mig_Q_10</t>
-  </si>
-  <si>
-    <t>mig_Q_11</t>
-  </si>
-  <si>
-    <t>mig_Q_12</t>
-  </si>
-  <si>
-    <t>mig_Q_13</t>
-  </si>
-  <si>
-    <t>mig_Q_14</t>
-  </si>
-  <si>
-    <t>mig_Q_15</t>
-  </si>
-  <si>
-    <t>mig_Q_16</t>
-  </si>
-  <si>
-    <t>mig_Q_17</t>
-  </si>
-  <si>
-    <t>mig_NQ_2</t>
-  </si>
-  <si>
-    <t>mig_NQ_3</t>
-  </si>
-  <si>
-    <t>mig_NQ_4</t>
-  </si>
-  <si>
-    <t>mig_NQ_5</t>
-  </si>
-  <si>
-    <t>mig_NQ_6</t>
-  </si>
-  <si>
-    <t>mig_NQ_7</t>
-  </si>
-  <si>
-    <t>mig_NQ_8</t>
-  </si>
-  <si>
-    <t>mig_NQ_9</t>
-  </si>
-  <si>
-    <t>mig_NQ_10</t>
-  </si>
-  <si>
-    <t>mig_NQ_11</t>
-  </si>
-  <si>
-    <t>mig_NQ_12</t>
-  </si>
-  <si>
-    <t>mig_NQ_13</t>
-  </si>
-  <si>
-    <t>mig_NQ_14</t>
-  </si>
-  <si>
-    <t>mig_NQ_15</t>
-  </si>
-  <si>
-    <t>mig_NQ_16</t>
-  </si>
-  <si>
-    <t>mig_NQ_17</t>
-  </si>
-  <si>
-    <t>mig_Q_2</t>
-  </si>
-  <si>
-    <t>mig_Q_3</t>
-  </si>
-  <si>
-    <t>mig_Q_4</t>
-  </si>
-  <si>
-    <t>mig_Q_5</t>
-  </si>
-  <si>
-    <t>mig_Q_6</t>
-  </si>
-  <si>
-    <t>mig_Q_7</t>
-  </si>
-  <si>
-    <t>mig_Q_8</t>
-  </si>
-  <si>
-    <t>mig_Q_9</t>
-  </si>
-  <si>
-    <t>mig_Q_10</t>
-  </si>
-  <si>
-    <t>mig_Q_11</t>
-  </si>
-  <si>
-    <t>mig_Q_12</t>
-  </si>
-  <si>
-    <t>mig_Q_13</t>
-  </si>
-  <si>
-    <t>mig_Q_14</t>
-  </si>
-  <si>
-    <t>mig_Q_15</t>
-  </si>
-  <si>
-    <t>mig_Q_16</t>
-  </si>
-  <si>
-    <t>mig_Q_17</t>
-  </si>
-  <si>
-    <t>mig_NQ_2</t>
-  </si>
-  <si>
-    <t>mig_NQ_3</t>
-  </si>
-  <si>
-    <t>mig_NQ_4</t>
-  </si>
-  <si>
-    <t>mig_NQ_5</t>
-  </si>
-  <si>
-    <t>mig_NQ_6</t>
-  </si>
-  <si>
-    <t>mig_NQ_7</t>
-  </si>
-  <si>
-    <t>mig_NQ_8</t>
-  </si>
-  <si>
-    <t>mig_NQ_9</t>
-  </si>
-  <si>
-    <t>mig_NQ_10</t>
-  </si>
-  <si>
-    <t>mig_NQ_11</t>
-  </si>
-  <si>
-    <t>mig_NQ_12</t>
-  </si>
-  <si>
-    <t>mig_NQ_13</t>
-  </si>
-  <si>
-    <t>mig_NQ_14</t>
-  </si>
-  <si>
-    <t>mig_NQ_15</t>
-  </si>
-  <si>
-    <t>mig_NQ_16</t>
-  </si>
-  <si>
-    <t>mig_NQ_17</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>mig_Q_2</t>
   </si>
@@ -633,7 +129,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -642,27 +138,13 @@
       <diagonal/>
     </border>
     <border/>
-    <border/>
-    <border/>
-    <border/>
-    <border/>
-    <border/>
-    <border/>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -672,7 +154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO33"/>
+  <dimension ref="A1:AO32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="true"/>
@@ -686,7 +168,7 @@
     <col min="9" max="9" width="16.42578125" customWidth="true"/>
     <col min="10" max="10" width="16.42578125" customWidth="true"/>
     <col min="11" max="11" width="16.42578125" customWidth="true"/>
-    <col min="12" max="12" width="16.42578125" customWidth="true"/>
+    <col min="12" max="12" width="16.28515625" customWidth="true"/>
     <col min="13" max="13" width="16.42578125" customWidth="true"/>
     <col min="14" max="14" width="16.42578125" customWidth="true"/>
     <col min="15" max="15" width="16.42578125" customWidth="true"/>
@@ -695,4149 +177,4027 @@
     <col min="18" max="18" width="16.42578125" customWidth="true"/>
     <col min="19" max="19" width="16.42578125" customWidth="true"/>
     <col min="20" max="20" width="16.42578125" customWidth="true"/>
-    <col min="21" max="21" width="16.42578125" customWidth="true"/>
-    <col min="22" max="22" width="16.42578125" customWidth="true"/>
-    <col min="23" max="23" width="15.7109375" customWidth="true"/>
-    <col min="24" max="24" width="15.42578125" customWidth="true"/>
+    <col min="21" max="21" width="16.28515625" customWidth="true"/>
+    <col min="22" max="22" width="15.7109375" customWidth="true"/>
+    <col min="23" max="23" width="16.42578125" customWidth="true"/>
+    <col min="24" max="24" width="16.42578125" customWidth="true"/>
     <col min="25" max="25" width="16.42578125" customWidth="true"/>
-    <col min="26" max="26" width="16.42578125" customWidth="true"/>
+    <col min="26" max="26" width="16.28515625" customWidth="true"/>
     <col min="27" max="27" width="15.7109375" customWidth="true"/>
-    <col min="28" max="28" width="15.7109375" customWidth="true"/>
-    <col min="29" max="29" width="15.7109375" customWidth="true"/>
-    <col min="30" max="30" width="15.42578125" customWidth="true"/>
-    <col min="31" max="31" width="15.42578125" customWidth="true"/>
-    <col min="32" max="32" width="15.42578125" customWidth="true"/>
-    <col min="33" max="33" width="15.42578125" customWidth="true"/>
-    <col min="34" max="34" width="15.42578125" customWidth="true"/>
+    <col min="28" max="28" width="16.42578125" customWidth="true"/>
+    <col min="29" max="29" width="16.42578125" customWidth="true"/>
+    <col min="30" max="30" width="16.42578125" customWidth="true"/>
+    <col min="31" max="31" width="16.42578125" customWidth="true"/>
+    <col min="32" max="32" width="15.7109375" customWidth="true"/>
+    <col min="33" max="33" width="16.42578125" customWidth="true"/>
+    <col min="34" max="34" width="15.5703125" customWidth="true"/>
     <col min="35" max="35" width="16.42578125" customWidth="true"/>
-    <col min="36" max="36" width="15.7109375" customWidth="true"/>
+    <col min="36" max="36" width="16.42578125" customWidth="true"/>
     <col min="37" max="37" width="15.7109375" customWidth="true"/>
-    <col min="38" max="38" width="15.42578125" customWidth="true"/>
-    <col min="39" max="39" width="15.42578125" customWidth="true"/>
-    <col min="40" max="40" width="15.42578125" customWidth="true"/>
+    <col min="38" max="38" width="16.42578125" customWidth="true"/>
+    <col min="39" max="39" width="16.42578125" customWidth="true"/>
+    <col min="40" max="40" width="16.28515625" customWidth="true"/>
     <col min="41" max="41" width="15.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="B1" s="0">
-        <v>-0.44726131189217022</v>
+        <v>-0.4828926172556337</v>
       </c>
       <c r="C1" s="0">
-        <v>-0.36914315052464836</v>
+        <v>-0.39484432944967157</v>
       </c>
       <c r="D1" s="0">
-        <v>-0.37300933490262422</v>
+        <v>-0.39945191280445391</v>
       </c>
       <c r="E1" s="0">
-        <v>-0.37252326236856126</v>
+        <v>-0.39834168732770092</v>
       </c>
       <c r="F1" s="0">
-        <v>-0.35442939666455564</v>
+        <v>-0.3784133910899401</v>
       </c>
       <c r="G1" s="0">
-        <v>-0.3325867631175855</v>
+        <v>-0.35574995031790402</v>
       </c>
       <c r="H1" s="0">
-        <v>-0.33589175986139724</v>
+        <v>-0.359516829389113</v>
       </c>
       <c r="I1" s="0">
-        <v>-0.3405174763785298</v>
+        <v>-0.36429880065535408</v>
       </c>
       <c r="J1" s="0">
-        <v>-0.36332093854591141</v>
+        <v>-0.38738242537821532</v>
       </c>
       <c r="K1" s="0">
-        <v>-0.3411407980530059</v>
+        <v>-0.3641086410795345</v>
       </c>
       <c r="L1" s="0">
-        <v>-0.32796983850718536</v>
+        <v>-0.35128488612178393</v>
       </c>
       <c r="M1" s="0">
-        <v>-0.35816074040762857</v>
+        <v>-0.38378950777053367</v>
       </c>
       <c r="N1" s="0">
-        <v>-0.39199561409953987</v>
+        <v>-0.4200921881236116</v>
       </c>
       <c r="O1" s="0">
-        <v>-0.4471368803890074</v>
+        <v>-0.47903679194646986</v>
       </c>
       <c r="P1" s="0">
-        <v>-0.48084828304877447</v>
+        <v>-0.51589120389303478</v>
       </c>
       <c r="Q1" s="0">
-        <v>-0.46652123327721062</v>
+        <v>-0.50200016859607388</v>
       </c>
       <c r="R1" s="0">
-        <v>-0.46390298605986258</v>
+        <v>-0.49921390661362564</v>
       </c>
       <c r="S1" s="0">
-        <v>-0.45153292834668868</v>
+        <v>-0.48610791761536642</v>
       </c>
       <c r="T1" s="0">
-        <v>-0.43592860767132346</v>
+        <v>-0.46972525477307958</v>
       </c>
       <c r="U1" s="0">
-        <v>-0.43672168946432383</v>
+        <v>-0.4705878246758266</v>
       </c>
       <c r="V1" s="0">
-        <v>-0.43261945944728797</v>
+        <v>-0.46591448442666866</v>
       </c>
       <c r="W1" s="0">
-        <v>-0.43758192652992484</v>
+        <v>-0.47109859662545556</v>
       </c>
       <c r="X1" s="0">
-        <v>-0.44440202423966135</v>
+        <v>-0.47846425737199805</v>
       </c>
       <c r="Y1" s="0">
-        <v>-0.45149807951239551</v>
+        <v>-0.48596345182845058</v>
       </c>
       <c r="Z1" s="0">
-        <v>-0.46292639152740389</v>
+        <v>-0.49786784709042442</v>
       </c>
       <c r="AA1" s="0">
-        <v>-0.45248147114409781</v>
+        <v>-0.4867442581190432</v>
       </c>
       <c r="AB1" s="0">
-        <v>-0.43772372803985582</v>
+        <v>-0.47109127948726198</v>
       </c>
       <c r="AC1" s="0">
-        <v>-0.41783594159099446</v>
+        <v>-0.44999491615696785</v>
       </c>
       <c r="AD1" s="0">
-        <v>-0.40655877800291129</v>
+        <v>-0.43782211731522108</v>
       </c>
       <c r="AE1" s="0">
-        <v>-0.41091630005462393</v>
+        <v>-0.44211897148839935</v>
       </c>
       <c r="AF1" s="0">
-        <v>-0.41843819002776772</v>
+        <v>-0.44999956751630066</v>
       </c>
       <c r="AG1" s="0">
-        <v>-0.41756202764977474</v>
+        <v>-0.44920634999768333</v>
       </c>
       <c r="AH1" s="0">
-        <v>-0.40971265710146298</v>
+        <v>-0.44100530628683865</v>
       </c>
       <c r="AI1" s="0">
-        <v>-0.39789833865400437</v>
+        <v>-0.42807732332472559</v>
       </c>
       <c r="AJ1" s="0">
-        <v>-0.38746318626010229</v>
+        <v>-0.41666476244874778</v>
       </c>
       <c r="AK1" s="0">
-        <v>-0.3821398646666968</v>
+        <v>-0.41055240020246042</v>
       </c>
       <c r="AL1" s="0">
-        <v>-0.38192233664322683</v>
+        <v>-0.40987310015475004</v>
       </c>
       <c r="AM1" s="0">
-        <v>-0.38234125283036119</v>
+        <v>-0.40996687840468754</v>
       </c>
       <c r="AN1" s="0">
-        <v>-0.37912346563453064</v>
+        <v>-0.40612812220922107</v>
       </c>
       <c r="AO1" s="0">
-        <v>-0.37207387365439981</v>
+        <v>-0.39836042775243857</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.47880771499948205</v>
+        <v>-0.4924378346666668</v>
       </c>
       <c r="C2" s="0">
-        <v>-0.00064627396979410889</v>
+        <v>0.0024309395604166228</v>
       </c>
       <c r="D2" s="0">
-        <v>0.00018312026495126421</v>
+        <v>0.0032764860163193572</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.0015700047159400432</v>
+        <v>0.0015240661836805054</v>
       </c>
       <c r="F2" s="0">
-        <v>-0.00063505995688339922</v>
+        <v>0.0025398906496527647</v>
       </c>
       <c r="G2" s="0">
-        <v>0.0026919206285099251</v>
+        <v>0.0058814356847221583</v>
       </c>
       <c r="H2" s="0">
-        <v>0.0016692021167747373</v>
+        <v>0.0046392121753471849</v>
       </c>
       <c r="I2" s="0">
-        <v>-8.6455450690969826e-05</v>
+        <v>0.0028296230326388398</v>
       </c>
       <c r="J2" s="0">
-        <v>-0.008303486742639421</v>
+        <v>-0.0052937343649305801</v>
       </c>
       <c r="K2" s="0">
-        <v>0.0061311684188237736</v>
+        <v>0.0096502604302082795</v>
       </c>
       <c r="L2" s="0">
-        <v>0.002492665390036175</v>
+        <v>0.0058964723180554568</v>
       </c>
       <c r="M2" s="0">
-        <v>0.0022318949756262585</v>
+        <v>0.0052421690552082465</v>
       </c>
       <c r="N2" s="0">
-        <v>0.0035715495223050397</v>
+        <v>0.0065872710795137901</v>
       </c>
       <c r="O2" s="0">
-        <v>0.0034555337579774137</v>
+        <v>0.0065116594881944323</v>
       </c>
       <c r="P2" s="0">
-        <v>0.0029008637925752034</v>
+        <v>0.0060557431211805679</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.0026838434061236538</v>
+        <v>0.0056347478972221809</v>
       </c>
       <c r="R2" s="0">
-        <v>0.0030956704666160739</v>
+        <v>0.0055935890295138457</v>
       </c>
       <c r="S2" s="0">
-        <v>0.0034135617514798877</v>
+        <v>0.0059527638048610387</v>
       </c>
       <c r="T2" s="0">
-        <v>0.0054975792200159801</v>
+        <v>0.0080285476020832691</v>
       </c>
       <c r="U2" s="0">
-        <v>0.0040095088043512472</v>
+        <v>0.0064638396833332501</v>
       </c>
       <c r="V2" s="0">
-        <v>0.0040403876502772551</v>
+        <v>0.0065268080954860586</v>
       </c>
       <c r="W2" s="0">
-        <v>0.0048028451673184924</v>
+        <v>0.0074163786656248898</v>
       </c>
       <c r="X2" s="0">
-        <v>0.0045406036708912634</v>
+        <v>0.0072179089003471253</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.0048008342744096932</v>
+        <v>0.0074642189670138248</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.0046861521274530471</v>
+        <v>0.0073814699718749432</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.0045289433363621123</v>
+        <v>0.0073296608760416437</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.00457687873561341</v>
+        <v>0.0073358705371526778</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.0046543657206043476</v>
+        <v>0.0073532877222222126</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.0047555844295341099</v>
+        <v>0.007384699726388777</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.0047150777167476177</v>
+        <v>0.0073862817781249479</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.0045406817779693465</v>
+        <v>0.0073580622982638566</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.0044386551399621665</v>
+        <v>0.0073436392979165932</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.004467384214106751</v>
+        <v>0.007356508797222161</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.0045143161269602938</v>
+        <v>0.007372994631597185</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.0045486035792373647</v>
+        <v>0.0073862928249999182</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.004546098008672228</v>
+        <v>0.0073908031833332388</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.0044920337440940705</v>
+        <v>0.0073830307298610731</v>
       </c>
       <c r="AM2" s="0">
-        <v>0.0044149938224959939</v>
+        <v>0.0073692589871527381</v>
       </c>
       <c r="AN2" s="0">
-        <v>0.0043658186224450057</v>
+        <v>0.0073613844149305052</v>
       </c>
       <c r="AO2" s="0">
-        <v>0.0043638484198814664</v>
+        <v>0.0073641002729166183</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.47872825914897399</v>
+        <v>-0.49379786766666678</v>
       </c>
       <c r="C3" s="0">
-        <v>-5.3159446124939613e-05</v>
+        <v>0.0030417055368054946</v>
       </c>
       <c r="D3" s="0">
-        <v>5.0888083150180119e-05</v>
+        <v>0.0030446016201388089</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.00070412999249941377</v>
+        <v>0.0022842387965277271</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.00018870197301190661</v>
+        <v>0.0028488282114582653</v>
       </c>
       <c r="G3" s="0">
-        <v>0.001934859810363565</v>
+        <v>0.005030728112847104</v>
       </c>
       <c r="H3" s="0">
-        <v>0.0010598391742976387</v>
+        <v>0.0040821300322915754</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.00034627662091551992</v>
+        <v>0.0024693637326388402</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.0069977922497858058</v>
+        <v>-0.0041916467312500538</v>
       </c>
       <c r="K3" s="0">
-        <v>0.007588370611202544</v>
+        <v>0.010720124317708302</v>
       </c>
       <c r="L3" s="0">
-        <v>0.0032845330520310245</v>
+        <v>0.0065641840201388635</v>
       </c>
       <c r="M3" s="0">
-        <v>0.0017133420005925881</v>
+        <v>0.0049700329944444288</v>
       </c>
       <c r="N3" s="0">
-        <v>0.0032920311670212032</v>
+        <v>0.0061352898788193388</v>
       </c>
       <c r="O3" s="0">
-        <v>0.0034552685786040649</v>
+        <v>0.0062676732513888278</v>
       </c>
       <c r="P3" s="0">
-        <v>0.0027702768133184841</v>
+        <v>0.0056290780864582945</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.0017574502021153182</v>
+        <v>0.0047370104256943546</v>
       </c>
       <c r="R3" s="0">
-        <v>0.0019127355944216773</v>
+        <v>0.0046801776065971681</v>
       </c>
       <c r="S3" s="0">
-        <v>0.0026971190458636718</v>
+        <v>0.0049690354031248782</v>
       </c>
       <c r="T3" s="0">
-        <v>0.0045862193011654839</v>
+        <v>0.0068935491503471225</v>
       </c>
       <c r="U3" s="0">
-        <v>0.0034023674734629528</v>
+        <v>0.0056437958729166349</v>
       </c>
       <c r="V3" s="0">
-        <v>0.0037726743049525391</v>
+        <v>0.0059729179263888765</v>
       </c>
       <c r="W3" s="0">
-        <v>0.0046502891450257433</v>
+        <v>0.0068839560357638607</v>
       </c>
       <c r="X3" s="0">
-        <v>0.0047595381535229242</v>
+        <v>0.0071082276739583006</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.0049804731047050632</v>
+        <v>0.0074045194552082583</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.0048966742190908463</v>
+        <v>0.0072987098635415859</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.004835644269742867</v>
+        <v>0.0072749557506943674</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.0046949291268807425</v>
+        <v>0.0072512147545137906</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.0047621613869786028</v>
+        <v>0.0072725276343749146</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.0048596996696590455</v>
+        <v>0.0073037269184027531</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.0049706111034334977</v>
+        <v>0.0073372405038193977</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.0049298593550914926</v>
+        <v>0.0073425902333332793</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.0047457154038292315</v>
+        <v>0.0073194858822915876</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.0046387628960360416</v>
+        <v>0.0073089759510415742</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.0046714550160493196</v>
+        <v>0.007323926134722214</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.0047233514406865851</v>
+        <v>0.007341988999652771</v>
       </c>
       <c r="AK3" s="0">
-        <v>0.0047616394041393173</v>
+        <v>0.007356899240972159</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.0047604381944313379</v>
+        <v>0.0073632659690971436</v>
       </c>
       <c r="AM3" s="0">
-        <v>0.0047036793708022384</v>
+        <v>0.0073574736579860578</v>
       </c>
       <c r="AN3" s="0">
-        <v>0.0046222036243005471</v>
+        <v>0.0073457416975694079</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.0045705513897718042</v>
+        <v>0.0073395865520832215</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.48023304445544734</v>
+        <v>-0.49740144366666672</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.00043639452705629411</v>
+        <v>0.0024989323968749315</v>
       </c>
       <c r="D4" s="0">
-        <v>-3.8351879539655354e-05</v>
+        <v>0.0029152952829860639</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.0008240093634657164</v>
+        <v>0.0020152306572916445</v>
       </c>
       <c r="F4" s="0">
-        <v>0.00035212347230745289</v>
+        <v>0.0032092524850693698</v>
       </c>
       <c r="G4" s="0">
-        <v>0.00090357224249476564</v>
+        <v>0.0037973479076388599</v>
       </c>
       <c r="H4" s="0">
-        <v>0.00026458229105325026</v>
+        <v>0.0031572829878471769</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.00078101204498864929</v>
+        <v>0.0020581324152777474</v>
       </c>
       <c r="J4" s="0">
-        <v>-0.0045115521179441842</v>
+        <v>-0.0018554714916667056</v>
       </c>
       <c r="K4" s="0">
-        <v>0.006134114311951655</v>
+        <v>0.0089876397249999407</v>
       </c>
       <c r="L4" s="0">
-        <v>0.003092407832651356</v>
+        <v>0.0058474221979166185</v>
       </c>
       <c r="M4" s="0">
-        <v>0.0015629952349722198</v>
+        <v>0.0046153907045138878</v>
       </c>
       <c r="N4" s="0">
-        <v>0.0023688418161338931</v>
+        <v>0.0054451271347221164</v>
       </c>
       <c r="O4" s="0">
-        <v>0.0029486138349620328</v>
+        <v>0.0055214583892360678</v>
       </c>
       <c r="P4" s="0">
-        <v>0.0024577969624251517</v>
+        <v>0.0049916878871527071</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.0016535966698173477</v>
+        <v>0.0042598296197915997</v>
       </c>
       <c r="R4" s="0">
-        <v>0.0016588644538443331</v>
+        <v>0.0044293702190971165</v>
       </c>
       <c r="S4" s="0">
-        <v>0.001841960035304735</v>
+        <v>0.0043745725295138418</v>
       </c>
       <c r="T4" s="0">
-        <v>0.004035523325018997</v>
+        <v>0.0059992753732638349</v>
       </c>
       <c r="U4" s="0">
-        <v>0.003058749930472171</v>
+        <v>0.0050024250413193694</v>
       </c>
       <c r="V4" s="0">
-        <v>0.003264342585644342</v>
+        <v>0.00517256714861103</v>
       </c>
       <c r="W4" s="0">
-        <v>0.0040557442544742472</v>
+        <v>0.0059071297638887965</v>
       </c>
       <c r="X4" s="0">
-        <v>0.0041268448420505588</v>
+        <v>0.0059875766854166068</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.0040197311931188251</v>
+        <v>0.0060034072010416439</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.0037511977156240439</v>
+        <v>0.0058107605621526837</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.0038344358745150964</v>
+        <v>0.0058724321215277153</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.0038387898041483126</v>
+        <v>0.0059196320479165676</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.0037146966706816387</v>
+        <v>0.0059284319496527016</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.0038002551304623933</v>
+        <v>0.0059614437920138541</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.0039110739527127292</v>
+        <v>0.0059963379499998748</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.0040363656872483</v>
+        <v>0.0060331389152776804</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.0039958378264378092</v>
+        <v>0.0060445265736110421</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.0037985432340723602</v>
+        <v>0.0060298905569444172</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.0036849148403184095</v>
+        <v>0.0060255473798610515</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.003723572386509777</v>
+        <v>0.0060436922517360103</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.0037830049458139614</v>
+        <v>0.0060643351229165976</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.0038274449440508507</v>
+        <v>0.0060818967482638153</v>
       </c>
       <c r="AM4" s="0">
-        <v>0.0038283012458907306</v>
+        <v>0.00609110322743045</v>
       </c>
       <c r="AN4" s="0">
-        <v>0.0037680738524394908</v>
+        <v>0.0060886364562499073</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.0036804563481211972</v>
+        <v>0.0060801792420137613</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>172</v>
+        <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>-0.4827887915091037</v>
+        <v>-0.50274217366666674</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.00093305878912203211</v>
+        <v>0.0018718560552081764</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.00039476648597719377</v>
+        <v>0.0023693725916666404</v>
       </c>
       <c r="E5" s="0">
-        <v>0.00096979470390512468</v>
+        <v>0.0037398089274304769</v>
       </c>
       <c r="F5" s="0">
-        <v>0.0014857990543022392</v>
+        <v>0.0041568167986110738</v>
       </c>
       <c r="G5" s="0">
-        <v>0.00028413810071137302</v>
+        <v>0.002931806471527687</v>
       </c>
       <c r="H5" s="0">
-        <v>-0.00010334559595664983</v>
+        <v>0.0025658316555554617</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.0007894111737963283</v>
+        <v>0.0019016814190971898</v>
       </c>
       <c r="J5" s="0">
-        <v>-0.0028407615835654432</v>
+        <v>-0.00017144462326390639</v>
       </c>
       <c r="K5" s="0">
-        <v>0.0033968240278848261</v>
+        <v>0.0059972802607637932</v>
       </c>
       <c r="L5" s="0">
-        <v>0.0023570413477065344</v>
+        <v>0.0047908967972221115</v>
       </c>
       <c r="M5" s="0">
-        <v>0.0015094581776927685</v>
+        <v>0.0039442918208332798</v>
       </c>
       <c r="N5" s="0">
-        <v>0.0021125915897757253</v>
+        <v>0.0049348732881943627</v>
       </c>
       <c r="O5" s="0">
-        <v>0.0019084614321338567</v>
+        <v>0.0047281903177083251</v>
       </c>
       <c r="P5" s="0">
-        <v>0.0019418997467842147</v>
+        <v>0.0041786772211804832</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.0013796007075831396</v>
+        <v>0.0035906633548610789</v>
       </c>
       <c r="R5" s="0">
-        <v>0.0014270607882068131</v>
+        <v>0.0037480568298610679</v>
       </c>
       <c r="S5" s="0">
-        <v>0.0013841283584009045</v>
+        <v>0.0038882681749999315</v>
       </c>
       <c r="T5" s="0">
-        <v>0.0029271538241418815</v>
+        <v>0.0051590866725693138</v>
       </c>
       <c r="U5" s="0">
-        <v>0.0027058040595424604</v>
+        <v>0.0042231317510415534</v>
       </c>
       <c r="V5" s="0">
-        <v>0.0030333876344351141</v>
+        <v>0.0045637529944443367</v>
       </c>
       <c r="W5" s="0">
-        <v>0.0035366971368161471</v>
+        <v>0.0050200172732637891</v>
       </c>
       <c r="X5" s="0">
-        <v>0.0035849620568428331</v>
+        <v>0.004976146280902761</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.0035911178332263538</v>
+        <v>0.0049901479562499684</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.0031871496164249113</v>
+        <v>0.0047273029826387933</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.0031818022912238897</v>
+        <v>0.0048164074361110587</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.0032833576772886008</v>
+        <v>0.0048908601809026786</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.0032841576486102309</v>
+        <v>0.0049393252482638483</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.0031616482061682105</v>
+        <v>0.0049696540892359984</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.0032650272767845157</v>
+        <v>0.005011268697916571</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.0033949676435666709</v>
+        <v>0.0050524328465277333</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.0035407298414859567</v>
+        <v>0.0050948672354166336</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.0035033909035794286</v>
+        <v>0.0051169453545137911</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.0032926918956808771</v>
+        <v>0.0051172932142360414</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.0031735287858333239</v>
+        <v>0.0051242388326387944</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.0032215423000871435</v>
+        <v>0.0051479494885416366</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.003292251469204921</v>
+        <v>0.0051732006107638182</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.003345982329356012</v>
+        <v>0.005195313597916639</v>
       </c>
       <c r="AN5" s="0">
-        <v>0.0033510137443018007</v>
+        <v>0.005209632444097223</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.0032876550610315691</v>
+        <v>0.0052129319298610532</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>173</v>
+        <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.48122513474749917</v>
+        <v>-0.50470724166666681</v>
       </c>
       <c r="C6" s="0">
-        <v>-0.00069250784800500842</v>
+        <v>0.0020329393027777032</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.00072108933922543361</v>
+        <v>0.0019076739225694088</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.00017252818368934664</v>
+        <v>0.0023872155673609896</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.00063601395281320805</v>
+        <v>0.0018722671517359402</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.00039916462106276418</v>
+        <v>0.0019753683065971699</v>
       </c>
       <c r="H6" s="0">
-        <v>-0.00048142949975665816</v>
+        <v>0.0019185220874999294</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.0010028043989358526</v>
+        <v>0.0014377883645832479</v>
       </c>
       <c r="J6" s="0">
-        <v>-0.0025812088772941277</v>
+        <v>-8.6631589930608044e-05</v>
       </c>
       <c r="K6" s="0">
-        <v>0.0018240523753960125</v>
+        <v>0.0043818390083332215</v>
       </c>
       <c r="L6" s="0">
-        <v>0.0012392455903026955</v>
+        <v>0.0034525498385415969</v>
       </c>
       <c r="M6" s="0">
-        <v>0.00091508063954931496</v>
+        <v>0.0029860478597221744</v>
       </c>
       <c r="N6" s="0">
-        <v>0.0018266515949459383</v>
+        <v>0.0039348617381943498</v>
       </c>
       <c r="O6" s="0">
-        <v>0.0016440489266426606</v>
+        <v>0.0041621555437499902</v>
       </c>
       <c r="P6" s="0">
-        <v>0.0012213701768027385</v>
+        <v>0.0037453569201388315</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.0011969144506278062</v>
+        <v>0.0030639825461804548</v>
       </c>
       <c r="R6" s="0">
-        <v>0.0012197740889111075</v>
+        <v>0.0030819299315972266</v>
       </c>
       <c r="S6" s="0">
-        <v>0.001273255678725993</v>
+        <v>0.0032569399291665917</v>
       </c>
       <c r="T6" s="0">
-        <v>0.0024738097868804987</v>
+        <v>0.0046652203520832769</v>
       </c>
       <c r="U6" s="0">
-        <v>0.002262584166552839</v>
+        <v>0.004082002109374927</v>
       </c>
       <c r="V6" s="0">
-        <v>0.0032169208956970285</v>
+        <v>0.0042423503826388145</v>
       </c>
       <c r="W6" s="0">
-        <v>0.0034177816179182252</v>
+        <v>0.004443875804513886</v>
       </c>
       <c r="X6" s="0">
-        <v>0.0033448249670005037</v>
+        <v>0.0042965368072915852</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.0034536461093880866</v>
+        <v>0.0042997017378471067</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.0031001760098184339</v>
+        <v>0.0039547885434027541</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.0030988927970268532</v>
+        <v>0.0041294267520832761</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.0031145081655162277</v>
+        <v>0.0042514497774304716</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.0032219700726250911</v>
+        <v>0.0043240983423610824</v>
       </c>
       <c r="AD6" s="0">
-        <v>0.00323753089180423</v>
+        <v>0.0043932093618054826</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.0031231030976869856</v>
+        <v>0.0044558482190971693</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.0032519266498872157</v>
+        <v>0.0045108069107638879</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.003408605062526826</v>
+        <v>0.004562116408333261</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.0035824161462768567</v>
+        <v>0.0046135225465277476</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.0035541118943258621</v>
+        <v>0.0046536129124999945</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.0033328496453527423</v>
+        <v>0.0046786317267360489</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.0032109406821726472</v>
+        <v>0.004703596206249939</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.0032731859843662114</v>
+        <v>0.004736462968749966</v>
       </c>
       <c r="AM6" s="0">
-        <v>0.0033599629452635282</v>
+        <v>0.0047691069586804904</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.003427376166149132</v>
+        <v>0.0047986735402776879</v>
       </c>
       <c r="AO6" s="0">
-        <v>0.0034398137263500494</v>
+        <v>0.0048213356777776495</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>174</v>
+        <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>-0.48003154174720664</v>
+        <v>-0.50929118566666676</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.001450334737728487</v>
+        <v>0.00093254572500001132</v>
       </c>
       <c r="D7" s="0">
-        <v>-0.0011528640951902203</v>
+        <v>0.001278245295138869</v>
       </c>
       <c r="E7" s="0">
-        <v>-0.0010139597323016725</v>
+        <v>0.0013040787659721613</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.00041141794567517431</v>
+        <v>0.0017960121371528581</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.00081334240700015048</v>
+        <v>0.0013575378864583154</v>
       </c>
       <c r="H7" s="0">
-        <v>-0.00085431658771822905</v>
+        <v>0.001146133818402784</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.0011626440656327675</v>
+        <v>0.00087212198611108559</v>
       </c>
       <c r="J7" s="0">
-        <v>-0.00243194361383825</v>
+        <v>-0.00032131552430553299</v>
       </c>
       <c r="K7" s="0">
-        <v>0.0012450565408889114</v>
+        <v>0.0035036356555554482</v>
       </c>
       <c r="L7" s="0">
-        <v>0.00085900126009885724</v>
+        <v>0.0029570276322914979</v>
       </c>
       <c r="M7" s="0">
-        <v>0.00048532935517886511</v>
+        <v>0.0022077812732638202</v>
       </c>
       <c r="N7" s="0">
-        <v>0.0012033349275739624</v>
+        <v>0.0027746268947916874</v>
       </c>
       <c r="O7" s="0">
-        <v>0.0013738142284016042</v>
+        <v>0.0029406845124999026</v>
       </c>
       <c r="P7" s="0">
-        <v>0.00085210026992715848</v>
+        <v>0.0029134241031248402</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.00083360156583511813</v>
+        <v>0.0029242377586805035</v>
       </c>
       <c r="R7" s="0">
-        <v>0.0012963156906844464</v>
+        <v>0.0026114381111109757</v>
       </c>
       <c r="S7" s="0">
-        <v>0.0014992877190453946</v>
+        <v>0.0028073177999999306</v>
       </c>
       <c r="T7" s="0">
-        <v>0.0025512208341338383</v>
+        <v>0.004000067188194345</v>
       </c>
       <c r="U7" s="0">
-        <v>0.0019915218097699694</v>
+        <v>0.0036220217538193715</v>
       </c>
       <c r="V7" s="0">
-        <v>0.0027893266793266314</v>
+        <v>0.0039912563232638578</v>
       </c>
       <c r="W7" s="0">
-        <v>0.0038895022470258334</v>
+        <v>0.0041017242652777166</v>
       </c>
       <c r="X7" s="0">
-        <v>0.0034715106376480009</v>
+        <v>0.0036738158229165934</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.0036600328521652625</v>
+        <v>0.00377826995173608</v>
       </c>
       <c r="Z7" s="0">
-        <v>0.0035086239902280547</v>
+        <v>0.0034961525284721295</v>
       </c>
       <c r="AA7" s="0">
-        <v>0.0036971730467271757</v>
+        <v>0.003713637877430509</v>
       </c>
       <c r="AB7" s="0">
-        <v>0.0036708151967850822</v>
+        <v>0.00389534270381936</v>
       </c>
       <c r="AC7" s="0">
-        <v>0.0036997970643742328</v>
+        <v>0.0040493114489583149</v>
       </c>
       <c r="AD7" s="0">
-        <v>0.0038435386097986357</v>
+        <v>0.0041461614218749054</v>
       </c>
       <c r="AE7" s="0">
-        <v>0.0038814152138405</v>
+        <v>0.0042465224371526786</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.0037671939015503364</v>
+        <v>0.004347754480902688</v>
       </c>
       <c r="AG7" s="0">
-        <v>0.003931717232402987</v>
+        <v>0.0044180753145832705</v>
       </c>
       <c r="AH7" s="0">
-        <v>0.0041279671577751365</v>
+        <v>0.0044813893180555295</v>
       </c>
       <c r="AI7" s="0">
-        <v>0.0043442449969414709</v>
+        <v>0.0045436759805554941</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.0043237287584966255</v>
+        <v>0.0046055337437499455</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.0040755477010931962</v>
+        <v>0.0046603354708332767</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.0039421162005892629</v>
+        <v>0.0047070564114582436</v>
       </c>
       <c r="AM7" s="0">
-        <v>0.0040240406716185451</v>
+        <v>0.0047509264465277479</v>
       </c>
       <c r="AN7" s="0">
-        <v>0.0041342505921941886</v>
+        <v>0.0047925061677082659</v>
       </c>
       <c r="AO7" s="0">
-        <v>0.0042212661305847665</v>
+        <v>0.0048311798524304783</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>175</v>
+        <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>-0.47671406557554208</v>
+        <v>-0.51378135466666675</v>
       </c>
       <c r="C8" s="0">
-        <v>-0.0017098659653945747</v>
+        <v>0.0004059450753471916</v>
       </c>
       <c r="D8" s="0">
-        <v>-0.0018354693796918675</v>
+        <v>0.00023814120034715367</v>
       </c>
       <c r="E8" s="0">
-        <v>-0.00016439814433139022</v>
+        <v>0.001946030269791676</v>
       </c>
       <c r="F8" s="0">
-        <v>-0.00027728107600588636</v>
+        <v>0.0016896779281250223</v>
       </c>
       <c r="G8" s="0">
-        <v>-0.0013837728688707585</v>
+        <v>0.00041058338437493982</v>
       </c>
       <c r="H8" s="0">
-        <v>-0.001329528114448808</v>
+        <v>0.00044884156944446918</v>
       </c>
       <c r="I8" s="0">
-        <v>-0.0017348961874466551</v>
+        <v>-0.00015662179270847787</v>
       </c>
       <c r="J8" s="0">
-        <v>-0.002712538629090766</v>
+        <v>-0.001072589937152757</v>
       </c>
       <c r="K8" s="0">
-        <v>0.00051901192337694413</v>
+        <v>0.0023349780392359913</v>
       </c>
       <c r="L8" s="0">
-        <v>0.00027263569268209942</v>
+        <v>0.0020153852305555549</v>
       </c>
       <c r="M8" s="0">
-        <v>3.4117418769241681e-05</v>
+        <v>0.0016128073020833518</v>
       </c>
       <c r="N8" s="0">
-        <v>0.00060493111728621152</v>
+        <v>0.0017621648211804124</v>
       </c>
       <c r="O8" s="0">
-        <v>0.00066381839077489513</v>
+        <v>0.0015929735565970997</v>
       </c>
       <c r="P8" s="0">
-        <v>0.00051056718228953413</v>
+        <v>0.0014230496871527332</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.00060560566792888793</v>
+        <v>0.0021408942746526938</v>
       </c>
       <c r="R8" s="0">
-        <v>0.00091408372590306985</v>
+        <v>0.0024854256684025962</v>
       </c>
       <c r="S8" s="0">
-        <v>0.0012702720208886409</v>
+        <v>0.0018883146305554992</v>
       </c>
       <c r="T8" s="0">
-        <v>0.0023154534243786662</v>
+        <v>0.0029113134458332857</v>
       </c>
       <c r="U8" s="0">
-        <v>0.0019893879099134315</v>
+        <v>0.0026816231465277007</v>
       </c>
       <c r="V8" s="0">
-        <v>0.0023788866607457604</v>
+        <v>0.0033249129062499772</v>
       </c>
       <c r="W8" s="0">
-        <v>0.0030615555283495244</v>
+        <v>0.0034441387840277171</v>
       </c>
       <c r="X8" s="0">
-        <v>0.0034333596317617787</v>
+        <v>0.0025651893951388889</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.0037801013399258454</v>
+        <v>0.0029283120281249353</v>
       </c>
       <c r="Z8" s="0">
-        <v>0.0037801072901120225</v>
+        <v>0.0028156913565971498</v>
       </c>
       <c r="AA8" s="0">
-        <v>0.0041677908944367514</v>
+        <v>0.003058181833333284</v>
       </c>
       <c r="AB8" s="0">
-        <v>0.0043730065770713478</v>
+        <v>0.00328505338923607</v>
       </c>
       <c r="AC8" s="0">
-        <v>0.0043548898152495075</v>
+        <v>0.0035160737649304603</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.0044189907254966188</v>
+        <v>0.0037268028659721559</v>
       </c>
       <c r="AE8" s="0">
-        <v>0.0046141428370075066</v>
+        <v>0.0038565059298610875</v>
       </c>
       <c r="AF8" s="0">
-        <v>0.0046841592435456492</v>
+        <v>0.0039982449756943983</v>
       </c>
       <c r="AG8" s="0">
-        <v>0.004573632742059297</v>
+        <v>0.0041515557222221991</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.0047879370161840185</v>
+        <v>0.0042427660364582351</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.0050384650218069371</v>
+        <v>0.0043220130076388474</v>
       </c>
       <c r="AJ8" s="0">
-        <v>0.0053128523035827491</v>
+        <v>0.004398737899652728</v>
       </c>
       <c r="AK8" s="0">
-        <v>0.0053049396703973573</v>
+        <v>0.0044901340677082624</v>
       </c>
       <c r="AL8" s="0">
-        <v>0.0050237100054028594</v>
+        <v>0.0045858364611111035</v>
       </c>
       <c r="AM8" s="0">
-        <v>0.0048773403591650388</v>
+        <v>0.0046626343802082526</v>
       </c>
       <c r="AN8" s="0">
-        <v>0.0049870990495839984</v>
+        <v>0.0047216237052082888</v>
       </c>
       <c r="AO8" s="0">
-        <v>0.0051301242250866297</v>
+        <v>0.0047756225399305232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>176</v>
+        <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>-0.47333654983260626</v>
+        <v>-0.52019021066666682</v>
       </c>
       <c r="C9" s="0">
-        <v>-0.0027325144384951483</v>
+        <v>-0.0008740037187500169</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.0026447414233570221</v>
+        <v>-0.000789853942708473</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.0024982279448358957</v>
+        <v>-0.00068247235694451902</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.0028403443420224606</v>
+        <v>-0.0011233589993057116</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.002480072873055239</v>
+        <v>-0.00092194845520832212</v>
       </c>
       <c r="H9" s="0">
-        <v>-0.0023248894493110295</v>
+        <v>-0.00087354198020839213</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.0025076044603681846</v>
+        <v>-0.0010799711399307466</v>
       </c>
       <c r="J9" s="0">
-        <v>-0.003224707639192359</v>
+        <v>-0.0019961272604167571</v>
       </c>
       <c r="K9" s="0">
-        <v>-0.00077407130855550177</v>
+        <v>0.00061035932708331051</v>
       </c>
       <c r="L9" s="0">
-        <v>-0.00064226584115906205</v>
+        <v>0.00067062152951380405</v>
       </c>
       <c r="M9" s="0">
-        <v>-0.00077614945192422402</v>
+        <v>0.00047321419305557198</v>
       </c>
       <c r="N9" s="0">
-        <v>-0.00017087640009838534</v>
+        <v>0.00090692773749989674</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.00017868852626112819</v>
+        <v>0.00035806956249989554</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.00036936482825578043</v>
+        <v>-0.0001039490652778299</v>
       </c>
       <c r="Q9" s="0">
-        <v>8.5297883985091527e-05</v>
+        <v>0.00034396624409716026</v>
       </c>
       <c r="R9" s="0">
-        <v>0.00028693882621100286</v>
+        <v>0.0012650117579861009</v>
       </c>
       <c r="S9" s="0">
-        <v>0.00084604653083242276</v>
+        <v>0.0018397947829861265</v>
       </c>
       <c r="T9" s="0">
-        <v>0.0019851376048860558</v>
+        <v>0.0018347045982638473</v>
       </c>
       <c r="U9" s="0">
-        <v>0.0016661635322137158</v>
+        <v>0.0014005294354166305</v>
       </c>
       <c r="V9" s="0">
-        <v>0.0022917611520406056</v>
+        <v>0.0021666703392360103</v>
       </c>
       <c r="W9" s="0">
-        <v>0.0025619749858899477</v>
+        <v>0.002699854906944299</v>
       </c>
       <c r="X9" s="0">
-        <v>0.002715078811804883</v>
+        <v>0.002136571004166643</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.0039915650714220097</v>
+        <v>0.0019201368218748622</v>
       </c>
       <c r="Z9" s="0">
-        <v>0.0038714263748072519</v>
+        <v>0.0017896289451387886</v>
       </c>
       <c r="AA9" s="0">
-        <v>0.0042508537418281533</v>
+        <v>0.0020374872777776383</v>
       </c>
       <c r="AB9" s="0">
-        <v>0.0046569094560783286</v>
+        <v>0.0022408224246527331</v>
       </c>
       <c r="AC9" s="0">
-        <v>0.0049069695840325278</v>
+        <v>0.0024987079545137898</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.0049238840993690025</v>
+        <v>0.0028082118652777432</v>
       </c>
       <c r="AE9" s="0">
-        <v>0.005033805466738539</v>
+        <v>0.0030839596048610747</v>
       </c>
       <c r="AF9" s="0">
-        <v>0.0052918058714209182</v>
+        <v>0.0032488551611110084</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.0054011478690863535</v>
+        <v>0.003436010707986048</v>
       </c>
       <c r="AH9" s="0">
-        <v>0.0052948802667586725</v>
+        <v>0.0036473845156249633</v>
       </c>
       <c r="AI9" s="0">
-        <v>0.0055703082854008934</v>
+        <v>0.0037607336652776828</v>
       </c>
       <c r="AJ9" s="0">
-        <v>0.0058885349099337403</v>
+        <v>0.0038574999402776759</v>
       </c>
       <c r="AK9" s="0">
-        <v>0.0062354506725634806</v>
+        <v>0.0039501025979165596</v>
       </c>
       <c r="AL9" s="0">
-        <v>0.0062442161141966213</v>
+        <v>0.004075554295833228</v>
       </c>
       <c r="AM9" s="0">
-        <v>0.0059230421370876085</v>
+        <v>0.0042186965527776787</v>
       </c>
       <c r="AN9" s="0">
-        <v>0.0057611739534196849</v>
+        <v>0.0043300146256943228</v>
       </c>
       <c r="AO9" s="0">
-        <v>0.0059062291576458814</v>
+        <v>0.0044063985809027475</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>177</v>
+        <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>-0.46922614682829761</v>
+        <v>-0.5267394556666668</v>
       </c>
       <c r="C10" s="0">
-        <v>-0.0038225017972868813</v>
+        <v>-0.0019022347256943961</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.0038511176792528912</v>
+        <v>-0.0020057106954862736</v>
       </c>
       <c r="E10" s="0">
-        <v>-0.0033869195487313264</v>
+        <v>-0.0015554537170140437</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.0030904602475158027</v>
+        <v>-0.0013172738322917441</v>
       </c>
       <c r="G10" s="0">
-        <v>-0.0034308840470465007</v>
+        <v>-0.0017330117083332866</v>
       </c>
       <c r="H10" s="0">
-        <v>-0.0035872600856778347</v>
+        <v>-0.0021028096680556487</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.0036835273636638965</v>
+        <v>-0.0023348679204862064</v>
       </c>
       <c r="J10" s="0">
-        <v>-0.0042592122504391816</v>
+        <v>-0.0029175823281250013</v>
       </c>
       <c r="K10" s="0">
-        <v>-0.0025532582155671224</v>
+        <v>-0.0013572235100693941</v>
       </c>
       <c r="L10" s="0">
-        <v>-0.0022630159069482736</v>
+        <v>-0.0011525842541667561</v>
       </c>
       <c r="M10" s="0">
-        <v>-0.0021354875205431556</v>
+        <v>-0.0011169942826390056</v>
       </c>
       <c r="N10" s="0">
-        <v>-0.001483743230543344</v>
+        <v>-0.00052226170069458178</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.0012300954904311268</v>
+        <v>-0.0005229103572917948</v>
       </c>
       <c r="P10" s="0">
-        <v>-0.001765701031080813</v>
+        <v>-0.0016596589326389752</v>
       </c>
       <c r="Q10" s="0">
-        <v>-0.0012483789202817897</v>
+        <v>-0.0014247299197917007</v>
       </c>
       <c r="R10" s="0">
-        <v>-0.00065437972308440839</v>
+        <v>-0.00088592610034732202</v>
       </c>
       <c r="S10" s="0">
-        <v>-0.00022772535217158163</v>
+        <v>0.0003199413437500187</v>
       </c>
       <c r="T10" s="0">
-        <v>0.00094187529684258697</v>
+        <v>0.0014482753961805313</v>
       </c>
       <c r="U10" s="0">
-        <v>0.0010761990535097521</v>
+        <v>0.0001898584534721923</v>
       </c>
       <c r="V10" s="0">
-        <v>0.0016522528209919063</v>
+        <v>0.00067134313923611355</v>
       </c>
       <c r="W10" s="0">
-        <v>0.0022485538850229858</v>
+        <v>0.001358094420833178</v>
       </c>
       <c r="X10" s="0">
-        <v>0.0021365009932022838</v>
+        <v>0.0015104520295138313</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.0029392161919400972</v>
+        <v>0.0014999876482638124</v>
       </c>
       <c r="Z10" s="0">
-        <v>0.0035988616855635036</v>
+        <v>0.00036500025729163665</v>
       </c>
       <c r="AA10" s="0">
-        <v>0.0038152045589892603</v>
+        <v>0.0005824089204860541</v>
       </c>
       <c r="AB10" s="0">
-        <v>0.0042552745189372021</v>
+        <v>0.00083626301076383802</v>
       </c>
       <c r="AC10" s="0">
-        <v>0.0047561092749863754</v>
+        <v>0.0010690753232638905</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.0051002648481903723</v>
+        <v>0.0013957404496526826</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.0051791823498448242</v>
+        <v>0.0017984108541665988</v>
       </c>
       <c r="AF10" s="0">
-        <v>0.0053667073763332129</v>
+        <v>0.0021589161857638035</v>
       </c>
       <c r="AG10" s="0">
-        <v>0.0057022284316892713</v>
+        <v>0.0023638208388888637</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.0058719343624971665</v>
+        <v>0.002608641327083272</v>
       </c>
       <c r="AI10" s="0">
-        <v>0.0057966955060015923</v>
+        <v>0.0028979250843749198</v>
       </c>
       <c r="AJ10" s="0">
-        <v>0.0061488443809375459</v>
+        <v>0.0030408956402777076</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.006547014303586729</v>
+        <v>0.0031593398409721089</v>
       </c>
       <c r="AL10" s="0">
-        <v>0.0069786023773559802</v>
+        <v>0.0032716487899304703</v>
       </c>
       <c r="AM10" s="0">
-        <v>0.0070202280928007843</v>
+        <v>0.0034421725854166248</v>
       </c>
       <c r="AN10" s="0">
-        <v>0.0066788395172929227</v>
+        <v>0.0036509971350693893</v>
       </c>
       <c r="AO10" s="0">
-        <v>0.0065181561088925033</v>
+        <v>0.0038111977003472135</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>-0.46580074312599562</v>
+        <v>-0.53416697766666676</v>
       </c>
       <c r="C11" s="0">
-        <v>-0.0046347963244698365</v>
+        <v>-0.0023926686965278776</v>
       </c>
       <c r="D11" s="0">
-        <v>-0.0046530351509976309</v>
+        <v>-0.0023956012697916576</v>
       </c>
       <c r="E11" s="0">
-        <v>-0.0045526697213157385</v>
+        <v>-0.0023713778809028039</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.0044441535597322668</v>
+        <v>-0.0023343691312500692</v>
       </c>
       <c r="G11" s="0">
-        <v>-0.0044973629793343406</v>
+        <v>-0.0024873625361112595</v>
       </c>
       <c r="H11" s="0">
-        <v>-0.0045068807682909218</v>
+        <v>-0.0025324071260417478</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.0045984910873528295</v>
+        <v>-0.0028309569968750781</v>
       </c>
       <c r="J11" s="0">
-        <v>-0.0052815717251761818</v>
+        <v>-0.0036447205833334273</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.0041421596000414951</v>
+        <v>-0.0024393636083335215</v>
       </c>
       <c r="L11" s="0">
-        <v>-0.0039313638760848924</v>
+        <v>-0.0025981001586805616</v>
       </c>
       <c r="M11" s="0">
-        <v>-0.0038481888975432921</v>
+        <v>-0.0026393443673611294</v>
       </c>
       <c r="N11" s="0">
-        <v>-0.003255247148021112</v>
+        <v>-0.0021597313083334671</v>
       </c>
       <c r="O11" s="0">
-        <v>-0.002890113533134675</v>
+        <v>-0.0019357323868055554</v>
       </c>
       <c r="P11" s="0">
-        <v>-0.0031633324284907616</v>
+        <v>-0.0025086462586805247</v>
       </c>
       <c r="Q11" s="0">
-        <v>-0.0031899801155906293</v>
+        <v>-0.0031029726152779213</v>
       </c>
       <c r="R11" s="0">
-        <v>-0.0027318237462555239</v>
+        <v>-0.0030071145479166894</v>
       </c>
       <c r="S11" s="0">
-        <v>-0.0020031819978312271</v>
+        <v>-0.0024106809215278524</v>
       </c>
       <c r="T11" s="0">
-        <v>-0.0006874345707475471</v>
+        <v>-0.00032664623194444964</v>
       </c>
       <c r="U11" s="0">
-        <v>-0.00023189254339839316</v>
+        <v>-6.0833586458475253e-05</v>
       </c>
       <c r="V11" s="0">
-        <v>9.3717840789708795e-05</v>
+        <v>-0.0012201200368057163</v>
       </c>
       <c r="W11" s="0">
-        <v>0.00089443870661587432</v>
+        <v>-0.0005914646861112649</v>
       </c>
       <c r="X11" s="0">
-        <v>0.0011276352669762346</v>
+        <v>-0.00033705003506945361</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.0016686869296466122</v>
+        <v>0.00049665725243058876</v>
       </c>
       <c r="Z11" s="0">
-        <v>0.0020302098547785308</v>
+        <v>-9.9045952777876423e-05</v>
       </c>
       <c r="AA11" s="0">
-        <v>0.0028245698318855039</v>
+        <v>-0.0012790440298611769</v>
       </c>
       <c r="AB11" s="0">
-        <v>0.0030338277491364085</v>
+        <v>-0.0010957909861111781</v>
       </c>
       <c r="AC11" s="0">
-        <v>0.003523266823841853</v>
+        <v>-0.0008573763458333836</v>
       </c>
       <c r="AD11" s="0">
-        <v>0.0041346559081435474</v>
+        <v>-0.00059094257881958569</v>
       </c>
       <c r="AE11" s="0">
-        <v>0.0046152596016577063</v>
+        <v>-0.00017166774375004801</v>
       </c>
       <c r="AF11" s="0">
-        <v>0.0048248732562815588</v>
+        <v>0.00036943384444443252</v>
       </c>
       <c r="AG11" s="0">
-        <v>0.0051560371069968025</v>
+        <v>0.00085960465173606825</v>
       </c>
       <c r="AH11" s="0">
-        <v>0.0055970230031713308</v>
+        <v>0.0011210676368055283</v>
       </c>
       <c r="AI11" s="0">
-        <v>0.0058729221667762066</v>
+        <v>0.0014550042184026668</v>
       </c>
       <c r="AJ11" s="0">
-        <v>0.005892583392077988</v>
+        <v>0.0018683357249999477</v>
       </c>
       <c r="AK11" s="0">
-        <v>0.0063464615137763247</v>
+        <v>0.002057800126041565</v>
       </c>
       <c r="AL11" s="0">
-        <v>0.0068426148763114369</v>
+        <v>0.0022094327899305211</v>
       </c>
       <c r="AM11" s="0">
-        <v>0.0073753528072630914</v>
+        <v>0.0023517921927082575</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.0074875140062831136</v>
+        <v>0.0025946531288194023</v>
       </c>
       <c r="AO11" s="0">
-        <v>0.0071815022250575344</v>
+        <v>0.0029112293253472084</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>179</v>
+        <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>-0.46299133347111643</v>
+        <v>-0.54010278066666673</v>
       </c>
       <c r="C12" s="0">
-        <v>-0.0042518415929578279</v>
+        <v>-0.0012589136989583629</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.0042973649919578194</v>
+        <v>-0.0013484904135416817</v>
       </c>
       <c r="E12" s="0">
-        <v>-0.0040759065308804687</v>
+        <v>-0.0011104577222222911</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.0042897694640181006</v>
+        <v>-0.0014117062124999755</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.0044971072432772874</v>
+        <v>-0.0017060296013888801</v>
       </c>
       <c r="H12" s="0">
-        <v>-0.0046358179102136132</v>
+        <v>-0.0019329867430557526</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.004482918420275539</v>
+        <v>-0.0018152979701390182</v>
       </c>
       <c r="J12" s="0">
-        <v>-0.0052720398913033151</v>
+        <v>-0.0027931833152778909</v>
       </c>
       <c r="K12" s="0">
-        <v>-0.00490472243618717</v>
+        <v>-0.0024556320791667688</v>
       </c>
       <c r="L12" s="0">
-        <v>-0.0044379756244972146</v>
+        <v>-0.0020892245600695478</v>
       </c>
       <c r="M12" s="0">
-        <v>-0.004961491959499631</v>
+        <v>-0.0030010287576388581</v>
       </c>
       <c r="N12" s="0">
-        <v>-0.0045739158272504743</v>
+        <v>-0.0027473303048612951</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.0045316604982063025</v>
+        <v>-0.002898969580902854</v>
       </c>
       <c r="P12" s="0">
-        <v>-0.0045733374856247178</v>
+        <v>-0.0031300779326389741</v>
       </c>
       <c r="Q12" s="0">
-        <v>-0.0044829587438070528</v>
+        <v>-0.0032947748263889576</v>
       </c>
       <c r="R12" s="0">
-        <v>-0.0046752546350502522</v>
+        <v>-0.0040389289263889072</v>
       </c>
       <c r="S12" s="0">
-        <v>-0.0045739894159584904</v>
+        <v>-0.0043563784843749787</v>
       </c>
       <c r="T12" s="0">
-        <v>-0.0035050489756459635</v>
+        <v>-0.0035194275847222345</v>
       </c>
       <c r="U12" s="0">
-        <v>-0.0025886618697923414</v>
+        <v>-0.0020370071708334372</v>
       </c>
       <c r="V12" s="0">
-        <v>-0.0019375240396663496</v>
+        <v>-0.0016345595069445773</v>
       </c>
       <c r="W12" s="0">
-        <v>-0.0019056842230233406</v>
+        <v>-0.0031020246708333152</v>
       </c>
       <c r="X12" s="0">
-        <v>-0.0016085104008307649</v>
+        <v>-0.0030855958704860695</v>
       </c>
       <c r="Y12" s="0">
-        <v>-0.00072740080405769847</v>
+        <v>-0.0022165050329860936</v>
       </c>
       <c r="Z12" s="0">
-        <v>-0.00033088900843530888</v>
+        <v>-0.0016095349246528787</v>
       </c>
       <c r="AA12" s="0">
-        <v>0.00013880602062171787</v>
+        <v>-0.0021270662722222564</v>
       </c>
       <c r="AB12" s="0">
-        <v>0.00032067958366216454</v>
+        <v>-0.0039886739572917995</v>
       </c>
       <c r="AC12" s="0">
-        <v>0.00053929908436184393</v>
+        <v>-0.0038247649531251149</v>
       </c>
       <c r="AD12" s="0">
-        <v>0.0011257000385050397</v>
+        <v>-0.0035526264684028197</v>
       </c>
       <c r="AE12" s="0">
-        <v>0.0018626545562051011</v>
+        <v>-0.0032389964229166956</v>
       </c>
       <c r="AF12" s="0">
-        <v>0.002548967504293842</v>
+        <v>-0.002680240570138992</v>
       </c>
       <c r="AG12" s="0">
-        <v>0.0030156930015521333</v>
+        <v>-0.0019187707357640202</v>
       </c>
       <c r="AH12" s="0">
-        <v>0.0036011396080772307</v>
+        <v>-0.0012243522788195071</v>
       </c>
       <c r="AI12" s="0">
-        <v>0.0041922489350655345</v>
+        <v>-0.00087084777118062728</v>
       </c>
       <c r="AJ12" s="0">
-        <v>0.0046546324246899418</v>
+        <v>-0.00039050541805563197</v>
       </c>
       <c r="AK12" s="0">
-        <v>0.0048905014364045707</v>
+        <v>0.00022761121423597788</v>
       </c>
       <c r="AL12" s="0">
-        <v>0.0054801345306000337</v>
+        <v>0.00049480840277776796</v>
       </c>
       <c r="AM12" s="0">
-        <v>0.0060960963610020014</v>
+        <v>0.00070404531944434591</v>
       </c>
       <c r="AN12" s="0">
-        <v>0.0067489962565769335</v>
+        <v>0.00090023518784715373</v>
       </c>
       <c r="AO12" s="0">
-        <v>0.0070033991602961865</v>
+        <v>0.001266679946180516</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>180</v>
+        <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>-0.45997612626361922</v>
+        <v>-0.54377568666666676</v>
       </c>
       <c r="C13" s="0">
-        <v>-0.0028280648696995536</v>
+        <v>0.00093759804756943276</v>
       </c>
       <c r="D13" s="0">
-        <v>-0.0027777613547997348</v>
+        <v>0.00098620421249984115</v>
       </c>
       <c r="E13" s="0">
-        <v>-0.0028992729317079413</v>
+        <v>0.00083020382152776406</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.002902550466579612</v>
+        <v>0.00080985442673608965</v>
       </c>
       <c r="G13" s="0">
-        <v>-0.002990897329596065</v>
+        <v>0.00067133596319435187</v>
       </c>
       <c r="H13" s="0">
-        <v>-0.0031530363004935169</v>
+        <v>0.00046256228749985782</v>
       </c>
       <c r="I13" s="0">
-        <v>-0.0031617454646445942</v>
+        <v>0.00039138240312497352</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.0035183220881225274</v>
+        <v>-2.0058576736258459e-05</v>
       </c>
       <c r="K13" s="0">
-        <v>-0.0035218176517475275</v>
+        <v>-7.5497335763952123e-05</v>
       </c>
       <c r="L13" s="0">
-        <v>-0.0034364580888188723</v>
+        <v>-7.8916111805549249e-05</v>
       </c>
       <c r="M13" s="0">
-        <v>-0.0038216088593286957</v>
+        <v>-0.00062485710902782099</v>
       </c>
       <c r="N13" s="0">
-        <v>-0.0042034235322278568</v>
+        <v>-0.0012866804635417459</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.004474359985212728</v>
+        <v>-0.0017404332861110641</v>
       </c>
       <c r="P13" s="0">
-        <v>-0.0046450779681558307</v>
+        <v>-0.0020971036072916513</v>
       </c>
       <c r="Q13" s="0">
-        <v>-0.0047816297102924454</v>
+        <v>-0.0024026201020832536</v>
       </c>
       <c r="R13" s="0">
-        <v>-0.0048926128790389711</v>
+        <v>-0.0027633389982638645</v>
       </c>
       <c r="S13" s="0">
-        <v>-0.005520890232192821</v>
+        <v>-0.003872841089583412</v>
       </c>
       <c r="T13" s="0">
-        <v>-0.0053126840034615763</v>
+        <v>-0.004067966273264001</v>
       </c>
       <c r="U13" s="0">
-        <v>-0.0052162971277612269</v>
+        <v>-0.004350294063888982</v>
       </c>
       <c r="V13" s="0">
-        <v>-0.0044625549657682506</v>
+        <v>-0.0032110383677084178</v>
       </c>
       <c r="W13" s="0">
-        <v>-0.003869067654803271</v>
+        <v>-0.0029478177281250231</v>
       </c>
       <c r="X13" s="0">
-        <v>-0.0050639054102452064</v>
+        <v>-0.0055348130409723639</v>
       </c>
       <c r="Y13" s="0">
-        <v>-0.0045150614785918752</v>
+        <v>-0.0052908920253472713</v>
       </c>
       <c r="Z13" s="0">
-        <v>-0.0040614599039330845</v>
+        <v>-0.0049824363972222896</v>
       </c>
       <c r="AA13" s="0">
-        <v>-0.0032915828275329462</v>
+        <v>-0.0040781414652778514</v>
       </c>
       <c r="AB13" s="0">
-        <v>-0.0032604713470853475</v>
+        <v>-0.0050326874284722933</v>
       </c>
       <c r="AC13" s="0">
-        <v>-0.0041921407980913261</v>
+        <v>-0.0078827918295139576</v>
       </c>
       <c r="AD13" s="0">
-        <v>-0.0039694340804264372</v>
+        <v>-0.0077441287843751372</v>
       </c>
       <c r="AE13" s="0">
-        <v>-0.0034454168487788039</v>
+        <v>-0.0076003622874999954</v>
       </c>
       <c r="AF13" s="0">
-        <v>-0.002821868179392506</v>
+        <v>-0.0074809151940973262</v>
       </c>
       <c r="AG13" s="0">
-        <v>-0.0020645199674011461</v>
+        <v>-0.006946257474305606</v>
       </c>
       <c r="AH13" s="0">
-        <v>-0.0013666174998336333</v>
+        <v>-0.0060468370194445287</v>
       </c>
       <c r="AI13" s="0">
-        <v>-0.00050447041027629203</v>
+        <v>-0.0051731678572917716</v>
       </c>
       <c r="AJ13" s="0">
-        <v>0.00013024756931018233</v>
+        <v>-0.0048484907340278216</v>
       </c>
       <c r="AK13" s="0">
-        <v>0.0007717637972144975</v>
+        <v>-0.0042609321079861706</v>
       </c>
       <c r="AL13" s="0">
-        <v>0.0013412376673299642</v>
+        <v>-0.0033738271392361741</v>
       </c>
       <c r="AM13" s="0">
-        <v>0.0020187487426246431</v>
+        <v>-0.0030846431871527922</v>
       </c>
       <c r="AN13" s="0">
-        <v>0.0026711191724088645</v>
+        <v>-0.0029026082815972734</v>
       </c>
       <c r="AO13" s="0">
-        <v>0.003364145181511291</v>
+        <v>-0.0027317998805556076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>-0.45706267950298318</v>
+        <v>-0.5451120816666668</v>
       </c>
       <c r="C14" s="0">
-        <v>-0.0010571449703710711</v>
+        <v>0.003258952246874891</v>
       </c>
       <c r="D14" s="0">
-        <v>-0.0010420372526225297</v>
+        <v>0.0032760685607639006</v>
       </c>
       <c r="E14" s="0">
-        <v>-0.0010831834292016618</v>
+        <v>0.0032246138975694505</v>
       </c>
       <c r="F14" s="0">
-        <v>-0.0011146743225792788</v>
+        <v>0.0031830448809027079</v>
       </c>
       <c r="G14" s="0">
-        <v>-0.0011583813347889049</v>
+        <v>0.0031236138211804261</v>
       </c>
       <c r="H14" s="0">
-        <v>-0.0012716324072058471</v>
+        <v>0.0029819970364582948</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.0012921391135378157</v>
+        <v>0.0029446201718749125</v>
       </c>
       <c r="J14" s="0">
-        <v>-0.0015513781708056396</v>
+        <v>0.0026328376343749404</v>
       </c>
       <c r="K14" s="0">
-        <v>-0.0014810746453941537</v>
+        <v>0.0027135135340277117</v>
       </c>
       <c r="L14" s="0">
-        <v>-0.0015311291412434813</v>
+        <v>0.0026138630072917168</v>
       </c>
       <c r="M14" s="0">
-        <v>-0.0018517376341583014</v>
+        <v>0.0022043917052082525</v>
       </c>
       <c r="N14" s="0">
-        <v>-0.0020528633191080337</v>
+        <v>0.0019227563847221685</v>
       </c>
       <c r="O14" s="0">
-        <v>-0.0025845364445012953</v>
+        <v>0.0012052864961804581</v>
       </c>
       <c r="P14" s="0">
-        <v>-0.0028608095050117743</v>
+        <v>0.00081122831666646843</v>
       </c>
       <c r="Q14" s="0">
-        <v>-0.0032018081503859541</v>
+        <v>0.00033378712395826238</v>
       </c>
       <c r="R14" s="0">
-        <v>-0.0034751248687193703</v>
+        <v>-6.6506729166748713e-05</v>
       </c>
       <c r="S14" s="0">
-        <v>-0.0038547752168035521</v>
+        <v>-0.00064838009062506696</v>
       </c>
       <c r="T14" s="0">
-        <v>-0.0043357814658718796</v>
+        <v>-0.0014533225062499655</v>
       </c>
       <c r="U14" s="0">
-        <v>-0.0049807372528715699</v>
+        <v>-0.0024880300899305929</v>
       </c>
       <c r="V14" s="0">
-        <v>-0.0056674962378029936</v>
+        <v>-0.0035229568670138711</v>
       </c>
       <c r="W14" s="0">
-        <v>-0.0048984206311136758</v>
+        <v>-0.0025350514833334392</v>
       </c>
       <c r="X14" s="0">
-        <v>-0.0051051929667324525</v>
+        <v>-0.0031276072906249999</v>
       </c>
       <c r="Y14" s="0">
-        <v>-0.0068490227580884078</v>
+        <v>-0.005907369944791796</v>
       </c>
       <c r="Z14" s="0">
-        <v>-0.0071534458198518336</v>
+        <v>-0.0065680051218749425</v>
       </c>
       <c r="AA14" s="0">
-        <v>-0.0069923648856798915</v>
+        <v>-0.0066074517086806006</v>
       </c>
       <c r="AB14" s="0">
-        <v>-0.006622276334814714</v>
+        <v>-0.0062425581288195753</v>
       </c>
       <c r="AC14" s="0">
-        <v>-0.0075349189055119448</v>
+        <v>-0.0080290279454862112</v>
       </c>
       <c r="AD14" s="0">
-        <v>-0.0098563548791290589</v>
+        <v>-0.01189313716840279</v>
       </c>
       <c r="AE14" s="0">
-        <v>-0.0097651334087855424</v>
+        <v>-0.011911753951041604</v>
       </c>
       <c r="AF14" s="0">
-        <v>-0.0098129069578811179</v>
+        <v>-0.012378818603819619</v>
       </c>
       <c r="AG14" s="0">
-        <v>-0.0099587263071218568</v>
+        <v>-0.013069032662847258</v>
       </c>
       <c r="AH14" s="0">
-        <v>-0.0097159958675542835</v>
+        <v>-0.013143930084027922</v>
       </c>
       <c r="AI14" s="0">
-        <v>-0.0091520460244908231</v>
+        <v>-0.012514007937500071</v>
       </c>
       <c r="AJ14" s="0">
-        <v>-0.0084732801191806373</v>
+        <v>-0.011963127190972367</v>
       </c>
       <c r="AK14" s="0">
-        <v>-0.0083020812828148993</v>
+        <v>-0.012166992061805659</v>
       </c>
       <c r="AL14" s="0">
-        <v>-0.0078596616087951432</v>
+        <v>-0.011874903290972239</v>
       </c>
       <c r="AM14" s="0">
-        <v>-0.0070908471903534664</v>
+        <v>-0.010917204029513961</v>
       </c>
       <c r="AN14" s="0">
-        <v>-0.0068187266301604765</v>
+        <v>-0.011096065855208337</v>
       </c>
       <c r="AO14" s="0">
-        <v>-0.0066430668884595034</v>
+        <v>-0.011439692864236073</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>-0.4544758345315128</v>
+        <v>-0.54538401416666682</v>
       </c>
       <c r="C15" s="0">
-        <v>-0.00021882356822267024</v>
+        <v>0.0043119079489583037</v>
       </c>
       <c r="D15" s="0">
-        <v>-0.00022082520252508786</v>
+        <v>0.0043097073163192992</v>
       </c>
       <c r="E15" s="0">
-        <v>-0.00022670684913689287</v>
+        <v>0.0043023794392359482</v>
       </c>
       <c r="F15" s="0">
-        <v>-0.00023302216038983969</v>
+        <v>0.0042947198850694637</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.00024746685234733334</v>
+        <v>0.0042760345576388073</v>
       </c>
       <c r="H15" s="0">
-        <v>-0.00026337800718589932</v>
+        <v>0.0042547477750000109</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.00028856718161646144</v>
+        <v>0.0042229447024304543</v>
       </c>
       <c r="J15" s="0">
-        <v>-0.00034070605698777179</v>
+        <v>0.0041604741687499827</v>
       </c>
       <c r="K15" s="0">
-        <v>-0.00034621447970101249</v>
+        <v>0.004153557117708262</v>
       </c>
       <c r="L15" s="0">
-        <v>-0.00033539299245144427</v>
+        <v>0.0041590607614583322</v>
       </c>
       <c r="M15" s="0">
-        <v>-0.00046215420676193331</v>
+        <v>0.0040002896982638259</v>
       </c>
       <c r="N15" s="0">
-        <v>-0.00055387382428051524</v>
+        <v>0.003884843759374923</v>
       </c>
       <c r="O15" s="0">
-        <v>-0.00069393367241260551</v>
+        <v>0.0037090139468749501</v>
       </c>
       <c r="P15" s="0">
-        <v>-0.00094502805750340535</v>
+        <v>0.0033863861090277503</v>
       </c>
       <c r="Q15" s="0">
-        <v>-0.0011515967151416451</v>
+        <v>0.0031246095690972146</v>
       </c>
       <c r="R15" s="0">
-        <v>-0.0013517656613510898</v>
+        <v>0.0028637848652778302</v>
       </c>
       <c r="S15" s="0">
-        <v>-0.0015513056528376756</v>
+        <v>0.0026007332305554298</v>
       </c>
       <c r="T15" s="0">
-        <v>-0.0018505687481742417</v>
+        <v>0.0021905642597221937</v>
       </c>
       <c r="U15" s="0">
-        <v>-0.0024404485168751933</v>
+        <v>0.0014016080451388917</v>
       </c>
       <c r="V15" s="0">
-        <v>-0.0031720815884108133</v>
+        <v>0.00044295978958319715</v>
       </c>
       <c r="W15" s="0">
-        <v>-0.0036883230642568154</v>
+        <v>-0.00025985552013907485</v>
       </c>
       <c r="X15" s="0">
-        <v>-0.0033911283599077913</v>
+        <v>9.9626981597155349e-05</v>
       </c>
       <c r="Y15" s="0">
-        <v>-0.0040599444211939506</v>
+        <v>-0.00086567061666686929</v>
       </c>
       <c r="Z15" s="0">
-        <v>-0.0057932139829883211</v>
+        <v>-0.0031994744954861867</v>
       </c>
       <c r="AA15" s="0">
-        <v>-0.0063008109814751689</v>
+        <v>-0.0039627835774306286</v>
       </c>
       <c r="AB15" s="0">
-        <v>-0.0067282844595136782</v>
+        <v>-0.004589484615625028</v>
       </c>
       <c r="AC15" s="0">
-        <v>-0.0067710495719411901</v>
+        <v>-0.0046975563597222436</v>
       </c>
       <c r="AD15" s="0">
-        <v>-0.0081776772164711686</v>
+        <v>-0.0067036266996527427</v>
       </c>
       <c r="AE15" s="0">
-        <v>-0.010691036382916963</v>
+        <v>-0.010157834427083401</v>
       </c>
       <c r="AF15" s="0">
-        <v>-0.010837966058514725</v>
+        <v>-0.010414189185763978</v>
       </c>
       <c r="AG15" s="0">
-        <v>-0.011478040554670443</v>
+        <v>-0.011406405736805514</v>
       </c>
       <c r="AH15" s="0">
-        <v>-0.012309522129443085</v>
+        <v>-0.012681243906250139</v>
       </c>
       <c r="AI15" s="0">
-        <v>-0.012741534092863882</v>
+        <v>-0.013426156884375096</v>
       </c>
       <c r="AJ15" s="0">
-        <v>-0.01256234783951421</v>
+        <v>-0.013283622095139003</v>
       </c>
       <c r="AK15" s="0">
-        <v>-0.012612215720783637</v>
+        <v>-0.013555566696875077</v>
       </c>
       <c r="AL15" s="0">
-        <v>-0.013070724969404923</v>
+        <v>-0.014364485482986189</v>
       </c>
       <c r="AM15" s="0">
-        <v>-0.01315612610941258</v>
+        <v>-0.014652180604861176</v>
       </c>
       <c r="AN15" s="0">
-        <v>-0.01268598063398213</v>
+        <v>-0.014147040361111141</v>
       </c>
       <c r="AO15" s="0">
-        <v>-0.013165227767042376</v>
+        <v>-0.015058574748263998</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>-0.45231714383433369</v>
+        <v>-0.5454146542666668</v>
       </c>
       <c r="C16" s="0">
-        <v>-2.4486285907121541e-05</v>
+        <v>0.0045521309862500692</v>
       </c>
       <c r="D16" s="0">
-        <v>-2.5414501399534384e-05</v>
+        <v>0.004551325316319299</v>
       </c>
       <c r="E16" s="0">
-        <v>-2.5643048990497963e-05</v>
+        <v>0.0045509407163194515</v>
       </c>
       <c r="F16" s="0">
-        <v>-2.611008635317047e-05</v>
+        <v>0.0045505511084722458</v>
       </c>
       <c r="G16" s="0">
-        <v>-2.7335182329835117e-05</v>
+        <v>0.0045488375643748524</v>
       </c>
       <c r="H16" s="0">
-        <v>-3.174009328571481e-05</v>
+        <v>0.0045438292174304626</v>
       </c>
       <c r="I16" s="0">
-        <v>-4.2384103439818688e-05</v>
+        <v>0.0045307833797222363</v>
       </c>
       <c r="J16" s="0">
-        <v>-4.7946899678796839e-05</v>
+        <v>0.0045242903538889045</v>
       </c>
       <c r="K16" s="0">
-        <v>-4.636176113270718e-05</v>
+        <v>0.0045264007223609903</v>
       </c>
       <c r="L16" s="0">
-        <v>-5.2182991936766676e-05</v>
+        <v>0.0045189494759722013</v>
       </c>
       <c r="M16" s="0">
-        <v>-7.7499295111194133e-05</v>
+        <v>0.0044885830363887713</v>
       </c>
       <c r="N16" s="0">
-        <v>-9.1649016949690854e-05</v>
+        <v>0.0044685073614582063</v>
       </c>
       <c r="O16" s="0">
-        <v>-0.00010658222541531925</v>
+        <v>0.0044490970392360172</v>
       </c>
       <c r="P16" s="0">
-        <v>-0.00013726566629967962</v>
+        <v>0.004411862891666507</v>
       </c>
       <c r="Q16" s="0">
-        <v>-0.0002150102580149027</v>
+        <v>0.0043163303388888963</v>
       </c>
       <c r="R16" s="0">
-        <v>-0.00025834856054507416</v>
+        <v>0.004261338590972108</v>
       </c>
       <c r="S16" s="0">
-        <v>-0.00032441576282388196</v>
+        <v>0.004178010708333236</v>
       </c>
       <c r="T16" s="0">
-        <v>-0.00039785222209759441</v>
+        <v>0.004084635047569396</v>
       </c>
       <c r="U16" s="0">
-        <v>-0.00055836115857749169</v>
+        <v>0.003880079288194338</v>
       </c>
       <c r="V16" s="0">
-        <v>-0.00081512089676866184</v>
+        <v>0.0035548711395831933</v>
       </c>
       <c r="W16" s="0">
-        <v>-0.0010725270413565746</v>
+        <v>0.0032287018555555709</v>
       </c>
       <c r="X16" s="0">
-        <v>-0.0013088088358125805</v>
+        <v>0.0029211234142361153</v>
       </c>
       <c r="Y16" s="0">
-        <v>-0.0012830993519907796</v>
+        <v>0.0029509672239582678</v>
       </c>
       <c r="Z16" s="0">
-        <v>-0.0017437709560330639</v>
+        <v>0.0023515397579860768</v>
       </c>
       <c r="AA16" s="0">
-        <v>-0.002483157854851592</v>
+        <v>0.0013980344854166433</v>
       </c>
       <c r="AB16" s="0">
-        <v>-0.0028694146788614816</v>
+        <v>0.00088194582083323024</v>
       </c>
       <c r="AC16" s="0">
-        <v>-0.0031337977260460503</v>
+        <v>0.00052156769340272382</v>
       </c>
       <c r="AD16" s="0">
-        <v>-0.0032171327007279316</v>
+        <v>0.00039018913437505187</v>
       </c>
       <c r="AE16" s="0">
-        <v>-0.0040750963797110962</v>
+        <v>-0.00073699508923608104</v>
       </c>
       <c r="AF16" s="0">
-        <v>-0.0052826286270493683</v>
+        <v>-0.0023153351940972114</v>
       </c>
       <c r="AG16" s="0">
-        <v>-0.0053706295514880376</v>
+        <v>-0.0024710858680555559</v>
       </c>
       <c r="AH16" s="0">
-        <v>-0.0058732045004176725</v>
+        <v>-0.0031633479461806715</v>
       </c>
       <c r="AI16" s="0">
-        <v>-0.0064531672280942476</v>
+        <v>-0.0039778078072916223</v>
       </c>
       <c r="AJ16" s="0">
-        <v>-0.0068213610465700514</v>
+        <v>-0.0045377240145834108</v>
       </c>
       <c r="AK16" s="0">
-        <v>-0.0067551904750610126</v>
+        <v>-0.0045329532954861973</v>
       </c>
       <c r="AL16" s="0">
-        <v>-0.007035663967127348</v>
+        <v>-0.0049929822718750572</v>
       </c>
       <c r="AM16" s="0">
-        <v>-0.0073872938537746236</v>
+        <v>-0.0055636083506945821</v>
       </c>
       <c r="AN16" s="0">
-        <v>-0.0074899764976742444</v>
+        <v>-0.0058231000187500825</v>
       </c>
       <c r="AO16" s="0">
-        <v>-0.0072454638997024867</v>
+        <v>-0.005628624446180619</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>-0.32180801969403589</v>
+        <v>-0.31117788041103289</v>
       </c>
       <c r="C17" s="0">
-        <v>-0.24835391559249614</v>
+        <v>-0.23541067968596968</v>
       </c>
       <c r="D17" s="0">
-        <v>-0.24106280321397716</v>
+        <v>-0.22728820051482168</v>
       </c>
       <c r="E17" s="0">
-        <v>-0.25204606578150579</v>
+        <v>-0.23888906605653948</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.23647635633247516</v>
+        <v>-0.22422071734019139</v>
       </c>
       <c r="G17" s="0">
-        <v>-0.20380063737077947</v>
+        <v>-0.19172630703164179</v>
       </c>
       <c r="H17" s="0">
-        <v>-0.20358581062784248</v>
+        <v>-0.19131704841236713</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.2129573704653433</v>
+        <v>-0.20056858547375017</v>
       </c>
       <c r="J17" s="0">
-        <v>-0.26268537140661191</v>
+        <v>-0.25012216655180564</v>
       </c>
       <c r="K17" s="0">
-        <v>-0.23550634104633489</v>
+        <v>-0.22315630456115182</v>
       </c>
       <c r="L17" s="0">
-        <v>-0.20065272573098819</v>
+        <v>-0.18808467899294051</v>
       </c>
       <c r="M17" s="0">
-        <v>-0.22820829269792009</v>
+        <v>-0.21480172231507882</v>
       </c>
       <c r="N17" s="0">
-        <v>-0.26095962894372471</v>
+        <v>-0.24666685562155805</v>
       </c>
       <c r="O17" s="0">
-        <v>-0.31651067901876928</v>
+        <v>-0.30093392663928681</v>
       </c>
       <c r="P17" s="0">
-        <v>-0.33516575233036111</v>
+        <v>-0.3185099169438329</v>
       </c>
       <c r="Q17" s="0">
-        <v>-0.29577657503756777</v>
+        <v>-0.27887122783754204</v>
       </c>
       <c r="R17" s="0">
-        <v>-0.29544165464999511</v>
+        <v>-0.27848435743881578</v>
       </c>
       <c r="S17" s="0">
-        <v>-0.28332722052968318</v>
+        <v>-0.26650123039459789</v>
       </c>
       <c r="T17" s="0">
-        <v>-0.26433955356375172</v>
+        <v>-0.24766387710750482</v>
       </c>
       <c r="U17" s="0">
-        <v>-0.26656667277197676</v>
+        <v>-0.24978785084856531</v>
       </c>
       <c r="V17" s="0">
-        <v>-0.26985882499920971</v>
+        <v>-0.25318788634898454</v>
       </c>
       <c r="W17" s="0">
-        <v>-0.2778370240562813</v>
+        <v>-0.26105715902030557</v>
       </c>
       <c r="X17" s="0">
-        <v>-0.28314950592105975</v>
+        <v>-0.26618632837044781</v>
       </c>
       <c r="Y17" s="0">
-        <v>-0.29142796441726215</v>
+        <v>-0.27434822013443649</v>
       </c>
       <c r="Z17" s="0">
-        <v>-0.30792782178134298</v>
+        <v>-0.29072766790040006</v>
       </c>
       <c r="AA17" s="0">
-        <v>-0.29609850403139792</v>
+        <v>-0.27914608162049126</v>
       </c>
       <c r="AB17" s="0">
-        <v>-0.27933588911271917</v>
+        <v>-0.26267245837337638</v>
       </c>
       <c r="AC17" s="0">
-        <v>-0.25733682873041347</v>
+        <v>-0.24104149236037958</v>
       </c>
       <c r="AD17" s="0">
-        <v>-0.24959548975679502</v>
+        <v>-0.23355749774627971</v>
       </c>
       <c r="AE17" s="0">
-        <v>-0.26204215611929976</v>
+        <v>-0.24599093634348607</v>
       </c>
       <c r="AF17" s="0">
-        <v>-0.27396811903430662</v>
+        <v>-0.25775643223659706</v>
       </c>
       <c r="AG17" s="0">
-        <v>-0.27229398784930742</v>
+        <v>-0.25598857464745711</v>
       </c>
       <c r="AH17" s="0">
-        <v>-0.26343876284208384</v>
+        <v>-0.24715890675525681</v>
       </c>
       <c r="AI17" s="0">
-        <v>-0.25172374070099907</v>
+        <v>-0.23602202399367767</v>
       </c>
       <c r="AJ17" s="0">
-        <v>-0.24271651795351434</v>
+        <v>-0.227464963063087</v>
       </c>
       <c r="AK17" s="0">
-        <v>-0.24128398114117788</v>
+        <v>-0.22648570323560008</v>
       </c>
       <c r="AL17" s="0">
-        <v>-0.24557351815178197</v>
+        <v>-0.23112223582062935</v>
       </c>
       <c r="AM17" s="0">
-        <v>-0.24934086584961379</v>
+        <v>-0.23517931979196971</v>
       </c>
       <c r="AN17" s="0">
-        <v>-0.24794350263994924</v>
+        <v>-0.2342672635837228</v>
       </c>
       <c r="AO17" s="0">
-        <v>-0.24229388427584642</v>
+        <v>-0.22904368626774246</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>-0.40816927199948205</v>
+        <v>-0.4217993916666668</v>
       </c>
       <c r="C18" s="0">
-        <v>-0.0015079719626350796</v>
+        <v>-0.00038800602777788826</v>
       </c>
       <c r="D18" s="0">
-        <v>0.00042728031800165489</v>
+        <v>0.001584937964583311</v>
       </c>
       <c r="E18" s="0">
-        <v>-0.003663345315116584</v>
+        <v>-0.0025038902940972552</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.0014818075439845257</v>
+        <v>-0.00013345134270842385</v>
       </c>
       <c r="G18" s="0">
-        <v>0.0062811478108948937</v>
+        <v>0.0076631940197915971</v>
       </c>
       <c r="H18" s="0">
-        <v>0.0038948049391408501</v>
+        <v>0.0047647064777776582</v>
       </c>
       <c r="I18" s="0">
-        <v>-0.00020172908472759765</v>
+        <v>0.0005423724506944394</v>
       </c>
       <c r="J18" s="0">
-        <v>-0.019374801743863967</v>
+        <v>-0.01841208667187505</v>
       </c>
       <c r="K18" s="0">
-        <v>0.014306059354742662</v>
+        <v>0.016457395785763884</v>
       </c>
       <c r="L18" s="0">
-        <v>0.0058162189431997247</v>
+        <v>0.0076983245763888042</v>
       </c>
       <c r="M18" s="0">
-        <v>0.005207754943127918</v>
+        <v>0.006171607600694351</v>
       </c>
       <c r="N18" s="0">
-        <v>0.0083336142407887115</v>
+        <v>0.0093101947715277245</v>
       </c>
       <c r="O18" s="0">
-        <v>0.0080629137465370038</v>
+        <v>0.0091337804739582973</v>
       </c>
       <c r="P18" s="0">
-        <v>0.0067686815380856857</v>
+        <v>0.0080699755934027784</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.0062623016142885346</v>
+        <v>0.0070876446093749434</v>
       </c>
       <c r="R18" s="0">
-        <v>0.0072232310556554213</v>
+        <v>0.0069916013677083222</v>
       </c>
       <c r="S18" s="0">
-        <v>0.0079649784090813358</v>
+        <v>0.0078296779350693901</v>
       </c>
       <c r="T18" s="0">
-        <v>0.012827684813588591</v>
+        <v>0.012673183568402746</v>
       </c>
       <c r="U18" s="0">
-        <v>0.0093555195434861793</v>
+        <v>0.0090222118475693502</v>
       </c>
       <c r="V18" s="0">
-        <v>0.009427570528352025</v>
+        <v>0.0091691154499998762</v>
       </c>
       <c r="W18" s="0">
-        <v>0.011206638379371359</v>
+        <v>0.01124507486458326</v>
       </c>
       <c r="X18" s="0">
-        <v>0.010594741565412957</v>
+        <v>0.010781919059374923</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.011201945995699458</v>
+        <v>0.011356600768055614</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.010934354663839019</v>
+        <v>0.011163509114236081</v>
       </c>
       <c r="AA18" s="0">
-        <v>0.010567534462549988</v>
+        <v>0.01104261085347219</v>
       </c>
       <c r="AB18" s="0">
-        <v>0.010679385016649279</v>
+        <v>0.011057077729861031</v>
       </c>
       <c r="AC18" s="0">
-        <v>0.010860185025781843</v>
+        <v>0.011097694327777741</v>
       </c>
       <c r="AD18" s="0">
-        <v>0.011096365635797523</v>
+        <v>0.011170974005555445</v>
       </c>
       <c r="AE18" s="0">
-        <v>0.011001847016782751</v>
+        <v>0.011174645488194357</v>
       </c>
       <c r="AF18" s="0">
-        <v>0.010594924170671982</v>
+        <v>0.011108785589583281</v>
       </c>
       <c r="AG18" s="0">
-        <v>0.010356861670950179</v>
+        <v>0.011075117525347178</v>
       </c>
       <c r="AH18" s="0">
-        <v>0.010423895532697791</v>
+        <v>0.011105132902083314</v>
       </c>
       <c r="AI18" s="0">
-        <v>0.010533404307279004</v>
+        <v>0.011143589201736026</v>
       </c>
       <c r="AJ18" s="0">
-        <v>0.010613409985105071</v>
+        <v>0.011174609382638812</v>
       </c>
       <c r="AK18" s="0">
-        <v>0.010607560720017117</v>
+        <v>0.011185120936111015</v>
       </c>
       <c r="AL18" s="0">
-        <v>0.010481411747257918</v>
+        <v>0.011166977427430502</v>
       </c>
       <c r="AM18" s="0">
-        <v>0.010301652930195804</v>
+        <v>0.011134836386111013</v>
       </c>
       <c r="AN18" s="0">
-        <v>0.01018690948548695</v>
+        <v>0.011116453798263815</v>
       </c>
       <c r="AO18" s="0">
-        <v>0.010182312957646433</v>
+        <v>0.011122784832638788</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>-0.409903193148974</v>
+        <v>-0.42497280166666679</v>
       </c>
       <c r="C19" s="0">
-        <v>-0.00012403869571397941</v>
+        <v>0.0010369078552083244</v>
       </c>
       <c r="D19" s="0">
-        <v>0.00011873784877303173</v>
+        <v>0.0010437049055554985</v>
       </c>
       <c r="E19" s="0">
-        <v>-0.0016429716253436033</v>
+        <v>-0.00073040200763890926</v>
       </c>
       <c r="F19" s="0">
-        <v>-0.00044030361560526421</v>
+        <v>0.00058703429930545472</v>
       </c>
       <c r="G19" s="0">
-        <v>0.0045146722122708649</v>
+        <v>0.0056780529211805097</v>
       </c>
       <c r="H19" s="0">
-        <v>0.0024729577400278702</v>
+        <v>0.0034646966395833201</v>
       </c>
       <c r="I19" s="0">
-        <v>-0.00080797844880275971</v>
+        <v>-0.00029839255173613657</v>
       </c>
       <c r="J19" s="0">
-        <v>-0.016328180273322002</v>
+        <v>-0.015840694646527875</v>
       </c>
       <c r="K19" s="0">
-        <v>0.01770619677138352</v>
+        <v>0.018953452050347153</v>
       </c>
       <c r="L19" s="0">
-        <v>0.0076639084904716048</v>
+        <v>0.0092562241909721066</v>
       </c>
       <c r="M19" s="0">
-        <v>0.003997797691870919</v>
+        <v>0.0055365574239581985</v>
       </c>
       <c r="N19" s="0">
-        <v>0.0076814060563827891</v>
+        <v>0.0082555069704860484</v>
       </c>
       <c r="O19" s="0">
-        <v>0.0080622943262543822</v>
+        <v>0.008564418338888824</v>
       </c>
       <c r="P19" s="0">
-        <v>0.0064639792668091944</v>
+        <v>0.0070743744638888661</v>
       </c>
       <c r="Q19" s="0">
-        <v>0.0041007181382692881</v>
+        <v>0.0049928911590277347</v>
       </c>
       <c r="R19" s="0">
-        <v>0.0044630497322280527</v>
+        <v>0.0048602783166665784</v>
       </c>
       <c r="S19" s="0">
-        <v>0.0062932797379492977</v>
+        <v>0.0055342771774304919</v>
       </c>
       <c r="T19" s="0">
-        <v>0.010701177059874611</v>
+        <v>0.01002481172256936</v>
       </c>
       <c r="U19" s="0">
-        <v>0.0079388580690142319</v>
+        <v>0.0071087335357638004</v>
       </c>
       <c r="V19" s="0">
-        <v>0.008802908342489979</v>
+        <v>0.007876671920486078</v>
       </c>
       <c r="W19" s="0">
-        <v>0.010850675659815845</v>
+        <v>0.010002772263194404</v>
       </c>
       <c r="X19" s="0">
-        <v>0.011105589334398425</v>
+        <v>0.010526010825347154</v>
       </c>
       <c r="Y19" s="0">
-        <v>0.011621103565734259</v>
+        <v>0.011217315767013736</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.011425572844545262</v>
+        <v>0.010970398336458187</v>
       </c>
       <c r="AA19" s="0">
-        <v>0.011283169986555097</v>
+        <v>0.010914956693749922</v>
       </c>
       <c r="AB19" s="0">
-        <v>0.010954833641299289</v>
+        <v>0.010859537818055431</v>
       </c>
       <c r="AC19" s="0">
-        <v>0.011111709581527851</v>
+        <v>0.010909248660069426</v>
       </c>
       <c r="AD19" s="0">
-        <v>0.011339300514894346</v>
+        <v>0.01098203054062491</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.011598090610410727</v>
+        <v>0.011060209115624886</v>
       </c>
       <c r="AF19" s="0">
-        <v>0.01150300547139177</v>
+        <v>0.011072679143402708</v>
       </c>
       <c r="AG19" s="0">
-        <v>0.011073333966089949</v>
+        <v>0.011018753018055494</v>
       </c>
       <c r="AH19" s="0">
-        <v>0.010823779757417495</v>
+        <v>0.01099421908923609</v>
       </c>
       <c r="AI19" s="0">
-        <v>0.010900062704114921</v>
+        <v>0.011029092884027647</v>
       </c>
       <c r="AJ19" s="0">
-        <v>0.011021153706846198</v>
+        <v>0.01107122862048604</v>
       </c>
       <c r="AK19" s="0">
-        <v>0.011110491633479991</v>
+        <v>0.011106009176041542</v>
       </c>
       <c r="AL19" s="0">
-        <v>0.011107688775095659</v>
+        <v>0.01112085635312493</v>
       </c>
       <c r="AM19" s="0">
-        <v>0.01097525186520526</v>
+        <v>0.011107333555902765</v>
       </c>
       <c r="AN19" s="0">
-        <v>0.010785140492433842</v>
+        <v>0.011079950613541611</v>
       </c>
       <c r="AO19" s="0">
-        <v>0.010664619588045154</v>
+        <v>0.011065583190277728</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>-0.41621274645544737</v>
+        <v>-0.43338114566666674</v>
       </c>
       <c r="C20" s="0">
-        <v>-0.0010182552034322945</v>
+        <v>-0.00022962808159726622</v>
       </c>
       <c r="D20" s="0">
-        <v>-8.9488705743212549e-05</v>
+        <v>0.00074189412013880808</v>
       </c>
       <c r="E20" s="0">
-        <v>-0.0019226865674850102</v>
+        <v>-0.0013581909208333917</v>
       </c>
       <c r="F20" s="0">
-        <v>0.00082162139583535909</v>
+        <v>0.0014278414548610234</v>
       </c>
       <c r="G20" s="0">
-        <v>0.0021083345921868446</v>
+        <v>0.0028000989322916059</v>
       </c>
       <c r="H20" s="0">
-        <v>0.00061735963957554318</v>
+        <v>0.0013066506666666311</v>
       </c>
       <c r="I20" s="0">
-        <v>-0.0018223614514897846</v>
+        <v>-0.0012580099402778608</v>
       </c>
       <c r="J20" s="0">
-        <v>-0.010526956262020326</v>
+        <v>-0.010389718157291727</v>
       </c>
       <c r="K20" s="0">
-        <v>0.014312931767435755</v>
+        <v>0.01491088036180549</v>
       </c>
       <c r="L20" s="0">
-        <v>0.0072156195699711323</v>
+        <v>0.0075837578666665961</v>
       </c>
       <c r="M20" s="0">
-        <v>0.0036469901753863887</v>
+        <v>0.0047090358781249342</v>
       </c>
       <c r="N20" s="0">
-        <v>0.0055272959174953451</v>
+        <v>0.0066451033934027404</v>
       </c>
       <c r="O20" s="0">
-        <v>0.0068801002815780943</v>
+        <v>0.006823220734375024</v>
       </c>
       <c r="P20" s="0">
-        <v>0.0057348579255082077</v>
+        <v>0.0055871011749998867</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.0038583912691222411</v>
+        <v>0.0038794440736110158</v>
       </c>
       <c r="R20" s="0">
-        <v>0.003870683431851929</v>
+        <v>0.0042750544302082036</v>
       </c>
       <c r="S20" s="0">
-        <v>0.0042979070955604937</v>
+        <v>0.004147188919097212</v>
       </c>
       <c r="T20" s="0">
-        <v>0.009416219797926062</v>
+        <v>0.0079381587420137567</v>
       </c>
       <c r="U20" s="0">
-        <v>0.0071370838114025448</v>
+        <v>0.005612180948958212</v>
       </c>
       <c r="V20" s="0">
-        <v>0.0076168006866538795</v>
+        <v>0.0060091750142360345</v>
       </c>
       <c r="W20" s="0">
-        <v>0.0094634036201390326</v>
+        <v>0.0077235807038193993</v>
       </c>
       <c r="X20" s="0">
-        <v>0.0096293049911503892</v>
+        <v>0.0079112106690972239</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.0093793734374276183</v>
+        <v>0.0079480945399305059</v>
       </c>
       <c r="Z20" s="0">
-        <v>0.0087527949767569058</v>
+        <v>0.0074985513166666573</v>
       </c>
       <c r="AA20" s="0">
-        <v>0.0089470186940189822</v>
+        <v>0.0076424275357638294</v>
       </c>
       <c r="AB20" s="0">
-        <v>0.0089571742360450846</v>
+        <v>0.0077525286618055356</v>
       </c>
       <c r="AC20" s="0">
-        <v>0.0086676262052247099</v>
+        <v>0.007773042706597233</v>
       </c>
       <c r="AD20" s="0">
-        <v>0.0088672629710788153</v>
+        <v>0.0078500509069443503</v>
       </c>
       <c r="AE20" s="0">
-        <v>0.0091258398896630899</v>
+        <v>0.0079314522618054717</v>
       </c>
       <c r="AF20" s="0">
-        <v>0.0094181878973640942</v>
+        <v>0.0080173054486110673</v>
       </c>
       <c r="AG20" s="0">
-        <v>0.0093236225818386087</v>
+        <v>0.0080438614010416298</v>
       </c>
       <c r="AH20" s="0">
-        <v>0.0088632684934372707</v>
+        <v>0.0080096971090277691</v>
       </c>
       <c r="AI20" s="0">
-        <v>0.0085981352808932598</v>
+        <v>0.0079995503635416076</v>
       </c>
       <c r="AJ20" s="0">
-        <v>0.008688335608071529</v>
+        <v>0.0080418765208332688</v>
       </c>
       <c r="AK20" s="0">
-        <v>0.008827009899931737</v>
+        <v>0.0080900313465277485</v>
       </c>
       <c r="AL20" s="0">
-        <v>0.0089307058826348928</v>
+        <v>0.0081310018600694312</v>
       </c>
       <c r="AM20" s="0">
-        <v>0.008932702880712684</v>
+        <v>0.0081524742031249819</v>
       </c>
       <c r="AN20" s="0">
-        <v>0.0087921726556920432</v>
+        <v>0.0081467110833332024</v>
       </c>
       <c r="AO20" s="0">
-        <v>0.0085877317990998847</v>
+        <v>0.0081269706229166183</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>-0.42588946850910375</v>
+        <v>-0.44584285066666679</v>
       </c>
       <c r="C21" s="0">
-        <v>-0.0021771368115430234</v>
+        <v>-0.0016929006274306602</v>
       </c>
       <c r="D21" s="0">
-        <v>-0.00092112083035511549</v>
+        <v>-0.00053203257951395244</v>
       </c>
       <c r="E21" s="0">
-        <v>0.0022628552793705348</v>
+        <v>0.0026656970340276924</v>
       </c>
       <c r="F21" s="0">
-        <v>0.0034668631564467312</v>
+        <v>0.0036386730857638221</v>
       </c>
       <c r="G21" s="0">
-        <v>0.00066298952371429687</v>
+        <v>0.00078040116562494389</v>
       </c>
       <c r="H21" s="0">
-        <v>-0.00024114039056538639</v>
+        <v>-7.3522930902847339e-05</v>
       </c>
       <c r="I21" s="0">
-        <v>-0.001841959405524729</v>
+        <v>-0.001623173168402825</v>
       </c>
       <c r="J21" s="0">
-        <v>-0.0066284440431901848</v>
+        <v>-0.0064604493565972865</v>
       </c>
       <c r="K21" s="0">
-        <v>0.0079259223537857526</v>
+        <v>0.0079332359864582869</v>
       </c>
       <c r="L21" s="0">
-        <v>0.0054997634482404911</v>
+        <v>0.0051184563190971857</v>
       </c>
       <c r="M21" s="0">
-        <v>0.0035220684294871574</v>
+        <v>0.0031430747552083638</v>
       </c>
       <c r="N21" s="0">
-        <v>0.0049293807243475651</v>
+        <v>0.0054544612791666012</v>
       </c>
       <c r="O21" s="0">
-        <v>0.004453077615495904</v>
+        <v>0.0049722206628471368</v>
       </c>
       <c r="P21" s="0">
-        <v>0.0045310974686461059</v>
+        <v>0.0036900277295138224</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.0032190702582109987</v>
+        <v>0.0023180118624999135</v>
       </c>
       <c r="R21" s="0">
-        <v>0.0033298081724826289</v>
+        <v>0.0026852815420138616</v>
       </c>
       <c r="S21" s="0">
-        <v>0.0032296308660102468</v>
+        <v>0.0030124517874999808</v>
       </c>
       <c r="T21" s="0">
-        <v>0.0068300242860726557</v>
+        <v>0.0059776949951387826</v>
       </c>
       <c r="U21" s="0">
-        <v>0.0063135431240617379</v>
+        <v>0.0037938018111111078</v>
       </c>
       <c r="V21" s="0">
-        <v>0.0070779041470153126</v>
+        <v>0.0045885823934027061</v>
       </c>
       <c r="W21" s="0">
-        <v>0.0082522916971833338</v>
+        <v>0.0056536759885416621</v>
       </c>
       <c r="X21" s="0">
-        <v>0.0083649101772453882</v>
+        <v>0.0055512564687499877</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.0083792743221403065</v>
+        <v>0.0055838595124999002</v>
       </c>
       <c r="Z21" s="0">
-        <v>0.0074366821198623145</v>
+        <v>0.0049705135118055521</v>
       </c>
       <c r="AA21" s="0">
-        <v>0.0074242063313184059</v>
+        <v>0.0051784002684027728</v>
       </c>
       <c r="AB21" s="0">
-        <v>0.0076611656398231087</v>
+        <v>0.0053520884295138451</v>
       </c>
       <c r="AC21" s="0">
-        <v>0.0076630347872742033</v>
+        <v>0.0054651517434027297</v>
       </c>
       <c r="AD21" s="0">
-        <v>0.007377179481059315</v>
+        <v>0.0055358966809027086</v>
       </c>
       <c r="AE21" s="0">
-        <v>0.0076183966904427303</v>
+        <v>0.0056329763586804305</v>
       </c>
       <c r="AF21" s="0">
-        <v>0.0079215891980636277</v>
+        <v>0.0057290057520832383</v>
       </c>
       <c r="AG21" s="0">
-        <v>0.0082617026450046427</v>
+        <v>0.0058280040406249456</v>
       </c>
       <c r="AH21" s="0">
-        <v>0.0081745791380935517</v>
+        <v>0.0058795048920138315</v>
       </c>
       <c r="AI21" s="0">
-        <v>0.0076829477417179604</v>
+        <v>0.0058803021878471862</v>
       </c>
       <c r="AJ21" s="0">
-        <v>0.0074048998484819162</v>
+        <v>0.0058964952152776862</v>
       </c>
       <c r="AK21" s="0">
-        <v>0.0075169314114821861</v>
+        <v>0.0059518084913193769</v>
       </c>
       <c r="AL21" s="0">
-        <v>0.0076819220501992969</v>
+        <v>0.0060107199128471289</v>
       </c>
       <c r="AM21" s="0">
-        <v>0.0078072914946468175</v>
+        <v>0.0060623046819444082</v>
       </c>
       <c r="AN21" s="0">
-        <v>0.0078190320402959923</v>
+        <v>0.0060957073156249764</v>
       </c>
       <c r="AO21" s="0">
-        <v>0.0076711944906110996</v>
+        <v>0.0061033976059027828</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>-0.42694590074749916</v>
+        <v>-0.4504280076666668</v>
       </c>
       <c r="C22" s="0">
-        <v>-0.0016158510297062945</v>
+        <v>-0.0013175390503472606</v>
       </c>
       <c r="D22" s="0">
-        <v>-0.0016825434071647827</v>
+        <v>-0.0016098284611111846</v>
       </c>
       <c r="E22" s="0">
-        <v>-0.00040256541159894299</v>
+        <v>-0.00049082650173620703</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.0014840325395545917</v>
+        <v>-0.0016924214045139227</v>
       </c>
       <c r="G22" s="0">
-        <v>-0.00093138381649843227</v>
+        <v>-0.001451706351388915</v>
       </c>
       <c r="H22" s="0">
-        <v>-0.0011233358497749202</v>
+        <v>-0.0015843413118056251</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.002339875298202343</v>
+        <v>-0.0027060017048611273</v>
       </c>
       <c r="J22" s="0">
-        <v>-0.0060228200470196502</v>
+        <v>-0.0062629608541667214</v>
       </c>
       <c r="K22" s="0">
-        <v>0.0042561215085720749</v>
+        <v>0.0041634312350694036</v>
       </c>
       <c r="L22" s="0">
-        <v>0.0028915739760021486</v>
+        <v>0.0019953471888888297</v>
       </c>
       <c r="M22" s="0">
-        <v>0.0021351891419389979</v>
+        <v>0.00090687783854159765</v>
       </c>
       <c r="N22" s="0">
-        <v>0.0042621887045311002</v>
+        <v>0.0031208449579859239</v>
       </c>
       <c r="O22" s="0">
-        <v>0.0038361138628514313</v>
+        <v>0.0036512442298610721</v>
       </c>
       <c r="P22" s="0">
-        <v>0.0028498633955303387</v>
+        <v>0.0026787347069443528</v>
       </c>
       <c r="Q22" s="0">
-        <v>0.0027928010174461115</v>
+        <v>0.0010888800055555144</v>
       </c>
       <c r="R22" s="0">
-        <v>0.0028461385748112522</v>
+        <v>0.0011307896406250184</v>
       </c>
       <c r="S22" s="0">
-        <v>0.0029709292333512383</v>
+        <v>0.0015391748357638235</v>
       </c>
       <c r="T22" s="0">
-        <v>0.0057722247680171979</v>
+        <v>0.0048251917461805682</v>
       </c>
       <c r="U22" s="0">
-        <v>0.0052793636879378547</v>
+        <v>0.0034643731940971483</v>
       </c>
       <c r="V22" s="0">
-        <v>0.0075061494232930293</v>
+        <v>0.0038385266579860082</v>
       </c>
       <c r="W22" s="0">
-        <v>0.007974824091466437</v>
+        <v>0.0043092446899304915</v>
       </c>
       <c r="X22" s="0">
-        <v>0.0078045915556491097</v>
+        <v>0.0039654373899304365</v>
       </c>
       <c r="Y22" s="0">
-        <v>0.0080585069048962343</v>
+        <v>0.0039727855937499168</v>
       </c>
       <c r="Z22" s="0">
-        <v>0.0072337433732522771</v>
+        <v>0.003167942596180473</v>
       </c>
       <c r="AA22" s="0">
-        <v>0.0072307491930625467</v>
+        <v>0.0035754061770832402</v>
       </c>
       <c r="AB22" s="0">
-        <v>0.0072671837535565054</v>
+        <v>0.0038600981211804331</v>
       </c>
       <c r="AC22" s="0">
-        <v>0.0075179311184302988</v>
+        <v>0.0040295925909721864</v>
       </c>
       <c r="AD22" s="0">
-        <v>0.0075542400298483914</v>
+        <v>0.0041908318934026911</v>
       </c>
       <c r="AE22" s="0">
-        <v>0.0072872405782788974</v>
+        <v>0.0043369694836804537</v>
       </c>
       <c r="AF22" s="0">
-        <v>0.0075878285504222265</v>
+        <v>0.0044651892298611107</v>
       </c>
       <c r="AG22" s="0">
-        <v>0.0079534130778585732</v>
+        <v>0.0045848976357637525</v>
       </c>
       <c r="AH22" s="0">
-        <v>0.0083589710079793877</v>
+        <v>0.0047048299239582656</v>
       </c>
       <c r="AI22" s="0">
-        <v>0.0082929274711216472</v>
+        <v>0.0047983609885415826</v>
       </c>
       <c r="AJ22" s="0">
-        <v>0.0077766504888135968</v>
+        <v>0.0048567282496527189</v>
       </c>
       <c r="AK22" s="0">
-        <v>0.0074921942413934683</v>
+        <v>0.0049149661423610871</v>
       </c>
       <c r="AL22" s="0">
-        <v>0.0076374329805304342</v>
+        <v>0.0049916453593749077</v>
       </c>
       <c r="AM22" s="0">
-        <v>0.0078399125899761279</v>
+        <v>0.0050678060135415648</v>
       </c>
       <c r="AN22" s="0">
-        <v>0.0079972097550333743</v>
+        <v>0.0051367865277777156</v>
       </c>
       <c r="AO22" s="0">
-        <v>0.0080262326607979939</v>
+        <v>0.0051896597600693539</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>-0.43186423374720662</v>
+        <v>-0.46112387766666674</v>
       </c>
       <c r="C23" s="0">
-        <v>-0.0033841156803448014</v>
+        <v>-0.003886332039583329</v>
       </c>
       <c r="D23" s="0">
-        <v>-0.0026900165759548567</v>
+        <v>-0.0030797290847222594</v>
       </c>
       <c r="E23" s="0">
-        <v>-0.0023659047497256447</v>
+        <v>-0.0030192821527778579</v>
       </c>
       <c r="F23" s="0">
-        <v>-0.00095997716555379364</v>
+        <v>-0.0018714807243055973</v>
       </c>
       <c r="G23" s="0">
-        <v>-0.0018977982624895917</v>
+        <v>-0.0028943771069445123</v>
       </c>
       <c r="H23" s="0">
-        <v>-0.0019934053918534422</v>
+        <v>-0.0033876407812500342</v>
       </c>
       <c r="I23" s="0">
-        <v>-0.0027128351941650419</v>
+        <v>-0.0040269042048611814</v>
       </c>
       <c r="J23" s="0">
-        <v>-0.005674536037423461</v>
+        <v>-0.0068115672350695378</v>
       </c>
       <c r="K23" s="0">
-        <v>0.0029051316364292479</v>
+        <v>0.0021132323618054949</v>
       </c>
       <c r="L23" s="0">
-        <v>0.0020043375248539053</v>
+        <v>0.00083835553090266801</v>
       </c>
       <c r="M23" s="0">
-        <v>0.00113243614157299</v>
+        <v>-0.00090980805972229462</v>
       </c>
       <c r="N23" s="0">
-        <v>0.0028077802053609324</v>
+        <v>0.0004129450465276685</v>
       </c>
       <c r="O23" s="0">
-        <v>0.0032055652816473379</v>
+        <v>0.00080050194201386482</v>
       </c>
       <c r="P23" s="0">
-        <v>0.0019882329836743984</v>
+        <v>0.0007369422468749276</v>
       </c>
       <c r="Q23" s="0">
-        <v>0.0019450706125934136</v>
+        <v>0.00076228644062498142</v>
       </c>
       <c r="R23" s="0">
-        <v>0.003024737278263856</v>
+        <v>3.2487967708271469e-05</v>
       </c>
       <c r="S23" s="0">
-        <v>0.0034983379905950684</v>
+        <v>0.0004896178350693994</v>
       </c>
       <c r="T23" s="0">
-        <v>0.0059528505514463426</v>
+        <v>0.0032727660305555402</v>
       </c>
       <c r="U23" s="0">
-        <v>0.0046468839304850129</v>
+        <v>0.0023907547420138342</v>
       </c>
       <c r="V23" s="0">
-        <v>0.0065084289184287325</v>
+        <v>0.0032523477034721586</v>
       </c>
       <c r="W23" s="0">
-        <v>0.009075504950748714</v>
+        <v>0.0035106707927083365</v>
       </c>
       <c r="X23" s="0">
-        <v>0.0081001908211786877</v>
+        <v>0.0025122120260416265</v>
       </c>
       <c r="Y23" s="0">
-        <v>0.0085400779473638333</v>
+        <v>0.0027559330055554883</v>
       </c>
       <c r="Z23" s="0">
-        <v>0.0081867892489994043</v>
+        <v>0.0020976397177082107</v>
       </c>
       <c r="AA23" s="0">
-        <v>0.0086267370885192429</v>
+        <v>0.0026050920892360385</v>
       </c>
       <c r="AB23" s="0">
-        <v>0.0085652357514767186</v>
+        <v>0.0030290575847222168</v>
       </c>
       <c r="AC23" s="0">
-        <v>0.0086328617348296333</v>
+        <v>0.0033883091184027099</v>
       </c>
       <c r="AD23" s="0">
-        <v>0.008968257422863557</v>
+        <v>0.0036142810135416092</v>
       </c>
       <c r="AE23" s="0">
-        <v>0.0090566341861387789</v>
+        <v>0.0038484452260415525</v>
       </c>
       <c r="AF23" s="0">
-        <v>0.0087901197907951367</v>
+        <v>0.0040846464479165623</v>
       </c>
       <c r="AG23" s="0">
-        <v>0.0091740072294510533</v>
+        <v>0.0042487198111110245</v>
       </c>
       <c r="AH23" s="0">
-        <v>0.0096319237014751979</v>
+        <v>0.0043964448722221272</v>
       </c>
       <c r="AI23" s="0">
-        <v>0.01013657199286333</v>
+        <v>0.0045417734322916173</v>
       </c>
       <c r="AJ23" s="0">
-        <v>0.010088699144180591</v>
+        <v>0.0046861001951388195</v>
       </c>
       <c r="AK23" s="0">
-        <v>0.0095096103640835428</v>
+        <v>0.0048139654413193456</v>
       </c>
       <c r="AL23" s="0">
-        <v>0.0091982724065090005</v>
+        <v>0.0049229780611110274</v>
       </c>
       <c r="AM23" s="0">
-        <v>0.009389428526088206</v>
+        <v>0.0050253357798610279</v>
       </c>
       <c r="AN23" s="0">
-        <v>0.0096465837151198386</v>
+        <v>0.0051223495899305185</v>
       </c>
       <c r="AO23" s="0">
-        <v>0.009849621597009306</v>
+        <v>0.0052125860840276927</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>-0.43453364957554208</v>
+        <v>-0.47160093866666675</v>
       </c>
       <c r="C24" s="0">
-        <v>-0.0039896875859208869</v>
+        <v>-0.005117257937152897</v>
       </c>
       <c r="D24" s="0">
-        <v>-0.0042827626031000654</v>
+        <v>-0.005508937337500075</v>
       </c>
       <c r="E24" s="0">
-        <v>-0.00038359605392562779</v>
+        <v>-0.001523492978819486</v>
       </c>
       <c r="F24" s="0">
-        <v>-0.00064698912686156351</v>
+        <v>-0.0021217072690972736</v>
       </c>
       <c r="G24" s="0">
-        <v>-0.0032288024616695665</v>
+        <v>-0.0051058421104167029</v>
       </c>
       <c r="H24" s="0">
-        <v>-0.0031022341913188867</v>
+        <v>-0.0050166100937500402</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.0040480917959517804</v>
+        <v>-0.0064291369590279146</v>
       </c>
       <c r="J24" s="0">
-        <v>-0.0063292574426357939</v>
+        <v>-0.0085663428923611895</v>
       </c>
       <c r="K24" s="0">
-        <v>0.0012110271545461293</v>
+        <v>-0.00061558860243060565</v>
       </c>
       <c r="L24" s="0">
-        <v>0.00063614930816757731</v>
+        <v>-0.0013603017368056256</v>
       </c>
       <c r="M24" s="0">
-        <v>7.9607643794665783e-05</v>
+        <v>-0.0022994787444444711</v>
       </c>
       <c r="N24" s="0">
-        <v>0.001411504990820156</v>
+        <v>-0.0019507703725694658</v>
       </c>
       <c r="O24" s="0">
-        <v>0.0015489098613225005</v>
+        <v>-0.0023454098805556481</v>
       </c>
       <c r="P24" s="0">
-        <v>0.0011913240920088386</v>
+        <v>-0.0027418261333334573</v>
       </c>
       <c r="Q24" s="0">
-        <v>0.0014130798413484191</v>
+        <v>-0.001066627794097331</v>
       </c>
       <c r="R24" s="0">
-        <v>0.0021328620018644662</v>
+        <v>-0.00026249539652783982</v>
       </c>
       <c r="S24" s="0">
-        <v>0.0029639677658923058</v>
+        <v>-0.001655569434375114</v>
       </c>
       <c r="T24" s="0">
-        <v>0.0054027259649738757</v>
+        <v>0.00073159652083321135</v>
       </c>
       <c r="U24" s="0">
-        <v>0.0046419048655264028</v>
+        <v>0.0001958482822915766</v>
       </c>
       <c r="V24" s="0">
-        <v>0.0055507355669827674</v>
+        <v>0.0016969575204860421</v>
       </c>
       <c r="W24" s="0">
-        <v>0.007143630232815501</v>
+        <v>0.0019758782951387888</v>
       </c>
       <c r="X24" s="0">
-        <v>0.0080111728326868192</v>
+        <v>-7.497210520840316e-05</v>
       </c>
       <c r="Y24" s="0">
-        <v>0.0088202374093412916</v>
+        <v>0.00077233001527771171</v>
       </c>
       <c r="Z24" s="0">
-        <v>0.0088202483940802434</v>
+        <v>0.00050954129374991552</v>
       </c>
       <c r="AA24" s="0">
-        <v>0.0097248453446240335</v>
+        <v>0.0010753632902777417</v>
       </c>
       <c r="AB24" s="0">
-        <v>0.010203681987923652</v>
+        <v>0.0016047557034721831</v>
       </c>
       <c r="AC24" s="0">
-        <v>0.010161409543672728</v>
+        <v>0.0021438198447916164</v>
       </c>
       <c r="AD24" s="0">
-        <v>0.010310977076644356</v>
+        <v>0.0026355339218748779</v>
       </c>
       <c r="AE24" s="0">
-        <v>0.010766333003503104</v>
+        <v>0.002938187574305529</v>
       </c>
       <c r="AF24" s="0">
-        <v>0.010929705159211267</v>
+        <v>0.0032689231975693849</v>
       </c>
       <c r="AG24" s="0">
-        <v>0.010671807473866646</v>
+        <v>0.0036266548263888532</v>
       </c>
       <c r="AH24" s="0">
-        <v>0.011171853088248307</v>
+        <v>0.0038394893041665545</v>
       </c>
       <c r="AI24" s="0">
-        <v>0.011756418409458846</v>
+        <v>0.0040244060826388215</v>
       </c>
       <c r="AJ24" s="0">
-        <v>0.01239665506693588</v>
+        <v>0.0042034369267360261</v>
       </c>
       <c r="AK24" s="0">
-        <v>0.012378192847108116</v>
+        <v>0.0044167011059026975</v>
       </c>
       <c r="AL24" s="0">
-        <v>0.011721991345939875</v>
+        <v>0.0046400129656248845</v>
       </c>
       <c r="AM24" s="0">
-        <v>0.011380459529961084</v>
+        <v>0.0048192102906249312</v>
       </c>
       <c r="AN24" s="0">
-        <v>0.011636564423786466</v>
+        <v>0.0049568578302082713</v>
       </c>
       <c r="AO24" s="0">
-        <v>0.011970290449473564</v>
+        <v>0.0050828599215276826</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>-0.43970127483260618</v>
+        <v>-0.48655493566666674</v>
       </c>
       <c r="C25" s="0">
-        <v>-0.0063758676898219568</v>
+        <v>-0.0081075655635417521</v>
       </c>
       <c r="D25" s="0">
-        <v>-0.0061710640190068555</v>
+        <v>-0.0079113979746528451</v>
       </c>
       <c r="E25" s="0">
-        <v>-0.0058291983293127791</v>
+        <v>-0.007660462713194538</v>
       </c>
       <c r="F25" s="0">
-        <v>-0.0066274685582406456</v>
+        <v>-0.00868934077986111</v>
       </c>
       <c r="G25" s="0">
-        <v>-0.0057868386414476336</v>
+        <v>-0.0082185092909722313</v>
       </c>
       <c r="H25" s="0">
-        <v>-0.0054247404128997534</v>
+        <v>-0.0081056604725694981</v>
       </c>
       <c r="I25" s="0">
-        <v>-0.0058510761677140755</v>
+        <v>-0.0085869279527778786</v>
       </c>
       <c r="J25" s="0">
-        <v>-0.0075243162516370199</v>
+        <v>-0.010724527568402809</v>
       </c>
       <c r="K25" s="0">
-        <v>-0.0018061664178034009</v>
+        <v>-0.0046432437107639668</v>
       </c>
       <c r="L25" s="0">
-        <v>-0.0014986210250522158</v>
+        <v>-0.0045009423927084291</v>
       </c>
       <c r="M25" s="0">
-        <v>-0.0018110144189971145</v>
+        <v>-0.0049612200767361614</v>
       </c>
       <c r="N25" s="0">
-        <v>-0.00039871123572216005</v>
+        <v>-0.0039487889006944998</v>
       </c>
       <c r="O25" s="0">
-        <v>-0.0004169399257831774</v>
+        <v>-0.0052291500319445183</v>
       </c>
       <c r="P25" s="0">
-        <v>-0.00086185229710411537</v>
+        <v>-0.0063071547961806029</v>
       </c>
       <c r="Q25" s="0">
-        <v>0.00019902679164651715</v>
+        <v>-0.0052616203486112179</v>
       </c>
       <c r="R25" s="0">
-        <v>0.0006695258654779157</v>
+        <v>-0.0031120558069445128</v>
       </c>
       <c r="S25" s="0">
-        <v>0.0019741082074348215</v>
+        <v>-0.0017704263652778543</v>
       </c>
       <c r="T25" s="0">
-        <v>0.0046319874425747587</v>
+        <v>-0.0017819424868056322</v>
       </c>
       <c r="U25" s="0">
-        <v>0.003887713668687176</v>
+        <v>-0.0027945545631944957</v>
       </c>
       <c r="V25" s="0">
-        <v>0.005347442750442688</v>
+        <v>-0.0010067563979167526</v>
       </c>
       <c r="W25" s="0">
-        <v>0.005977941664917219</v>
+        <v>0.00023841460416662574</v>
       </c>
       <c r="X25" s="0">
-        <v>0.0063351836232259373</v>
+        <v>-0.0010757396680556308</v>
       </c>
       <c r="Y25" s="0">
-        <v>0.0093136522289993806</v>
+        <v>-0.0015806695628473024</v>
       </c>
       <c r="Z25" s="0">
-        <v>0.0090333272390577535</v>
+        <v>-0.0018851712489583172</v>
       </c>
       <c r="AA25" s="0">
-        <v>0.0099186602729033346</v>
+        <v>-0.0013068391388890164</v>
       </c>
       <c r="AB25" s="0">
-        <v>0.010866123970660946</v>
+        <v>-0.00083232240034725267</v>
       </c>
       <c r="AC25" s="0">
-        <v>0.011449596331568612</v>
+        <v>-0.00023052584618066252</v>
       </c>
       <c r="AD25" s="0">
-        <v>0.011489062534020433</v>
+        <v>0.00049170704826384613</v>
       </c>
       <c r="AE25" s="0">
-        <v>0.011745548026708741</v>
+        <v>0.0011351725055554489</v>
       </c>
       <c r="AF25" s="0">
-        <v>0.012347547731156094</v>
+        <v>0.0015199736555554515</v>
       </c>
       <c r="AG25" s="0">
-        <v>0.012602678632187003</v>
+        <v>0.0019567109621527194</v>
       </c>
       <c r="AH25" s="0">
-        <v>0.012354722497741166</v>
+        <v>0.0024499553503471438</v>
       </c>
       <c r="AI25" s="0">
-        <v>0.012997384728283323</v>
+        <v>0.0027144668934027676</v>
       </c>
       <c r="AJ25" s="0">
-        <v>0.013739914487686133</v>
+        <v>0.0029402861538194163</v>
       </c>
       <c r="AK25" s="0">
-        <v>0.014549385902648149</v>
+        <v>0.0031563877999999379</v>
       </c>
       <c r="AL25" s="0">
-        <v>0.014569838901951571</v>
+        <v>0.0034491337152777746</v>
       </c>
       <c r="AM25" s="0">
-        <v>0.013820429111233656</v>
+        <v>0.003783151068402768</v>
       </c>
       <c r="AN25" s="0">
-        <v>0.013442740464457592</v>
+        <v>0.0040429179815971716</v>
       </c>
       <c r="AO25" s="0">
-        <v>0.013781202003333104</v>
+        <v>0.0042211655624999067</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>-0.44432319982829754</v>
+        <v>-0.50183650866666674</v>
       </c>
       <c r="C26" s="0">
-        <v>-0.0089191718227017991</v>
+        <v>-0.010513222674652767</v>
       </c>
       <c r="D26" s="0">
-        <v>-0.0089859406601919267</v>
+        <v>-0.010754909527777745</v>
       </c>
       <c r="E26" s="0">
-        <v>-0.0079028123932760042</v>
+        <v>-0.0097036309208333726</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.007211072690439857</v>
+        <v>-0.009148143000694553</v>
       </c>
       <c r="G26" s="0">
-        <v>-0.0080053977011733668</v>
+        <v>-0.010116900013541708</v>
       </c>
       <c r="H26" s="0">
-        <v>-0.0083702726837856511</v>
+        <v>-0.010979937268402906</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.0085948976980118053</v>
+        <v>-0.011520611781250079</v>
       </c>
       <c r="J26" s="0">
-        <v>-0.009938161251024924</v>
+        <v>-0.012880098122916739</v>
       </c>
       <c r="K26" s="0">
-        <v>-0.0059576037610547528</v>
+        <v>-0.0092402835402778383</v>
       </c>
       <c r="L26" s="0">
-        <v>-0.0052803698205134975</v>
+        <v>-0.0087600528815972578</v>
       </c>
       <c r="M26" s="0">
-        <v>-0.0049828036984713164</v>
+        <v>-0.0086766464027778212</v>
       </c>
       <c r="N26" s="0">
-        <v>-0.0034620681293324185</v>
+        <v>-0.0072881452284723203</v>
       </c>
       <c r="O26" s="0">
-        <v>-0.0028702230690704766</v>
+        <v>-0.0072889998722222571</v>
       </c>
       <c r="P26" s="0">
-        <v>-0.0041199681101561914</v>
+        <v>-0.0099411158114583453</v>
       </c>
       <c r="Q26" s="0">
-        <v>-0.0029128822978613522</v>
+        <v>-0.0093924477524305883</v>
       </c>
       <c r="R26" s="0">
-        <v>-0.0015268848000998814</v>
+        <v>-0.0081345702395833608</v>
       </c>
       <c r="S26" s="0">
-        <v>-0.00053136067119646802</v>
+        <v>-0.005320095408680614</v>
       </c>
       <c r="T26" s="0">
-        <v>0.0021977099506973463</v>
+        <v>-0.0026864367812500225</v>
       </c>
       <c r="U26" s="0">
-        <v>0.0025111301248560425</v>
+        <v>-0.0056217527256945954</v>
       </c>
       <c r="V26" s="0">
-        <v>0.0038552578780133295</v>
+        <v>-0.0044979618562500656</v>
       </c>
       <c r="W26" s="0">
-        <v>0.0052466241403223424</v>
+        <v>-0.0028940446138890352</v>
       </c>
       <c r="X26" s="0">
-        <v>0.0049851676884396512</v>
+        <v>-0.0025380881312500603</v>
       </c>
       <c r="Y26" s="0">
-        <v>0.0068581708188279467</v>
+        <v>-0.0025621971819444487</v>
       </c>
       <c r="Z26" s="0">
-        <v>0.0083973440458843251</v>
+        <v>-0.0052104018597223245</v>
       </c>
       <c r="AA26" s="0">
-        <v>0.008902145229039482</v>
+        <v>-0.0047031117739584349</v>
       </c>
       <c r="AB26" s="0">
-        <v>0.009928973248487849</v>
+        <v>-0.0041106880100695298</v>
       </c>
       <c r="AC26" s="0">
-        <v>0.011097587087871064</v>
+        <v>-0.0035673538034723395</v>
       </c>
       <c r="AD26" s="0">
-        <v>0.011900617350078468</v>
+        <v>-0.0028049887322917346</v>
       </c>
       <c r="AE26" s="0">
-        <v>0.012084760407702677</v>
+        <v>-0.0018652901402778643</v>
       </c>
       <c r="AF26" s="0">
-        <v>0.012522317028648089</v>
+        <v>-0.0010239942343751038</v>
       </c>
       <c r="AG26" s="0">
-        <v>0.013305199120177857</v>
+        <v>-0.00054577660833343613</v>
       </c>
       <c r="AH26" s="0">
-        <v>0.013701180474859076</v>
+        <v>2.5568946874998666e-05</v>
       </c>
       <c r="AI26" s="0">
-        <v>0.013525621589272396</v>
+        <v>0.00070065029444438265</v>
       </c>
       <c r="AJ26" s="0">
-        <v>0.014347304146918927</v>
+        <v>0.0010343296520832768</v>
       </c>
       <c r="AK26" s="0">
-        <v>0.015276365375035683</v>
+        <v>0.0013107695729165925</v>
       </c>
       <c r="AL26" s="0">
-        <v>0.016283404326733586</v>
+        <v>0.0015728894173610568</v>
       </c>
       <c r="AM26" s="0">
-        <v>0.016380530662771398</v>
+        <v>0.0019708377284720639</v>
       </c>
       <c r="AN26" s="0">
-        <v>0.015583960723146162</v>
+        <v>0.0024581532444443721</v>
       </c>
       <c r="AO26" s="0">
-        <v>0.015209029958383524</v>
+        <v>0.0028320014618055112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>194</v>
+        <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>-0.45080115812599564</v>
+        <v>-0.51916739266666678</v>
       </c>
       <c r="C27" s="0">
-        <v>-0.010814523556398503</v>
+        <v>-0.011664872419444583</v>
       </c>
       <c r="D27" s="0">
-        <v>-0.010857080440751732</v>
+        <v>-0.011672009658680649</v>
       </c>
       <c r="E27" s="0">
-        <v>-0.010622896349736899</v>
+        <v>-0.011614740287500092</v>
       </c>
       <c r="F27" s="0">
-        <v>-0.010369690772010831</v>
+        <v>-0.01152882767430552</v>
       </c>
       <c r="G27" s="0">
-        <v>-0.010493848240901715</v>
+        <v>-0.011884119567708351</v>
       </c>
       <c r="H27" s="0">
-        <v>-0.01051605392531435</v>
+        <v>-0.011989874944791701</v>
       </c>
       <c r="I27" s="0">
-        <v>-0.010729811914701681</v>
+        <v>-0.012684922148958444</v>
       </c>
       <c r="J27" s="0">
-        <v>-0.01232366827032072</v>
+        <v>-0.014583533618750144</v>
       </c>
       <c r="K27" s="0">
-        <v>-0.0096650383116729799</v>
+        <v>-0.011773261176736105</v>
       </c>
       <c r="L27" s="0">
-        <v>-0.0091731817992883879</v>
+        <v>-0.012139527500347302</v>
       </c>
       <c r="M27" s="0">
-        <v>-0.0089791077167225564</v>
+        <v>-0.012235208857639013</v>
       </c>
       <c r="N27" s="0">
-        <v>-0.0075955747671396789</v>
+        <v>-0.011115026003125084</v>
       </c>
       <c r="O27" s="0">
-        <v>-0.0067435992439810466</v>
+        <v>-0.010591470204861175</v>
       </c>
       <c r="P27" s="0">
-        <v>-0.0073811079556000414</v>
+        <v>-0.011927511020833392</v>
       </c>
       <c r="Q27" s="0">
-        <v>-0.0074432871812877832</v>
+        <v>-0.013313501559722329</v>
       </c>
       <c r="R27" s="0">
-        <v>-0.0063742556528392225</v>
+        <v>-0.013089013577083419</v>
       </c>
       <c r="S27" s="0">
-        <v>-0.0046740909507276829</v>
+        <v>-0.01169637650312505</v>
       </c>
       <c r="T27" s="0">
-        <v>-0.0016040147092895585</v>
+        <v>-0.0068323150520833709</v>
       </c>
       <c r="U27" s="0">
-        <v>-0.00054108289038434787</v>
+        <v>-0.0062101185572916995</v>
       </c>
       <c r="V27" s="0">
-        <v>0.00021867616254056532</v>
+        <v>-0.0089145125434028083</v>
       </c>
       <c r="W27" s="0">
-        <v>0.0020870234480727667</v>
+        <v>-0.0074453653864583469</v>
       </c>
       <c r="X27" s="0">
-        <v>0.0026311498236422093</v>
+        <v>-0.0068509722972222575</v>
       </c>
       <c r="Y27" s="0">
-        <v>0.0038936033698730443</v>
+        <v>-0.0049050355357639908</v>
       </c>
       <c r="Z27" s="0">
-        <v>0.0047371573278166546</v>
+        <v>-0.0062946853208334375</v>
       </c>
       <c r="AA27" s="0">
-        <v>0.0065906617403683754</v>
+        <v>-0.0090479556600694955</v>
       </c>
       <c r="AB27" s="0">
-        <v>0.0070789298364085651</v>
+        <v>-0.0086201537458334143</v>
       </c>
       <c r="AC27" s="0">
-        <v>0.0082209552114190787</v>
+        <v>-0.0080637676711806106</v>
       </c>
       <c r="AD27" s="0">
-        <v>0.009647531074789828</v>
+        <v>-0.0074418983354166968</v>
       </c>
       <c r="AE27" s="0">
-        <v>0.010768938692989394</v>
+        <v>-0.0064633271208334175</v>
       </c>
       <c r="AF27" s="0">
-        <v>0.011258035730625782</v>
+        <v>-0.0052005199190973128</v>
       </c>
       <c r="AG27" s="0">
-        <v>0.012030752715628146</v>
+        <v>-0.0040565729965277852</v>
       </c>
       <c r="AH27" s="0">
-        <v>0.013059721051611572</v>
+        <v>-0.0034462996086805919</v>
       </c>
       <c r="AI27" s="0">
-        <v>0.013703484722477788</v>
+        <v>-0.0026669429045140247</v>
       </c>
       <c r="AJ27" s="0">
-        <v>0.013749362159758194</v>
+        <v>-0.00170234626666671</v>
       </c>
       <c r="AK27" s="0">
-        <v>0.014808411198811433</v>
+        <v>-0.0012601227982639287</v>
       </c>
       <c r="AL27" s="0">
-        <v>0.015966102534545945</v>
+        <v>-0.00090618664340280652</v>
       </c>
       <c r="AM27" s="0">
-        <v>0.017209158172735384</v>
+        <v>-0.00057390014270841758</v>
       </c>
       <c r="AN27" s="0">
-        <v>0.017470866592903589</v>
+        <v>-7.1221833333754217e-06</v>
       </c>
       <c r="AO27" s="0">
-        <v>0.016756838613557923</v>
+        <v>0.00073164878402770528</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>-0.45590615247111643</v>
+        <v>-0.53301759966666673</v>
       </c>
       <c r="C28" s="0">
-        <v>-0.0099209637664135486</v>
+        <v>-0.0090284972559027121</v>
       </c>
       <c r="D28" s="0">
-        <v>-0.010027184265056333</v>
+        <v>-0.009237775144444571</v>
       </c>
       <c r="E28" s="0">
-        <v>-0.0095104487568517526</v>
+        <v>-0.0086812845586806686</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.010009460798887593</v>
+        <v>-0.0093850933097222589</v>
       </c>
       <c r="G28" s="0">
-        <v>-0.0104932502343138</v>
+        <v>-0.010069708306250202</v>
       </c>
       <c r="H28" s="0">
-        <v>-0.010816907272367504</v>
+        <v>-0.010600266620486187</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.01046014326446415</v>
+        <v>-0.010323775892014053</v>
       </c>
       <c r="J28" s="0">
-        <v>-0.012301426696862183</v>
+        <v>-0.012605086473263971</v>
       </c>
       <c r="K28" s="0">
-        <v>-0.011444351400615393</v>
+        <v>-0.011820612478125048</v>
       </c>
       <c r="L28" s="0">
-        <v>-0.01035527792577895</v>
+        <v>-0.010960663456944464</v>
       </c>
       <c r="M28" s="0">
-        <v>-0.011576815572165833</v>
+        <v>-0.013087889567014011</v>
       </c>
       <c r="N28" s="0">
-        <v>-0.010672468930250867</v>
+        <v>-0.01249465267395844</v>
       </c>
       <c r="O28" s="0">
-        <v>-0.0105738752977666</v>
+        <v>-0.012847498785069411</v>
       </c>
       <c r="P28" s="0">
-        <v>-0.010671120281660118</v>
+        <v>-0.013385585935763999</v>
       </c>
       <c r="Q28" s="0">
-        <v>-0.010460237537501804</v>
+        <v>-0.013768837003125145</v>
       </c>
       <c r="R28" s="0">
-        <v>-0.010908927432271953</v>
+        <v>-0.015504090262500103</v>
       </c>
       <c r="S28" s="0">
-        <v>-0.010672641921057768</v>
+        <v>-0.016243898938888945</v>
       </c>
       <c r="T28" s="0">
-        <v>-0.0081784478441498942</v>
+        <v>-0.014289367375000084</v>
       </c>
       <c r="U28" s="0">
-        <v>-0.0060402095113846199</v>
+        <v>-0.010827555134027889</v>
       </c>
       <c r="V28" s="0">
-        <v>-0.0045208900925547968</v>
+        <v>-0.0098874589253472589</v>
       </c>
       <c r="W28" s="0">
-        <v>-0.0044465974708758904</v>
+        <v>-0.013308334465277849</v>
       </c>
       <c r="X28" s="0">
-        <v>-0.003753191169581227</v>
+        <v>-0.013268611578125089</v>
       </c>
       <c r="Y28" s="0">
-        <v>-0.0016972675428011397</v>
+        <v>-0.011239795984027801</v>
       </c>
       <c r="Z28" s="0">
-        <v>-0.00077207473586099473</v>
+        <v>-0.009822831701041701</v>
       </c>
       <c r="AA28" s="0">
-        <v>0.00032387952998669256</v>
+        <v>-0.011029956322569479</v>
       </c>
       <c r="AB28" s="0">
-        <v>0.00074825164569980451</v>
+        <v>-0.015373035491666742</v>
       </c>
       <c r="AC28" s="0">
-        <v>0.0012583640483083691</v>
+        <v>-0.014990411317708341</v>
       </c>
       <c r="AD28" s="0">
-        <v>0.0026266339413092421</v>
+        <v>-0.014355261232638861</v>
       </c>
       <c r="AE28" s="0">
-        <v>0.0043461923473238073</v>
+        <v>-0.013623110477083422</v>
       </c>
       <c r="AF28" s="0">
-        <v>0.0059475920776617675</v>
+        <v>-0.012318866155208386</v>
       </c>
       <c r="AG28" s="0">
-        <v>0.0070366175217523308</v>
+        <v>-0.010541669198263992</v>
       </c>
       <c r="AH28" s="0">
-        <v>0.0084026591350254143</v>
+        <v>-0.0089209674107639803</v>
       </c>
       <c r="AI28" s="0">
-        <v>0.0097819133303556072</v>
+        <v>-0.0080957697034723108</v>
       </c>
       <c r="AJ28" s="0">
-        <v>0.010860809608097877</v>
+        <v>-0.0069746484479167314</v>
       </c>
       <c r="AK28" s="0">
-        <v>0.011411169734456106</v>
+        <v>-0.0055320871829862006</v>
       </c>
       <c r="AL28" s="0">
-        <v>0.012786979053269365</v>
+        <v>-0.0049083658670139307</v>
       </c>
       <c r="AM28" s="0">
-        <v>0.01422422517567129</v>
+        <v>-0.0044199066579861945</v>
       </c>
       <c r="AN28" s="0">
-        <v>0.015747657463394182</v>
+        <v>-0.0039619158298611623</v>
       </c>
       <c r="AO28" s="0">
-        <v>0.016341264040691139</v>
+        <v>-0.0031066826611111367</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>-0.45778815226361919</v>
+        <v>-0.54158771266666672</v>
       </c>
       <c r="C29" s="0">
-        <v>-0.0065988184161977492</v>
+        <v>-0.0039109346621529761</v>
       </c>
       <c r="D29" s="0">
-        <v>-0.0064814432147647372</v>
+        <v>-0.0037979551149306401</v>
       </c>
       <c r="E29" s="0">
-        <v>-0.0067649716799555448</v>
+        <v>-0.0041612129076388227</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.0067726186482217621</v>
+        <v>-0.0042096328048610854</v>
       </c>
       <c r="G29" s="0">
-        <v>-0.0069787612750279449</v>
+        <v>-0.0045308783208334313</v>
       </c>
       <c r="H29" s="0">
-        <v>-0.0073570833678180958</v>
+        <v>-0.0050193586375000265</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.0073774060306054934</v>
+        <v>-0.0051834620947917021</v>
       </c>
       <c r="J29" s="0">
-        <v>-0.0082094188722860451</v>
+        <v>-0.0061431805916668525</v>
       </c>
       <c r="K29" s="0">
-        <v>-0.0082175745207442863</v>
+        <v>-0.0062758815513889177</v>
       </c>
       <c r="L29" s="0">
-        <v>-0.0080184027667799529</v>
+        <v>-0.0062789768881944541</v>
       </c>
       <c r="M29" s="0">
-        <v>-0.0089170873919991456</v>
+        <v>-0.0075527637656251922</v>
       </c>
       <c r="N29" s="0">
-        <v>-0.0098079867358946138</v>
+        <v>-0.0090959757437500954</v>
       </c>
       <c r="O29" s="0">
-        <v>-0.010440173751234905</v>
+        <v>-0.010153666255902749</v>
       </c>
       <c r="P29" s="0">
-        <v>-0.010838516538798249</v>
+        <v>-0.010984778813541873</v>
       </c>
       <c r="Q29" s="0">
-        <v>-0.011157136044247895</v>
+        <v>-0.011696457617361156</v>
       </c>
       <c r="R29" s="0">
-        <v>-0.011416096610626869</v>
+        <v>-0.012537220877430588</v>
       </c>
       <c r="S29" s="0">
-        <v>-0.012882077488217791</v>
+        <v>-0.015125132893055615</v>
       </c>
       <c r="T29" s="0">
-        <v>-0.0123962619545116</v>
+        <v>-0.015578887767013938</v>
       </c>
       <c r="U29" s="0">
-        <v>-0.012171359244544044</v>
+        <v>-0.016234366640625053</v>
       </c>
       <c r="V29" s="0">
-        <v>-0.010412627812995123</v>
+        <v>-0.013575225233333377</v>
       </c>
       <c r="W29" s="0">
-        <v>-0.0090278243016717052</v>
+        <v>-0.012957286889236252</v>
       </c>
       <c r="X29" s="0">
-        <v>-0.011815779397702952</v>
+        <v>-0.018991799845486157</v>
       </c>
       <c r="Y29" s="0">
-        <v>-0.010535144063148871</v>
+        <v>-0.018421365559722291</v>
       </c>
       <c r="Z29" s="0">
-        <v>-0.0094767399484810833</v>
+        <v>-0.017700926025000063</v>
       </c>
       <c r="AA29" s="0">
-        <v>-0.0076803590380409292</v>
+        <v>-0.015590269610416707</v>
       </c>
       <c r="AB29" s="0">
-        <v>-0.0076077665300977593</v>
+        <v>-0.017816270021527858</v>
       </c>
       <c r="AC29" s="0">
-        <v>-0.0097816613562425325</v>
+        <v>-0.024465945248263954</v>
       </c>
       <c r="AD29" s="0">
-        <v>-0.0092620124019232586</v>
+        <v>-0.024142062533680619</v>
       </c>
       <c r="AE29" s="0">
-        <v>-0.008039305034049371</v>
+        <v>-0.023806279572569533</v>
       </c>
       <c r="AF29" s="0">
-        <v>-0.0065843582995107064</v>
+        <v>-0.023527039596875077</v>
       </c>
       <c r="AG29" s="0">
-        <v>-0.0048172144834719433</v>
+        <v>-0.022278856618402842</v>
       </c>
       <c r="AH29" s="0">
-        <v>-0.0031887732198438434</v>
+        <v>-0.020179589306250079</v>
       </c>
       <c r="AI29" s="0">
-        <v>-0.001177098903745899</v>
+        <v>-0.018140447436458373</v>
       </c>
       <c r="AJ29" s="0">
-        <v>0.00030391166172377693</v>
+        <v>-0.01738231551805558</v>
       </c>
       <c r="AK29" s="0">
-        <v>0.0018007822470658685</v>
+        <v>-0.016010827393055593</v>
       </c>
       <c r="AL29" s="0">
-        <v>0.0031295545571032868</v>
+        <v>-0.013940426909375081</v>
       </c>
       <c r="AM29" s="0">
-        <v>0.0047104139589932981</v>
+        <v>-0.013265203390277813</v>
       </c>
       <c r="AN29" s="0">
-        <v>0.0062326121225194653</v>
+        <v>-0.012840021098958321</v>
       </c>
       <c r="AO29" s="0">
-        <v>0.0078496715306570763</v>
+        <v>-0.012441061004166754</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>197</v>
+        <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>-0.45665656750298311</v>
+        <v>-0.54470596966666673</v>
       </c>
       <c r="C30" s="0">
-        <v>-0.0024666714852504268</v>
+        <v>0.0015001926267360632</v>
       </c>
       <c r="D30" s="0">
-        <v>-0.0024314200350681325</v>
+        <v>0.0015392712246526941</v>
       </c>
       <c r="E30" s="0">
-        <v>-0.0025274267242783588</v>
+        <v>0.0014200025954861366</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.0026009048649671684</v>
+        <v>0.0013223560906248104</v>
       </c>
       <c r="G30" s="0">
-        <v>-0.0027028901706483421</v>
+        <v>0.0011846292989583507</v>
       </c>
       <c r="H30" s="0">
-        <v>-0.0029671412834801902</v>
+        <v>0.00085329297951375338</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.0030149933736907109</v>
+        <v>0.00076750649965273742</v>
       </c>
       <c r="J30" s="0">
-        <v>-0.0036198833424055388</v>
+        <v>4.0027719097168735e-05</v>
       </c>
       <c r="K30" s="0">
-        <v>-0.0034558399515352001</v>
+        <v>0.00022597760347220497</v>
       </c>
       <c r="L30" s="0">
-        <v>-0.0035726336629017252</v>
+        <v>-2.846737500060946e-06</v>
       </c>
       <c r="M30" s="0">
-        <v>-0.0043207214797026938</v>
+        <v>-0.00095864890625008137</v>
       </c>
       <c r="N30" s="0">
-        <v>-0.004790015467392994</v>
+        <v>-0.0016151427767361346</v>
       </c>
       <c r="O30" s="0">
-        <v>-0.0060305855915541162</v>
+        <v>-0.0032883001253473099</v>
       </c>
       <c r="P30" s="0">
-        <v>-0.0066752233994118448</v>
+        <v>-0.0042068890385417168</v>
       </c>
       <c r="Q30" s="0">
-        <v>-0.007470884852656956</v>
+        <v>-0.0053202039111112098</v>
       </c>
       <c r="R30" s="0">
-        <v>-0.0081086250831529094</v>
+        <v>-0.0062534039732639046</v>
       </c>
       <c r="S30" s="0">
-        <v>-0.0089944757269261877</v>
+        <v>-0.0076106143114582636</v>
       </c>
       <c r="T30" s="0">
-        <v>-0.010116823420367738</v>
+        <v>-0.0094877758368056009</v>
       </c>
       <c r="U30" s="0">
-        <v>-0.011621720421610637</v>
+        <v>-0.0118995733152778</v>
       </c>
       <c r="V30" s="0">
-        <v>-0.013224159386450773</v>
+        <v>-0.014313182577430639</v>
       </c>
       <c r="W30" s="0">
-        <v>-0.011429650304175587</v>
+        <v>-0.012005452432639063</v>
       </c>
       <c r="X30" s="0">
-        <v>-0.011912117311850157</v>
+        <v>-0.013386563485763836</v>
       </c>
       <c r="Y30" s="0">
-        <v>-0.015981051214488395</v>
+        <v>-0.019871628778125039</v>
       </c>
       <c r="Z30" s="0">
-        <v>-0.016691373969128898</v>
+        <v>-0.021412679689236158</v>
       </c>
       <c r="AA30" s="0">
-        <v>-0.01631551828763772</v>
+        <v>-0.021504170919791732</v>
       </c>
       <c r="AB30" s="0">
-        <v>-0.015451977725093158</v>
+        <v>-0.02065137602951389</v>
       </c>
       <c r="AC30" s="0">
-        <v>-0.01758147816900224</v>
+        <v>-0.024819082692708494</v>
       </c>
       <c r="AD30" s="0">
-        <v>-0.0229981607741091</v>
+        <v>-0.033834730972222338</v>
       </c>
       <c r="AE30" s="0">
-        <v>-0.022785309732781867</v>
+        <v>-0.033877714831944516</v>
       </c>
       <c r="AF30" s="0">
-        <v>-0.022896783122773712</v>
+        <v>-0.034967086986458396</v>
       </c>
       <c r="AG30" s="0">
-        <v>-0.023237027439425517</v>
+        <v>-0.036577007666666717</v>
       </c>
       <c r="AH30" s="0">
-        <v>-0.022670656803242151</v>
+        <v>-0.036751095365625042</v>
       </c>
       <c r="AI30" s="0">
-        <v>-0.021354774944863264</v>
+        <v>-0.035280617147916749</v>
       </c>
       <c r="AJ30" s="0">
-        <v>-0.01977098511317793</v>
+        <v>-0.033994579103472256</v>
       </c>
       <c r="AK30" s="0">
-        <v>-0.019371522547619313</v>
+        <v>-0.034469633501041763</v>
       </c>
       <c r="AL30" s="0">
-        <v>-0.018339211364380936</v>
+        <v>-0.033787477229861196</v>
       </c>
       <c r="AM30" s="0">
-        <v>-0.016545310777491384</v>
+        <v>-0.031552243043055594</v>
       </c>
       <c r="AN30" s="0">
-        <v>-0.015910361526515537</v>
+        <v>-0.031968998651388969</v>
       </c>
       <c r="AO30" s="0">
-        <v>-0.015500489571315834</v>
+        <v>-0.032770223580902924</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>198</v>
+        <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>-0.4544322979315128</v>
+        <v>-0.54534047756666681</v>
       </c>
       <c r="C31" s="0">
-        <v>-0.00051058732401432216</v>
+        <v>0.0039535637670137236</v>
       </c>
       <c r="D31" s="0">
-        <v>-0.00051525939014451794</v>
+        <v>0.0039479872076387803</v>
       </c>
       <c r="E31" s="0">
-        <v>-0.00052898240585952383</v>
+        <v>0.0039311985107639558</v>
       </c>
       <c r="F31" s="0">
-        <v>-0.00054371923395535315</v>
+        <v>0.0039129269628472843</v>
       </c>
       <c r="G31" s="0">
-        <v>-0.00057742369064911481</v>
+        <v>0.0038699645795139408</v>
       </c>
       <c r="H31" s="0">
-        <v>-0.00061454793251458639</v>
+        <v>0.0038197284993054526</v>
       </c>
       <c r="I31" s="0">
-        <v>-0.00067332461681746114</v>
+        <v>0.0037462733489582729</v>
       </c>
       <c r="J31" s="0">
-        <v>-0.00079498013992573835</v>
+        <v>0.0036005643979166724</v>
       </c>
       <c r="K31" s="0">
-        <v>-0.00080783336838291531</v>
+        <v>0.0035830918406249972</v>
       </c>
       <c r="L31" s="0">
-        <v>-0.00078258422451299436</v>
+        <v>0.0035980027520833291</v>
       </c>
       <c r="M31" s="0">
-        <v>-0.0010783616421569109</v>
+        <v>0.0032271539124998365</v>
       </c>
       <c r="N31" s="0">
-        <v>-0.0012923729811947782</v>
+        <v>0.0029581440552082228</v>
       </c>
       <c r="O31" s="0">
-        <v>-0.001619178467124005</v>
+        <v>0.0025482794249999108</v>
       </c>
       <c r="P31" s="0">
-        <v>-0.0022050651341745664</v>
+        <v>0.0017961337673609856</v>
       </c>
       <c r="Q31" s="0">
-        <v>-0.0026870577844113064</v>
+        <v>0.0011857150527776476</v>
       </c>
       <c r="R31" s="0">
-        <v>-0.0031541202098193666</v>
+        <v>0.00057752446354153442</v>
       </c>
       <c r="S31" s="0">
-        <v>-0.0036197133057016551</v>
+        <v>-3.6038247916758692e-05</v>
       </c>
       <c r="T31" s="0">
-        <v>-0.0043179926878662567</v>
+        <v>-0.00099262433506952519</v>
       </c>
       <c r="U31" s="0">
-        <v>-0.005694378872708683</v>
+        <v>-0.0028318831413194348</v>
       </c>
       <c r="V31" s="0">
-        <v>-0.0074015249238778003</v>
+        <v>-0.0050680408711806235</v>
       </c>
       <c r="W31" s="0">
-        <v>-0.0086060875990128793</v>
+        <v>-0.0067043191402776925</v>
       </c>
       <c r="X31" s="0">
-        <v>-0.0079126317379460409</v>
+        <v>-0.0058665940197917266</v>
       </c>
       <c r="Y31" s="0">
-        <v>-0.0094732027651996953</v>
+        <v>-0.0081184630506945243</v>
       </c>
       <c r="Z31" s="0">
-        <v>-0.013517499395478083</v>
+        <v>-0.013564113029861158</v>
       </c>
       <c r="AA31" s="0">
-        <v>-0.014701891072522677</v>
+        <v>-0.015344501526041721</v>
       </c>
       <c r="AB31" s="0">
-        <v>-0.015699329680991581</v>
+        <v>-0.016805570882986287</v>
       </c>
       <c r="AC31" s="0">
-        <v>-0.015799115885448911</v>
+        <v>-0.01705700104687502</v>
       </c>
       <c r="AD31" s="0">
-        <v>-0.019081245678720438</v>
+        <v>-0.021737090006944459</v>
       </c>
       <c r="AE31" s="0">
-        <v>-0.024945752502265772</v>
+        <v>-0.029796268637152845</v>
       </c>
       <c r="AF31" s="0">
-        <v>-0.025288587962913389</v>
+        <v>-0.03039393700034726</v>
       </c>
       <c r="AG31" s="0">
-        <v>-0.026782095569690856</v>
+        <v>-0.032708618756597363</v>
       </c>
       <c r="AH31" s="0">
-        <v>-0.028722219577493435</v>
+        <v>-0.035682615259374995</v>
       </c>
       <c r="AI31" s="0">
-        <v>-0.029730246941222616</v>
+        <v>-0.037420001842013995</v>
       </c>
       <c r="AJ31" s="0">
-        <v>-0.029312144350073399</v>
+        <v>-0.037086676453125078</v>
       </c>
       <c r="AK31" s="0">
-        <v>-0.029428504174874304</v>
+        <v>-0.037720476380208479</v>
       </c>
       <c r="AL31" s="0">
-        <v>-0.030498360421657045</v>
+        <v>-0.03960722051527793</v>
       </c>
       <c r="AM31" s="0">
-        <v>-0.030697626371043119</v>
+        <v>-0.040277776795138998</v>
       </c>
       <c r="AN31" s="0">
-        <v>-0.029600622261705678</v>
+        <v>-0.039098396064930652</v>
       </c>
       <c r="AO31" s="0">
-        <v>-0.030718864731891893</v>
+        <v>-0.041224594138194626</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>199</v>
+        <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>-0.45231446063433361</v>
+        <v>-0.54541197106666672</v>
       </c>
       <c r="C32" s="0">
-        <v>-5.7134618956733441e-05</v>
+        <v>0.0045124071440277849</v>
       </c>
       <c r="D32" s="0">
-        <v>-5.9300431025699485e-05</v>
+        <v>0.0045102694634722154</v>
       </c>
       <c r="E32" s="0">
-        <v>-5.9833766897887664e-05</v>
+        <v>0.0045095187714583318</v>
       </c>
       <c r="F32" s="0">
-        <v>-6.0923514077548813e-05</v>
+        <v>0.0045084015092360366</v>
       </c>
       <c r="G32" s="0">
-        <v>-6.378205802293202e-05</v>
+        <v>0.0045047051177081743</v>
       </c>
       <c r="H32" s="0">
-        <v>-7.4060272493292612e-05</v>
+        <v>0.0044927174282637363</v>
       </c>
       <c r="I32" s="0">
-        <v>-9.8896412505933284e-05</v>
+        <v>0.0044626546604166198</v>
       </c>
       <c r="J32" s="0">
-        <v>-0.00011187579770455258</v>
+        <v>0.0044475144107638531</v>
       </c>
       <c r="K32" s="0">
-        <v>-0.00010817730557660665</v>
+        <v>0.0044517793884026879</v>
       </c>
       <c r="L32" s="0">
-        <v>-0.00012176020486598382</v>
+        <v>0.0044354161468749265</v>
       </c>
       <c r="M32" s="0">
-        <v>-0.00018083144187319711</v>
+        <v>0.0043643043180555674</v>
       </c>
       <c r="N32" s="0">
-        <v>-0.00021384675048402579</v>
+        <v>0.004317611502777762</v>
       </c>
       <c r="O32" s="0">
-        <v>-0.00024869107023739456</v>
+        <v>0.0042725044243054899</v>
       </c>
       <c r="P32" s="0">
-        <v>-0.00032028566563419014</v>
+        <v>0.0041859532246526507</v>
       </c>
       <c r="Q32" s="0">
-        <v>-0.00050169074283423765</v>
+        <v>0.003963213027777801</v>
       </c>
       <c r="R32" s="0">
-        <v>-0.00060281375620402367</v>
+        <v>0.0038350598843749366</v>
       </c>
       <c r="S32" s="0">
-        <v>-0.00075697023912268957</v>
+        <v>0.0036406869486110822</v>
       </c>
       <c r="T32" s="0">
-        <v>-0.00092832180329566194</v>
+        <v>0.0034229388395832228</v>
       </c>
       <c r="U32" s="0">
-        <v>-0.0013028444665454386</v>
+        <v>0.0029473897579860293</v>
       </c>
       <c r="V32" s="0">
-        <v>-0.0019019505815254245</v>
+        <v>0.0021897186388887264</v>
       </c>
       <c r="W32" s="0">
-        <v>-0.0025025618815665562</v>
+        <v>0.0014305542409721599</v>
       </c>
       <c r="X32" s="0">
-        <v>-0.0030538861278310292</v>
+        <v>0.00071678860763879594</v>
       </c>
       <c r="Y32" s="0">
-        <v>-0.0029938981546451249</v>
+        <v>0.00078266272013871553</v>
       </c>
       <c r="Z32" s="0">
-        <v>-0.0040687991715432914</v>
+        <v>-0.00061375666875007617</v>
       </c>
       <c r="AA32" s="0">
-        <v>-0.005794035150385568</v>
+        <v>-0.0028400341274306138</v>
       </c>
       <c r="AB32" s="0">
-        <v>-0.0066953007989423718</v>
+        <v>-0.0040447646208333632</v>
       </c>
       <c r="AC32" s="0">
-        <v>-0.0073121965165059422</v>
+        <v>-0.0048849999204861883</v>
       </c>
       <c r="AD32" s="0">
-        <v>-0.0075066429091649178</v>
+        <v>-0.0051908826555556731</v>
       </c>
       <c r="AE32" s="0">
-        <v>-0.0095085584934587741</v>
+        <v>-0.0078203014243056757</v>
       </c>
       <c r="AF32" s="0">
-        <v>-0.01232613324818288</v>
+        <v>-0.011502506117708311</v>
       </c>
       <c r="AG32" s="0">
-        <v>-0.012531470227604924</v>
+        <v>-0.011865469710069521</v>
       </c>
       <c r="AH32" s="0">
-        <v>-0.013704143286042192</v>
+        <v>-0.01348028351111108</v>
       </c>
       <c r="AI32" s="0">
-        <v>-0.015057390376488178</v>
+        <v>-0.015380084540277839</v>
       </c>
       <c r="AJ32" s="0">
-        <v>-0.01591650761959823</v>
+        <v>-0.01668583036527771</v>
       </c>
       <c r="AK32" s="0">
-        <v>-0.015762112049275079</v>
+        <v>-0.016673968436111242</v>
       </c>
       <c r="AL32" s="0">
-        <v>-0.016416548589963942</v>
+        <v>-0.017746629263194591</v>
       </c>
       <c r="AM32" s="0">
-        <v>-0.017237017562276191</v>
+        <v>-0.019077346566319542</v>
       </c>
       <c r="AN32" s="0">
-        <v>-0.017476612376172262</v>
+        <v>-0.0196820841395835</v>
       </c>
       <c r="AO32" s="0">
-        <v>-0.016906082336107853</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0">
-        <v>0.17760153411939283</v>
-      </c>
-      <c r="B33" s="0">
-        <v>-0.82237107008060717</v>
-      </c>
-      <c r="C33" s="0">
-        <v>-0.00033334425406091809</v>
-      </c>
-      <c r="D33" s="0">
-        <v>-0.00034597983092969392</v>
-      </c>
-      <c r="E33" s="0">
-        <v>-0.00034909184318239093</v>
-      </c>
-      <c r="F33" s="0">
-        <v>-0.00035544910359617057</v>
-      </c>
-      <c r="G33" s="0">
-        <v>-0.0003721273913372587</v>
-      </c>
-      <c r="H33" s="0">
-        <v>-0.00043209398046407412</v>
-      </c>
-      <c r="I33" s="0">
-        <v>-0.00057699696555798218</v>
-      </c>
-      <c r="J33" s="0">
-        <v>-0.00065272450399398384</v>
-      </c>
-      <c r="K33" s="0">
-        <v>-0.0006311458588503095</v>
-      </c>
-      <c r="L33" s="0">
-        <v>-0.00071039355161692957</v>
-      </c>
-      <c r="M33" s="0">
-        <v>-0.0010550368991119816</v>
-      </c>
-      <c r="N33" s="0">
-        <v>-0.0012308093136172518</v>
-      </c>
-      <c r="O33" s="0">
-        <v>-0.0014502343671583069</v>
-      </c>
-      <c r="P33" s="0">
-        <v>-0.0018686621620274942</v>
-      </c>
-      <c r="Q33" s="0">
-        <v>-0.0029270408631835148</v>
-      </c>
-      <c r="R33" s="0">
-        <v>-0.0035170334078489336</v>
-      </c>
-      <c r="S33" s="0">
-        <v>-0.004416430616909074</v>
-      </c>
-      <c r="T33" s="0">
-        <v>-0.0054161607914803584</v>
-      </c>
-      <c r="U33" s="0">
-        <v>-0.0076012592925799004</v>
-      </c>
-      <c r="V33" s="0">
-        <v>-0.011096661750890835</v>
-      </c>
-      <c r="W33" s="0">
-        <v>-0.014600838958597328</v>
-      </c>
-      <c r="X33" s="0">
-        <v>-0.017817466319240381</v>
-      </c>
-      <c r="Y33" s="0">
-        <v>-0.017467476233566211</v>
-      </c>
-      <c r="Z33" s="0">
-        <v>-0.023738829518760871</v>
-      </c>
-      <c r="AA33" s="0">
-        <v>-0.033804475070951669</v>
-      </c>
-      <c r="AB33" s="0">
-        <v>-0.039062780648447537</v>
-      </c>
-      <c r="AC33" s="0">
-        <v>-0.042661971461493323</v>
-      </c>
-      <c r="AD33" s="0">
-        <v>-0.043796446293101865</v>
-      </c>
-      <c r="AE33" s="0">
-        <v>-0.055476334937258939</v>
-      </c>
-      <c r="AF33" s="0">
-        <v>-0.071915076321652865</v>
-      </c>
-      <c r="AG33" s="0">
-        <v>-0.073113086621749507</v>
-      </c>
-      <c r="AH33" s="0">
-        <v>-0.079954882037466035</v>
-      </c>
-      <c r="AI33" s="0">
-        <v>-0.087850209518657532</v>
-      </c>
-      <c r="AJ33" s="0">
-        <v>-0.092862603138524985</v>
-      </c>
-      <c r="AK33" s="0">
-        <v>-0.091961809904449368</v>
-      </c>
-      <c r="AL33" s="0">
-        <v>-0.095780029323117175</v>
-      </c>
-      <c r="AM33" s="0">
-        <v>-0.10056693499447066</v>
-      </c>
-      <c r="AN33" s="0">
-        <v>-0.10196481794227819</v>
+        <v>-0.01922756012777771</v>
       </c>
     </row>
   </sheetData>

--- a/mig_shocks.xlsx
+++ b/mig_shocks.xlsx
@@ -13,7 +13,775 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
   <si>
     <t>mig_Q_2</t>
   </si>
@@ -129,7 +897,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -138,13 +906,29 @@
       <diagonal/>
     </border>
     <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -202,7 +986,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="B1" s="0">
         <v>-0.4828926172556337</v>
@@ -327,7 +1111,7 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="B2" s="0">
         <v>-0.4924378346666668</v>
@@ -452,7 +1236,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>2</v>
+        <v>258</v>
       </c>
       <c r="B3" s="0">
         <v>-0.49379786766666678</v>
@@ -577,7 +1361,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>3</v>
+        <v>259</v>
       </c>
       <c r="B4" s="0">
         <v>-0.49740144366666672</v>
@@ -702,7 +1486,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="B5" s="0">
         <v>-0.50274217366666674</v>
@@ -827,7 +1611,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>5</v>
+        <v>261</v>
       </c>
       <c r="B6" s="0">
         <v>-0.50470724166666681</v>
@@ -952,7 +1736,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>6</v>
+        <v>262</v>
       </c>
       <c r="B7" s="0">
         <v>-0.50929118566666676</v>
@@ -1077,7 +1861,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>7</v>
+        <v>263</v>
       </c>
       <c r="B8" s="0">
         <v>-0.51378135466666675</v>
@@ -1202,7 +1986,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>8</v>
+        <v>264</v>
       </c>
       <c r="B9" s="0">
         <v>-0.52019021066666682</v>
@@ -1327,7 +2111,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>9</v>
+        <v>265</v>
       </c>
       <c r="B10" s="0">
         <v>-0.5267394556666668</v>
@@ -1452,7 +2236,7 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>10</v>
+        <v>266</v>
       </c>
       <c r="B11" s="0">
         <v>-0.53416697766666676</v>
@@ -1577,7 +2361,7 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>11</v>
+        <v>267</v>
       </c>
       <c r="B12" s="0">
         <v>-0.54010278066666673</v>
@@ -1702,7 +2486,7 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="B13" s="0">
         <v>-0.54377568666666676</v>
@@ -1827,7 +2611,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>13</v>
+        <v>269</v>
       </c>
       <c r="B14" s="0">
         <v>-0.5451120816666668</v>
@@ -1952,7 +2736,7 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>14</v>
+        <v>270</v>
       </c>
       <c r="B15" s="0">
         <v>-0.54538401416666682</v>
@@ -2077,7 +2861,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>15</v>
+        <v>271</v>
       </c>
       <c r="B16" s="0">
         <v>-0.5454146542666668</v>
@@ -2202,7 +2986,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="B17" s="0">
         <v>-0.31117788041103289</v>
@@ -2327,7 +3111,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="B18" s="0">
         <v>-0.4217993916666668</v>
@@ -2452,7 +3236,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="B19" s="0">
         <v>-0.42497280166666679</v>
@@ -2577,7 +3361,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="B20" s="0">
         <v>-0.43338114566666674</v>
@@ -2702,7 +3486,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="B21" s="0">
         <v>-0.44584285066666679</v>
@@ -2827,7 +3611,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="B22" s="0">
         <v>-0.4504280076666668</v>
@@ -2952,7 +3736,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>22</v>
+        <v>278</v>
       </c>
       <c r="B23" s="0">
         <v>-0.46112387766666674</v>
@@ -3077,7 +3861,7 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>23</v>
+        <v>279</v>
       </c>
       <c r="B24" s="0">
         <v>-0.47160093866666675</v>
@@ -3202,7 +3986,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="B25" s="0">
         <v>-0.48655493566666674</v>
@@ -3327,7 +4111,7 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>25</v>
+        <v>281</v>
       </c>
       <c r="B26" s="0">
         <v>-0.50183650866666674</v>
@@ -3452,7 +4236,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>26</v>
+        <v>282</v>
       </c>
       <c r="B27" s="0">
         <v>-0.51916739266666678</v>
@@ -3577,7 +4361,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>27</v>
+        <v>283</v>
       </c>
       <c r="B28" s="0">
         <v>-0.53301759966666673</v>
@@ -3702,7 +4486,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>28</v>
+        <v>284</v>
       </c>
       <c r="B29" s="0">
         <v>-0.54158771266666672</v>
@@ -3827,7 +4611,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>29</v>
+        <v>285</v>
       </c>
       <c r="B30" s="0">
         <v>-0.54470596966666673</v>
@@ -3952,7 +4736,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="B31" s="0">
         <v>-0.54534047756666681</v>
@@ -4077,7 +4861,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>31</v>
+        <v>287</v>
       </c>
       <c r="B32" s="0">
         <v>-0.54541197106666672</v>

--- a/mig_shocks.xlsx
+++ b/mig_shocks.xlsx
@@ -13,7 +13,199 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="352">
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
   <si>
     <t>mig_Q_2</t>
   </si>
@@ -897,7 +1089,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -914,11 +1106,13 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -929,6 +1123,8 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,7 +1182,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="B1" s="0">
         <v>-0.4828926172556337</v>
@@ -1111,7 +1307,7 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>257</v>
+        <v>321</v>
       </c>
       <c r="B2" s="0">
         <v>-0.4924378346666668</v>
@@ -1236,7 +1432,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>258</v>
+        <v>322</v>
       </c>
       <c r="B3" s="0">
         <v>-0.49379786766666678</v>
@@ -1361,7 +1557,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="B4" s="0">
         <v>-0.49740144366666672</v>
@@ -1486,7 +1682,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>260</v>
+        <v>324</v>
       </c>
       <c r="B5" s="0">
         <v>-0.50274217366666674</v>
@@ -1611,7 +1807,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>261</v>
+        <v>325</v>
       </c>
       <c r="B6" s="0">
         <v>-0.50470724166666681</v>
@@ -1736,7 +1932,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>262</v>
+        <v>326</v>
       </c>
       <c r="B7" s="0">
         <v>-0.50929118566666676</v>
@@ -1861,7 +2057,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="B8" s="0">
         <v>-0.51378135466666675</v>
@@ -1986,7 +2182,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="B9" s="0">
         <v>-0.52019021066666682</v>
@@ -2111,7 +2307,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>265</v>
+        <v>329</v>
       </c>
       <c r="B10" s="0">
         <v>-0.5267394556666668</v>
@@ -2236,7 +2432,7 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>266</v>
+        <v>330</v>
       </c>
       <c r="B11" s="0">
         <v>-0.53416697766666676</v>
@@ -2361,7 +2557,7 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="B12" s="0">
         <v>-0.54010278066666673</v>
@@ -2486,7 +2682,7 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="B13" s="0">
         <v>-0.54377568666666676</v>
@@ -2611,7 +2807,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="B14" s="0">
         <v>-0.5451120816666668</v>
@@ -2736,7 +2932,7 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="B15" s="0">
         <v>-0.54538401416666682</v>
@@ -2861,7 +3057,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="B16" s="0">
         <v>-0.5454146542666668</v>
@@ -2986,7 +3182,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="B17" s="0">
         <v>-0.31117788041103289</v>
@@ -3111,7 +3307,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="B18" s="0">
         <v>-0.4217993916666668</v>
@@ -3236,7 +3432,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="B19" s="0">
         <v>-0.42497280166666679</v>
@@ -3361,7 +3557,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>275</v>
+        <v>339</v>
       </c>
       <c r="B20" s="0">
         <v>-0.43338114566666674</v>
@@ -3486,7 +3682,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>276</v>
+        <v>340</v>
       </c>
       <c r="B21" s="0">
         <v>-0.44584285066666679</v>
@@ -3611,7 +3807,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>277</v>
+        <v>341</v>
       </c>
       <c r="B22" s="0">
         <v>-0.4504280076666668</v>
@@ -3736,7 +3932,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="B23" s="0">
         <v>-0.46112387766666674</v>
@@ -3861,7 +4057,7 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="B24" s="0">
         <v>-0.47160093866666675</v>
@@ -3986,7 +4182,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="B25" s="0">
         <v>-0.48655493566666674</v>
@@ -4111,7 +4307,7 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>281</v>
+        <v>345</v>
       </c>
       <c r="B26" s="0">
         <v>-0.50183650866666674</v>
@@ -4236,7 +4432,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>282</v>
+        <v>346</v>
       </c>
       <c r="B27" s="0">
         <v>-0.51916739266666678</v>
@@ -4361,7 +4557,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="B28" s="0">
         <v>-0.53301759966666673</v>
@@ -4486,7 +4682,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="B29" s="0">
         <v>-0.54158771266666672</v>
@@ -4611,7 +4807,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="B30" s="0">
         <v>-0.54470596966666673</v>
@@ -4736,7 +4932,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>286</v>
+        <v>350</v>
       </c>
       <c r="B31" s="0">
         <v>-0.54534047756666681</v>
@@ -4861,7 +5057,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>287</v>
+        <v>351</v>
       </c>
       <c r="B32" s="0">
         <v>-0.54541197106666672</v>
